--- a/docs/research/MASTER_VIDEO_DATABASE.xlsx
+++ b/docs/research/MASTER_VIDEO_DATABASE.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Video Knowledge Hub" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TradingLab (Toàn bộ 109 Video)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +30,18 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,8 +54,20 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,13 +75,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -426,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -497,7 +550,7 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
         </is>
@@ -514,20 +567,1328 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TradingLab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>How to Avoid False Breakouts (Avoid The Trap)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Quy tắc Phân biệt Fakeout vs Breakout &amp; Bộ lọc Fibonacci Golden Zone:
+1. Fakeout (Phá vỡ giả): Nến chỉ quét râu (wick) qua đỉnh/đáy rồi đóng nến ngược lại bên trong -&gt; Tín hiệu từ chối giá và gom thanh khoản.
+2. Breakout (Phá vỡ thật): Thân nến (body) đóng cửa vượt qua đỉnh/đáy -&gt; Xác nhận lực đẩy.
+3. Nguyên tắc vàng: Muốn giá tăng, hãy chờ giá giảm hồi về trước; muốn giá giảm, hãy chờ giá tăng hồi lên trước. Tuyệt đối KHÔNG FOMO mua ngay đỉnh breakout.
+4. Setup Mua tối thượng (Double Confluences):
+   - Bước 1: Quét râu Fakeout đáy cũ (loại bỏ phe Bán).
+   - Bước 2: Thân nến Breakout đóng trên đỉnh cũ (xác nhận phe Mua vào).
+   - Bước 3: Kéo Fibonacci (0.618 - 0.706 - 0.79) từ đáy Fakeout lên đỉnh Breakout.
+   - Bước 4: Chờ giá hồi về Golden Zone (0.618 - 0.79) mới kích hoạt Buy. SL đặt dưới đáy Fakeout, TP tại đỉnh Breakout. R:R cực cao.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>What if I told you false breakouts are
+one of the most common ways traders lose
+money? They see price break a high,
+enter the trade expecting it to go up,
+and unfortunately price does exactly the
+opposite. If only there's a way to avoid
+these false breakouts completely to make
+sure this never happens to you again, or
+even better, know when they are about to
+happen. Well, actually there is. There
+is a way. With this technique, you will
+not only be able to know when these
+false breakouts are about to happen, but
+you will also be able to take advantage
+of them for high probability moves. Now,
+I just released my Telegram. I share all
+the plays I'm watching, useful trading
+tips, and a sh- ton of value. The best
+part is it's completely free to join. If
+you want to check it out, I'll leave it
+in the pinned comment. A very common
+setup you will see is this, where price
+moves and creates a high. The specific
+point we are going to be focusing on is
+the break of this high. Now, there are
+two scenarios that can happen. Scenario
+one, price breaks the high and closes
+above the high. Scenario two, price
+breaks the high and just wicks above the
+high and ends up closing beneath it. If
+scenario two happens, where the candle
+breaks the high but closes beneath it,
+this is what's called a fakeout. How we
+know this is a fakeout is because price
+rose above the high and left behind a
+large upper wick. What this is showing
+us is that buyers attempted to go
+higher, but then an influx of sellers
+stepped in and got the price back down.
+Which, if this happens, especially at a
+high, there's a high probability chance
+that we could get more confluences for a
+trade to the downside. But what happens
+if price closes above the high? If price
+closes above the high, this is now
+considered a breakout. Now, you might be
+thinking to yourself, well, if the other
+scenario was {quote} {unquote} a bad
+scenario, this scenario must mean price
+will move higher. Which, what I see a
+lot of people do is enter long trades as
+soon as they see this candle close above
+the recent high, expecting it to keep
+heading upwards. Which, if you are doing
+this, it's one of the worst mistakes you
+can possibly make. You see, if you're
+entering right here, your risk-reward is
+going to be absolutely trash. Because,
+where are you going to place your stop
+loss? You could place it below this low,
+but then your stop loss is going to be
+so massive, and if you do get a losing
+trade, you're going to take a big hit.
+Yeah, you could make your stop loss
+smaller, but just because price breaks
+this high doesn't exactly mean it's
+going to keep shooting up directly from
+here. So, you have a major problem.
+While yes, price closing above a high
+does give bullish tendencies, it doesn't
+exactly mean you should enter right
+away. Which brings me to one of the best
+words of advice I can possibly give you.
+If you want price to go higher, you
+actually want price to go lower first.
+If you want price to go lower, you want
+price to go higher first. Once you
+understand this concept, your trading
+will change forever. So, going back to
+our scenarios, if price breaks the high,
+but just wicks above it and closes
+beneath it, this is indeed a fake out.
+But, we don't want to just enter a short
+trade immediately. We first want price
+to come up first, get a better entry,
+then enter. Same thing with the opposite
+scenario. If price breaks the previous
+high, but closes above it, this is
+indeed a breakout, but we don't want to
+enter a long trade immediately. We want
+price to come back down first, get a
+better entry, then enter. So, now you
+know the difference between a breakout
+and a fake out, and we can start reading
+the markets a lot better. But, not only
+that, we can combine the two to get some
+scary good results. Here's what I mean.
+So, here we have an uptrend. We have our
+low right here, we have our high right
+here. Now, price can do anything here.
+We're not trying to predict price, we're
+trying to read it. Price ends up going
+lower. While going lower, it does end up
+breaking this low. Now, this This the
+point we need to start paying close
+attention. If we look closely while
+doing this, it didn't close below it. It
+just wicked beneath it, which shows us
+that sellers try to push price beneath
+this low, but buyers stepped in and
+fought them off at this level, which
+shows us this is not a breakout, but a
+fake out. But this in itself is not
+enough reasoning for us to enter just
+quite yet. So, let's keep watching.
+After doing this, price starts heading
+upwards, backing up the idea the fake
+out to take effect. As it goes up, it
+starts heading towards this recent high.
+As price crosses this high, it does
+something that backs our thesis even
+more. While doing this break, the candle
+closed above the high, which would be
+considered a breakout. So, now we have
+two confluences. We have our fake out to
+the downside, then we have a breakout to
+the upside, both showing signs of
+wanting to go up. Here, we have a
+different scenario. Price made both a
+high and a low, but this time price
+moves upwards first. While moving
+upwards, it breaks this recent high.
+While doing so, it crossed the high, but
+it just wicked above it and ended up
+closing beneath it, showing buyers try
+to go up, but sellers took control and
+brought the price back down. After doing
+this, price starts heading lower,
+backing up the idea the fake out is
+taking effect. While moving lower, it
+breaks the recent low. Not only did it
+break it, it closed beneath it, giving
+us a breakout to the downside. We have
+our fake out to the upside, our breakout
+to the downside, which can give us the
+idea there's a great chance for a
+downward move, which is exactly what
+happens. So, now you understand the
+difference between a breakout and a fake
+out and understand how to use them
+together. But, there's still a problem.
+Say if you do get a fake out, then
+directly after get a breakout, if you
+entered as soon as the breakout happens,
+we still have the same problem that I
+mentioned before. Where will you put
+your stop loss? Sure, you could put it
+here, but then your risk to reward is
+&amp;gt;&amp;gt; [music]
+&amp;gt;&amp;gt; not really the best. Because if you do
+get a losing trade, your loss will still
+be pretty significant. So, we need a way
+to not only make our stop loss smaller,
+so our losses are smaller, but we also
+need a way to make our wins bigger. And
+in order to do that, we need to get a
+better entry. To do this, go to
+TradingView. If you don't yet have it,
+I'll leave a link in the description. Go
+to your chart, grab the Fibonacci
+retracement tool on the left. Place it
+on your chart. Next, go to the settings
+of the Fibonacci, make the values 0,
+0.706, 0.618, 1, and 0.79. This will
+leave us with three main levels that
+look like this. These levels are what's
+called
+or where price has the highest
+probability of pulling back to and
+reversing. Which, if you're thinking
+like I'm thinking, we can use this to
+our advantage. Here, price moves and
+creates a high and a low. It ends up
+breaking our low, we look closely and it
+just wicked beneath it, showing buyers
+are stepping in at this level, leaving
+behind a fake out to the downside. After
+doing so, it starts rising back up,
+backing up the idea the fake out is
+taking effect. While doing so, it breaks
+the previous high. Not only that, it
+closed above it. Once this happens, grab
+your Fibonacci tool, mark from the fake
+out to the breakout. This will leave
+behind our golden zone. Price starts
+coming down and enters into our golden
+zone. Now, you are not entering at the
+breakout, you let price come down first
+into our golden zone, so you get a way
+better entry. Now, you can place your
+stop loss below the low, which is
+smaller than before. Set your take
+profits at the high, and then finally,
+just watch the play play out. Boom, easy
+winning trade. Hopefully, I got the idea
+in your head that you not only need a
+breakout, but you need a fake out
+alongside with it. On top of that, let
+price retrace back down before entering.
+Once you do that, your trading will
+change forever. Thanks for watching.
+I'll be posting some of my trade ideas
+inside my Telegram. See you in there.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2yePksvT64I</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TradingLab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>You're Using Liquidity Wrong</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Quy tắc phân biệt Vùng Cản Thật (Real Zone) và Vùng Mồi Nhử (Inducement Zone):
+1. Vùng B (Inducement): Là đỉnh hồi đầu tiên (minor high/low) sau cú phá vỡ. Nếu phía trên Vùng B còn khoảng trống Imbalance (FVG) chưa lấp, Vùng B 100% là bẫy mồi nhử thanh khoản -&gt; CẤM vào lệnh tại B.
+2. Săn thanh khoản (Liquidity Sweep): Smart Money sẽ đẩy giá phá thủng đỉnh B để quét sạch lệnh Stop Loss của Retail Traders, lấp đầy FVG (đóng vai trò nam châm hút giá).
+3. Vùng A (Extreme Zone): Là vùng Order Block cực trị tại nến khởi nguồn cú sập/tăng mạnh.
+4. Điểm vào lệnh: Chỉ vào lệnh khi giá quét qua đỉnh B, lấp FVG và chạm Vùng A.
+5. SL: Đặt trên đỉnh Vùng A. TP: Vùng Demand/Supply đối diện. Tỷ lệ R:R tối ưu đạt 1:5+.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[00:00:00] Is this liquidity? Is this liquidity? Is
+[00:00:02] this liquidity? Or is this liquidity? If
+[00:00:05] you cannot answer this question, you are
+[00:00:07] using liquidity wrong. Liquidity is one
+[00:00:09] of the most powerful tools in technical
+[00:00:12] analysis, because you are essentially
+[00:00:13] taking advantage of the losers in the
+[00:00:15] market. And I see time and time again of
+[00:00:18] traders trying to use liquidity but
+[00:00:20] using it completely wrong. You see, one
+[00:00:23] setup you will normally see is this. At
+[00:00:25] this current point, we have three
+[00:00:28] available options for a potential
+[00:00:30] liquidity points. One here, one here,
+[00:00:32] and one right here. Let's say you chose
+[00:00:35] this low as your preferred liquidity
+[00:00:37] point. If you did choose this low, you
+[00:00:39] are absolutely wrong. The reasoning for
+[00:00:41] this is because we don't yet have what's
+[00:00:43] called inducement. Inducement is part of
+[00:00:46] liquidity. They go hand in hand.
+[00:00:48] Inducement is simple. It's a fake zone
+[00:00:50] to attract other traders with the simple
+[00:00:53] goal of trapping them. Trapping them to
+[00:00:56] take their money. Now, what we have here
+[00:00:58] is a downwards move with two supply
+[00:01:00] zones. Zone A right here and zone B
+[00:01:03] here. Two options. Because of this, a
+[00:01:05] lot of people will naturally enter a
+[00:01:07] short when price comes to zone B. Now,
+[00:01:10] with this, we now know in the back of
+[00:01:12] our head, there will be a lot of sell
+[00:01:14] orders in this area right here. However,
+[00:01:17] this supply zone is not the strongest
+[00:01:20] zone. Not only that, it's what I call an
+[00:01:23] inducement zone. A zone that is a trap.
+[00:01:26] Meaning, price will come up to the zone,
+[00:01:28] traders will enter short expecting price
+[00:01:30] to move down from here, and set their
+[00:01:32] stop loss somewhere around this
+[00:01:34] location. But then, price unfortunately
+[00:01:36] hits their stop loss, proceeds to move
+[00:01:38] up to the real zone, and all of those
+[00:01:41] previous shorters will now lose this
+[00:01:43] exact trade. Then, after hitting their
+[00:01:45] stop loss, price does the real move and
+[00:01:47] heads downwards. And all of those
+[00:01:49] shorters will say, "Ah, it was just an
+[00:01:52] unlucky trade." But in reality, it
+[00:01:54] wasn't. There's actually a lot of logic
+[00:01:56] behind this setup. And if they only knew
+[00:01:58] what inducement actually was, they would
+[00:02:00] have won this trade. So, going to our
+[00:02:02] example, our inducement zone was
+[00:02:04] actually right here, and our real zone
+[00:02:07] was above it. So, the question is, how
+[00:02:09] do we decipher what a real zone is and
+[00:02:12] what an inducement zone is? Well, that's
+[00:02:14] a great question. An inducement zone
+[00:02:15] will always have two things, liquidity
+[00:02:18] and imbalance. So, going back to our
+[00:02:20] example, we have our two supply zones
+[00:02:22] again. But, I want you to pay close
+[00:02:24] attention to something. Notice this gap
+[00:02:26] right here. Price never came up to this
+[00:02:29] gap. Price never filled this gap,
+[00:02:31] meaning there's an imbalance on this
+[00:02:33] chart. Now, say if price did something
+[00:02:35] like this, where it did retest this zone
+[00:02:37] and didn't leave behind a gap, then
+[00:02:40] yeah, zone B would have been the correct
+[00:02:41] zone to sell from and those shorters
+[00:02:44] would have been right. But, that's not
+[00:02:45] what happened. Price left behind this
+[00:02:48] imbalance. Now, the thing with
+[00:02:49] imbalance, price will want to retest
+[00:02:51] this imbalance eventually. It will act
+[00:02:53] as almost a magnet. And notice where
+[00:02:55] that magnet is, above zone B. Because of
+[00:02:59] this, zone B will act as our inducement
+[00:03:01] zone, our fake zone to attract traders
+[00:03:04] to enter. It'll act as our liquidity.
+[00:03:07] And because of this inducement zone
+[00:03:09] attracting traders to enter here, we
+[00:03:11] will use these losing traders to our
+[00:03:13] advantage. Because the people that are
+[00:03:15] entering here, they will put their stop
+[00:03:18] orders above this high, which will act
+[00:03:21] as our liquidity. So, now we have two
+[00:03:23] important things. We have a gap here, an
+[00:03:25] imbalance that is acting as a magnet to
+[00:03:27] pull price upwards, and we also have a
+[00:03:29] bunch of stop loss orders right here
+[00:03:31] because of this inducement zone, which
+[00:03:33] will work beautifully together as price
+[00:03:35] is always attracted to both imbalances
+[00:03:38] and stop orders. And will naturally want
+[00:03:41] to reach for those losses, fill the gap,
+[00:03:43] then afterwards hit the strongest supply
+[00:03:45] zone, then do the real move down. Now,
+[00:03:48] what I want you to do is go on any chart
+[00:03:50] and look for a liquidity and inducement
+[00:03:53] and just look how often it works. Like
+[00:03:55] here, here, and here. Let's test out
+[00:03:58] what you learned and try it out on some
+[00:04:00] real chart examples. Here we have an
+[00:04:02] uptrend. What we're first going to do is
+[00:04:04] mark the first candle of this uptrend,
+[00:04:06] which is our area of demand. After this,
+[00:04:08] price retraces back down. While doing
+[00:04:11] this retracement, price left behind
+[00:04:13] something very interesting. It left
+[00:04:15] behind two separate supply zones. We can
+[00:04:17] mark our supply zones by simply marking
+[00:04:20] wick to wick from the candle that
+[00:04:21] started a large drop-off. So we have
+[00:04:23] zone A right here and zone B right here.
+[00:04:26] Two supply zones to choose from, but I
+[00:04:29] also want you to pay close attention to
+[00:04:31] something. Price did not only retrace,
+[00:04:33] it fell hard and left behind a bearish
+[00:04:36] fair value gap. And pay attention to
+[00:04:39] where that fair value gap is, above zone
+[00:04:42] B. Now price will want to retest this
+[00:04:44] imbalance. It will naturally want to
+[00:04:46] fill this gap. It will want to test this
+[00:04:48] price again. And in order to do that, it
+[00:04:51] has to break through zone B. So this
+[00:04:54] high from zone B will act as our
+[00:04:57] liquidity point. Because all of those
+[00:04:59] traders who were entering shorts early
+[00:05:01] at zone B will likely be leaving their
+[00:05:04] stop orders right above this high, which
+[00:05:06] again will act as our liquidity. So we
+[00:05:08] not only have an inducement zone, but we
+[00:05:10] have a fair value gap right above it
+[00:05:12] acting as a magnet that price will
+[00:05:15] naturally want to fill. Not only that,
+[00:05:16] but we have all the stop orders from
+[00:05:18] people entering early at zone B acting
+[00:05:22] as our liquidity. Which all of these
+[00:05:24] paired together is extremely powerful.
+[00:05:27] Price comes up, hits zone B. Since we
+[00:05:29] know zone B is an inducement zone, or in
+[00:05:31] other words, a trap, we don't enter yet.
+[00:05:34] Price naturally wants to hit the gap
+[00:05:35] above it, which it does. While doing so,
+[00:05:38] it naturally enters into zone A. We
+[00:05:41] enter a short, place our stop loss above
+[00:05:43] the high, we set our take profit at the
+[00:05:45] demand zone we marked before. And if you
+[00:05:47] do this strategy right, you will always
+[00:05:50] have a great risk to reward, meaning
+[00:05:52] your losses will be small and your wins
+[00:05:54] will be big. Here we have a 5x risk
+[00:05:57] reward. And notice what happens. The
+[00:05:59] moment price touches our supply zone, it
+[00:06:02] retraces immediately at this point and
+[00:06:05] hits our take profit. This trade is not
+[00:06:08] luck. It's done by design. And the
+[00:06:10] moment you start looking for inducement,
+[00:06:12] fair value gaps, and liquidity on your
+[00:06:14] charts, you'll be blown away by how
+[00:06:17] often it works. Let's try a long
+[00:06:19] scenario. Here we have an uptrend. With
+[00:06:21] this uptrend, it's a little different.
+[00:06:23] This time we have three demand zones to
+[00:06:25] choose from. One here, here, and here.
+[00:06:28] So, let's break it down. We know the
+[00:06:30] first zone is an inducement zone because
+[00:06:32] there's a gap beneath it. We also know
+[00:06:35] the second zone is an inducement zone as
+[00:06:37] well because there's a gap beneath that
+[00:06:39] one, too. Both these inducement zones
+[00:06:42] will act as our liquidity. When working
+[00:06:44] with inducement zones, if there's ever a
+[00:06:46] gap beneath the demand zone where price
+[00:06:48] hasn't touched before, it immediately
+[00:06:50] makes the demand zone invalid. Keep that
+[00:06:53] in mind. Let's see what happens next.
+[00:06:54] Price starts heading sharply downwards.
+[00:06:57] So, we grab the first candle of this
+[00:06:59] downwards move. This is our supply zone.
+[00:07:02] Price continues to move downwards,
+[00:07:04] breaking through all the inducement
+[00:07:06] zones. Comes down to our original true
+[00:07:08] zone. This is where we enter. We're
+[00:07:10] going to set our stop loss below the
+[00:07:12] demand zone, and we're going to set our
+[00:07:14] take profit at the supply zone. Again,
+[00:07:17] notice the risk reward. Big potential
+[00:07:19] win, small potential loss. The moment
+[00:07:22] price hits the true demand zone, it goes
+[00:07:24] up immediately from here and hits our
+[00:07:26] take profit with ease. Now, I just
+[00:07:29] released my Telegram. I share all the
+[00:07:31] plays I'm watching, useful trading tips,
+[00:07:33] and a ton of value. The best part
+[00:07:35] is it's completely free to join. If you
+[00:07:37] want to check it out, I'll leave it in
+[00:07:39] the pinned comment. Well, that's how you
+[00:07:40] use liquidity with inducement. Try it
+[00:07:43] out yourself and let me know how it
+[00:07:45] works for you. See you next time.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7:50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RKU7D9PxLgY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Wysetrade</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ULTIMATE Supertrend Indicator Trading Strategy (FREE FULL COURSE)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Khóa học chiến lược Supertrend toàn diện: 1. Tham số chuẩn Factor 2.5 - 3.0 (ATR 10). 2. Không trade tín hiệu đảo chiều độc lập (tránh whipsaw). 3. Quy tắc hợp lưu: Supertrend định hướng Bias + Price Action/Key Levels kích hoạt Entry. 4. Chiến lược Dynamic Trailing Stoploss theo dải Supertrend bắt trọn sóng dài. 5. Bộ lọc đa khung thời gian (HTF Trend Filter).</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[00:00:00] One of the most effective trading tools
+[00:00:02] is the super trend indicator, but you'd
+[00:00:04] be surprised that most traders actually
+[00:00:06] use it incorrectly. We're going to show
+[00:00:08] you how to use it like a pro. Please hit
+[00:00:10] the like button as it allows for our
+[00:00:12] team to continue to produce more free
+[00:00:14] content on YouTube.
+[00:00:16] Let's start with the super trend basics.
+[00:00:21] To access the super trend indicator, go
+[00:00:23] to indicators,
+[00:00:25] type in super trend, click it, and it'll
+[00:00:29] overlay on your charts. We alter the
+[00:00:32] factor setting between 2.5 or three
+[00:00:34] depending on the asset we are trading,
+[00:00:36] but also based on the strategy we are
+[00:00:39] using. The super trend indicator is a
+[00:00:41] trend following indicator that
+[00:00:43] integrates ATR or average true range to
+[00:00:46] gauge market volatility. You use the
+[00:00:48] super trend indicator to help identify
+[00:00:51] your directional bias, meaning whether
+[00:00:53] to trade with a bullish bias or a
+[00:00:55] bearish bias. When price is in the
+[00:00:57] green, it is bullish and in an uptrend.
+[00:01:00] When price is in the red, it is bearish
+[00:01:02] and in a downtrend. When price breaks
+[00:01:05] below the green super trend, it often
+[00:01:07] leads to a trend change from an uptrend
+[00:01:09] to a downtrend.
+[00:01:11] When price breaks above the red super
+[00:01:13] trend, it often leads to a trend change
+[00:01:15] from a downtrend to an uptrend.
+[00:01:17] If you want to use the exact charting
+[00:01:19] platform we are using right now, the
+[00:01:21] link is in the description below.
+[00:01:24] Let's now get into some strategies using
+[00:01:27] the super trend indicator. Strategy
+[00:01:29] number one, entering long trades while
+[00:01:32] in the green and short trades while in
+[00:01:34] the red.
+[00:01:36] So when price is in the green, you want
+[00:01:38] to look for long trade setups as you
+[00:01:40] have a bullish bias. This reversal point
+[00:01:43] gives you a key level. You have multiple
+[00:01:46] long entry points through the touches at
+[00:01:48] the key level. Another entry point at
+[00:01:50] the break of the descending triangle
+[00:01:52] pattern. Another entry point at the
+[00:01:55] break of the ascending triangle pattern.
+[00:01:57] Again, you are only looking for long
+[00:01:59] trade setups while in the green of the
+[00:02:02] super trend indicator as it gives you a
+[00:02:04] bullish bias and bullish momentum. So,
+[00:02:06] you are trading with the long advantage.
+[00:02:09] Jumping to bearish.
+[00:02:12] While price is in the red, you want to
+[00:02:13] look for short trade setups as you have
+[00:02:15] a bearish bias. This reversal point
+[00:02:18] gives you a key level. Short trade setup
+[00:02:20] here.
+[00:02:22] These reversal points give you a trend
+[00:02:24] line. Short trade setup here. Again, you
+[00:02:27] are only looking for short trade setups
+[00:02:29] while in the red of the super trend
+[00:02:31] indicator as it gives you a bearish bias
+[00:02:33] and bearish momentum. So, you are
+[00:02:35] trading with a short advantage. Moving
+[00:02:38] on to the next strategy. Trailing your
+[00:02:40] stop loss using the super trend
+[00:02:42] indicator.
+[00:02:45] Price breaks below the green super trend
+[00:02:47] and into the red giving you a bearish
+[00:02:49] bias. This reversal point gives you a
+[00:02:52] key level short trade setup here.
+[00:02:55] When you see the super trend indicator
+[00:02:57] moving sideways and horizontally, that
+[00:02:59] is where you put your stop loss. you put
+[00:03:01] it slightly above the sideways super
+[00:03:04] trend band as it acts as a barrier and
+[00:03:06] often protects your stop-loss from being
+[00:03:09] touched.
+[00:03:10] Notice how the super trend indicator is
+[00:03:12] moving sideways here. So you would trail
+[00:03:15] your stop loss to here slightly above
+[00:03:18] it, leaving some space to breathe. You
+[00:03:20] had a manual exit point through the
+[00:03:22] break of the super trend indicator and
+[00:03:24] higher high or through here where price
+[00:03:26] would have hit your stop loss.
+[00:03:29] Now that price is in the green and
+[00:03:30] bullish, you are looking for long
+[00:03:32] trades. These reversal points gives you
+[00:03:35] a key level. Long trade setup one is
+[00:03:38] here. Stop loss is placed here where the
+[00:03:41] super trend is moving sideways. The
+[00:03:43] super trend band acts as a barrier
+[00:03:46] between price and your stop loss. So it
+[00:03:48] protects your stop loss from
+[00:03:49] accidentally getting hit before
+[00:03:51] continuing the trend. This reversal
+[00:03:54] point gives you a key level. Long trade
+[00:03:56] setup here.
+[00:03:59] Stop loss is placed here where the super
+[00:04:01] trend is moving sideways. Descending
+[00:04:04] triangle pattern and break. Long trade
+[00:04:06] setup here.
+[00:04:08] Your trailing stop loss is moved here
+[00:04:10] where the sideways super trend indicator
+[00:04:12] is clear. Again, multiple sideways super
+[00:04:16] trend indicator movements allowing you
+[00:04:17] to trail the stop loss upwards.
+[00:04:21] Once price breaks through the green and
+[00:04:22] into the red with a massive bearish red
+[00:04:25] candle, your stop losses would have been
+[00:04:27] hit and you would automatically be
+[00:04:28] exited from your long trades with a
+[00:04:30] profit. Let's show this again.
+[00:04:36] Price breaks below the green super trend
+[00:04:38] and into the red, giving you a bearish
+[00:04:40] bias. These reversal points give you a
+[00:04:43] key level. Short trade setup here and
+[00:04:46] stop loss above the sideways super trend
+[00:04:48] indicator. This reversal point gives you
+[00:04:51] a key level. Short trade set up here.
+[00:04:55] Trailing stop-loss moved to here where
+[00:04:57] the super trend is moving sideways.
+[00:04:59] These reversal points give you a key
+[00:05:01] level. Short trade set up here. Trailing
+[00:05:04] stop-loss moved to here where the super
+[00:05:07] trend is moving sideways. And again,
+[00:05:09] trailing stop-loss moved here where the
+[00:05:11] super trend is moving sideways. Once
+[00:05:13] price breaks from red to green with the
+[00:05:16] massive bullish green candle, your stop
+[00:05:17] losses would have all been hit and you
+[00:05:19] would be automatically exited from your
+[00:05:21] short trades with a profit.
+[00:05:24] Price moves into the green super trend,
+[00:05:26] giving you a bullish bias. These
+[00:05:28] reversal points give you a key level.
+[00:05:30] Long trades set up here. Stop loss
+[00:05:32] placed here below the horizontal super
+[00:05:34] trend indicator. All these horizontal
+[00:05:37] sideways super trend movements allow you
+[00:05:39] to continue and trail your stop loss
+[00:05:40] upwards. Now, after you find highquality
+[00:05:43] trade setups, you need a reliable
+[00:05:45] brokerage to actually enter and exit
+[00:05:47] trades on. In 90 seconds, I'll show you
+[00:05:50] how Mumu checks all the boxes. First,
+[00:05:52] fees. Traders like us who trade actively
+[00:05:55] know that fees can add up quickly. On
+[00:05:57] Mumu, it's $0 commissions for stocks,
+[00:06:00] options, and ETFs, plus $0 equity
+[00:06:03] options contract fees. That makes a big
+[00:06:06] difference when calculating your
+[00:06:08] riskreward per trade. Fees aren't the
+[00:06:10] only thing. Speed of execution affects
+[00:06:12] your trading cost, and Mumu checks that
+[00:06:14] box as well. Another thing that's great
+[00:06:17] about Mumu is the free level two
+[00:06:18] real-time quotes, including options.
+[00:06:21] That's how we spot walls and liquidity
+[00:06:23] as they form. Many platforms charge
+[00:06:25] extra for this, but Mumu doesn't. Last
+[00:06:28] is reliability, because we are choosing
+[00:06:30] a broker for the long run. Mumu is a
+[00:06:33] reliable and globally trusted broker
+[00:06:35] with over 27 million users across the
+[00:06:38] world. Mumu is licensed in many major
+[00:06:40] markets, is a FINRA member with SIPC
+[00:06:44] coverage, and with over 100 plus
+[00:06:46] industry awards. The best part about
+[00:06:48] Mumu is that it fully integrates into
+[00:06:50] Trading View. Just open the trading
+[00:06:52] panel at the bottom, and you'll see
+[00:06:53] Mumu, the highest rated broker available
+[00:06:55] on Trading View. Use the link below this
+[00:06:58] video to open your account and get the
+[00:07:00] promo offers. Then select Mumu in the
+[00:07:03] panel to start buying and selling
+[00:07:04] directly within Trading View. The link
+[00:07:06] below this video will get you up to
+[00:07:09] $1,000 worth of Nvidia shares while
+[00:07:11] earning 8.1% APY on your cash. You want
+[00:07:15] to maximize your gains as much as
+[00:07:17] possible. So, thank you to Mumu for
+[00:07:19] sponsoring this video.
+[00:07:22] Let's now get into super trend band
+[00:07:25] touches.
+[00:07:29] While price is in the green of the super
+[00:07:31] trend indicator and in a bullish
+[00:07:33] uptrend, the lower band acts as a
+[00:07:35] support level. This here is what you're
+[00:07:37] looking for where price touches the
+[00:07:39] lower band of the super trend indicator
+[00:07:41] and presents a highquality long trade
+[00:07:43] setup. It's even better when you have a
+[00:07:45] candlestick pattern form when the touch
+[00:07:47] of the lower band occurs such as this
+[00:07:49] long wick candle going in the opposite
+[00:07:52] direction.
+[00:07:54] While price is in the red of the super
+[00:07:56] trend indicator and in a bearish
+[00:07:58] downtrend, the upper band acts as a
+[00:08:00] resistance level. This here is what
+[00:08:02] you're looking for where price touches
+[00:08:04] the upper band of the super trend
+[00:08:05] indicator and presents a highquality
+[00:08:07] short trade setup. As always, using an
+[00:08:10] indicator on its own isn't enough. You
+[00:08:13] need to combine super trend band touches
+[00:08:16] with key levels.
+[00:08:21] This is the dollar CAD currency pair.
+[00:08:23] Price is in the red of the super trend.
+[00:08:26] So you are looking for short trade
+[00:08:27] setups. This reversal point gives you a
+[00:08:29] key level. As price comes up, it forms a
+[00:08:32] long wick candle that touches the upper
+[00:08:34] band and the key level, which presents a
+[00:08:36] highquality short trade setup. Again,
+[00:08:38] price comes up and touches the upper
+[00:08:41] band and the key level, presenting
+[00:08:43] another highquality short trade setup.
+[00:08:45] Price then breaks above the band and
+[00:08:47] forms a higher high and enters into the
+[00:08:49] green of the super trend. Meaning you
+[00:08:51] are now bullish in your bias and looking
+[00:08:53] for long trade setups. These reversal
+[00:08:56] points give you a very key level with
+[00:08:57] multiple touches. Price comes down and
+[00:09:00] touches the lower band and the key level
+[00:09:02] and forms a long candle with a candle
+[00:09:04] color change presenting a highquality
+[00:09:06] long trade setup. Again price touches
+[00:09:09] the lower band and the key level
+[00:09:10] presenting another highquality long
+[00:09:12] trade setup. These reversal points give
+[00:09:15] you a key zone, very long wick candle
+[00:09:17] touching the lower band and the key zone
+[00:09:19] presenting another highquality long
+[00:09:22] trade setup. Let's show this again.
+[00:09:27] These reversal points give you a key
+[00:09:28] level. Long wick candle touches the
+[00:09:31] lower band and the key level presenting
+[00:09:32] a long trade setup trend line placed
+[00:09:35] like this. And once it broke above with
+[00:09:37] the higher high and bullish momentum
+[00:09:38] candle, your trend continuation upwards
+[00:09:40] is confirmed. You had a gap down occur
+[00:09:43] into the lower band which presented a
+[00:09:46] gap fill long trade setup. Let's show
+[00:09:49] this again.
+[00:09:52] Price breaks above and enters the green
+[00:09:54] giving you a bullish bias and you are
+[00:09:56] also at the start of a fresh trend
+[00:09:58] change which means price has room to
+[00:10:00] move further. This reversal point gives
+[00:10:03] you a key level. Price pulls back and
+[00:10:05] forms multiple longw candles at the
+[00:10:07] lower band and the key level presenting
+[00:10:09] a long trade setup. This is also an
+[00:10:12] inverse head and shoulders pattern.
+[00:10:14] Neckline here and once price broke above
+[00:10:16] the neckline long continuation entry
+[00:10:18] point as your trade setup here was your
+[00:10:20] trigger event that gave you a confirmed
+[00:10:23] bullish directional bias and you are now
+[00:10:25] riding the wave of the confirmed upwards
+[00:10:27] momentum. Let's show one more.
+[00:10:33] This is the Kiwi dollar 12hour time
+[00:10:35] frame. These reversal points give you a
+[00:10:37] key level. As price comes up, you had a
+[00:10:40] double top pattern that touches the
+[00:10:41] upper band and the key level presenting
+[00:10:43] a short trade setup. This reversal point
+[00:10:46] here gives you another key level. Price
+[00:10:48] comes up, forms multiple longwid candles
+[00:10:51] at the upper band and the key level
+[00:10:53] presenting a short trade setup. Place a
+[00:10:55] trend line like this and once it broke,
+[00:10:57] trend continuation downwards confirmed.
+[00:11:00] Now, a very key concept you must
+[00:11:03] understand. Price action is king and
+[00:11:06] price action always comes first. You
+[00:11:08] then use indicators to support what you
+[00:11:11] have already identified and established
+[00:11:13] with price action.
+[00:11:15] This is the Euro Dollar 1 hour time
+[00:11:17] frame. Price is above the green super
+[00:11:19] trend giving you a bullish bias. Price
+[00:11:22] then breaks into the red of the super
+[00:11:24] trend giving you a bearish bias. This
+[00:11:26] long candle at resistance and the upper
+[00:11:29] super trend band presented a short trade
+[00:11:31] setup. Now, when price came back up, you
+[00:11:34] notice these multiple longwick candles
+[00:11:36] at the upper band and at the recent
+[00:11:38] resistance level. And you think to
+[00:11:40] yourself, this is a great short trade
+[00:11:41] setup, and you enter short. And then
+[00:11:43] what happens? Price breaks right through
+[00:11:46] with the massive bullish engulfing
+[00:11:48] candle, and you lose money. The reason
+[00:11:50] this happens is because you are not
+[00:11:52] looking at the big picture and not
+[00:11:54] looking at price action from a larger
+[00:11:56] scope. You are too zoomed in. Let's
+[00:11:59] break down exactly what you got wrong.
+[00:12:02] One, the big picture trend is an
+[00:12:04] uptrend, meaning this could just be a
+[00:12:06] short-term pullback and not a true trend
+[00:12:08] change. Two, you had this key sup</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=As6Sr3OzhzE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRADING RUSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>How I Increased Win Rate In Trading (WITH PROOF)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5 Quy tắc tăng Win Rate dựa trên dữ liệu thực nghiệm: 1. Tỷ lệ R:R tối ưu 1.5:1 (Sweet Spot). 2. Đặt TP dưới Swing High khi pullback sâu. 3. Mua sát đáy Support và chốt sớm khi vừa thoát vùng cản. 4. Hạ R:R khi thị trường xấu để bảo vệ vốn. 5. Kiên nhẫn đứng ngoài khi không có setup.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[00:00:01] when I started trading around 8 years
+[00:00:03] ago I saw many people giving advice on
+[00:00:05] how to get a high win rate but no one
+[00:00:07] showed any proof I mean who knows if
+[00:00:09] they were even getting a high win rate
+[00:00:11] themselves maybe they were just talking
+[00:00:13] big and losing money behind the scenes
+[00:00:15] so I'm creating the kind of video that
+[00:00:17] my beginner self would have found useful
+[00:00:20] because now I have proof since I have
+[00:00:22] shared live trade setups with patreon
+[00:00:24] supporters for multiple years I now have
+[00:00:26] long-term data that shows the way I
+[00:00:28] trade not only worked but also achieved
+[00:00:30] a relatively High win rate getting a
+[00:00:32] high win rate with just 10 or so trades
+[00:00:34] is easy we can get lucky but getting a
+[00:00:37] good win rate and making profits in the
+[00:00:39] long run that's more important in the
+[00:00:41] live setups I have shared over the years
+[00:00:43] I was able to get a 67.8 3% win rate
+[00:00:47] across approximately 398 trades these
+[00:00:50] include both long-term and short-term
+[00:00:52] trades for short-term trades only I
+[00:00:55] achieved a
+[00:00:56] 57.2% win rate across approximately 200
+[00:01:00] 148 trades that's a lot of Trades so
+[00:01:03] here are five simple rules I follow to
+[00:01:05] get a win rate that actually worked in
+[00:01:07] the longterm number five when I first
+[00:01:10] started trading many gurus said to set
+[00:01:12] big profit targets they said your profit
+[00:01:15] Target should be bigger than your
+[00:01:16] stop-loss so that when you lose the next
+[00:01:18] trade can easily make up for it but
+[00:01:21] almost every time I tried this instead
+[00:01:23] of big profits I ended up with big
+[00:01:25] losses these gurus even showed
+[00:01:27] screenshots of big profits but they were
+[00:01:29] probably showing only handpicked setups
+[00:01:32] because when I started testing things
+[00:01:34] myself and making decisions based on
+[00:01:36] data I found something really important
+[00:01:38] in my testing using High reward risk
+[00:01:40] ratios above 2:1 in the trending markets
+[00:01:43] not only lowered the win rate but also
+[00:01:45] reduced the overall profit using lower
+[00:01:48] reward risk ratios increased the win
+[00:01:50] rate but lowered the profit potential
+[00:01:52] again so the profit made went down
+[00:01:54] whether I aimed for targets that were
+[00:01:56] too big or too small why does this
+[00:01:58] happen in trending markets prices often
+[00:02:01] move up and down in a zigzag pattern
+[00:02:03] instead of making strong moves when I
+[00:02:06] used a reward risk ratio that was too
+[00:02:08] high The Profit Target was so far that
+[00:02:11] there was enough time for the trend to
+[00:02:12] weaken start ranging or reverse
+[00:02:15] completely most Trends simply don't last
+[00:02:18] forever on the other hand since the
+[00:02:19] price has a higher chance of moving in
+[00:02:21] the trend Direction when I used a lower
+[00:02:23] reward risk ratio I was literally
+[00:02:26] stopping myself from making more profit
+[00:02:28] from my testing the best best reward
+[00:02:30] risk ratio in a trending Market is
+[00:02:32] around 1.5 to1 this ratio gave a good
+[00:02:35] win rate and kept the profit relatively
+[00:02:38] high in trending markets that's one of
+[00:02:40] the reasons I have used the 1.5 to1
+[00:02:43] ratio from the very first video when I
+[00:02:45] did similar tests again on the trading
+[00:02:47] Rush channel the results were very
+[00:02:49] similar so around a 1.5 to1 ratio is the
+[00:02:52] sweet spot for me to keep a high win
+[00:02:54] rate while still making good profits but
+[00:02:57] remember this is only for the normal
+[00:02:58] trending Market if I spot a news-driven
+[00:03:01] move or something causing a big strong
+[00:03:03] Trend then I prefer using big profit
+[00:03:05] targets but in most trending markets I
+[00:03:07] like to use around a 1.5 to1 ratio as
+[00:03:10] it's the best according to data it keeps
+[00:03:13] the profit potential High while getting
+[00:03:15] a relatively High win rate number four
+[00:03:17] in my beginner days I would wait for the
+[00:03:19] price to pull back in an uptrend take a
+[00:03:21] long entry and set the profit Target
+[00:03:23] above the swing High it made sense
+[00:03:26] because the price was more likely to
+[00:03:27] move above the swing high in a strong
+[00:03:29] uptrend
+[00:03:30] however not all uptrends are strong many
+[00:03:33] are slow I realized that if the pullback
+[00:03:36] was big the swing High could become a
+[00:03:38] strong resistance area when that happens
+[00:03:41] many Traders can close their long
+[00:03:43] positions before reaching the swing High
+[00:03:45] creating higher selling pressure others
+[00:03:47] might take new short trades from the
+[00:03:49] resistance creating even more selling
+[00:03:51] pressure this can lead to the price
+[00:03:53] moving sideways slowing down from this
+[00:03:56] resistance or even reversing completely
+[00:03:59] I saw this happened many times when I
+[00:04:00] set my profit targets way above the
+[00:04:02] swing high resistance to improve my win
+[00:04:05] rate and trade quality I started setting
+[00:04:07] my profit targets below the swing High
+[00:04:09] Resistance this way even if the price
+[00:04:12] slows down or reverses from the
+[00:04:14] resistance my profit targets had a much
+[00:04:16] higher chance of being hit of course if
+[00:04:19] there's strong news pushing the price
+[00:04:20] beyond the swing High I'm fine with
+[00:04:22] setting the target above it but in
+[00:04:24] regular Trends setting the profit Target
+[00:04:26] below the swing High worked much better
+[00:04:28] for me number number three trading
+[00:04:30] reversal setups often made me take
+[00:04:32] trades against the current trend for
+[00:04:34] example if there's a support area the
+[00:04:36] price is probably moving towards it as a
+[00:04:38] downtrend we know that the price usually
+[00:04:41] moves in the direction of the trend but
+[00:04:43] it also has a higher chance of reversing
+[00:04:45] from strong support areas according to
+[00:04:48] data the way I draw support and
+[00:04:50] resistance Works around 60% of the time
+[00:04:53] so I'm obviously not going to ignore the
+[00:04:55] support setup completely but when the
+[00:04:57] price gets near support many things can
+[00:04:59] happen the price can reverse if the
+[00:05:01] downtrend is weaker than the support
+[00:05:03] buying pressure it can move sideways if
+[00:05:05] both pressures are equal or it can
+[00:05:07] continue the downtrend if selling
+[00:05:09] pressure is stronger in two out of these
+[00:05:11] three scenarios setting a big profit
+[00:05:13] Target from the support area doesn't
+[00:05:16] trigger The Profit Target so what I like
+[00:05:18] to do is buy inside the support as much
+[00:05:21] as possible and exit as soon as the
+[00:05:24] buying pressure ends in my experience
+[00:05:26] the higher buying pressure usually ends
+[00:05:28] when the price is no longer in or near
+[00:05:30] the support so I set my profit targets
+[00:05:33] closer to the support by exiting trades
+[00:05:35] quickly when support pressure ends I've
+[00:05:37] been able to increase the win rate of my
+[00:05:39] support resistance setups
+[00:05:41] significantly number two when market
+[00:05:44] conditions get bad and I start losing
+[00:05:46] more trades than usual or when a setup
+[00:05:48] just doesn't feel right I like to use
+[00:05:50] lower reward risk ratios such as below
+[00:05:52] 1:1 this increases the win rate in
+[00:05:55] uncertain markets or with lowquality
+[00:05:57] setups helping me manage losses is
+[00:05:59] better during tough times from the
+[00:06:02] previous data we know a 1.5 to1 reward
+[00:06:05] risk ratio is the most optimal in
+[00:06:07] trending markets but when the trend
+[00:06:09] becomes bad or slow temporarily
+[00:06:12] switching to a lower reward risk ratio
+[00:06:14] has helped me maintain my profits
+[00:06:16] instead of giving them back while
+[00:06:18] maintaining a high win
+[00:06:20] rate number one when I was a beginner
+[00:06:23] and had found a strategy that actually
+[00:06:24] worked I used to get a good winning
+[00:06:26] streak from time to time but soon after
+[00:06:28] I would give back all the profits by
+[00:06:30] overtrading in bad markets I didn't know
+[00:06:32] the value of patience back then I
+[00:06:34] thought I knew patience in trading but
+[00:06:36] whenever I opened my charts I would find
+[00:06:39] trades within a few minutes or even
+[00:06:41] seconds so my actual patience was just
+[00:06:43] around 30 seconds that's stupid a proper
+[00:06:46] Trader should not find trades every
+[00:06:48] single time they open their charts but
+[00:06:50] that was beginner me now after trading
+[00:06:52] for more than 10,000 hours in the live
+[00:06:55] markets I've learned to go multiple
+[00:06:57] weeks and even months without trading if
+[00:06:59] I don't see anything worth trading
+[00:07:01] stopping trading when the markets get
+[00:07:03] bad is what kept me from giving back the
+[00:07:05] profits and helped me maintain the high
+[00:07:07] win rate in the long run now we don't
+[00:07:09] have superpowers we can't see into the
+[00:07:11] future and stop trading just before the
+[00:07:13] markets get bad we will still lose some
+[00:07:16] trades in the bad Market because it
+[00:07:17] takes a little time to realize the
+[00:07:19] market has gotten bad but once I know
+[00:07:21] the market isn't right for my strategy
+[00:07:23] the most important thing I've learned is
+[00:07:25] to stop trading and save money as some
+[00:07:28] random guy once said no no trading is
+[00:07:30] also part of trading it's called saving
+[00:07:32] money instead of losing it on wrong
+[00:07:34] trades that's all
+[00:07:42] [Music]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7:44</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IpSlHWMGgY4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The Trading Channel</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The Only Price Action Trading Video You Will Ever Need (Full Course)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Khóa học Price Action toàn diện: Xác định cấu trúc thị trường (Market Structure), các vùng Hỗ trợ/Kháng cự chính (Major Support &amp; Resistance), đường Xu hướng (Trendlines), các mô hình nến kích hoạt lệnh (Engulfing, Pin bar) và cách đo lường tỷ lệ R:R tối thiểu 1:2.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>**`[00:00:00]`** this video currently has over 21 million this video currently has over 21 million views on YouTube and the reason so many views on YouTube and the reason so many views on YouTube and the reason so many Traders found that video valuable is Traders found that video valuable is Traders found that video valuable is because I poured a ton of time and because I poured a ton of time and because I poured a ton of time and effort to ensure that by the end of that.
+**`[00:00:12]`** effort to ensure that by the end of that effort to ensure that by the end of that video Traders knew everything they video Traders knew everything they video Traders knew everything they needed to know about technical analysis needed to know about technical analysis needed to know about technical analysis in this video I'm doing the same exact in this video I'm doing the same exact in this video I'm doing the same exact thing for Price action so throughout the.
+**`[00:00:21]`** thing for Price action so throughout the thing for Price action so throughout the next 50 minutes you are going to learn next 50 minutes you are going to learn next 50 minutes you are going to learn everything from the complete basics of everything from the complete basics of everything from the complete basics of price action to a full price action price action to a full price action price action to a full price action trading system that I've utilize to pull.
+**`[00:00:30]`** trading system that I've utilize to pull trading system that I've utilize to pull profits out of the market for over 8 profits out of the market for over 8 profits out of the market for over 8 years so if you are a beginner or years so if you are a beginner or years so if you are a beginner or struggling Trader that's currently struggling Trader that's currently struggling Trader that's currently having trouble with any part of price.
+**`[00:00:38]`** having trouble with any part of price having trouble with any part of price action trading or that currently doesn't action trading or that currently doesn't action trading or that currently doesn't have a price action trading system and have a price action trading system and have a price action trading system and trading plan then this video is made for trading plan then this video is made for trading plan then this video is made for you so if you're ready to learn.
+**`[00:00:46]`** you so if you're ready to learn you so if you're ready to learn everything you need to know about price everything you need to know about price everything you need to know about price action over the next 50 minutes sit back action over the next 50 minutes sit back action over the next 50 minutes sit back relax and I'll be right back after the relax and I'll be right back after the relax and I'll be right back after the intro and a swim.
+**`[00:00:56]`** intro and a swim intro and a swim [Music] [Music] [Music] welcome back and let's go aad and get welcome back and let's go aad and get welcome back and let's go aad and get started with what is price action started with what is price action started with what is price action trading price action trading is a.
+**`[00:01:07]`** trading price action trading is a trading price action trading is a technique that allows traders to trade technique that allows traders to trade technique that allows traders to trade not based on indicators but instead not based on indicators but instead not based on indicators but instead based on previous and current price based on previous and current price based on previous and current price movements and the way we make money by.
+**`[00:01:18]`** movements and the way we make money by movements and the way we make money by trading based on price action is by trading based on price action is by trading based on price action is by taking a look at different price action taking a look at different price action taking a look at different price action factors factors such as Trend reversals factors factors such as Trend reversals factors factors such as Trend reversals major levels of structure breakouts.
+**`[00:01:28]`** major levels of structure breakouts major levels of structure breakouts Candlestick patterns chart patterns and Candlestick patterns chart patterns and Candlestick patterns chart patterns and so much more but all of these factors so much more but all of these factors so much more but all of these factors are utilized and combined in order to are utilized and combined in order to are utilized and combined in order to help us make more informed and more.
+**`[00:01:38]`** help us make more informed and more help us make more informed and more accurate trading decisions so now I'm accurate trading decisions so now I'm accurate trading decisions so now I'm going to be diving into each of these going to be diving into each of these going to be diving into each of these price action factors and explaining them price action factors and explaining them price action factors and explaining them to you in detail so that you can not.
+**`[00:01:46]`** to you in detail so that you can not to you in detail so that you can not only spot them in your own trading but only spot them in your own trading but only spot them in your own trading but utilize them to make more accurate utilize them to make more accurate utilize them to make more accurate trading decisions and a little later in trading decisions and a little later in trading decisions and a little later in the video I'm also going to be showing.
+**`[00:01:54]`** the video I'm also going to be showing the video I'm also going to be showing you an entire rules-based price action you an entire rules-based price action you an entire rules-based price action trading strategy so let's go ahead and trading strategy so let's go ahead and trading strategy so let's go ahead and get started with lesson number get started with lesson number get started with lesson number [Music].
+**`[00:02:04]`** [Music] [Music] one I have a very simple set of rules one I have a very simple set of rules one I have a very simple set of rules that helps me to identify trending that helps me to identify trending that helps me to identify trending markets visualizing a trending Market is markets visualizing a trending Market is markets visualizing a trending Market is very easy an uptrend is higher highs and.
+**`[00:02:13]`** very easy an uptrend is higher highs and very easy an uptrend is higher highs and higher lows a downtrend is lower lows higher lows a downtrend is lower lows higher lows a downtrend is lower lows and lower Highs but for those of you who and lower Highs but for those of you who and lower Highs but for those of you who are beginner and struggling Traders I are beginner and struggling Traders I are beginner and struggling Traders I understand that it can be daunting to.
+**`[00:02:21]`** understand that it can be daunting to understand that it can be daunting to look at a chart and try to determine look at a chart and try to determine look at a chart and try to determine what the trend is so with that being the what the trend is so with that being the what the trend is so with that being the case let me explain my exact rules for case let me explain my exact rules for case let me explain my exact rules for identifying Trend right now the first.
+**`[00:02:29]`** identifying Trend right now the first identifying Trend right now the first step in ident ifying a trending Market step in ident ifying a trending Market step in ident ifying a trending Market is understanding major swing highs and is understanding major swing highs and is understanding major swing highs and lows because these are what we're going lows because these are what we're going lows because these are what we're going to use to determine if price is in fact.
+**`[00:02:38]`** to use to determine if price is in fact to use to determine if price is in fact continuing in Trend or starting to continuing in Trend or starting to continuing in Trend or starting to reverse so when identifying Trend I reverse so when identifying Trend I reverse so when identifying Trend I always pick a starting point it's going always pick a starting point it's going always pick a starting point it's going to be right here in this case and this.
+**`[00:02:46]`** to be right here in this case and this to be right here in this case and this starting point has a push higher to a starting point has a push higher to a starting point has a push higher to a new swing High how do I know this is a new swing High how do I know this is a new swing High how do I know this is a new swing High well because a pullback new swing High well because a pullback new swing High well because a pullback happened right after it now for a.
+**`[00:02:55]`** happened right after it now for a happened right after it now for a pullback I have very specific rules I pullback I have very specific rules I pullback I have very specific rules I want to see two opposite color candles want to see two opposite color candles want to see two opposite color candles for a pullback to exist so if we're in for a pullback to exist so if we're in for a pullback to exist so if we're in an uptrend I want to see at least two.
+**`[00:03:05]`** an uptrend I want to see at least two an uptrend I want to see at least two red candles they don't have to be red candles they don't have to be red candles they don't have to be consecutive but they do have to be consecutive but they do have to be consecutive but they do have to be larger red candles I don't want to see larger red candles I don't want to see larger red candles I don't want to see two little dogey red candles that.
+**`[00:03:12]`** two little dogey red candles that two little dogey red candles that wouldn't count as a pullback but these wouldn't count as a pullback but these wouldn't count as a pullback but these two candles would count as a pullback two candles would count as a pullback two candles would count as a pullback for me after that pullback occurs I want for me after that pullback occurs I want for me after that pullback occurs I want to see price break into new Highs at.
+**`[00:03:21]`** to see price break into new Highs at to see price break into new Highs at this point I can identify two different this point I can identify two different this point I can identify two different things and that is Major swing highs and things and that is Major swing highs and things and that is Major swing highs and lows so at first we have our pushup from lows so at first we have our pushup from lows so at first we have our pushup from here to our new swing High we then have.
+**`[00:03:30]`** here to our new swing High we then have here to our new swing High we then have a pullback right here's the lowest point a pullback right here's the lowest point a pullback right here's the lowest point of that pullback and we have a break and of that pullback and we have a break and of that pullback and we have a break and close above our previous swing High when close above our previous swing High when close above our previous swing High when this happens I just take a horizontal.
+**`[00:03:40]`** this happens I just take a horizontal this happens I just take a horizontal line and I put it at the lowest point of line and I put it at the lowest point of line and I put it at the lowest point of our previous pullback before the our previous pullback before the our previous pullback before the breaking close into new structure highs breaking close into new structure highs breaking close into new structure highs so we need to see this one two three.
+**`[00:03:50]`** so we need to see this one two three so we need to see this one two three move meaning a move up a pullback and move meaning a move up a pullback and move meaning a move up a pullback and then a breaking close above the swing then a breaking close above the swing then a breaking close above the swing high that was previously created at the high that was previously created at the high that was previously created at the point that we have this pullback and we.
+**`[00:03:59]`** point that we have this pullback and we point that we have this pullback and we have a breaking close above the swing have a breaking close above the swing have a breaking close above the swing High we can point out our major swing High we can point out our major swing High we can point out our major swing low the reason this is important in low the reason this is important in low the reason this is important in identifying trend is that this Market is.
+**`[00:04:08]`** identifying trend is that this Market is identifying trend is that this Market is considered to be in an uptrend unless a considered to be in an uptrend unless a considered to be in an uptrend unless a candle closes below this previous swing candle closes below this previous swing candle closes below this previous swing low which again is the lowest point in low which again is the lowest point in low which again is the lowest point in the previous pullback so I continue.
+**`[00:04:21]`** the previous pullback so I continue the previous pullback so I continue doing this by putting a horizontal line doing this by putting a horizontal line doing this by putting a horizontal line at our swing High which is our major at our swing High which is our major at our swing High which is our major swing High which is where our pullback swing High which is where our pullback swing High which is where our pullback started and during this pullback as long.
+**`[00:04:30]`** started and during this pullback as long started and during this pullback as long as we stay above this previous swing low as we stay above this previous swing low as we stay above this previous swing low and we don't have a candle that closes and we don't have a candle that closes and we don't have a candle that closes below it we can actually have a wick below it we can actually have a wick below it we can actually have a wick come down here that's completely fine I.
+**`[00:04:38]`** come down here that's completely fine I come down here that's completely fine I just don't want to see a close below just don't want to see a close below just don't want to see a close below this area as long as that close below this area as long as that close below this area as long as that close below doesn't happen I'm still considering doesn't happen I'm still considering doesn't happen I'm still considering this Market to be in an uptrend and this.
+**`[00:04:47]`** this Market to be in an uptrend and this this Market to be in an uptrend and this process just continues as we go higher process just continues as we go higher process just continues as we go higher this move here we go from the low of our this move here we go from the low of our this move here we go from the low of our pullback we break and close above that pullback we break and close a</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47:16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=td5TjsqDCKw</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>🔴 ƯU TIÊN 2 (Mới thêm - Khóa học 2.5h)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Jason Graystone</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trading for Beginners Part 1 - FULL TRADING COURSE TUTORIAL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Khóa học Trading cơ bản đến nâng cao 2.5 giờ: Bản chất thị trường tài chính, quản lý rủi ro và vốn (Risk Management 1%), toán học xác suất trong trading, xây dựng kế hoạch giao dịch (Trading Plan), tâm lý kỷ luật và nhật ký giao dịch.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>**`[00:00:00]`** all right welcome to the video this is all right welcome to the video this is trading for beginners or trading for trading for beginners or trading for trading for beginners or trading for dummies as the thumbnail says and the dummies as the thumbnail says and the dummies as the thumbnail says and the goal of this video is to get you from goal of this video is to get you from goal of this video is to get you from struggling or zero profits or complete.
+**`[00:00:10]`** struggling or zero profits or complete struggling or zero profits or complete beginner right through to consistently beginner right through to consistently beginner right through to consistently profitable Trader which means it's a profitable Trader which means it's a profitable Trader which means it's a comp like complete and comprehensive comp like complete and comprehensive comp like complete and comprehensive program all in itself which means it's.
+**`[00:00:20]`** program all in itself which means it's program all in itself which means it's going to be a long video but my goal is going to be a long video but my goal is going to be a long video but my goal is to get you to consistently profitable to get you to consistently profitable to get you to consistently profitable Trader after watching this video and Trader after watching this video and Trader after watching this video and that's a bold claim but this is.
+**`[00:00:27]`** that's a bold claim but this is that's a bold claim but this is something I've been meaning to put out something I've been meaning to put out something I've been meaning to put out for years and years now because there is for years and years now because there is for years and years now because there is so much crap out there and there's so so much crap out there and there's so so much crap out there and there's so many Educators and fake gurus and scams.
+**`[00:00:37]`** many Educators and fake gurus and scams many Educators and fake gurus and scams trying to take your money and not trying to take your money and not trying to take your money and not providing any value in return so I had providing any value in return so I had providing any value in return so I had enough of all of that and I thought I'm enough of all of that and I thought I'm enough of all of that and I thought I'm just going to give everything away for.
+**`[00:00:44]`** just going to give everything away for just going to give everything away for free to the trading Community once and free to the trading Community once and free to the trading Community once and for all and I'm going to invite you into for all and I'm going to invite you into for all and I'm going to invite you into my trading office as I walk you through my trading office as I walk you through my trading office as I walk you through every component you're going to need.
+**`[00:00:53]`** every component you're going to need every component you're going to need directionally correct so that you get directionally correct so that you get directionally correct so that you get there as quickly as possible without all there as quickly as possible without all there as quickly as possible without all the fluff without all the Showmanship the fluff without all the Showmanship the fluff without all the Showmanship and by the end of this program.
+**`[00:01:00]`** and by the end of this program and by the end of this program you are going to be the most confident you are going to be the most confident you are going to be the most confident and competent Trader that you could and competent Trader that you could and competent Trader that you could possibly dream of being so if that possibly dream of being so if that possibly dream of being so if that sounds good to you I encourage you to.
+**`[00:01:07]`** sounds good to you I encourage you to sounds good to you I encourage you to bookmark this video put it into your bookmark this video put it into your bookmark this video put it into your favorite subscribe to the channel if you favorite subscribe to the channel if you favorite subscribe to the channel if you want to and over the sections of this want to and over the sections of this want to and over the sections of this video I'm going to be covering what your.
+**`[00:01:15]`** video I'm going to be covering what your video I'm going to be covering what your expectation should be what you need in expectation should be what you need in expectation should be what you need in terms of the gear the basics how to read terms of the gear the basics how to read terms of the gear the basics how to read price finding your way around a chart price finding your way around a chart price finding your way around a chart understanding what Forex or trading.
+**`[00:01:24]`** understanding what Forex or trading understanding what Forex or trading actually is and how to navigate the actually is and how to navigate the actually is and how to navigate the markets I'm going to teach you how to markets I'm going to teach you how to markets I'm going to teach you how to read price I'm going to teach you how to read price I'm going to teach you how to read price I'm going to teach you how to identify patterns that happen frequently.
+**`[00:01:32]`** identify patterns that happen frequently identify patterns that happen frequently in the market and then I'm going to in the market and then I'm going to in the market and then I'm going to teach you how to build systems out of teach you how to build systems out of teach you how to build systems out of those patterns and then how to go and those patterns and then how to go and those patterns and then how to go and test those patterns and then how to go.
+**`[00:01:39]`** test those patterns and then how to go test those patterns and then how to go and trade them live I'm going to cover and trade them live I'm going to cover and trade them live I'm going to cover everything from Brokers to gear to everything from Brokers to gear to everything from Brokers to gear to platforms to price to markets to platforms to price to markets to platforms to price to markets to everything by the end of this video.
+**`[00:01:48]`** everything by the end of this video everything by the end of this video there's not going to be anything that there's not going to be anything that there's not going to be anything that you're going to need other than to go you're going to need other than to go you're going to need other than to go and practice and become better and and practice and become better and and practice and become better and better so why am I doing this well some.
+**`[00:01:55]`** better so why am I doing this well some better so why am I doing this well some of you might know me some of you might of you might know me some of you might of you might know me some of you might not know me some of you might be not know me some of you might be not know me some of you might be subscribed to my channel and over the subscribed to my channel and over the subscribed to my channel and over the years I've built a phenomenal community.
+**`[00:02:02]`** years I've built a phenomenal community years I've built a phenomenal community in the trading community and the reason in the trading community and the reason in the trading community and the reason for that is through transparency and for that is through transparency and for that is through transparency and vulnerability of sharing my own trading vulnerability of sharing my own trading vulnerability of sharing my own trading insights my money isn't made from.
+**`[00:02:11]`** insights my money isn't made from insights my money isn't made from education my money comes from investing education my money comes from investing education my money comes from investing my portfolio and making my money work my portfolio and making my money work my portfolio and making my money work for me since the age of 22 I've been for me since the age of 22 I've been for me since the age of 22 I've been investing my money into various.
+**`[00:02:20]`** investing my money into various investing my money into various Investments buying businesses buying Investments buying businesses buying Investments buying businesses buying stocks putting them into index funds and stocks putting them into index funds and stocks putting them into index funds and ETFs and REITs and speculating and ETFs and REITs and speculating and ETFs and REITs and speculating and becoming a Trader and basically using my.
+**`[00:02:30]`** becoming a Trader and basically using my becoming a Trader and basically using my money and putting it to work in a way money and putting it to work in a way money and putting it to work in a way that allows me to grow it as quickly as that allows me to grow it as quickly as that allows me to grow it as quickly as possible that provides me with an income possible that provides me with an income possible that provides me with an income and in doing so I became completely.
+**`[00:02:38]`** and in doing so I became completely and in doing so I became completely financially free by the age of 29 now at financially free by the age of 29 now at financially free by the age of 29 now at the age of 29 when I became financially the age of 29 when I became financially the age of 29 when I became financially free no one knew who I was and after free no one knew who I was and after free no one knew who I was and after seeing all the crap out there online.
+**`[00:02:47]`** seeing all the crap out there online seeing all the crap out there online about trading I decided to just let about trading I decided to just let about trading I decided to just let everyone watch me trade let everyone see everyone watch me trade let everyone see everyone watch me trade let everyone see how a real Trader goes about their day how a real Trader goes about their day how a real Trader goes about their day if I was going to be doing it anyway I.
+**`[00:02:55]`** if I was going to be doing it anyway I if I was going to be doing it anyway I might as well share it with you guys and might as well share it with you guys and might as well share it with you guys and that's exactly what I did and in doing that's exactly what I did and in doing that's exactly what I did and in doing so over the years is I've become so over the years is I've become so over the years is I've become recognized as one of the most.
+**`[00:03:02]`** recognized as one of the most recognized as one of the most transparent and generous traders in the transparent and generous traders in the transparent and generous traders in the trading education space I've become very trading education space I've become very trading education space I've become very close friends with some of the best close friends with some of the best close friends with some of the best trading prop firm owners in the world.
+**`[00:03:10]`** trading prop firm owners in the world trading prop firm owners in the world some of the most reputable trading some of the most reputable trading some of the most reputable trading psychologists in the world and I've psychologists in the world and I've psychologists in the world and I've spoken on some of the most respected spoken on some of the most respected spoken on some of the most respected trading stages across the globe as well.
+**`[00:03:18]`** trading stages across the globe as well trading stages across the globe as well I started sharing my trading routine I started sharing my trading routine I started sharing my trading routine with the trading Community almost 10 with the trading Community almost 10 with the trading Community almost 10 years ago now and in this video I want years ago now and in this video I want years ago now and in this video I want to combine it and compress it all down.
+**`[00:03:25]`** to combine it and compress it all down to combine it and compress it all down so that you walk away feeling as if so that you walk away feeling as if so that you walk away feeling as if you've got more value from this one you've got more value from this one you've got more value from this one video than you have searching the video than you have searching the video than you have searching the internet for months and months and.
+**`[00:03:32]`** internet for months and months and internet for months and months and months maybe even years so why am I months maybe even years so why am I months maybe even years so why am I giving a completely comprehensive course giving a completely comprehensive course giving a completely comprehensive course away for free well here's the truth over away for free well here's the truth over away for free well here's the truth over the years there's been many scammers set.
+**`[00:03:41]`** the years there's been many scammers set the years there's been many scammers set up accounts there's hundreds of fake up accounts there's hundreds of fake up accounts there's hundreds of fake accounts of me and what they're doing is accounts of me and what they're doing is accounts of me and what they're doing is they're contacting people trying to scam they're contacting people trying to scam they're contacting people trying to scam their money and I don't want people to.
+**`[00:03:49]`** their money and I don't want people to their money and I don't want people to lose their money if you're going to lose their money if you're going to lose their money if you're going to become a good Trader the whole point is become a good Trader the whole point is become a good Trader the whole point is that you build wealth and keep money and that you build wealth and keep money and that you build wealth and keep money and not blow it and give it away and lose it.
+**`[00:03:56]`** not blow it and give it away and lose it not blow it and give it away and lose it right you want to build wealth and right you want to build wealth and right you want to build wealth and that's my goal as well so I don't want that's my goal as well so I don't want that's my goal as well so I don't want you to lose your money so how what could you to lose your money so how what could you to lose your money so how what could be the best move that I could make in.
+**`[00:04:05]`** be the best move that I could make in be the best move that I could make in order to eliminate those scams well just order to eliminate those scams well just order to eliminate those scams well just share my best information so that share my best information so that share my best information so that everyone comes here and then there's no everyone comes here and then there's no everyone comes here and then there's no question of what's the real deal and not.
+**`[00:04:16]`** question of what's the real deal and not question of what's the real deal and not only that you'll learn so much in this only that you'll learn so much in this only that you'll learn so much in this lesson that you won't need to go and lesson that yo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2:26:39</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_YVQN6_nkfs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Rayner Teo</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>The Ultimate Candlestick Patterns Trading Course (Khóa Học Nến Toàn Diện)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Hệ thống T.A.E Framework (Trend - Area of Value - Entry Trigger), kỹ thuật gộp nến đa khung (2 nến 1h = 1 nến Pin bar 2h), mô hình nến Engulfing, Hammer, Shooting Star, Morning/Evening Star, Tweezer. Quy tắc không trade nến độc lập mà phải tại cản/MA động.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t># TOÀN BỘ SCRIPT (LỜI THOẠI) KHÓA HỌC: THE ULTIMATE CANDLESTICK PATTERNS TRADING COURSE
 - **Kênh YouTube:** [Rayner Teo (@tradingwithrayner)](https://www.youtube.com/@tradingwithrayner)
@@ -592,324 +1953,24 @@
 **`[00:11:47]`** did close higher above the first so if you look at it this second candle over here it it closed higher above this one over here so that's why you got a bullish bullish close okay and similar for this right this candle it closed right but it didn't exceed the open of this candle so that's why it's still red on the two hour ti</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>38:10</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=C3KRwfj9F8Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Vnrebates</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Khám Phá Setup Giao Dịch Của Trader Nhận Payout 2 Triệu USD</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Đây là xét óp giúp Trader Can Pay Out gần 2 triệu đô từ ProfFirm. Chị tôi vai! Lấy giây bút ra ghi nè. Đầu tiên, chờ phiền Á kết thúc, đánh giấu đỉnh và đáy phiền Á. Kích theo, chờ 1 trong 2 vị trí này bị quét. Ở đây, đáy phiền Á đã bị quét. Vào khung M1, chờ phiền Âu mở cửa. Sau khi phiền Âu bắt đầu, giá đóng cửa tạo CISD. Vào lạnh mùa, Stop Loss dứa đáy vừa quét, thê pe ở đỉnh phiền Á. Nhưng nhớ quản lý lạnh, chốt 1 nữa ở đỉnh củ. Ông đã thử xét óp phiền Á này chưa? Comment cho tôi biết nhé!</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1m - 11m</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7696474697961196808</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Vnrebates</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Thế Nào Là Một Khối Order Block (OB) Chất Lượng</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Giả chạp OrderBlock rồi, mua được chưa ông? Thử đi! Sao kỳ với ta? Để tôi chỉ ông cách chọn ra OrderBlock chất lượng, sẽ cần những yếu tố gì. 1. OrderBlock đó phải tạo ra phá vỡ câu trúc BRS. 2. Theo sau OrderBlock, phải có 1 app Vega. 3. OrderBlock nằm ở vùng premium cho lệnh bán hoặc discount cho lệnh mua. Ở đây, OrderBlock giảm nằm ở premium. 4. Có quét thanh khoảng trước khi giá hồi về OrderBlock. Chỉ vào lệnh khi OrderBlock có ít nhất 3 trên 4 yếu tố. Vào lệnh bán tại OrderBlock, stoplock trên đỉnh OrderBlock RR12. Anh chọp TP luôn! Ông có chọn OrderBlock theo 4 yếu tố này chưa? Comment cho tôi biết nhé!</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1m - 11m</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7696091260565769490</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Vnrebates</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Fibonacci OTE Trong Forex: Cách Chọn Điểm Vào Lệnh An Toàn</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Gia phá đỉnh rồi quay về tét đỉnh con nén en-gu-fing mua thôi! Quang, nếu mua ở đây mà đặt stop-loss ngay dưới vùng đỉnh cũ thì rất không an toàn. Còn nếu đặt stop-loss dưới đấy thì rơ rơ lại rất thấp. Xem nè! Trời ơi, dính stop-loss rồi! Vậy phải làm sao hả ông? Bấu chốt là chúng ta phải tìm được điểm entry có stop-loss an toàn và rơ rơ tốt. Dùng Fibo OTE, kéo từ đáy lên đỉnh theo sưu hướng tăng. Lúc này, ông thấy vùng OTE từ 0.705 đến 0.79 trùng với FVG. Entry ở đây, stop-loss dưới đấy vẫn an toàn mà rơ rơ tốt hơn nhiều. Ông đã biết dùng OTE kết hợp FVG chưa? Comment cho tôi biết nhé!</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1m - 11m</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7695729577947155720</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Vnrebates</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Hướng Dẫn Toàn Diện Về Fair Value Gap (FVG)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Hôm nay sẽ là 1 video khá là dài Mình sẽ hướng dẫn cho anh em những cái thứ chi tiết và thật chiến nhất về FVG, 1 công cụ cực kìa bánh mẽ trong phương pháp ICT Đầu tiên FVG sẽ được chia hình 4 loại hả? Dạy đầu tiên mà chúng ta sẽ học, đó chính là FVG Breakaway Nó sẽ được hình thành từ 3 cái nến tăng liên tiếp với anh em Và nó sẽ là dạy mở rộng Thì khi anh em thấy xuất hiện 3 cái nến tăng liên tiếp Hình thành 1 cái FVG Nó báo hiệu 1 cái động lực tăng mạnh của thị trường Và khả năng cái nha, khả năng cao Những cái FVG Breakaway này á Đến 80% giá nó sẽ tăng tiếp tục Và nó không quay về test cái FVG Thói chúng ta sẽ xem bí dụ mà Ở đây chúng ta có Cây nến khung H1 Anh em thấy không? Đây là 3 cây nến tăng liên tiếp Và nó tạo ra 1 cái buồn FVG ở đây Đúng không? Thì anh em quay xác anh em thấy được đỏ ràng là Giá đó không có test về cái FVG này Ở đây cũng có rất nhiều trường hợp như vậy hả? Này nè mình Khi nó tạo ra 1 cái FVG Breakaway á Ở đây nè Anh em thấy không? Thì giá nó liên tiếp tục tăng lên, tăng lên, tăng lên Cho đến ngày hôm sau nó mới quay về test Mà khi mà nó đi xa như vậy nó quay về test Thì nó không còn mạnh nữa Những FVG được tạo ra thì chúng ta sẽ muốn nó phải test liền Thì khi anh em thấy FVG Breakaway như thế này nè Thì anh em sẽ phải vào trong khung M5 Để anh em tìm kiếm những lệnh tiếp diễn Ok, mình sẽ vào trong khung M5 Mình vào trong khung M5 nè Rồi, mình sẽ tui vào chỗ này Thì trong khung M5 nó lại tiếp tục tạo ra 1 cái FVG Đúng không? Ở đây Thì bây giờ anh em có thể follow hell cái FVG mở năm này rồi Tại vì khi mà nó tạo ra FVG Breakaway ở khung H1 Thì trong khung M5 nó cũng sẽ tạo 1 cái động lực tăng Và lúc này anh em chỉ cần mua ở cái FVG trong khung M5 là được Rồi chúng ta cùng xem giá chạy ha Giá quay về test cái FVG trong khung M5 nè Mà tăng lên Đó chính là cách mà chúng ta sẽ giao dịch với FVG Breakaway Tiếp tục mình sẽ đến với 1 cái FVG bình thường Đó là 1 cái FVG có 2 cái nến tăng và 1 cái nến giảm như thế này Nó không phải là dẹn mở rộng anh em ha Thì với cái FVG dẹn này Giá nó có khả năng test lại cái FVG Sau đó mới tăng ha Thì chúng ta sẽ cùng vào trong cái bí dụ của EU dưới đây Thì bí bí EU này sẽ khá ngược lại là sẽ gồm là 2 cái nến giảm và 1 cái nến tăng Thì nó là FVG dẹn thường nhưng mà nằm trong xuống giảm anh em ha Thì chúng ta cũng có 1 cái FVG chỗ này Mình sẽ đặt lên nó là FVG H1 đi Cho anh em dễ quay xác rồi Rồi bây giờ mình sẽ vào trong khung M5 Tại vì đây là FVG dẹn thường, không phải là dẹn Breakaway Thì giá có khả năng sẽ test lại ha Vào trong khung M5 Rồi mình chờ test lại cái FVG này Rồi thì khi nó test lại cái FVG này rồi Nhưng mà M5 vẫn đang là 1 cái xuống dẹn này, 1 xuống tăng ha Thì mình sẽ chờ nó phá vào cái đáy này Rồi thì khi nó phá vào cái đáy này Nó hình thành cho mình 1 cái FVG Mở 5 ở đây, đúng chưa? Mình sẽ NG ở cái FVG mở 5 này Đặt stop-lock ở trên đây Và đặt cái mức tê bê là 2R 2R này mà Cùng sẽ nhá nó chạy ha Giá test lại cái FVG này Và sạch xuống, đó chính là cách chúng ta ứng dụng FVG bình thường ha Rồi tiếp tục 1 vàng FVG nữa Đó là EFVG Cũng tương tự như thế này, chúng ta có 1 cái FVG tăng đúng không? Đây Và nếu như cái FVG tăng này Nó bị phá bởi 1 cái nến Thay là nhiều cái nến nhứng chìm ha Nó chung là nhứng chìm cái FVG Như thế này Đó Nhứng chìm ha Thì cái FVG này Nó sẽ không còn là FVG nữa Nhưng mà nó sẽ là EFVG Nó sẽ trành EFVG Thì với EFVG, nghĩa là 1 cái FVG bị nhứng chìm Chúng ta sẽ chờ nó test lại và xeo xuống Hoặc là nếu như nó tạo 3 cái nến giảm Mà 1 cái nến tăng nhứng chìm thì chúng ta sẽ bài lên ha Tương tự chúng ta có 1 cái bí vụ ở đây Thử này ha Đây là 3 cái nến giảm đúng chưa? 3 cái nến giảm 1, 2, 3 Nó tạo chúng ta 1 cái FVG Đúng không? Và cái FVG này đã bị nhứng chìm Bởi cái nến tăng này Thì chỗ này nó sẽ trở thành EFVG Rồi cái nhiệm vụ chúng ta chỉ là vì 3 lại khi giá test cái EFVG Đã X lời dưới đây và tề bên trên Rồi cùng xem giá chạy đẹp Giá test lại cái EFVG và Tiếp tục tăng lên Đó là cách xài EFVG ha Rồi 1 dạng FVG nữa Đó là B rồi B B được đựng dễ như thế nào Nếu dư Mình sẽ kéo 3 cái nến giảm Chưa có 3 cái nữa này đi Thì chúng ta sẽ có 1 cái FVG tăng đúng không? Nhưng nếu như cái FVG tăng này Bị nhứng chìm bởi 1 cái FVG giảm đối diện Đây, trái hẹn như thế này là 1 cái 3 cái nến giảm đúng không? 3 cái nến giảm này tạo 1 cái FVG đối diện ở đây Đúng chưa? Đó Thì đây gọi là B rồi B Hay gọi là Subton ha Đây là cái dạng mạnh nha ném Dạng mạnh của FVG đảo chiều Tại vì khi mà Nên nó biết là khi mà giá tạo 1 FVG Chứng đó động lực tăng nó rất là mạnh đúng không? Nhưng mà nó lại bị nhứng chìm Bởi 1 cái động lực giảm Chứng tạo là tại cái vị trí này nha Là cái bên bán nó nhảy vào rất mạnh Thì anh em sẽ canh nó test lại cái FVG này Để anh em bán xuống ha Đó chính là Subton Thì gọi là B rồi B Rồi chúng ta sẽ cùng nhau Nhìn vào cái ví dụ con HU với đây Đây Sau khi giá nó sang ra hành khoảng cái đỉnh bên đây Nè em thấy không? Này nó sang hành khoảng cái đỉnh nè Mình sẽ tua lại ha Nó sang hành khoảng cái đỉnh xong Nó tạo chúng ta 1 cái FVG Đúng chưa? FVG Rồi Và FVG này bị diễn em Bị nhứng chìm bởi cái FVG đối diện Chính là cái FVG này Đúng không? Này FVG tăng bị nhứng chìm bởi FVG giảm Sau đó nó test lại bằng cái nánh này Đây cái nánh này Khi nó tạo được cái FVG giảm nhứng chìm rồi Thì chúng ta tham cú Subton rồi Thì anh em sẽ đặt 1 cái lệnh cell Ngay tại cái FVG giảm được tạo ra X lời đặt trên đây Và TB TB về đáy gần nhất Chính là vị trí này Rồi cùng xem giá chạy ha Giá test lại Và sắp mạnh xuống ha Đó chính là Subton Bây giờ mình nói là khi sẽ là Subton Giá đi rất là mạnh đúng không? Nó sắp rất là mạnh ha Rồi tiếp tục Chúng ta đến với cái FVG Cuối cùng Cái FVG này không dùng để vào lệnh Mà FVG này dùng để làm gì anh em? Dùng để làm đến TB Làm đến TB ha Hay còn gọi là ReFVG ReFVG Nghĩa là sao? Nghĩa là Đây là cái điểm mà anh em sẽ chốt lời Cái điểm này sẽ chốt lời Nếu như anh em có lệnh mua Thì nếu như anh em có 1 cái lệnh mua ở đây Mình giả sử ở đây là 1 case FVG Đúng không? Anh em mua ở đây Anh em phải tới bệp đầu Tên bệp đầu thì đương nhiên là chúng ta sẽ Nhìn những cái cản rồi Thì ở đây có 1 cái FVG đói diện nữa nào Đúng không? Một cái FVG nó diễn nữa Thì nếu như anh em mua ở đây Anh em có thể TB ở đây Và nếu như nó lụng ở đây Thì nó sẽ lên đầu Nó sẽ tìm kiếm ở đâu tiếp Nó sẽ tìm kiếm cái FVG trên đây Thì cái FVG này cũng gọi là ReFVG luôn Và cái FVG này cũng gọi là ReFVG Cả hai cái này đều là ReFVG ha Tao cùng xem giá nó chạy tiếp Nó thì khi giá nó Nó lại tiếp tục Test về cái FVG này Đúng không? Đó tiện em có thể mua ha Có thể mua lên từ đây Rồi giá nó tiếp tục tăng lên thôi Rồi thì TB của này sẽ lâu TB này sẽ là cái ReFVG này Ở chỗ này nó cũng sẽ có 1 cái FVG nào Anh em cũng có thể mua ở cái FVG này Hét lờ dưới đây Và TB cũng về cái ReFVG luôn Hai lần chúng ta được TB về cái ReFVG này Và nếu em kia giá nó chạm đến cái ReFVG này ha Nó sẽ có phản ứng mạnh Mình không biết là nó có xuyên được cái FVG này không Hay là từ cái ReFVG này nó sẽ đảo chiều Nhưng đây là cái điểm TB đẹp nhất Đó thì đây là cái ứng dụng của ReFVG ha Rồi thì trong video hôm nay mình đã chia sẻ cho anh em Hết tất cả những các loại ReFVG có trên thị trường Hầu tiên là ReqAway ReFVG ReFVG bình thường ReFVG BW Và ReFVG Đó là những loại ReFVG mà anh em cần biết Để có thể áp dụng nó vào trong cái quá trình trái đình của mình ha Ok cám ơn em đã theo dõi video này Và nếu anh em thấy hay Các bạn có thể lưu video và bấm vào cái link bio Để tiếp cận những phương pháp trái đình hiệu quả nhất ha Ok cám ơn em đã theo dõi video</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1m - 11m</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7474060511584324885</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Vnrebates</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Xác Định Thanh Khoản Thị Trường (Liquidity ICT)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ICT đã từng nói, tị trường chỉ làm có 2 việc thôi Thứ nhất là quay thanh khỏe và thứ 2 là lắp này các FVG Điều này có nghĩa là nếu như anh em vào một cái lệnh nào đó mà anh em chưa tìm nấy thanh khỏe thì rất có thể anh em sẽ trở thành thanh khỏe ICT là một trader với quan điểm dâu dịch là tị trường luôn luôn tìm thanh khỏe trước khi có những bước đi tiếp theo Thì sau khi tham khảo vào cái tư duy của ICT thì mình đã rút ra được một số các bài học và hôm nay mình sẽ chia sẻ anh em để có thể tăng thêm một cái tự lời hắn của mình Ok, nè Ma, thì anh em nhìn 2 cái bí vụ với đây thì anh em thấy khi giá nó phải hướng tới một cái buồn giá nào đó thì sẽ có 2 trường hợp xảy ra đúng không? Một là giá chạm đứng cái buồn này và tăng lên Nếu anh em ba này sẽ thắng Còn hai, nó chạm buồn này nhưng mà nó không tăng mà nó xuyên luôn thì anh em sẽ thua Anh em nghĩ là chỉ có 2 trường hợp thôi hả? Còn 1 trường hợp nữa đó là giá nó vét đáy xong nó mới thanh Đó Vậy thì nếu như anh em chọn 1 cái chờ về đây anh em ba lên thì anh em có tới 2 trường hợp mà anh em có thể thua được và là cái này và cái này Vậy thì thông bình hơn nó sẽ chờ cái gì? Ta sẽ chờ giá nó vét xong rồi chúng ta mới bầu lệnh thì lúc đó anh em có thể loại được bớt thêm 1 trường hợp thua nữa thì cái thể thắng nó sẽ tăng lên đúng không? Rồi bây giờ nó sẽ cùng nhau nhìn vào cái trạng này Đây là 1 cái cấu chút tăng đúng rồi anh em, chút tăng này thì có nhiều nên sẽ canh 3 cái giá qua bên bùn đáy này Thì khi giá trạm bùn đáy này nó sức hiểm cơ nến bin ba đứt rau thì là phần anh em sẽ vào buồn ở đây x lờ dưới cái đáy này và bề bề thì chúng ta cùng xem giá nó đi như thế nào hả? Mới vụng ta 1 vài trành bị x lờ sau đó nó mới tăng lên thì mình sẽ vào lệnh khi này bị béc rồi và tiếp tục tăng lên nè sau khi béc xong anh em phải tăng lên nó đóng đến qua cái nến này thì lúc này đây chỉ là 1 cái phá bởi giả thôi nè thì chúng ta mới bắt đầu vào lệnh mua vị trí này đạt sublots như đây và tb lên trần cùng xem giá nó chạy hả? Sau khi được bấy đựng sublots rồi thì giá nó đi rất là nhanh và đạt được tb đó là cách để thông minh nhớ nè chờ giá quá thân ngoại thông chúng ta mới vào chúng ta sẽ có tự lệnh hắn cao hơn ok nè mà lô video lại để xem kì cứng thiết</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1m - 11m</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7446381153868598534</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SO Trading</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3 lỗi vào lệnh khiến bạn bị cắt lỗ oan (và cách sửa) Sửa lỗi quan trọ...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>3 lỗi vào lệnh khiến bạn bị cắt lỗ oan (và cách sửa) Sửa lỗi quan trọng hơn tìm phương pháp mới. 3 lỗi hay gặp: tin tín hiệu khung nhỏ mà quên khung lớn, vào lệnh ngược để gỡ, đóng lệnh vì giá lình xình. Nguồn: nội dung do SO TRADING tự biên soạn. #Shorts #Trading</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bị cắt lỗ oan liên tục, có thể lỗi nằm ở chính bạn, không phải phương pháp. Mới giao dịch, ai cũng đi tìm phương pháp tốt nhất. Nhưng sửa từng lỗi sai của mình còn quan trọng hơn nhiều. Lỗi thứ nhất: Thấy tín hiệu đẹp ở khung M5 mà quên nhìn khung lớn. Cấu trúc giảm, nến nhấn chìm, vậy mà vài nến sau đã dính cắt lỗ, lý do nằm ở khung M15, đợt giảm đó nằm giữa vùng bò rất mạnh. Gấu con đang đánh vào căn cứ của bò mẹ. Trước khi tin tín hiệu, hãy hỏi 3 điều: Khung lớn có ngược mình không? Phe mình đã thất bại mấy lần ở đó? Và giá có đang đi ngang lộn xộn không? Nếu có, hãy đứng ngoài. Lỗi thứ hai: Vào lệnh ngược lại để gỡ. Vừa bị cắt lỗ là muốn gỡ ngay. Lệnh đó đến từ cảm xúc, không phải từ phương pháp. Nguy hiểm nhất là khi lệnh gỡ lại thắng. Bạn tưởng cách này hiệu quả, lần sau gấp đôi khối lượng. Một lệnh thắng chẳng chứng minh được gì. Lỗi thứ ba: Đóng lệnh vì giá lình xình. Vừa đóng ở hòa vốn thì giá chạy thẳng tới điểm chốt lời. Một lệnh thắng bị biến thành lệnh hòa/thua. Đã có phương pháp được kiểm chứng thì hãy tin nó, đúng quy tắc vào lệnh, đúng quy tắc chốt lời, không để cảm xúc chen vào. Tóm lại: Nhìn khung lớn trước, không vào lệnh để gỡ, không đóng lệnh trái quy tắc. Sửa được 3 lỗi này đáng giá hơn tìm một phương pháp mới. Theo dõi SO Trading để giao dịch kỷ luật hơn mỗi ngày.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1:21</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696679708485897478</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -924,42 +1985,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SO Trading</t>
+          <t>Vnrebates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Đọc nến theo luật bò gấu: vẽ căn cứ, chờ tín hiệu Đọc nến là đọc hành...</t>
+          <t>Khám Phá Setup Giao Dịch Của Trader Nhận Payout 2 Triệu USD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Đọc nến theo luật bò gấu: vẽ căn cứ, chờ tín hiệu Đọc nến là đọc hành vi mua bán: phe nào chiếm ưu thế, phe nào cạn lực.</t>
+          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Đọc nén không phải thuộc tên mẫu nén, mà là xem phê nào đang thắng. Trước hết, vẽ căn cứ của hai phê, vùng bò và vùng gấu ở khung đang giao dịch và khung kề trên. Giá chạy qua lại giữa hai vùng, có tín hiệu thì bật lại, không có thể phá qua vào vùng đổi vai. Vùng mạnh nhất là nơi bắt đầu một con sóng với những cây nén thân dài và giúp. Nhưng vùng mạnh mới là sắc xuất, cần thêm tín hiệu, nén nhỏ, dần có dâu hoặc cặp nén nhấn trìm. Tín hiệu xuất hiện lưng trừng thì kém tin cậy hơn tín hiệu ngay tại căn cứ. Tín hiệu đẹp mà tỉ lệ lời lộ kém hoặc ngực bối cảnh thì vẫn bỏ qua, phá thật hay phá giả. Xem nhịp hồi. Hồi về vùng vừa phá rồi đi tiếp theo hướng phá là phá thật, dữ lệnh bằng căn cứ. Rồi cắt lỗ ra sau căn cứ mới nhất và chốt khi ra tới căn cứ của phê kia. Bụng đích là sắc xuất cao, không phải thắng mọi lệnh. Tâm lý ổn định thì lợi nhuận mới đều. Theo dõi Sotrading để học đọc lên mỗi ngày.</t>
+          <t>Đây là xét óp giúp Trader Can Pay Out gần 2 triệu đô từ ProfFirm. Chị tôi vai! Lấy giây bút ra ghi nè. Đầu tiên, chờ phiền Á kết thúc, đánh giấu đỉnh và đáy phiền Á. Kích theo, chờ 1 trong 2 vị trí này bị quét. Ở đây, đáy phiền Á đã bị quét. Vào khung M1, chờ phiền Âu mở cửa. Sau khi phiền Âu bắt đầu, giá đóng cửa tạo CISD. Vào lạnh mùa, Stop Loss dứa đáy vừa quét, thê pe ở đỉnh phiền Á. Nhưng nhớ quản lý lạnh, chốt 1 nữa ở đỉnh củ. Ông đã thử xét óp phiền Á này chưa? Comment cho tôi biết nhé!</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1m - 11m</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696533638371970325</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7696474697961196808</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -974,42 +2035,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SO Trading</t>
+          <t>Vnrebates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7 bài học sau một buổi luyện tập giao dịch trên dữ liệu quá khứ #Shor...</t>
+          <t>Thế Nào Là Một Khối Order Block (OB) Chất Lượng</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7 bài học sau một buổi luyện tập giao dịch trên dữ liệu quá khứ #Shorts Bảy bài học rút ra từ buổi luyện vào lệnh trên dữ liệu quá khứ BTCUSD (M15 + H1): bức tranh lớn, vùng cản, chờ tín hiệu, tỷ lệ lời/lỗ, lệnh chờ phá, quản lý lệnh và thống kê. Nguồn: nội dung do SO TRADING tự biên soạn. #Shorts #trading #bitcoin</t>
+          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Điện tập trên dữ liệu quá khứ, mình rút ra 7 bài học đáng giá 1. Xem bức tranh lớn trước. Khung lớn đi ngang thì đứng ngoài, hoặc chỉ canh vùng cản mạnh. 2. Chỉ vẽ vùng cản mạnh. Nơi bắt đầu còn sóng giúp. Vùng bị phá thì xóa đi. 3. Chờ phê ngực lại thất bại nhiều lần rồi mới vào. Đừng đặt sẵn lệnh trờ ngay vùng cản. 4. Tính tỉ lệ lời trên lỗ trước khi vào. Cản phía trước quá gần thì bỏ qua. 5. Dùng lệnh trờ phá để giá tự sắc nhận. Không phá thì lệnh không khớp, bạn không mất gì. 6. Rời cắt lỗ theo cấu trúc. Người mới cứ đặt chốt lời gấp đôi dùi do rồi để lệnh trại. 7. Đọc thống kê. Nhưng vài lệnh thì chưa nói lên điều gì. Cần hàng trăm lệnh mới đáng tin và chỉ luyện một phương pháp. Lặp lại đủ nhiều, nó sẽ thành phản xạ. Luyện tập không phải để đoán đúng từng lệnh, mà để đọc vùng cản, chờ tín hiệu và quản lý lệnh thành phản xạ. Theo dõi short reading để học thêm mỗi ngày.</t>
+          <t>Giả chạp OrderBlock rồi, mua được chưa ông? Thử đi! Sao kỳ với ta? Để tôi chỉ ông cách chọn ra OrderBlock chất lượng, sẽ cần những yếu tố gì. 1. OrderBlock đó phải tạo ra phá vỡ câu trúc BRS. 2. Theo sau OrderBlock, phải có 1 app Vega. 3. OrderBlock nằm ở vùng premium cho lệnh bán hoặc discount cho lệnh mua. Ở đây, OrderBlock giảm nằm ở premium. 4. Có quét thanh khoảng trước khi giá hồi về OrderBlock. Chỉ vào lệnh khi OrderBlock có ít nhất 3 trên 4 yếu tố. Vào lệnh bán tại OrderBlock, stoplock trên đỉnh OrderBlock RR12. Anh chọp TP luôn! Ông có chọn OrderBlock theo 4 yếu tố này chưa? Comment cho tôi biết nhé!</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1m - 11m</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696421857871908116</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7696091260565769490</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1024,42 +2085,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SO Trading</t>
+          <t>Vnrebates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vào lệnh phá vỡ: 7 bài học chọn cú phá đẹp Không phải cú phá vỡ vùng ...</t>
+          <t>Fibonacci OTE Trong Forex: Cách Chọn Điểm Vào Lệnh An Toàn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Vào lệnh phá vỡ: 7 bài học chọn cú phá đẹp Không phải cú phá vỡ vùng cản nào cũng đáng vào lệnh. 7 bài học: vùng nhiều đỉnh, khung lớn, độ nén, chốt lời, dời cắt lỗ, ưu nhược điểm so với chờ hồi. Nguồn: nội dung do SO TRADING cung cấp. Nội dung chỉ mang tính giáo dục, không phải khuyến nghị đầu tư. #Shorts #trading #phavo</t>
+          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Không phải cú pha vỡ nào cũng đáng vào lệnh. Đây là 7 bài học để chọn cú pha đẹp. Giá phá qua vùng cản mới chỉ là điều kiện đầu tiên chưa đủ để vào lệnh. Phá vùng nhiều đỉnh mạnh hơn phá một đỉnh vì phê bán đã rồn hết lực mà vẫn thua. Nhìn khung lớn hơn để biết phê mua có chiếm yêu thế. Và lệnh có thể đi xa tới đầu. Đẹp nhất là khi các đáy cao dần nén sát vùng đỉnh rồi bung lên. Cắt lỗ đặt dưới đáy gần nhất. Đặt trốt lời gấp đôi rủi do rồi nhìn sang bên trái. Có vùng cản nguy hiểm phía trước thì bỏ qua. Giá đi đúng hướng thì dời điểm cắt lỗ lên dưới đáy cao hơn mới. Lệnh phá vỡ cho kết quả rất nhanh vì phê ngược lại đã cạn lực. Nhưng chọn điểm vào kém thì cắt lỗ rất xa. Làm hỏng tỷ lệ lời trên lỗ. Chờ giá hồi về thì cắt lỗ ngắn hơn nhưng giá thường phải đi ngang một thời gian. Tìm vùng nhiều đỉnh, chờ giá nén rồi phá và chỉ vào khi phía trước còn chỗ chạy. Theo dõi SO Trading để xem thêm.</t>
+          <t>Gia phá đỉnh rồi quay về tét đỉnh con nén en-gu-fing mua thôi! Quang, nếu mua ở đây mà đặt stop-loss ngay dưới vùng đỉnh cũ thì rất không an toàn. Còn nếu đặt stop-loss dưới đấy thì rơ rơ lại rất thấp. Xem nè! Trời ơi, dính stop-loss rồi! Vậy phải làm sao hả ông? Bấu chốt là chúng ta phải tìm được điểm entry có stop-loss an toàn và rơ rơ tốt. Dùng Fibo OTE, kéo từ đáy lên đỉnh theo sưu hướng tăng. Lúc này, ông thấy vùng OTE từ 0.705 đến 0.79 trùng với FVG. Entry ở đây, stop-loss dưới đấy vẫn an toàn mà rơ rơ tốt hơn nhiều. Ông đã biết dùng OTE kết hợp FVG chưa? Comment cho tôi biết nhé!</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>1m - 11m</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696331802654280980</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7695729577947155720</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1074,42 +2135,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SO Trading</t>
+          <t>Vnrebates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Giao dịch như lính bắn tỉa: đo độ chính xác, đừng đếm số lệnh 7 bài h...</t>
+          <t>Hướng Dẫn Toàn Diện Về Fair Value Gap (FVG)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Giao dịch như lính bắn tỉa: đo độ chính xác, đừng đếm số lệnh 7 bài học từ hình ảnh lính bắn tỉa: chính xác hơn số lượng, kẻ thù là chính mình, phương pháp là vũ khí, luyện hàng nghìn lần, luyện trên dữ liệu quá khứ, tự bóp cò, khung nhỏ không nhiễu. Nguồn: nội dung do kênh SO TRADING tổng hợp. Chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #giaodich #trading</t>
+          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lính bán tỉa, không bán ít. Họ bán chính xác, bán tỉa là độ chính xác, không phải ít hay nhiều lệnh. Vào ít mà sai nhiều thì vẫn không giỏi, kẻ thù không phải thị trường. Bạn không điều khiển được giá, chỉ điều khiển được chính mình. Phương Pháp là vũ khí. Đừng ra chận tay không, cũng đừng mang quá nhiều thứ mà không thạo thứ nào. Sạ thủ giỏi bán hàng nghìn viên khi luyện tập. Simo hay he hạ khoảng 500 linh năm mục tiêu trong 100 ngày. Các luyện nhanh nhất là vào lệnh trên dữ liệu quá khứ. Một giờ tua biểu đồ bằng 6 tuần giao dịch thật. Càng nhiều lệnh, bạn càng sớm thấy lỗi của mình, mà không tốn một đồng tiền thật. Gia trận thì tự mình bóp cỏ. Theo tín hiệu mù quán, không ai có lợi nhuận ổn địch. Không nhỏ, không hề nhéo, chỉ là bạn chưa hiểu. Luyện đủ lâu, biểu đồ nào cũng đọc được. Đừng đếm số lệnh, hãy đò độ chính xác của mỗi phát bán theo dõi Soul Trading để luyện từng phát bán chính xác hơn.</t>
+          <t>Hôm nay sẽ là 1 video khá là dài Mình sẽ hướng dẫn cho anh em những cái thứ chi tiết và thật chiến nhất về FVG, 1 công cụ cực kìa bánh mẽ trong phương pháp ICT Đầu tiên FVG sẽ được chia hình 4 loại hả? Dạy đầu tiên mà chúng ta sẽ học, đó chính là FVG Breakaway Nó sẽ được hình thành từ 3 cái nến tăng liên tiếp với anh em Và nó sẽ là dạy mở rộng Thì khi anh em thấy xuất hiện 3 cái nến tăng liên tiếp Hình thành 1 cái FVG Nó báo hiệu 1 cái động lực tăng mạnh của thị trường Và khả năng cái nha, khả năng cao Những cái FVG Breakaway này á Đến 80% giá nó sẽ tăng tiếp tục Và nó không quay về test cái FVG Thói chúng ta sẽ xem bí dụ mà Ở đây chúng ta có Cây nến khung H1 Anh em thấy không? Đây là 3 cây nến tăng liên tiếp Và nó tạo ra 1 cái buồn FVG ở đây Đúng không? Thì anh em quay xác anh em thấy được đỏ ràng là Giá đó không có test về cái FVG này Ở đây cũng có rất nhiều trường hợp như vậy hả? Này nè mình Khi nó tạo ra 1 cái FVG Breakaway á Ở đây nè Anh em thấy không? Thì giá nó liên tiếp tục tăng lên, tăng lên, tăng lên Cho đến ngày hôm sau nó mới quay về test Mà khi mà nó đi xa như vậy nó quay về test Thì nó không còn mạnh nữa Những FVG được tạo ra thì chúng ta sẽ muốn nó phải test liền Thì khi anh em thấy FVG Breakaway như thế này nè Thì anh em sẽ phải vào trong khung M5 Để anh em tìm kiếm những lệnh tiếp diễn Ok, mình sẽ vào trong khung M5 Mình vào trong khung M5 nè Rồi, mình sẽ tui vào chỗ này Thì trong khung M5 nó lại tiếp tục tạo ra 1 cái FVG Đúng không? Ở đây Thì bây giờ anh em có thể follow hell cái FVG mở năm này rồi Tại vì khi mà nó tạo ra FVG Breakaway ở khung H1 Thì trong khung M5 nó cũng sẽ tạo 1 cái động lực tăng Và lúc này anh em chỉ cần mua ở cái FVG trong khung M5 là được Rồi chúng ta cùng xem giá chạy ha Giá quay về test cái FVG trong khung M5 nè Mà tăng lên Đó chính là cách mà chúng ta sẽ giao dịch với FVG Breakaway Tiếp tục mình sẽ đến với 1 cái FVG bình thường Đó là 1 cái FVG có 2 cái nến tăng và 1 cái nến giảm như thế này Nó không phải là dẹn mở rộng anh em ha Thì với cái FVG dẹn này Giá nó có khả năng test lại cái FVG Sau đó mới tăng ha Thì chúng ta sẽ cùng vào trong cái bí dụ của EU dưới đây Thì bí bí EU này sẽ khá ngược lại là sẽ gồm là 2 cái nến giảm và 1 cái nến tăng Thì nó là FVG dẹn thường nhưng mà nằm trong xuống giảm anh em ha Thì chúng ta cũng có 1 cái FVG chỗ này Mình sẽ đặt lên nó là FVG H1 đi Cho anh em dễ quay xác rồi Rồi bây giờ mình sẽ vào trong khung M5 Tại vì đây là FVG dẹn thường, không phải là dẹn Breakaway Thì giá có khả năng sẽ test lại ha Vào trong khung M5 Rồi mình chờ test lại cái FVG này Rồi thì khi nó test lại cái FVG này rồi Nhưng mà M5 vẫn đang là 1 cái xuống dẹn này, 1 xuống tăng ha Thì mình sẽ chờ nó phá vào cái đáy này Rồi thì khi nó phá vào cái đáy này Nó hình thành cho mình 1 cái FVG Mở 5 ở đây, đúng chưa? Mình sẽ NG ở cái FVG mở 5 này Đặt stop-lock ở trên đây Và đặt cái mức tê bê là 2R 2R này mà Cùng sẽ nhá nó chạy ha Giá test lại cái FVG này Và sạch xuống, đó chính là cách chúng ta ứng dụng FVG bình thường ha Rồi tiếp tục 1 vàng FVG nữa Đó là EFVG Cũng tương tự như thế này, chúng ta có 1 cái FVG tăng đúng không? Đây Và nếu như cái FVG tăng này Nó bị phá bởi 1 cái nến Thay là nhiều cái nến nhứng chìm ha Nó chung là nhứng chìm cái FVG Như thế này Đó Nhứng chìm ha Thì cái FVG này Nó sẽ không còn là FVG nữa Nhưng mà nó sẽ là EFVG Nó sẽ trành EFVG Thì với EFVG, nghĩa là 1 cái FVG bị nhứng chìm Chúng ta sẽ chờ nó test lại và xeo xuống Hoặc là nếu như nó tạo 3 cái nến giảm Mà 1 cái nến tăng nhứng chìm thì chúng ta sẽ bài lên ha Tương tự chúng ta có 1 cái bí vụ ở đây Thử này ha Đây là 3 cái nến giảm đúng chưa? 3 cái nến giảm 1, 2, 3 Nó tạo chúng ta 1 cái FVG Đúng không? Và cái FVG này đã bị nhứng chìm Bởi cái nến tăng này Thì chỗ này nó sẽ trở thành EFVG Rồi cái nhiệm vụ chúng ta chỉ là vì 3 lại khi giá test cái EFVG Đã X lời dưới đây và tề bên trên Rồi cùng xem giá chạy đẹp Giá test lại cái EFVG và Tiếp tục tăng lên Đó là cách xài EFVG ha Rồi 1 dạng FVG nữa Đó là B rồi B B được đựng dễ như thế nào Nếu dư Mình sẽ kéo 3 cái nến giảm Chưa có 3 cái nữa này đi Thì chúng ta sẽ có 1 cái FVG tăng đúng không? Nhưng nếu như cái FVG tăng này Bị nhứng chìm bởi 1 cái FVG giảm đối diện Đây, trái hẹn như thế này là 1 cái 3 cái nến giảm đúng không? 3 cái nến giảm này tạo 1 cái FVG đối diện ở đây Đúng chưa? Đó Thì đây gọi là B rồi B Hay gọi là Subton ha Đây là cái dạng mạnh nha ném Dạng mạnh của FVG đảo chiều Tại vì khi mà Nên nó biết là khi mà giá tạo 1 FVG Chứng đó động lực tăng nó rất là mạnh đúng không? Nhưng mà nó lại bị nhứng chìm Bởi 1 cái động lực giảm Chứng tạo là tại cái vị trí này nha Là cái bên bán nó nhảy vào rất mạnh Thì anh em sẽ canh nó test lại cái FVG này Để anh em bán xuống ha Đó chính là Subton Thì gọi là B rồi B Rồi chúng ta sẽ cùng nhau Nhìn vào cái ví dụ con HU với đây Đây Sau khi giá nó sang ra hành khoảng cái đỉnh bên đây Nè em thấy không? Này nó sang hành khoảng cái đỉnh nè Mình sẽ tua lại ha Nó sang hành khoảng cái đỉnh xong Nó tạo chúng ta 1 cái FVG Đúng chưa? FVG Rồi Và FVG này bị diễn em Bị nhứng chìm bởi cái FVG đối diện Chính là cái FVG này Đúng không? Này FVG tăng bị nhứng chìm bởi FVG giảm Sau đó nó test lại bằng cái nánh này Đây cái nánh này Khi nó tạo được cái FVG giảm nhứng chìm rồi Thì chúng ta tham cú Subton rồi Thì anh em sẽ đặt 1 cái lệnh cell Ngay tại cái FVG giảm được tạo ra X lời đặt trên đây Và TB TB về đáy gần nhất Chính là vị trí này Rồi cùng xem giá chạy ha Giá test lại Và sắp mạnh xuống ha Đó chính là Subton Bây giờ mình nói là khi sẽ là Subton Giá đi rất là mạnh đúng không? Nó sắp rất là mạnh ha Rồi tiếp tục Chúng ta đến với cái FVG Cuối cùng Cái FVG này không dùng để vào lệnh Mà FVG này dùng để làm gì anh em? Dùng để làm đến TB Làm đến TB ha Hay còn gọi là ReFVG ReFVG Nghĩa là sao? Nghĩa là Đây là cái điểm mà anh em sẽ chốt lời Cái điểm này sẽ chốt lời Nếu như anh em có lệnh mua Thì nếu như anh em có 1 cái lệnh mua ở đây Mình giả sử ở đây là 1 case FVG Đúng không? Anh em mua ở đây Anh em phải tới bệp đầu Tên bệp đầu thì đương nhiên là chúng ta sẽ Nhìn những cái cản rồi Thì ở đây có 1 cái FVG đói diện nữa nào Đúng không? Một cái FVG nó diễn nữa Thì nếu như anh em mua ở đây Anh em có thể TB ở đây Và nếu như nó lụng ở đây Thì nó sẽ lên đầu Nó sẽ tìm kiếm ở đâu tiếp Nó sẽ tìm kiếm cái FVG trên đây Thì cái FVG này cũng gọi là ReFVG luôn Và cái FVG này cũng gọi là ReFVG Cả hai cái này đều là ReFVG ha Tao cùng xem giá nó chạy tiếp Nó thì khi giá nó Nó lại tiếp tục Test về cái FVG này Đúng không? Đó tiện em có thể mua ha Có thể mua lên từ đây Rồi giá nó tiếp tục tăng lên thôi Rồi thì TB của này sẽ lâu TB này sẽ là cái ReFVG này Ở chỗ này nó cũng sẽ có 1 cái FVG nào Anh em cũng có thể mua ở cái FVG này Hét lờ dưới đây Và TB cũng về cái ReFVG luôn Hai lần chúng ta được TB về cái ReFVG này Và nếu em kia giá nó chạm đến cái ReFVG này ha Nó sẽ có phản ứng mạnh Mình không biết là nó có xuyên được cái FVG này không Hay là từ cái ReFVG này nó sẽ đảo chiều Nhưng đây là cái điểm TB đẹp nhất Đó thì đây là cái ứng dụng của ReFVG ha Rồi thì trong video hôm nay mình đã chia sẻ cho anh em Hết tất cả những các loại ReFVG có trên thị trường Hầu tiên là ReqAway ReFVG ReFVG bình thường ReFVG BW Và ReFVG Đó là những loại ReFVG mà anh em cần biết Để có thể áp dụng nó vào trong cái quá trình trái đình của mình ha Ok cám ơn em đã theo dõi video này Và nếu anh em thấy hay Các bạn có thể lưu video và bấm vào cái link bio Để tiếp cận những phương pháp trái đình hiệu quả nhất ha Ok cám ơn em đã theo dõi video</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1m - 11m</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696144076411817268</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7474060511584324885</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1124,38 +2185,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SO Trading</t>
+          <t>Vnrebates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kế hoạch một ngày giao dịch: 7 bài học để không chơi cho vui Giao dịc...</t>
+          <t>Xác Định Thanh Khoản Thị Trường (Liquidity ICT)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kế hoạch một ngày giao dịch: 7 bài học để không chơi cho vui Giao dịch thành công không cao siêu, nó dành cho người có kế hoạch. 7 bài học: coi giao dịch là công việc, chọn khung giờ cố định, lướt nhanh đầu ngày, đừng ép vào lệnh, luyện tập thật nhiều, không dán mắt vào giá, kiểm tra trước khi vào lệnh. Nguồn: nội dung do kênh SO TRADING tổng hợp. Nội dung chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #giaodich #trading #kehoach</t>
+          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Giao dịch như một trò chơi, đó là cách nhanh nhất để mất tiền, hãy coi giao dịch là công việc. Tự do, nhưng phải có kế hoạch rõ ràng, chọn một khung giờ cố định trùng lúc thị trường mạnh nhất, phiên Âu và phiên Mỹ không cần ngồi cả ngày. Não không thể tập trung liên tục, nhất là khi có tiền dính vào, đầu ngày, lượt nhanh các cặp tiền khoảng 10 phút để nắm su hướng, rồi tắt máy, đừng cố tìm lý do để vào lệnh. Không giao dịch cũng là một phần của công việc. Phần lớn thời gian là luyện tập, 99 phần chuẩn bị, một phần thực chiến để biểu đồ sắn nhưng đừng dám mắt vào giá. Liết trưa đầy một phút là đủ, trước khi vào lệnh, kiểm tra, su hướng lớn, vùng cản, điểm cắt lỗ và tỷ lệ lời trên lỗ, vào lệnh rồi thì đừng ngồi canh và đừng kỳ vọng thắng mọi lệnh vài lệnh không nói lên điều gì. Kết quả chỉ rõ khi số lệnh đủ nhiều, ưu khóa cần nhớ là chuẩn bị. Theo dõi show trading để xây kế hoạch giao dịch của riêng bạn.</t>
+          <t>ICT đã từng nói, tị trường chỉ làm có 2 việc thôi Thứ nhất là quay thanh khỏe và thứ 2 là lắp này các FVG Điều này có nghĩa là nếu như anh em vào một cái lệnh nào đó mà anh em chưa tìm nấy thanh khỏe thì rất có thể anh em sẽ trở thành thanh khỏe ICT là một trader với quan điểm dâu dịch là tị trường luôn luôn tìm thanh khỏe trước khi có những bước đi tiếp theo Thì sau khi tham khảo vào cái tư duy của ICT thì mình đã rút ra được một số các bài học và hôm nay mình sẽ chia sẻ anh em để có thể tăng thêm một cái tự lời hắn của mình Ok, nè Ma, thì anh em nhìn 2 cái bí vụ với đây thì anh em thấy khi giá nó phải hướng tới một cái buồn giá nào đó thì sẽ có 2 trường hợp xảy ra đúng không? Một là giá chạm đứng cái buồn này và tăng lên Nếu anh em ba này sẽ thắng Còn hai, nó chạm buồn này nhưng mà nó không tăng mà nó xuyên luôn thì anh em sẽ thua Anh em nghĩ là chỉ có 2 trường hợp thôi hả? Còn 1 trường hợp nữa đó là giá nó vét đáy xong nó mới thanh Đó Vậy thì nếu như anh em chọn 1 cái chờ về đây anh em ba lên thì anh em có tới 2 trường hợp mà anh em có thể thua được và là cái này và cái này Vậy thì thông bình hơn nó sẽ chờ cái gì? Ta sẽ chờ giá nó vét xong rồi chúng ta mới bầu lệnh thì lúc đó anh em có thể loại được bớt thêm 1 trường hợp thua nữa thì cái thể thắng nó sẽ tăng lên đúng không? Rồi bây giờ nó sẽ cùng nhau nhìn vào cái trạng này Đây là 1 cái cấu chút tăng đúng rồi anh em, chút tăng này thì có nhiều nên sẽ canh 3 cái giá qua bên bùn đáy này Thì khi giá trạm bùn đáy này nó sức hiểm cơ nến bin ba đứt rau thì là phần anh em sẽ vào buồn ở đây x lờ dưới cái đáy này và bề bề thì chúng ta cùng xem giá nó đi như thế nào hả? Mới vụng ta 1 vài trành bị x lờ sau đó nó mới tăng lên thì mình sẽ vào lệnh khi này bị béc rồi và tiếp tục tăng lên nè sau khi béc xong anh em phải tăng lên nó đóng đến qua cái nến này thì lúc này đây chỉ là 1 cái phá bởi giả thôi nè thì chúng ta mới bắt đầu vào lệnh mua vị trí này đạt sublots như đây và tb lên trần cùng xem giá nó chạy hả? Sau khi được bấy đựng sublots rồi thì giá nó đi rất là nhanh và đạt được tb đó là cách để thông minh nhớ nè chờ giá quá thân ngoại thông chúng ta mới vào chúng ta sẽ có tự lệnh hắn cao hơn ok nè mà lô video lại để xem kì cứng thiết</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1m - 11m</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696052072612973844</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7446381153868598534</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1179,33 +2240,33 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Độ nén của giá: 7 điều giúp cắt lỗ ngắn, thắng nhiều hơn #Shorts Độ n...</t>
+          <t>3 lỗi vào lệnh khiến bạn bị cắt lỗ oan (và cách sửa) Sửa lỗi quan trọ...</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Độ nén của giá: 7 điều giúp cắt lỗ ngắn, thắng nhiều hơn #Shorts Độ nén của giá là gì, vì sao giá nén rồi bung, cách nhìn hình dạng vùng nén và đặt cắt lỗ ngắn mà an toàn. Nội dung do kênh SO TRADING tổng hợp. Giao dịch luôn có rủi ro, đây không phải lời khuyên đầu tư. #Shorts #trading #giaodich</t>
+          <t>3 lỗi vào lệnh khiến bạn bị cắt lỗ oan (và cách sửa) Sửa lỗi quan trọng hơn tìm phương pháp mới. 3 lỗi hay gặp: tin tín hiệu khung nhỏ mà quên khung lớn, vào lệnh ngược để gỡ, đóng lệnh vì giá lình xình. Nguồn: nội dung do SO TRADING tự biên soạn. #Shorts #Trading</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Có một điều ít ai nói tới, nhưng giúp bạn thắng nhiều hơn và cắt lỗ ngắn hơn, đó là độ nén của giá. Hôm nay mình đi qua 7 điều cần nắm. 1. Giá đi ngang, đáy cao dần, đỉnh thấp dần, biên độ thu hẹp, tức là giá đăng nén. Nén càng sát nhau thì nén càng mạnh, sống bên trong càng lớn thì nén càng yếu. 2. Giá nén vì lực 2 phê ngang nhau, phê mua đẩy đáy lên, phê bán ép đỉnh xuống. 3. Nén thì sẽ bung như quả bóng bơm quá căng, nén càng mạnh, bung càng mạnh. Hướng bung thì nhìn bối cảnh lớn, trong xu hướng tăng dễ phá lên, trong vùng giảm dễ phá xuống. 4. Tất cả chỉ là sắc suất, việc của mình là tăng sắc suất, không tìm sự chắc chắn. 5. Tạm ra cần là hai phê ngang sức, đáy giúp lên là phê mua mạnh hơn, đỉnh giúp xuống là phê bán mạnh hơn, vùng giá mở rộng như cái loa thì đứng ngoài. Vì cả hai phê đều loạn. 6. Vùng nén cho điểm cắt lỗ vừa an toàn vừa ngắn vì vào lệnh ngay chỗ giá hẹp nhất. 7. Đừng rời cắt lỗ ra xa. Giá đã phá căn cứ thì phê kia đã thắng thế, tìm vùng nén, chờ giá bùng, vào lệnh với cắt lỗ ngắn. Theo dõi show trading để học thêm.</t>
+          <t>Bị cắt lỗ oan liên tục, có thể lỗi nằm ở chính bạn, không phải phương pháp. Mới giao dịch, ai cũng đi tìm phương pháp tốt nhất. Nhưng sửa từng lỗi sai của mình còn quan trọng hơn nhiều. Lỗi thứ nhất: Thấy tín hiệu đẹp ở khung M5 mà quên nhìn khung lớn. Cấu trúc giảm, nến nhấn chìm, vậy mà vài nến sau đã dính cắt lỗ, lý do nằm ở khung M15, đợt giảm đó nằm giữa vùng bò rất mạnh. Gấu con đang đánh vào căn cứ của bò mẹ. Trước khi tin tín hiệu, hãy hỏi 3 điều: Khung lớn có ngược mình không? Phe mình đã thất bại mấy lần ở đó? Và giá có đang đi ngang lộn xộn không? Nếu có, hãy đứng ngoài. Lỗi thứ hai: Vào lệnh ngược lại để gỡ. Vừa bị cắt lỗ là muốn gỡ ngay. Lệnh đó đến từ cảm xúc, không phải từ phương pháp. Nguy hiểm nhất là khi lệnh gỡ lại thắng. Bạn tưởng cách này hiệu quả, lần sau gấp đôi khối lượng. Một lệnh thắng chẳng chứng minh được gì. Lỗi thứ ba: Đóng lệnh vì giá lình xình. Vừa đóng ở hòa vốn thì giá chạy thẳng tới điểm chốt lời. Một lệnh thắng bị biến thành lệnh hòa/thua. Đã có phương pháp được kiểm chứng thì hãy tin nó, đúng quy tắc vào lệnh, đúng quy tắc chốt lời, không để cảm xúc chen vào. Tóm lại: Nhìn khung lớn trước, không vào lệnh để gỡ, không đóng lệnh trái quy tắc. Sửa được 3 lỗi này đáng giá hơn tìm một phương pháp mới. Theo dõi SO Trading để giao dịch kỷ luật hơn mỗi ngày.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1:10</t>
+          <t>1:21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695960796676803861</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696679708485897478</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1229,33 +2290,33 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hiểu đúng đa khung thời gian: 6 điều đừng học vẹt Sáu điều cần hiểu đ...</t>
+          <t>Đọc nến theo luật bò gấu: vẽ căn cứ, chờ tín hiệu Đọc nến là đọc hành...</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hiểu đúng đa khung thời gian: 6 điều đừng học vẹt Sáu điều cần hiểu đúng về đa khung thời gian trong giao dịch: không cần xem nhiều khung, không cần cùng hướng, vùng cản lớn nhỏ và cách vào lệnh theo cung cầu. #Shorts #trading #dakhungthoigian</t>
+          <t>Đọc nến theo luật bò gấu: vẽ căn cứ, chờ tín hiệu Đọc nến là đọc hành vi mua bán: phe nào chiếm ưu thế, phe nào cạn lực.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Xem nhiều khung thời gian hơn, không có nghĩa là giao dịch tốt hơn. Đa khung thời gian, ai cũng quan tâm, nhưng nhiều người chỉ học vẹt. Đây là 6 điều cần hiểu đúng. 1. Xem nhiều khung, không phải càng nhiều càng tốt. Lệnh ở khung 10 năm, chỉ 5 trong 1, 2 cây đến hức 4, còn chưa hết 1 đến ngày. Cùng quá lớn gần như không có tác dụng với lệnh đó. Xem chúng chỉ làm bạn phân vần khi tín hiệu đẹp xuất hiện. 2. Không cần mọi khung cùng 1 hướng. Khung lớn có thể đang giảm, nhưng 1 cây nén tăng của nó là cả su hướng tăng dài ở khung nhỏ. 3. Khung thời gian, chỉ là cách con người đóng khung giá. Giá đi thành 1 đường duy nhất như sợi chỉ, gom lại thì thành nén. 4. Không có vùng cản của 15 hay của 1. Chỉ có vùng cản lớn hơn và vùng cản nhỏ hơn. 5. Muốn nhìn tổng thể, hãy thu nhỏ biểu đồ hoặc lên đúng 1 khung kỳ trên. Đừng nhảy lên khung quá xa. 6. Vào lệnh theo kịch bản cung cầu. Giá phá đỉnh cũ rồi đi ngang, phê mua chiếm ưu thế thì chờ giá phá vùng đỉnh đó. Khi đó vào lệnh mua, cách lỗ đặt dưới vùng vừa phá chất lời nhắm tới vùng cản lớn hơn phía trên. Đừng học thuộc phải xem bao nhiêu khung. Hãy hiểu giá được tạo ra thế nào, rồi chọn cách nhìn thuận tiện nhất cho mình. Rưu duy sai giống con đỉa, bám càng lâu càng hút cạn tiền bạc. Theo dõi sò trading để giao dịch đúng bản chất.</t>
+          <t>Đọc nén không phải thuộc tên mẫu nén, mà là xem phê nào đang thắng. Trước hết, vẽ căn cứ của hai phê, vùng bò và vùng gấu ở khung đang giao dịch và khung kề trên. Giá chạy qua lại giữa hai vùng, có tín hiệu thì bật lại, không có thể phá qua vào vùng đổi vai. Vùng mạnh nhất là nơi bắt đầu một con sóng với những cây nén thân dài và giúp. Nhưng vùng mạnh mới là sắc xuất, cần thêm tín hiệu, nén nhỏ, dần có dâu hoặc cặp nén nhấn trìm. Tín hiệu xuất hiện lưng trừng thì kém tin cậy hơn tín hiệu ngay tại căn cứ. Tín hiệu đẹp mà tỉ lệ lời lộ kém hoặc ngực bối cảnh thì vẫn bỏ qua, phá thật hay phá giả. Xem nhịp hồi. Hồi về vùng vừa phá rồi đi tiếp theo hướng phá là phá thật, dữ lệnh bằng căn cứ. Rồi cắt lỗ ra sau căn cứ mới nhất và chốt khi ra tới căn cứ của phê kia. Bụng đích là sắc xuất cao, không phải thắng mọi lệnh. Tâm lý ổn định thì lợi nhuận mới đều. Theo dõi Sotrading để học đọc lên mỗi ngày.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1:19</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695799603068734741</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696533638371970325</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1279,17 +2340,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7 bài học sau 5 năm đi cùng thị trường | SO TRADING Bảy bài học kinh ...</t>
+          <t>7 bài học sau một buổi luyện tập giao dịch trên dữ liệu quá khứ #Shor...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7 bài học sau 5 năm đi cùng thị trường | SO TRADING Bảy bài học kinh nghiệm sau 5 năm tham gia thị trường: biết đứng ngoài, có kịch bản, quản lý rủi ro, tránh khoảng trống cuối tuần. #trading #crypto #fx</t>
+          <t>7 bài học sau một buổi luyện tập giao dịch trên dữ liệu quá khứ #Shorts Bảy bài học rút ra từ buổi luyện vào lệnh trên dữ liệu quá khứ BTCUSD (M15 + H1): bức tranh lớn, vùng cản, chờ tín hiệu, tỷ lệ lời/lỗ, lệnh chờ phá, quản lý lệnh và thống kê. Nguồn: nội dung do SO TRADING tự biên soạn. #Shorts #trading #bitcoin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SU Trading chia sẻ 5 năm trong thị trường mình rút ra 7 bài học này 1. Thị trường đi ngang thì đứng ngoài chỉ hành động khi khung lớn cho lý do rõ ràng 2. Có kịch bản trước khi vào lệnh Giá không phá nổi vùng cản thì thoát dù lời chưa nhiều 3. Điểm vào chưa đẹp thì chờ ở vùng tốt hơn để cắt lỗ gần hơn và rủi do nhỏ hơn 4. Lệnh đang lời thì rời cắt lỗ về hòa vốn và chốt trước 1 phần khi giá chạm vùng nguy hiểm 5. Đừng giữ lệnh ngắn hạn qua cuối tuần vì khoảng chống giá đầu tuần rất nguy hiểm 6. Đừng bắt đầu bằng khung thời gian nhỏ Chọn khung lớn đặt lệnh xong rồi để đó 7. Ýt yếu tố ủng hộ thì khả năng thắng thấp Và thua như vậy là bình thường, muốn biết phương pháp hiệu quả đến đâu Hãy thống kê theo từng cặp tiền và từng khung thời gian Tóm lại, đứng ngoài khi thị trường không rõ và luôn có kịch bản trước khi vào lệnh Đây là kinh nghiệm cá nhân, không phải lời khuyên đầu tư Gé SO Trading để cùng trao đổi thêm nhé!</t>
+          <t>Điện tập trên dữ liệu quá khứ, mình rút ra 7 bài học đáng giá 1. Xem bức tranh lớn trước. Khung lớn đi ngang thì đứng ngoài, hoặc chỉ canh vùng cản mạnh. 2. Chỉ vẽ vùng cản mạnh. Nơi bắt đầu còn sóng giúp. Vùng bị phá thì xóa đi. 3. Chờ phê ngực lại thất bại nhiều lần rồi mới vào. Đừng đặt sẵn lệnh trờ ngay vùng cản. 4. Tính tỉ lệ lời trên lỗ trước khi vào. Cản phía trước quá gần thì bỏ qua. 5. Dùng lệnh trờ phá để giá tự sắc nhận. Không phá thì lệnh không khớp, bạn không mất gì. 6. Rời cắt lỗ theo cấu trúc. Người mới cứ đặt chốt lời gấp đôi dùi do rồi để lệnh trại. 7. Đọc thống kê. Nhưng vài lệnh thì chưa nói lên điều gì. Cần hàng trăm lệnh mới đáng tin và chỉ luyện một phương pháp. Lặp lại đủ nhiều, nó sẽ thành phản xạ. Luyện tập không phải để đoán đúng từng lệnh, mà để đọc vùng cản, chờ tín hiệu và quản lý lệnh thành phản xạ. Theo dõi short reading để học thêm mỗi ngày.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1299,13 +2360,13 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695696836140616980</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696421857871908116</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1329,33 +2390,33 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7 bài học từ 3 lệnh thực tế: 2 thắng, 1 thua vì lỗi bất cẩn Hai lệnh ...</t>
+          <t>Vào lệnh phá vỡ: 7 bài học chọn cú phá đẹp Không phải cú phá vỡ vùng ...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7 bài học từ 3 lệnh thực tế: 2 thắng, 1 thua vì lỗi bất cẩn Hai lệnh thắng, một lệnh thua vì một lỗi bất cẩn. Bảy bài học về chờ xu hướng rõ, vào lệnh khi đủ yếu tố, đặt lệnh chờ, quản lý khối lượng, kiểm soát cảm xúc và giữ điểm cắt lỗ. Nguồn: kinh nghiệm giao dịch thực tế của SO TRADING. #Shorts #trading #giaodich</t>
+          <t>Vào lệnh phá vỡ: 7 bài học chọn cú phá đẹp Không phải cú phá vỡ vùng cản nào cũng đáng vào lệnh. 7 bài học: vùng nhiều đỉnh, khung lớn, độ nén, chốt lời, dời cắt lỗ, ưu nhược điểm so với chờ hồi. Nguồn: nội dung do SO TRADING cung cấp. Nội dung chỉ mang tính giáo dục, không phải khuyến nghị đầu tư. #Shorts #trading #phavo</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2 lệnh thắng, 1 lệnh thua vì 1 lỗi bất cảnh. Đây là 7 bài học đắt giá. 1. Su hướng gió là lợi thế lớn nhất. Nó không xuất hiện thường xuyên nên hãy kiên nhận trở. 2. Gom đủ 3 yếu tố rồi mới vào. Su hướng vung cản của phê mình và tín hiệu đến xác nhận. 3. Giá đã chạy xa thì đặt lệnh trở vùng đỉnh cũ. Không khớp cũng không mất tiền, tính khối lượng trước để biết thua mất bao nhiêu. Chốt lời mặc định gấp 2 lần rủi do. 4. Tận dụng núp phê nâu mở cửa, đầu giờ chiều giờ Việt Nam khi tín hiệu xuất hiện nhiều. 5. Vào lệnh xong đừng nhìn biểu đồ quá nhiều, nhìn nhiều dễ chốt sớm rồi tiếc, hãy gạt cảm xúc gắn với tiền. Chỉ vui khi làm đúng kịch bản, chỉ ái náy khi làm sai kịch bản. 6. Lệnh rủi do thì hoặc đứng ngoài, hoặc canh tới nơi tới chốn. Không canh được thì đóng lệnh. 7. Giữ điểm cắt lỗ, đừng rời hay bỏ, và xem lại lệnh cũ để thấy lỗi hay lặp lại. Còn vốn thì còn lấy lại được, và phần lời chính là kinh nghiệm, trở xu hướng rõ, đủ yếu tố mới vào, làm đúng kịch bản. Theo dõi SO Trading để học giao dịch có kỷ luật.</t>
+          <t>Không phải cú pha vỡ nào cũng đáng vào lệnh. Đây là 7 bài học để chọn cú pha đẹp. Giá phá qua vùng cản mới chỉ là điều kiện đầu tiên chưa đủ để vào lệnh. Phá vùng nhiều đỉnh mạnh hơn phá một đỉnh vì phê bán đã rồn hết lực mà vẫn thua. Nhìn khung lớn hơn để biết phê mua có chiếm yêu thế. Và lệnh có thể đi xa tới đầu. Đẹp nhất là khi các đáy cao dần nén sát vùng đỉnh rồi bung lên. Cắt lỗ đặt dưới đáy gần nhất. Đặt trốt lời gấp đôi rủi do rồi nhìn sang bên trái. Có vùng cản nguy hiểm phía trước thì bỏ qua. Giá đi đúng hướng thì dời điểm cắt lỗ lên dưới đáy cao hơn mới. Lệnh phá vỡ cho kết quả rất nhanh vì phê ngược lại đã cạn lực. Nhưng chọn điểm vào kém thì cắt lỗ rất xa. Làm hỏng tỷ lệ lời trên lỗ. Chờ giá hồi về thì cắt lỗ ngắn hơn nhưng giá thường phải đi ngang một thời gian. Tìm vùng nhiều đỉnh, chờ giá nén rồi phá và chỉ vào khi phía trước còn chỗ chạy. Theo dõi SO Trading để xem thêm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1:09</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695602506377809173</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696331802654280980</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1379,33 +2440,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3 lỗi tâm lý giao dịch khiến bạn cháy tài khoản (và cách sửa) Phương ...</t>
+          <t>Giao dịch như lính bắn tỉa: đo độ chính xác, đừng đếm số lệnh 7 bài h...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3 lỗi tâm lý giao dịch khiến bạn cháy tài khoản (và cách sửa) Phương pháp chỉ là một phần, tâm lý mới quyết định. 3 lỗi gần như ai cũng gặp: sợ bỏ lỡ (FOMO), trả thù thị trường, chốt lời sớm - gồng lỗ dài, cùng cách sửa đơn giản cho từng lỗi. Nguồn: nội dung BlackRose Admin (08/10/2026), biên soạn lại bởi SO TRADING. Nội dung chỉ mang tính tham khảo, không phải khuyến nghị đầu tư. #Shorts #trading #tamlygiaodich</t>
+          <t>Giao dịch như lính bắn tỉa: đo độ chính xác, đừng đếm số lệnh 7 bài học từ hình ảnh lính bắn tỉa: chính xác hơn số lượng, kẻ thù là chính mình, phương pháp là vũ khí, luyện hàng nghìn lần, luyện trên dữ liệu quá khứ, tự bóp cò, khung nhỏ không nhiễu. Nguồn: nội dung do kênh SO TRADING tổng hợp. Chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #giaodich #trading</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ba lỗi tâm lý này đang âm thầm đốt tài khoản của bạn. Phương pháp giao dịch không phải tất cả. Phần lớn thành công đến từ tâm lý. Lỗi 1. Sợ bỏ lỡ cơ hội. Thấy giá chạy, thấy người khác lời là vào lệnh bừa. Cách sửa, rời nhóm chát tín hiệu, tự luyện tập và xây chiến lược vào lệnh của riêng bạn. Lỗi 2. Chả thủ tị trường. Thua xong là gấp đôi khối lượng để gỡ lại. Cách sửa. Chỉ nắp ít khoảng 2 phần chăm vốn để có khoảng dừng mà tỉnh lại và đi từ nhỏ đến lớn. 10 đô và 1 nghìn đô cho cảm xúc rất khác nhau. Lỗi 3. Chốt lời sớm, gồng lỗ dài. Thắng thì ăn ít, thua thì lỗ nhiều. Cách sửa. Đặt sẵn chốt lời và cắt lỗ. Ban đầu cho 2 mức bằng nhau. Đặt xong thì đừng nhìn tài khoản. Giữ từ 1 tuần đến 1 tháng để thành thói quen. Ba lỗi như 3 tảng đá trên đường. Quay lại. Hoặc vượt qua từng tảng 1. Bạn đang vướng lỗi nào? Theo dõi sốt trading để học giao dịch bên vững hơn.</t>
+          <t>Lính bán tỉa, không bán ít. Họ bán chính xác, bán tỉa là độ chính xác, không phải ít hay nhiều lệnh. Vào ít mà sai nhiều thì vẫn không giỏi, kẻ thù không phải thị trường. Bạn không điều khiển được giá, chỉ điều khiển được chính mình. Phương Pháp là vũ khí. Đừng ra chận tay không, cũng đừng mang quá nhiều thứ mà không thạo thứ nào. Sạ thủ giỏi bán hàng nghìn viên khi luyện tập. Simo hay he hạ khoảng 500 linh năm mục tiêu trong 100 ngày. Các luyện nhanh nhất là vào lệnh trên dữ liệu quá khứ. Một giờ tua biểu đồ bằng 6 tuần giao dịch thật. Càng nhiều lệnh, bạn càng sớm thấy lỗi của mình, mà không tốn một đồng tiền thật. Gia trận thì tự mình bóp cỏ. Theo tín hiệu mù quán, không ai có lợi nhuận ổn địch. Không nhỏ, không hề nhéo, chỉ là bạn chưa hiểu. Luyện đủ lâu, biểu đồ nào cũng đọc được. Đừng đếm số lệnh, hãy đò độ chính xác của mỗi phát bán theo dõi Soul Trading để luyện từng phát bán chính xác hơn.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695389393443409173</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696144076411817268</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1429,33 +2490,33 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chứng khoán, tiền điện tử hay ngoại hối: chọn thị trường nào? So sánh...</t>
+          <t>Kế hoạch một ngày giao dịch: 7 bài học để không chơi cho vui Giao dịc...</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chứng khoán, tiền điện tử hay ngoại hối: chọn thị trường nào? So sánh 3 thị trường theo 4 đặc điểm: pháp lý, thanh khoản, thời gian giao dịch, nền tảng. Nguồn: nội dung do tác giả cung cấp. #Shorts #trading #xuhuong #crypto #fx</t>
+          <t>Kế hoạch một ngày giao dịch: 7 bài học để không chơi cho vui Giao dịch thành công không cao siêu, nó dành cho người có kế hoạch. 7 bài học: coi giao dịch là công việc, chọn khung giờ cố định, lướt nhanh đầu ngày, đừng ép vào lệnh, luyện tập thật nhiều, không dán mắt vào giá, kiểm tra trước khi vào lệnh. Nguồn: nội dung do kênh SO TRADING tổng hợp. Nội dung chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #giaodich #trading #kehoach</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Trứng khoán, tiền điện tử hay ngoại hối, chọn sai thị trường là mất tiền. Bối thị trường có đặc điểm riêng, hãy xét bốn thứ, pháp lý, thanh khoản, thời gian giao dịch và nền tảng. Pháp lý, trứng khoán được nhà nước bảo hộ chặt trẽ. Tiền điện tử và ngoại hối thì chưa được công nhận. Vì vậy, giữ số tiền lớn lâu dài thì trứng khoán an toàn hơn, đừng ném cả tài sản vào sản không tên tuổi. Thanh khoản, ngoại hối lớn nhất, rồi trứng khoán, rồi tiền điện tử. Nhưng trứng khoán Việt Nam thấp nhất nên chỉ hợp đầu tư dài hạn. Cổ phiếu và tiền điện tử dễ bị thao túng, biến động vài chục phần trăm. Cặp tiền lệch 1 phần trăm 1 ngày đã là nhiều. Thời gian, trứng khoán chỉ mở khoảng 4 tiếng 1 ngày, ngoại hối 24h, 5 ngày, tiền điện tử 24h, 7 ngày, nền tảng. Sanh ngoại hối giao dịch được tiền tệ, tiền điện tử, chỉ số và vàng. Nhưng đó là hợp đồng tranh lệch bạn không sở hữu tài sản. Tóm lại, trứng khoán hợp dài hạn, ngoại hối chỉ hợp ngắn hạn. Tiền điện tử hợp cả 2 nhưng rủi do cao, và dù chọn thị trường nào cũng phải chọn sản uy tín. Sanh kém thì ở đâu cũng dễ mất tiền, theo dõi để học cách bảo vệ và làm sinh lời đồng vốn của bạn mỗi ngày.</t>
+          <t>Giao dịch như một trò chơi, đó là cách nhanh nhất để mất tiền, hãy coi giao dịch là công việc. Tự do, nhưng phải có kế hoạch rõ ràng, chọn một khung giờ cố định trùng lúc thị trường mạnh nhất, phiên Âu và phiên Mỹ không cần ngồi cả ngày. Não không thể tập trung liên tục, nhất là khi có tiền dính vào, đầu ngày, lượt nhanh các cặp tiền khoảng 10 phút để nắm su hướng, rồi tắt máy, đừng cố tìm lý do để vào lệnh. Không giao dịch cũng là một phần của công việc. Phần lớn thời gian là luyện tập, 99 phần chuẩn bị, một phần thực chiến để biểu đồ sắn nhưng đừng dám mắt vào giá. Liết trưa đầy một phút là đủ, trước khi vào lệnh, kiểm tra, su hướng lớn, vùng cản, điểm cắt lỗ và tỷ lệ lời trên lỗ, vào lệnh rồi thì đừng ngồi canh và đừng kỳ vọng thắng mọi lệnh vài lệnh không nói lên điều gì. Kết quả chỉ rõ khi số lệnh đủ nhiều, ưu khóa cần nhớ là chuẩn bị. Theo dõi show trading để xây kế hoạch giao dịch của riêng bạn.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1:13</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695191312605187348</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696052072612973844</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1479,33 +2540,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Đầu tư và giao dịch khác nhau ở đâu? Đầu tư và giao dịch giống nhau ở...</t>
+          <t>Độ nén của giá: 7 điều giúp cắt lỗ ngắn, thắng nhiều hơn #Shorts Độ n...</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Đầu tư và giao dịch khác nhau ở đâu? Đầu tư và giao dịch giống nhau ở bản chất mua rẻ bán đắt, khác nhau ở thời gian giữ lệnh và tâm lý. Video giải thích ngắn gọn, dễ hiểu. #trading #fx #crypto</t>
+          <t>Độ nén của giá: 7 điều giúp cắt lỗ ngắn, thắng nhiều hơn #Shorts Độ nén của giá là gì, vì sao giá nén rồi bung, cách nhìn hình dạng vùng nén và đặt cắt lỗ ngắn mà an toàn. Nội dung do kênh SO TRADING tổng hợp. Giao dịch luôn có rủi ro, đây không phải lời khuyên đầu tư. #Shorts #trading #giaodich</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Đầu tư và giao dịch khác nhau ở đâu? Hầu hết mọi người đều hiểu sai, ở cả 3 thị trường, bản chất đều giống nhau, mua giá thấp, bán giá cao, chứng khoán, mua bán cổ phiếu, tức quyền sở hữu một phần công ty, tiền điện tử là Bitcoin và các đồng khác. Ngoại hối là Đô Là Mỹ, Yên Nhật khác nhau chính là thời gian giữ lệnh, giữ nhiều tháng, nhiều năm là đầu tư. Giữ theo food, giờ, ngay là giao dịch, đầu tư không tốn nhiều thời gian như giao dịch, nhưng vẫn mang lại nguồn thu nhập tốt, nhưng có người đầu tư mà nhìn giá cả ngày, lỗ thì mất ngủ. Đó là tâm lý giao dịch, ngược lại, có người giao dịch ít lệnh và đúng lúc vẫn có thời gian cho việc khác, che tên sản phẩm đi, chỉ còn nến và giá. Chọn thị trường theo đặc điểm, không phải vì biết nó trước, đầu tư hay giao dịch chỉ đa, kết quả nằm ở cách bạn dùng nó, theo dõi để học thêm nha.</t>
+          <t>Có một điều ít ai nói tới, nhưng giúp bạn thắng nhiều hơn và cắt lỗ ngắn hơn, đó là độ nén của giá. Hôm nay mình đi qua 7 điều cần nắm. 1. Giá đi ngang, đáy cao dần, đỉnh thấp dần, biên độ thu hẹp, tức là giá đăng nén. Nén càng sát nhau thì nén càng mạnh, sống bên trong càng lớn thì nén càng yếu. 2. Giá nén vì lực 2 phê ngang nhau, phê mua đẩy đáy lên, phê bán ép đỉnh xuống. 3. Nén thì sẽ bung như quả bóng bơm quá căng, nén càng mạnh, bung càng mạnh. Hướng bung thì nhìn bối cảnh lớn, trong xu hướng tăng dễ phá lên, trong vùng giảm dễ phá xuống. 4. Tất cả chỉ là sắc suất, việc của mình là tăng sắc suất, không tìm sự chắc chắn. 5. Tạm ra cần là hai phê ngang sức, đáy giúp lên là phê mua mạnh hơn, đỉnh giúp xuống là phê bán mạnh hơn, vùng giá mở rộng như cái loa thì đứng ngoài. Vì cả hai phê đều loạn. 6. Vùng nén cho điểm cắt lỗ vừa an toàn vừa ngắn vì vào lệnh ngay chỗ giá hẹp nhất. 7. Đừng rời cắt lỗ ra xa. Giá đã phá căn cứ thì phê kia đã thắng thế, tìm vùng nén, chờ giá bùng, vào lệnh với cắt lỗ ngắn. Theo dõi show trading để học thêm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1:10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694935798524742932</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695960796676803861</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1529,33 +2590,33 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4 bước vào lệnh chuẩn: cấu trúc, khung lớn, vùng cản, tín hiệu yếu dầ...</t>
+          <t>Hiểu đúng đa khung thời gian: 6 điều đừng học vẹt Sáu điều cần hiểu đ...</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4 bước vào lệnh chuẩn: cấu trúc, khung lớn, vùng cản, tín hiệu yếu dần Phương pháp vào lệnh gồm bốn bước kèm ví dụ ETHUSD khung M15. Nội dung do tác giả chia sẻ, không phải lời khuyên đầu tư.  #trading #fx #cypto</t>
+          <t>Hiểu đúng đa khung thời gian: 6 điều đừng học vẹt Sáu điều cần hiểu đúng về đa khung thời gian trong giao dịch: không cần xem nhiều khung, không cần cùng hướng, vùng cản lớn nhỏ và cách vào lệnh theo cung cầu. #Shorts #trading #dakhungthoigian</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Vào lệnh, đúng không phải đoán mò. Mà đi theo bốn bước. Bước 1, xác định cấu trúc trên khung đang giao dịch. Bước 2, tìm thêm yêu tố ủng hộ ở khung lớn hơn một bậc. Bước 3, chờ giá hồi về vùng cản quan trọng. Bước 4, chờ phê ngược lại yếu dần rồi mới vào lệnh. Ví dụ mua ATHSD 015, giá phá đỉnh 2 lần, đáy quan trọng vẫn được giữ. Chờ giá hồi về đỉnh cũ rồi mới mua, cắt lỗ dưới vùng đó. Lệnh lời gấp 3 rủi do, không xem thêm chỉ cần lớn hơn một bậc. 15 xem, 1, 1 xem, hư bốn, hư bốn xem khung ngày, cách này dùng được cho mọi thị trường. Khung lớn ủng hộ rõ, chỉ cần tín hiệu vừa phải ở khung nhỏ. Duyên đời mới chỉ là một chân của cái kiểu 3 chân. Theo rõi để xem 2 chân còn lại. Quán lý vốn và kỷ luật.</t>
+          <t>Xem nhiều khung thời gian hơn, không có nghĩa là giao dịch tốt hơn. Đa khung thời gian, ai cũng quan tâm, nhưng nhiều người chỉ học vẹt. Đây là 6 điều cần hiểu đúng. 1. Xem nhiều khung, không phải càng nhiều càng tốt. Lệnh ở khung 10 năm, chỉ 5 trong 1, 2 cây đến hức 4, còn chưa hết 1 đến ngày. Cùng quá lớn gần như không có tác dụng với lệnh đó. Xem chúng chỉ làm bạn phân vần khi tín hiệu đẹp xuất hiện. 2. Không cần mọi khung cùng 1 hướng. Khung lớn có thể đang giảm, nhưng 1 cây nén tăng của nó là cả su hướng tăng dài ở khung nhỏ. 3. Khung thời gian, chỉ là cách con người đóng khung giá. Giá đi thành 1 đường duy nhất như sợi chỉ, gom lại thì thành nén. 4. Không có vùng cản của 15 hay của 1. Chỉ có vùng cản lớn hơn và vùng cản nhỏ hơn. 5. Muốn nhìn tổng thể, hãy thu nhỏ biểu đồ hoặc lên đúng 1 khung kỳ trên. Đừng nhảy lên khung quá xa. 6. Vào lệnh theo kịch bản cung cầu. Giá phá đỉnh cũ rồi đi ngang, phê mua chiếm ưu thế thì chờ giá phá vùng đỉnh đó. Khi đó vào lệnh mua, cách lỗ đặt dưới vùng vừa phá chất lời nhắm tới vùng cản lớn hơn phía trên. Đừng học thuộc phải xem bao nhiêu khung. Hãy hiểu giá được tạo ra thế nào, rồi chọn cách nhìn thuận tiện nhất cho mình. Rưu duy sai giống con đỉa, bám càng lâu càng hút cạn tiền bạc. Theo dõi sò trading để giao dịch đúng bản chất.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1:19</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694847427051883796</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695799603068734741</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1579,17 +2640,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cách đọc cấu trúc thị trường: biết ngay phe mua hay phe bán thắng Các...</t>
+          <t>7 bài học sau 5 năm đi cùng thị trường | SO TRADING Bảy bài học kinh ...</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cách đọc cấu trúc thị trường: biết ngay phe mua hay phe bán thắng Cách đọc cấu trúc tăng, cấu trúc giảm và vùng đi ngang để biết nên mua, bán hay đứng ngoài. Nguồn: nội dung do tác giả cung cấp. #Shorts</t>
+          <t>7 bài học sau 5 năm đi cùng thị trường | SO TRADING Bảy bài học kinh nghiệm sau 5 năm tham gia thị trường: biết đứng ngoài, có kịch bản, quản lý rủi ro, tránh khoảng trống cuối tuần. #trading #crypto #fx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Phần lớn người giao dịch thua lỗ chỉ vì một lý do. Không biết phê nào đang thắng, họ đổi phương pháp liên tục, vào lệnh theo cảm hứng và càng thua càng mất kiểm soát. Việc đầu tiên cần làm là biết lực mua hay lực bán đang chiếm ưu thế. Cấu chúc tăng là đáy sau cao hơn đáy trước. Đỉnh sau cao hơn đỉnh trước. Cấu chúc giảm thì ngược lại. Đỉnh thấp dần và đáy thấp dần. Hãy coi đó là một cuộc chiến. Mỗi đỉnh cũ là căn cứ của phê bán. Phê mua phá qua thì phê bán phải lùi. Một đáy chỉ quan trọng khi con sóng đi lên từ đáy đó phá qua đỉnh cũ. Phá qua, nghĩa là nến đóng cửa vượt qua. Râu nến quét rồi rút lại thì không tính. Giá nằm giữa đỉnh cao nhất và đáy quan trọng thì bị kẹp, thường đi ngang. Phá xuống đáy quan trọng cũng chưa phải xu hướng giảm. Chỉ khi giá hồi lên rồi phá tiếp đáy vừa tạo. xu hướng giảm mới được xác nhận. Cấu chúc tăng thì yêu tiên mua. Cấu chúc giảm thì yêu tiên bán. Còn rằng co thì đứng ngoài. Theo dõi để học thêm cách đọc thị trường.</t>
+          <t>SU Trading chia sẻ 5 năm trong thị trường mình rút ra 7 bài học này 1. Thị trường đi ngang thì đứng ngoài chỉ hành động khi khung lớn cho lý do rõ ràng 2. Có kịch bản trước khi vào lệnh Giá không phá nổi vùng cản thì thoát dù lời chưa nhiều 3. Điểm vào chưa đẹp thì chờ ở vùng tốt hơn để cắt lỗ gần hơn và rủi do nhỏ hơn 4. Lệnh đang lời thì rời cắt lỗ về hòa vốn và chốt trước 1 phần khi giá chạm vùng nguy hiểm 5. Đừng giữ lệnh ngắn hạn qua cuối tuần vì khoảng chống giá đầu tuần rất nguy hiểm 6. Đừng bắt đầu bằng khung thời gian nhỏ Chọn khung lớn đặt lệnh xong rồi để đó 7. Ýt yếu tố ủng hộ thì khả năng thắng thấp Và thua như vậy là bình thường, muốn biết phương pháp hiệu quả đến đâu Hãy thống kê theo từng cặp tiền và từng khung thời gian Tóm lại, đứng ngoài khi thị trường không rõ và luôn có kịch bản trước khi vào lệnh Đây là kinh nghiệm cá nhân, không phải lời khuyên đầu tư Gé SO Trading để cùng trao đổi thêm nhé!</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1599,13 +2660,13 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694698536717356308</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695696836140616980</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1629,33 +2690,33 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Học nhiều phương pháp vẫn mất tiền? Vì bạn chưa kiểm chứng Vì sao nhi...</t>
+          <t>7 bài học từ 3 lệnh thực tế: 2 thắng, 1 thua vì lỗi bất cẩn Hai lệnh ...</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Học nhiều phương pháp vẫn mất tiền? Vì bạn chưa kiểm chứng Vì sao nhiều người học phương pháp giao dịch vẫn thua lỗ, và cách kiểm chứng phương pháp bằng thống kê trước khi dùng tiền thật. #trading #crypto #btc #xuhuong</t>
+          <t>7 bài học từ 3 lệnh thực tế: 2 thắng, 1 thua vì lỗi bất cẩn Hai lệnh thắng, một lệnh thua vì một lỗi bất cẩn. Bảy bài học về chờ xu hướng rõ, vào lệnh khi đủ yếu tố, đặt lệnh chờ, quản lý khối lượng, kiểm soát cảm xúc và giữ điểm cắt lỗ. Nguồn: kinh nghiệm giao dịch thực tế của SO TRADING. #Shorts #trading #giaodich</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Vì sao học nhiều phương pháp mà tài khoản vẫn cứ giảm, bạn tìm đủ loại phương pháp, cái nào nghe cũng hay như bí quyết, nhưng khi áp dụng thật, tài khoản cứ giảm dần vì có rất ít phương pháp thực sự đúng. Ngắn hạn, phương pháp nào cũng có lúc thắng lúc thua. Vào bừa cũng chỉ có 2 khả năng giá lên hoặc giá xuống. Vì vậy, hãy thống kê hàng trăm hàng nghìn lệnh. Nếu tỷ lệ thắng chỉ 50-50 thì chẳng khác gì may dùi. Hãy bỏ kiến thức chấp vá quay về biểu đồ giá. Mua giá thấp, bán giá cao hơn thì lời. Ngược lại thì lỗ, dù là chuyên gia hay người mới, lời hay lỗ cũng chỉ do giá. Hiểu cách giá di chuyển, bạn sẽ thấy quy luật, rút ra quý tắc, rồi kiểm trứng qua hàng trăm lệnh để biết tỷ lệ thắng và tỷ lệ lợi nhuận trên rủi do. Dùng tiền thật khi chưa kiểm trứng, giống như đi trong dừng mà không biết lối ra. Lộ trình đúng là tự nghiên cứu, thống kê kiểm trứng, rồi mới dùng tiền thật. Theo dõi kênh để học cách kiểm trứng phương pháp của riêng bạn.</t>
+          <t>2 lệnh thắng, 1 lệnh thua vì 1 lỗi bất cảnh. Đây là 7 bài học đắt giá. 1. Su hướng gió là lợi thế lớn nhất. Nó không xuất hiện thường xuyên nên hãy kiên nhận trở. 2. Gom đủ 3 yếu tố rồi mới vào. Su hướng vung cản của phê mình và tín hiệu đến xác nhận. 3. Giá đã chạy xa thì đặt lệnh trở vùng đỉnh cũ. Không khớp cũng không mất tiền, tính khối lượng trước để biết thua mất bao nhiêu. Chốt lời mặc định gấp 2 lần rủi do. 4. Tận dụng núp phê nâu mở cửa, đầu giờ chiều giờ Việt Nam khi tín hiệu xuất hiện nhiều. 5. Vào lệnh xong đừng nhìn biểu đồ quá nhiều, nhìn nhiều dễ chốt sớm rồi tiếc, hãy gạt cảm xúc gắn với tiền. Chỉ vui khi làm đúng kịch bản, chỉ ái náy khi làm sai kịch bản. 6. Lệnh rủi do thì hoặc đứng ngoài, hoặc canh tới nơi tới chốn. Không canh được thì đóng lệnh. 7. Giữ điểm cắt lỗ, đừng rời hay bỏ, và xem lại lệnh cũ để thấy lỗi hay lặp lại. Còn vốn thì còn lấy lại được, và phần lời chính là kinh nghiệm, trở xu hướng rõ, đủ yếu tố mới vào, làm đúng kịch bản. Theo dõi SO Trading để học giao dịch có kỷ luật.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1:09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694588383363861781</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695602506377809173</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1679,33 +2740,33 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Giá hồi cạn kiệt chưa? Cách chờ phe bán thất bại trước khi vào lệnh #...</t>
+          <t>3 lỗi tâm lý giao dịch khiến bạn cháy tài khoản (và cách sửa) Phương ...</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Giá hồi cạn kiệt chưa? Cách chờ phe bán thất bại trước khi vào lệnh #Shorts Khi nào nhịp hồi trong xu hướng đã cạn kiệt để vào lệnh thuận xu hướng? Tóm tắt cách đọc lực mua bán bằng hành động giá: chờ phe bán thất bại 2–3 lần, có nến xác nhận rồi mới vào, đặt dừng lỗ dưới vùng cản và chốt lời ở vùng phe bán.</t>
+          <t>3 lỗi tâm lý giao dịch khiến bạn cháy tài khoản (và cách sửa) Phương pháp chỉ là một phần, tâm lý mới quyết định. 3 lỗi gần như ai cũng gặp: sợ bỏ lỡ (FOMO), trả thù thị trường, chốt lời sớm - gồng lỗ dài, cùng cách sửa đơn giản cho từng lỗi. Nguồn: nội dung BlackRose Admin (08/10/2026), biên soạn lại bởi SO TRADING. Nội dung chỉ mang tính tham khảo, không phải khuyến nghị đầu tư. #Shorts #trading #tamlygiaodich</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Giá vừa hồi về vùng cản bạn có nên mua ngay không? Câu trả lời thường là chưa. Giao dịch theo xu hướng nghĩa là, xu hướng tăng thì canh mua, xu hướng giảm thì canh bán. Nhưng không ai đuổi theo giá đã chạy xa vì càng đi xa, lực mua càng yếu dần. Bạn chỉ vào lệnh khi giá hồi và đồng thời phải hỏi. Nhịp hồi này đã cạn kiệt thật chưa? Hãy nhìn lực hay phè. Tại vùng cản phê mua, hối lượng mua lớn hơn bán nên giá bật lên. Nếu phê bán phá được vùng đó, nó thành vùng của phê bán. Và giá sẽ tiếp tục bị đẩy xuống. Dấu hiệu cạn kiệt là phê bán nhiều lần không phán nổi vùng giá. Hai đáy là lực bán giảm. Ba đáy kèm đến mua mạnh mới là cơ hội đẹp. Còn chưa có tín hiệu thì cứ đứng ngoài chờ. Đừng mua vội nếu điểm dừng lỗ quá xa hoặc điểm vào sát vùng cản của phê bán. Dừng lỗ dưới vùng cản phê mua, chốt lời ở vùng phê bán. Không có gì chắc chắn 100% thì bạn kiểm soát được là tỷ lệ thắng và tỷ lệ lợi nhuận trên rủi do. Kinh nhẫn trở phê, bán thất bại, theo dõi để học thêm cách độc lực mua bán và đừng vào lệnh khi nhịp hồi chưa cạn kiệt.</t>
+          <t>Ba lỗi tâm lý này đang âm thầm đốt tài khoản của bạn. Phương pháp giao dịch không phải tất cả. Phần lớn thành công đến từ tâm lý. Lỗi 1. Sợ bỏ lỡ cơ hội. Thấy giá chạy, thấy người khác lời là vào lệnh bừa. Cách sửa, rời nhóm chát tín hiệu, tự luyện tập và xây chiến lược vào lệnh của riêng bạn. Lỗi 2. Chả thủ tị trường. Thua xong là gấp đôi khối lượng để gỡ lại. Cách sửa. Chỉ nắp ít khoảng 2 phần chăm vốn để có khoảng dừng mà tỉnh lại và đi từ nhỏ đến lớn. 10 đô và 1 nghìn đô cho cảm xúc rất khác nhau. Lỗi 3. Chốt lời sớm, gồng lỗ dài. Thắng thì ăn ít, thua thì lỗ nhiều. Cách sửa. Đặt sẵn chốt lời và cắt lỗ. Ban đầu cho 2 mức bằng nhau. Đặt xong thì đừng nhìn tài khoản. Giữ từ 1 tuần đến 1 tháng để thành thói quen. Ba lỗi như 3 tảng đá trên đường. Quay lại. Hoặc vượt qua từng tảng 1. Bạn đang vướng lỗi nào? Theo dõi sốt trading để học giao dịch bên vững hơn.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1:03</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694492170773908757</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695389393443409173</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1729,33 +2790,33 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tìm vùng mua Bitcoin bằng cuộc chiến mua bán | Nến nhấn chìm + Fibona...</t>
+          <t>Chứng khoán, tiền điện tử hay ngoại hối: chọn thị trường nào? So sánh...</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tìm vùng mua Bitcoin bằng cuộc chiến mua bán | Nến nhấn chìm + Fibonacci Cách đọc cuộc chiến phe mua - phe bán để tìm vùng mua Bitcoin, kết hợp nến nhấn chìm, Fibonacci và chia vốn nhiều giỏ.  #trading #crypto #btc</t>
+          <t>Chứng khoán, tiền điện tử hay ngoại hối: chọn thị trường nào? So sánh 3 thị trường theo 4 đặc điểm: pháp lý, thanh khoản, thời gian giao dịch, nền tảng. Nguồn: nội dung do tác giả cung cấp. #Shorts #trading #xuhuong #crypto #fx</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bitcoin giảm sâu, nhưng có một vùng giá mà phê mua luôn lao vào. Bạn có biết nó nằm ở đâu không? Thì trường tiền điện tử chạy theo Bitcoin. Bitcoin chiếm phần lớn vốn hóa nên nó tăng thì cả thị trường tăng theo. Nguồn đọc giá, hãy nhìn cuộc chiến mua bán. Phê mua đẩy giá lên, rồi phê bán lại kéo giá xuống. Khi giá phá vùng cản của phê mua, phê bán chiếm yếu thế, hãy tìm vùng cản kế tiếp của phê mua nơi giá có thể bật lại. Phê bán thất bại nhiều lần, bóng đến dài kéo giá lên. Đây là dấu hiệu lực bán đang yếu dần, đừng vội vào lệnh. Hãy chờ tín hiệu rõ ràng, như cặp nên nhấn chìm tăng giá tại vùng cản mạnh. Vùng đó càng đáng tin khi chùng với mức Fibonacci của sống tăng trước đó. Các đồng lớn đều tạo tín hiệu tương tự. Sau khi đã giảm sâu từ 60 đến 70-3% mua ở vùng này, nếu giá giảm thêm thì bạn vẫn mua rẻ hơn người mua ở đỉnh. Giá quay lại đỉnh, bạn đã lại gấp đôi, đừng bỏ hết, vốn vào một giò. Chiếc vào nhiều đồng lớn, chỉ cần một đồng bay cao là đủ bù các đồng còn lại. Theo dõi để xem thêm phân tích mỗi ngày, đây không phải lời khuyên tài chính.</t>
+          <t>Trứng khoán, tiền điện tử hay ngoại hối, chọn sai thị trường là mất tiền. Bối thị trường có đặc điểm riêng, hãy xét bốn thứ, pháp lý, thanh khoản, thời gian giao dịch và nền tảng. Pháp lý, trứng khoán được nhà nước bảo hộ chặt trẽ. Tiền điện tử và ngoại hối thì chưa được công nhận. Vì vậy, giữ số tiền lớn lâu dài thì trứng khoán an toàn hơn, đừng ném cả tài sản vào sản không tên tuổi. Thanh khoản, ngoại hối lớn nhất, rồi trứng khoán, rồi tiền điện tử. Nhưng trứng khoán Việt Nam thấp nhất nên chỉ hợp đầu tư dài hạn. Cổ phiếu và tiền điện tử dễ bị thao túng, biến động vài chục phần trăm. Cặp tiền lệch 1 phần trăm 1 ngày đã là nhiều. Thời gian, trứng khoán chỉ mở khoảng 4 tiếng 1 ngày, ngoại hối 24h, 5 ngày, tiền điện tử 24h, 7 ngày, nền tảng. Sanh ngoại hối giao dịch được tiền tệ, tiền điện tử, chỉ số và vàng. Nhưng đó là hợp đồng tranh lệch bạn không sở hữu tài sản. Tóm lại, trứng khoán hợp dài hạn, ngoại hối chỉ hợp ngắn hạn. Tiền điện tử hợp cả 2 nhưng rủi do cao, và dù chọn thị trường nào cũng phải chọn sản uy tín. Sanh kém thì ở đâu cũng dễ mất tiền, theo dõi để học cách bảo vệ và làm sinh lời đồng vốn của bạn mỗi ngày.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1:05</t>
+          <t>1:13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694281608039271701</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695191312605187348</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1779,33 +2840,33 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thị trường đi ngang: nhận biết &amp; tránh bị quét lệnh. #trading #fx #xu...</t>
+          <t>Đầu tư và giao dịch khác nhau ở đâu? Đầu tư và giao dịch giống nhau ở...</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thị trường đi ngang: nhận biết &amp; tránh bị quét lệnh. #trading #fx #xuhuong</t>
+          <t>Đầu tư và giao dịch khác nhau ở đâu? Đầu tư và giao dịch giống nhau ở bản chất mua rẻ bán đắt, khác nhau ở thời gian giữ lệnh và tâm lý. Video giải thích ngắn gọn, dễ hiểu. #trading #fx #crypto</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Lệnh của bạn hay bị quét. Thủ phạm chính là thị trường đi ngang. Thực tế không có lý thuyết nào xác định chính xác khi nào thị trường đi ngang. Nhưng có một cách dễ hiểu. Nhìn cuộc chiến giữa phê mua và phê bán. Phê mua phá đỉnh, phê bán phá đáy thì su hướng rõ ràng. Nhưng khi cả hai cùng thất bại, không ai chiêm yêu thế, thị trường bắt đầu đi ngang. Dấu hiệu nhận biết, ít nhất hai đỉnh và hai đáy ra cứ bật lại trong một hình chữ nhật. Thực tế, đỉnh đáy có thể lệch một chút. Giá phản ứng càng nhiều ở hai vùng cản thì vùng đi ngang cảng rõ. Chỉ khi một con sóng mạnh phá ra ngoài, một phê mới thật sự chiến thắng. Hãy chú ý biên độ. Nếu vùng đi ngang quá nhỏ so với sóng trước đó, su hướng cũ gần như không bị ảnh hưởng. Hãy nhìn khung thời gian lớn hơn. Đoạn trông như su hướng ở khung nhỏ có thể chỉ là một phần của vùng đi ngang ở khung H4 hay ngày. Ví dụ, giá hồi về vùng cản của phê bán, đỉnh thấp dần, rồi nến xanh phá vùng cản xác nhận lực bán đá cạn. Đó là điểm vào lệnh mua. Đặt cắt lỗ sau vùng cản, chốt lời ở các vùng cản kế tiếp và đừng chỉ chốt ở tỷ lệ một ăn một. Cần có lý do để kỳ vọng tỷ lệ cao hơn. Muốn xác xuất thắng cao. Hãy đứng ngoài khi thị trường đi ngang theo dõi để học thêm nhé!</t>
+          <t>Đầu tư và giao dịch khác nhau ở đâu? Hầu hết mọi người đều hiểu sai, ở cả 3 thị trường, bản chất đều giống nhau, mua giá thấp, bán giá cao, chứng khoán, mua bán cổ phiếu, tức quyền sở hữu một phần công ty, tiền điện tử là Bitcoin và các đồng khác. Ngoại hối là Đô Là Mỹ, Yên Nhật khác nhau chính là thời gian giữ lệnh, giữ nhiều tháng, nhiều năm là đầu tư. Giữ theo food, giờ, ngay là giao dịch, đầu tư không tốn nhiều thời gian như giao dịch, nhưng vẫn mang lại nguồn thu nhập tốt, nhưng có người đầu tư mà nhìn giá cả ngày, lỗ thì mất ngủ. Đó là tâm lý giao dịch, ngược lại, có người giao dịch ít lệnh và đúng lúc vẫn có thời gian cho việc khác, che tên sản phẩm đi, chỉ còn nến và giá. Chọn thị trường theo đặc điểm, không phải vì biết nó trước, đầu tư hay giao dịch chỉ đa, kết quả nằm ở cách bạn dùng nó, theo dõi để học thêm nha.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1:11</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694189318134369556</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694935798524742932</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1829,33 +2890,33 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lý thuyết Dow: vì sao vào lệnh theo sách vẫn thua? Lý thuyết Dow là n...</t>
+          <t>4 bước vào lệnh chuẩn: cấu trúc, khung lớn, vùng cản, tín hiệu yếu dầ...</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lý thuyết Dow: vì sao vào lệnh theo sách vẫn thua? Lý thuyết Dow là nền móng của phân tích kỹ thuật, nhưng áp dụng quá cứng nhắc rất dễ thua. Video tóm tắt nhược điểm của định nghĩa xu hướng và cách hỏi "phe mua hay phe bán đang chiếm ưu thế" trước mỗi lệnh. #trading #fx #xuhuong</t>
+          <t>4 bước vào lệnh chuẩn: cấu trúc, khung lớn, vùng cản, tín hiệu yếu dần Phương pháp vào lệnh gồm bốn bước kèm ví dụ ETHUSD khung M15. Nội dung do tác giả chia sẻ, không phải lời khuyên đầu tư.  #trading #fx #cypto</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Học lý thuyết đào mà vào lệnh vẫn thua. Vấn đề nằm ở chỗ áp dụng quá cứng nhắc. Lý thuyết đào là nền móng của phân tích kỹ thuật. Nhưng chỉ thuộc định nghĩa thì chưa đủ để giao dịch. Theo sách, gia pha đáy quan trọng nghĩa là su hướng tăng đã đảo chiều thành giảm. Nhưng đáy nào mới là đáy quan trọng. Khung hết bốn và khung hết, một cho da hai đáy khác nhau. Nhiều khi bạn vội canh bán, giá lại chạm vùng cản của phê mua và bật tăng trở lại. Bởi phá đáy ở khung nhỏ chỉ cho thấy phê bán thắng một hiệp. Bức tranh lớn, phê mua vẫn mạnh hơn. Vậy hãy tự hỏi, lúc này phê mua hay phê bán đang chiếm yêu thế? Vẽ các vùng cản gần nhất của hai phê, rồi so sánh xóng giảm với xóng tăng trước đó. Phê mua còn mạnh thì canh mua ở vùng cản của phê mua đặt cắt lỗ bên dưới, chốt lời ở các vùng cản phía trên. Đừng áp dụng máy móc, theo dõi kênh để học cách vào lệnh theo su hướng hiệu quả.</t>
+          <t>Vào lệnh, đúng không phải đoán mò. Mà đi theo bốn bước. Bước 1, xác định cấu trúc trên khung đang giao dịch. Bước 2, tìm thêm yêu tố ủng hộ ở khung lớn hơn một bậc. Bước 3, chờ giá hồi về vùng cản quan trọng. Bước 4, chờ phê ngược lại yếu dần rồi mới vào lệnh. Ví dụ mua ATHSD 015, giá phá đỉnh 2 lần, đáy quan trọng vẫn được giữ. Chờ giá hồi về đỉnh cũ rồi mới mua, cắt lỗ dưới vùng đó. Lệnh lời gấp 3 rủi do, không xem thêm chỉ cần lớn hơn một bậc. 15 xem, 1, 1 xem, hư bốn, hư bốn xem khung ngày, cách này dùng được cho mọi thị trường. Khung lớn ủng hộ rõ, chỉ cần tín hiệu vừa phải ở khung nhỏ. Duyên đời mới chỉ là một chân của cái kiểu 3 chân. Theo rõi để xem 2 chân còn lại. Quán lý vốn và kỷ luật.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694116254126263573</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694847427051883796</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1879,33 +2940,33 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vai Đầu Vai: 3 dấu hiệu mô hình đẹp và 2 điểm vào lệnh #Shorts Cách c...</t>
+          <t>Cách đọc cấu trúc thị trường: biết ngay phe mua hay phe bán thắng Các...</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Vai Đầu Vai: 3 dấu hiệu mô hình đẹp và 2 điểm vào lệnh #Shorts Cách chọn mô hình Vai Đầu Vai đẹp và hai điểm vào lệnh. Tóm ý từ video 'Phương Pháp Vào Lệnh Với Mô Hình VAI ĐẦU VAI Hoàn Hảo'</t>
+          <t>Cách đọc cấu trúc thị trường: biết ngay phe mua hay phe bán thắng Cách đọc cấu trúc tăng, cấu trúc giảm và vùng đi ngang để biết nên mua, bán hay đứng ngoài. Nguồn: nội dung do tác giả cung cấp. #Shorts</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Vài đầu vai nhìn đâu cũng thấy nhưng đa số vào lệnh sai ngay từ đầu. Vài đầu vai có 3 đỉnh, đỉnh giữa cao nhất, báo hiệu giá đảo chiều từ tăng sang giảm. Nhưng giá chỉ thật sự đảo chiều khi phá qua đường neckline, chưa phá thì phê bán chưa thắng. Dấu hiệu 1, các đỉnh trạm neckline phải nằm ngang nhau, không lệch quá nhiều. Dấu hiệu 2, vai phải càng gần neckline, phê bán càng yếu và điểm cắt lỗ càng gần. Dấu hiệu 3, mỗi bên có thể có nhiều vai, tranh chấp càng lâu thì cú phá càng đáng tin. Điểm vào thứ nhất, giá đóng cửa vượt neckline thì vào lệnh, cắt lỗ ở mức gần nhất. Điểm vào thứ 2, nếu nên phá quá dài, hãy chờ giá hồi về neckline dù mới vào, cẩn thận. Mô hình nhỏ nằm trong su hương lớn, ngược chiều rất dễ thất bại, hãy nhìn thêm vùng cản gần đó. Nếu giá chỉ chạy được 1 error thì bỏ qua, lưu lại 3 dấu hiệu này và theo dõi để học thêm. Nội dung chỉ mang tính giáo dục.</t>
+          <t>Phần lớn người giao dịch thua lỗ chỉ vì một lý do. Không biết phê nào đang thắng, họ đổi phương pháp liên tục, vào lệnh theo cảm hứng và càng thua càng mất kiểm soát. Việc đầu tiên cần làm là biết lực mua hay lực bán đang chiếm ưu thế. Cấu chúc tăng là đáy sau cao hơn đáy trước. Đỉnh sau cao hơn đỉnh trước. Cấu chúc giảm thì ngược lại. Đỉnh thấp dần và đáy thấp dần. Hãy coi đó là một cuộc chiến. Mỗi đỉnh cũ là căn cứ của phê bán. Phê mua phá qua thì phê bán phải lùi. Một đáy chỉ quan trọng khi con sóng đi lên từ đáy đó phá qua đỉnh cũ. Phá qua, nghĩa là nến đóng cửa vượt qua. Râu nến quét rồi rút lại thì không tính. Giá nằm giữa đỉnh cao nhất và đáy quan trọng thì bị kẹp, thường đi ngang. Phá xuống đáy quan trọng cũng chưa phải xu hướng giảm. Chỉ khi giá hồi lên rồi phá tiếp đáy vừa tạo. xu hướng giảm mới được xác nhận. Cấu chúc tăng thì yêu tiên mua. Cấu chúc giảm thì yêu tiên bán. Còn rằng co thì đứng ngoài. Theo dõi để học thêm cách đọc thị trường.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693923604710378772</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694698536717356308</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1929,33 +2990,33 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3 Bước Để Có Điểm Vào Lệnh Hoàn Hảo | Đọc Biểu Đồ Từ Khung Lớn Cách t...</t>
+          <t>Học nhiều phương pháp vẫn mất tiền? Vì bạn chưa kiểm chứng Vì sao nhi...</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3 Bước Để Có Điểm Vào Lệnh Hoàn Hảo | Đọc Biểu Đồ Từ Khung Lớn Cách tìm điểm vào lệnh có nhiều yếu tố ủng hộ: từ khung ngày, H4 đến H1. Nội dung chỉ để học, không phải lời khuyên đầu tư. #trading #fx #crypto</t>
+          <t>Học nhiều phương pháp vẫn mất tiền? Vì bạn chưa kiểm chứng Vì sao nhiều người học phương pháp giao dịch vẫn thua lỗ, và cách kiểm chứng phương pháp bằng thống kê trước khi dùng tiền thật. #trading #crypto #btc #xuhuong</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bạn vào lệnh đúng lúc mà vẫn thua. Vấn đề nằm ở chỗ này, điểm vào đẹp không đến từ một cây nén mà từ nhiều yếu tố cùng ủng hộ. Bước 1, nhìn khu ngài chỉ vẽ vùng cung cầu gần nhất. Một cây nén tăng quá mạnh thường không bền, đó là vùng bán tiềm năng. Bước 2, sang khung 4 giờ, chờ giá phá vùng cản bằng đến thân dài. Nên thân ngắn hay giúp chân thì cẩn thận rất dễ là phá giả. Bước 3, đừng đuổi giá, hãy chờ giá hồi về vùng rồi mới tìm tín hiệu. Mẫu nén đẹp chưa đủ, phải thấy bên kia lao vào rồi thất bại. Đừng dùng quá nhiều khung thời gian vì sẽ làm dối phân tích của bạn. Dừng lỗ đặt trên vùng cản, chốt lời mặc định khoảng 2 error. Đừng đặt chốt lời quá xa, chỉ cần thắng trên 50% là đã có lời. Lưu video lại và theo dõi để xem thêm cách đọc biểu đồ nhé.</t>
+          <t>Vì sao học nhiều phương pháp mà tài khoản vẫn cứ giảm, bạn tìm đủ loại phương pháp, cái nào nghe cũng hay như bí quyết, nhưng khi áp dụng thật, tài khoản cứ giảm dần vì có rất ít phương pháp thực sự đúng. Ngắn hạn, phương pháp nào cũng có lúc thắng lúc thua. Vào bừa cũng chỉ có 2 khả năng giá lên hoặc giá xuống. Vì vậy, hãy thống kê hàng trăm hàng nghìn lệnh. Nếu tỷ lệ thắng chỉ 50-50 thì chẳng khác gì may dùi. Hãy bỏ kiến thức chấp vá quay về biểu đồ giá. Mua giá thấp, bán giá cao hơn thì lời. Ngược lại thì lỗ, dù là chuyên gia hay người mới, lời hay lỗ cũng chỉ do giá. Hiểu cách giá di chuyển, bạn sẽ thấy quy luật, rút ra quý tắc, rồi kiểm trứng qua hàng trăm lệnh để biết tỷ lệ thắng và tỷ lệ lợi nhuận trên rủi do. Dùng tiền thật khi chưa kiểm trứng, giống như đi trong dừng mà không biết lối ra. Lộ trình đúng là tự nghiên cứu, thống kê kiểm trứng, rồi mới dùng tiền thật. Theo dõi kênh để học cách kiểm trứng phương pháp của riêng bạn.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693801024087264533</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694588383363861781</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1979,33 +3040,33 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3 bước tìm điểm vào lệnh đẹp trong trading Cách chọn điểm vào lệnh đơ...</t>
+          <t>Giá hồi cạn kiệt chưa? Cách chờ phe bán thất bại trước khi vào lệnh #...</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3 bước tìm điểm vào lệnh đẹp trong trading Cách chọn điểm vào lệnh đơn giản: nhìn cấu trúc thị trường, tìm vùng mua tiềm năng, chờ tín hiệu 3 giai đoạn. #trading #fx #crypto</t>
+          <t>Giá hồi cạn kiệt chưa? Cách chờ phe bán thất bại trước khi vào lệnh #Shorts Khi nào nhịp hồi trong xu hướng đã cạn kiệt để vào lệnh thuận xu hướng? Tóm tắt cách đọc lực mua bán bằng hành động giá: chờ phe bán thất bại 2–3 lần, có nến xác nhận rồi mới vào, đặt dừng lỗ dưới vùng cản và chốt lời ở vùng phe bán.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Một điểm và lệnh đơn giản mà rất nhiều người bỏ qua. Bước 1, nhìn cấu chúc thị trường. Tăng, giảm, đi ngang có quy luật hoặc đi ngang không quy luật, đi ngang không quy luật thì đứng ngoài. Vì rất dễ bị quét lệnh. Bước 2, tìm vùng mua tiềm năng. Đó là đầu con sóng tăng và đỉnh cũ vừa bị phá. Nhưng nếu giá phá quá yếu hoặc phá xa rồi bị kéo về mạnh thì vùng đó không còn tốt. Khi Phi Bonacci không phải 5 hoặc không phải 6, 1, 8 trùng đỉnh cũ, đó là vùng đẹp. Bước 3, trở tín hiệu. Giá chạm vùng có thể đảo chiều, quét giả hoặc đi tiếp. Giai đoạn 1, lực bán yếu dần, nén giút chân, giai đoạn 2, tranh chấp, những cây, nén nhỏ, đi ngang. Giai đoạn 3, một nén tăng mạnh bứt phá, xác nhận xu hướng. Thếu một giai đoạn thì đứng ngoài, kiên nhẫn, quản lý vốn, kiểm tra lại nhiều lần. Ý hiệu ích thì nhấn thích và đăng ký nhé. Nội dung chỉ để học, không phải lời quên đầu tư.</t>
+          <t>Giá vừa hồi về vùng cản bạn có nên mua ngay không? Câu trả lời thường là chưa. Giao dịch theo xu hướng nghĩa là, xu hướng tăng thì canh mua, xu hướng giảm thì canh bán. Nhưng không ai đuổi theo giá đã chạy xa vì càng đi xa, lực mua càng yếu dần. Bạn chỉ vào lệnh khi giá hồi và đồng thời phải hỏi. Nhịp hồi này đã cạn kiệt thật chưa? Hãy nhìn lực hay phè. Tại vùng cản phê mua, hối lượng mua lớn hơn bán nên giá bật lên. Nếu phê bán phá được vùng đó, nó thành vùng của phê bán. Và giá sẽ tiếp tục bị đẩy xuống. Dấu hiệu cạn kiệt là phê bán nhiều lần không phán nổi vùng giá. Hai đáy là lực bán giảm. Ba đáy kèm đến mua mạnh mới là cơ hội đẹp. Còn chưa có tín hiệu thì cứ đứng ngoài chờ. Đừng mua vội nếu điểm dừng lỗ quá xa hoặc điểm vào sát vùng cản của phê bán. Dừng lỗ dưới vùng cản phê mua, chốt lời ở vùng phê bán. Không có gì chắc chắn 100% thì bạn kiểm soát được là tỷ lệ thắng và tỷ lệ lợi nhuận trên rủi do. Kinh nhẫn trở phê, bán thất bại, theo dõi để học thêm cách độc lực mua bán và đừng vào lệnh khi nhịp hồi chưa cạn kiệt.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1:03</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693735707138854164</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694492170773908757</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2029,33 +3090,33 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vùng cung cầu trong trading. #trading #fx #Shorts</t>
+          <t>Tìm vùng mua Bitcoin bằng cuộc chiến mua bán | Nến nhấn chìm + Fibona...</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Vùng cung cầu trong trading. #trading #fx #Shorts</t>
+          <t>Tìm vùng mua Bitcoin bằng cuộc chiến mua bán | Nến nhấn chìm + Fibonacci Cách đọc cuộc chiến phe mua - phe bán để tìm vùng mua Bitcoin, kết hợp nến nhấn chìm, Fibonacci và chia vốn nhiều giỏ.  #trading #crypto #btc</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bẽ vùng cầu càng nhiều đường, bạn càng thua nhiều hơn, vì sao vùng cầu là nơi phe mua thắng thế, còn vùng cung là nơi phe bán thắng thế. Psylum phổ biến là vẽ mọi đường ngang đi qua thật nhiều đỉnh và đáy. Cách này không có quy tắc, đường nào cũng đúng, nên bạn không thể giao dịch được. Cách đúng thứ nhất, chỉ vẽ những vùng gần giá hiện tại nhất. Thứ 2, vẽ từ điểm cao nhất hoặc thấp nhất của đỉnh và đáy. Thứ 3, giá rời vùng càng nhanh và mạnh, vùng đó càng mạnh, nhưng vùng mạnh cũng đừng vào bừa. Hay chờ tín hiệu nên rõ ràng rồi, mới vào lệnh. Ví dụ thực tế, khung lớn phá đỉnh đi lên, giá hồi về vùng cầu, rồi tạo tín hiệu mua, sau đó giá tăng mạnh và chạm mục tiêu chốt lời. Kênh nhẫn chờ tín hiệu giúp bạn tránh một lệnh thua, theo dõi để xem thêm cách đọc biểu đồ, nội dung chỉ để học hỏi, không phải lời khuyên đầu tư.</t>
+          <t>Bitcoin giảm sâu, nhưng có một vùng giá mà phê mua luôn lao vào. Bạn có biết nó nằm ở đâu không? Thì trường tiền điện tử chạy theo Bitcoin. Bitcoin chiếm phần lớn vốn hóa nên nó tăng thì cả thị trường tăng theo. Nguồn đọc giá, hãy nhìn cuộc chiến mua bán. Phê mua đẩy giá lên, rồi phê bán lại kéo giá xuống. Khi giá phá vùng cản của phê mua, phê bán chiếm yếu thế, hãy tìm vùng cản kế tiếp của phê mua nơi giá có thể bật lại. Phê bán thất bại nhiều lần, bóng đến dài kéo giá lên. Đây là dấu hiệu lực bán đang yếu dần, đừng vội vào lệnh. Hãy chờ tín hiệu rõ ràng, như cặp nên nhấn chìm tăng giá tại vùng cản mạnh. Vùng đó càng đáng tin khi chùng với mức Fibonacci của sống tăng trước đó. Các đồng lớn đều tạo tín hiệu tương tự. Sau khi đã giảm sâu từ 60 đến 70-3% mua ở vùng này, nếu giá giảm thêm thì bạn vẫn mua rẻ hơn người mua ở đỉnh. Giá quay lại đỉnh, bạn đã lại gấp đôi, đừng bỏ hết, vốn vào một giò. Chiếc vào nhiều đồng lớn, chỉ cần một đồng bay cao là đủ bù các đồng còn lại. Theo dõi để xem thêm phân tích mỗi ngày, đây không phải lời khuyên tài chính.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1:05</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693564151402302740</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694281608039271701</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2079,33 +3140,33 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2 mẫu nến đảo chiều đáng học: chòm râu &amp; nhấn chìm lần hai Đọc nến từ...</t>
+          <t>Thị trường đi ngang: nhận biết &amp; tránh bị quét lệnh. #trading #fx #xu...</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2 mẫu nến đảo chiều đáng học: chòm râu &amp; nhấn chìm lần hai Đọc nến từ bản chất mua – bán và 2 mẫu nến đảo chiều tại vùng cản. Nội dung chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #trading #fx</t>
+          <t>Thị trường đi ngang: nhận biết &amp; tránh bị quét lệnh. #trading #fx #xuhuong</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nên nhấn chìm xuất hiện là đảo chiều. Chưa chắc đâu, mỗi cây nén là một cuộc chiến giữa phê mua và phê bán. Nén có 5 yếu tố, giám mở, giá đóng, cao nhất, thấp nhất và thời gian. Sau một sóng tăng, nên nhấn chìm giảm chỉ là nhịp hồi. Lực mua vẫn còn bẫu thứ nhất. Nên chỏm râu, từ 3 cây có râu dài trở lên. Râu càng dài, thị trường càng từ chối giám mạnh tại vùng đó. Bẫu thứ 2, nên nhấn chìm mở đỉnh, hoặc đáy lần thứ 2, đừng vào ở lần chạm đầu, hãy đợi nến đóng cửa rồi mới hành động. Đặt cắt lỗ dưới râu nén hoặc dưới vùng cản để kiểm soát rủi do. Điểm vào tốt phải có quý tắc rõ ràng đến nơi chỉ việc kiểm tra. Hãy tự hỏi, phê nào đang mạnh hơn? Theo dõi để học thêm và nhớ đây chỉ là kiến thức giáo dục.</t>
+          <t>Lệnh của bạn hay bị quét. Thủ phạm chính là thị trường đi ngang. Thực tế không có lý thuyết nào xác định chính xác khi nào thị trường đi ngang. Nhưng có một cách dễ hiểu. Nhìn cuộc chiến giữa phê mua và phê bán. Phê mua phá đỉnh, phê bán phá đáy thì su hướng rõ ràng. Nhưng khi cả hai cùng thất bại, không ai chiêm yêu thế, thị trường bắt đầu đi ngang. Dấu hiệu nhận biết, ít nhất hai đỉnh và hai đáy ra cứ bật lại trong một hình chữ nhật. Thực tế, đỉnh đáy có thể lệch một chút. Giá phản ứng càng nhiều ở hai vùng cản thì vùng đi ngang cảng rõ. Chỉ khi một con sóng mạnh phá ra ngoài, một phê mới thật sự chiến thắng. Hãy chú ý biên độ. Nếu vùng đi ngang quá nhỏ so với sóng trước đó, su hướng cũ gần như không bị ảnh hưởng. Hãy nhìn khung thời gian lớn hơn. Đoạn trông như su hướng ở khung nhỏ có thể chỉ là một phần của vùng đi ngang ở khung H4 hay ngày. Ví dụ, giá hồi về vùng cản của phê bán, đỉnh thấp dần, rồi nến xanh phá vùng cản xác nhận lực bán đá cạn. Đó là điểm vào lệnh mua. Đặt cắt lỗ sau vùng cản, chốt lời ở các vùng cản kế tiếp và đừng chỉ chốt ở tỷ lệ một ăn một. Cần có lý do để kỳ vọng tỷ lệ cao hơn. Muốn xác xuất thắng cao. Hãy đứng ngoài khi thị trường đi ngang theo dõi để học thêm nhé!</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>1:11</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693471867973176596</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694189318134369556</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2129,33 +3190,33 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>#fx #crypto #trading #sotrading #fomc</t>
+          <t>Lý thuyết Dow: vì sao vào lệnh theo sách vẫn thua? Lý thuyết Dow là n...</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>#fx #crypto #trading #sotrading #fomc</t>
+          <t>Lý thuyết Dow: vì sao vào lệnh theo sách vẫn thua? Lý thuyết Dow là nền móng của phân tích kỹ thuật, nhưng áp dụng quá cứng nhắc rất dễ thua. Video tóm tắt nhược điểm của định nghĩa xu hướng và cách hỏi "phe mua hay phe bán đang chiếm ưu thế" trước mỗi lệnh. #trading #fx #xuhuong</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Đã bao giờ bạn ngồi thẫn thờ trước màn hình lúc 3 giờ sáng, nhìn chân chân vào con số không tròn chính chưa? Ánh sáng đỏ từ nến sắp hắt lên khuôn mặt phở phạc, và hai bàn tay thì lạnh toát. Cảm giác đó, sự tuyệt vọng đến tột cùng. Bạn gục đầu xuống, tự tác vào mặt mình vì sự ngu ngốc. Tại sao không giết khoát cắt lỗ? Tại sao lại gun dày kéo dày? Tại sao lại mù quán ô lín bấu viếu vào một phép màu? Nhưng điều đâm nắt trái tim bạn không phải là những con số vô chi. Số tiền đó lẽ ra là tiền bìm sữa cho con. Bạn phải gượng cười, nuốt ngược cái hố sâu hấm vào dạ dày. Bạn thấy mình giống một kẻ lừa đảo thảm hại. Bạn gào thét đổ lỗi cho nhà cái quét râu. Nhưng sâu thằm, bạn biết rõ sự thật. Chẳng ai xan tìm bạn cả. Chính sự do dự bóp nghẹt stop loss đã tạo ra phịt tài khoản. Chính lòng tham của bạn đã tự tay châm ngòi nổ. Thị trường không có sự chắc ẩn. Lối thoát duy nhất là giết chết cảm xúc. Đánh như một cổ máy máu lạnh. Tự bóp chết cảm xúc. Hay để thị trường bóp chết bạn.</t>
+          <t>Học lý thuyết đào mà vào lệnh vẫn thua. Vấn đề nằm ở chỗ áp dụng quá cứng nhắc. Lý thuyết đào là nền móng của phân tích kỹ thuật. Nhưng chỉ thuộc định nghĩa thì chưa đủ để giao dịch. Theo sách, gia pha đáy quan trọng nghĩa là su hướng tăng đã đảo chiều thành giảm. Nhưng đáy nào mới là đáy quan trọng. Khung hết bốn và khung hết, một cho da hai đáy khác nhau. Nhiều khi bạn vội canh bán, giá lại chạm vùng cản của phê mua và bật tăng trở lại. Bởi phá đáy ở khung nhỏ chỉ cho thấy phê bán thắng một hiệp. Bức tranh lớn, phê mua vẫn mạnh hơn. Vậy hãy tự hỏi, lúc này phê mua hay phê bán đang chiếm yêu thế? Vẽ các vùng cản gần nhất của hai phê, rồi so sánh xóng giảm với xóng tăng trước đó. Phê mua còn mạnh thì canh mua ở vùng cản của phê mua đặt cắt lỗ bên dưới, chốt lời ở các vùng cản phía trên. Đừng áp dụng máy móc, theo dõi kênh để học cách vào lệnh theo su hướng hiệu quả.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7687234989431278868</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694116254126263573</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2179,33 +3240,33 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>#trading #cpi #sotrading #crypto #fx</t>
+          <t>Vai Đầu Vai: 3 dấu hiệu mô hình đẹp và 2 điểm vào lệnh #Shorts Cách c...</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>#trading #cpi #sotrading #crypto #fx</t>
+          <t>Vai Đầu Vai: 3 dấu hiệu mô hình đẹp và 2 điểm vào lệnh #Shorts Cách chọn mô hình Vai Đầu Vai đẹp và hai điểm vào lệnh. Tóm ý từ video 'Phương Pháp Vào Lệnh Với Mô Hình VAI ĐẦU VAI Hoàn Hảo'</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn</t>
+          <t>Vài đầu vai nhìn đâu cũng thấy nhưng đa số vào lệnh sai ngay từ đầu. Vài đầu vai có 3 đỉnh, đỉnh giữa cao nhất, báo hiệu giá đảo chiều từ tăng sang giảm. Nhưng giá chỉ thật sự đảo chiều khi phá qua đường neckline, chưa phá thì phê bán chưa thắng. Dấu hiệu 1, các đỉnh trạm neckline phải nằm ngang nhau, không lệch quá nhiều. Dấu hiệu 2, vai phải càng gần neckline, phê bán càng yếu và điểm cắt lỗ càng gần. Dấu hiệu 3, mỗi bên có thể có nhiều vai, tranh chấp càng lâu thì cú phá càng đáng tin. Điểm vào thứ nhất, giá đóng cửa vượt neckline thì vào lệnh, cắt lỗ ở mức gần nhất. Điểm vào thứ 2, nếu nên phá quá dài, hãy chờ giá hồi về neckline dù mới vào, cẩn thận. Mô hình nhỏ nằm trong su hương lớn, ngược chiều rất dễ thất bại, hãy nhìn thêm vùng cản gần đó. Nếu giá chỉ chạy được 1 error thì bỏ qua, lưu lại 3 dấu hiệu này và theo dõi để học thêm. Nội dung chỉ mang tính giáo dục.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1:10</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7686468492828331285</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693923604710378772</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2229,33 +3290,33 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>#trading #cpi #fx #sotrading #crypto</t>
+          <t>3 Bước Để Có Điểm Vào Lệnh Hoàn Hảo | Đọc Biểu Đồ Từ Khung Lớn Cách t...</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>#trading #cpi #fx #sotrading #crypto</t>
+          <t>3 Bước Để Có Điểm Vào Lệnh Hoàn Hảo | Đọc Biểu Đồ Từ Khung Lớn Cách tìm điểm vào lệnh có nhiều yếu tố ủng hộ: từ khung ngày, H4 đến H1. Nội dung chỉ để học, không phải lời khuyên đầu tư. #trading #fx #crypto</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Cùng nhận một tín hiệu. Tại sao mỗi người lại có một kết quả khác nhau? Ba người cùng nhận được một tín hiệu với đầy đủ điểm vào, điểm dừng và mục tiêu. Người đầu tiên thực hiện đúng vùng giá, chọn khối lượng phù hợp và chỉ chấp nhận mức dùi do đã tính trước. Người thứ 2 xem tín hiệu muộn. Giá đã chạy khỏi vùng vào nhưng vì sợ bỏ lỡ nên vẫn quyết định tham gia. Người thứ 3 thấy cơ hội hấp dẫn nên tự ý tăng khối lượng lên nhiều lần. Khi thị trường biến động ngược hướng, người đầu chịu đúng dùi do trong kế hoạch, người thứ 2 tổn thất lớn, còn người thứ 3 chạm giấy hạn, thổi bay tài khoản. Như vậy, vấn đề không chỉ nằm ở tín hiệu. Cùng một tín hiệu, nhưng điểm vào, khối lượng và cách kiểm soát dùi do khác nhau sẽ tạo ra kết quả hoàn toàn khác nhau. Đó là lý do mình phát triển hệ thống tiếp nhận và thực thi tín hiệu tự động. Hệ thống hỗ trợ thiết lập điểm vào, điểm dừng, mục tiêu và khối lượng chuẩn sát dựa trên mức dùi do bạn đã cài. Hệ thống không hứa hẹn mọi lệnh đều thắng. Mục tiêu là hạn chế sai sót và ép bạn tuân thủ, tín hiệu, tín hiệu tạo cơ hội, nhưng thực hiện quyết định kết quả, bạn hay gặp vấn đề điểm vào, khối lượng hay cảm xúc, bình luận để xem hệ thống hoạt động nhá.</t>
+          <t>Bạn vào lệnh đúng lúc mà vẫn thua. Vấn đề nằm ở chỗ này, điểm vào đẹp không đến từ một cây nén mà từ nhiều yếu tố cùng ủng hộ. Bước 1, nhìn khu ngài chỉ vẽ vùng cung cầu gần nhất. Một cây nén tăng quá mạnh thường không bền, đó là vùng bán tiềm năng. Bước 2, sang khung 4 giờ, chờ giá phá vùng cản bằng đến thân dài. Nên thân ngắn hay giúp chân thì cẩn thận rất dễ là phá giả. Bước 3, đừng đuổi giá, hãy chờ giá hồi về vùng rồi mới tìm tín hiệu. Mẫu nén đẹp chưa đủ, phải thấy bên kia lao vào rồi thất bại. Đừng dùng quá nhiều khung thời gian vì sẽ làm dối phân tích của bạn. Dừng lỗ đặt trên vùng cản, chốt lời mặc định khoảng 2 error. Đừng đặt chốt lời quá xa, chỉ cần thắng trên 50% là đã có lời. Lưu video lại và theo dõi để xem thêm cách đọc biểu đồ nhé.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1:10</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7686097369682922772</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693801024087264533</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2279,33 +3340,33 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>#trading #cpi #fx #sotrading #crypto</t>
+          <t>3 bước tìm điểm vào lệnh đẹp trong trading Cách chọn điểm vào lệnh đơ...</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>#trading #cpi #fx #sotrading #crypto</t>
+          <t>3 bước tìm điểm vào lệnh đẹp trong trading Cách chọn điểm vào lệnh đơn giản: nhìn cấu trúc thị trường, tìm vùng mua tiềm năng, chờ tín hiệu 3 giai đoạn. #trading #fx #crypto</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nếu tay bạn dùn lên và nhịp tim đập thỉnh thịch mỗi khi bấm lệnh, thì hãy rút sạch tiền và xóa áp đi. Bạn không phải là một trader, bạn đang tự nguyện bước vào lò mổ. Mạng xã hội đã lừa rối bạn, những video khoe siêu xe, những cú chốt lời xanh mướt x5 x10 tài khoản chỉ sau một đêm. Đó chỉ là mồi nhử và sự tham laam của bạn, chính là chiếc lưỡi câu. Họ làm bạn nghiện cái cảm giác nghẹt thờ, Nghiện lượng hốc môn kích thích bơm thẳng lên áo mỗi khi nến rật lên rật xuống, mắt bạn rán chặt vào màn hình trường đường quest stop lot. Bạn tưởng mình đang phân bằng chính những đồng áo máu của gia đình mình. Và đây là sự thật tàn nhẫn nhất mà đám thầy bà ngoài kia không bao giờ dám nói cho bạn biết. Một hệ thống giao dịch thực sự kiếm được tiền nó tẻ nhạt đến mức đáng sợ. Đúng vậy, chán ngắt. Trong khi bạn đang gào thét, đập bàn đập ghế vì một lệnh lỗ, thì những kẻ đang âm thầm lấy tiền của bạn ngoài kia. Họ vô cảm. Họ coi tiền trên màn hình chỉ là con số, đó là trò chơi của sắc xuất. Kỳ luật không phải gồng mình chịu đựng, nó là cố máy máu lạnh, không hy vọng, cũng không có sợ hãi, nhạt nhéo như việc bạn đánh dăng. Đã đến lúc bạn phải lựa chọn, hoặc là tự tay bóp chết cảm xúc và ảo tưởng của mình. Hoặc là để thị trường nhai nát tài khoản của bạn và nhổ ra không thương tiếc.</t>
+          <t>Một điểm và lệnh đơn giản mà rất nhiều người bỏ qua. Bước 1, nhìn cấu chúc thị trường. Tăng, giảm, đi ngang có quy luật hoặc đi ngang không quy luật, đi ngang không quy luật thì đứng ngoài. Vì rất dễ bị quét lệnh. Bước 2, tìm vùng mua tiềm năng. Đó là đầu con sóng tăng và đỉnh cũ vừa bị phá. Nhưng nếu giá phá quá yếu hoặc phá xa rồi bị kéo về mạnh thì vùng đó không còn tốt. Khi Phi Bonacci không phải 5 hoặc không phải 6, 1, 8 trùng đỉnh cũ, đó là vùng đẹp. Bước 3, trở tín hiệu. Giá chạm vùng có thể đảo chiều, quét giả hoặc đi tiếp. Giai đoạn 1, lực bán yếu dần, nén giút chân, giai đoạn 2, tranh chấp, những cây, nén nhỏ, đi ngang. Giai đoạn 3, một nén tăng mạnh bứt phá, xác nhận xu hướng. Thếu một giai đoạn thì đứng ngoài, kiên nhẫn, quản lý vốn, kiểm tra lại nhiều lần. Ý hiệu ích thì nhấn thích và đăng ký nhé. Nội dung chỉ để học, không phải lời quên đầu tư.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1:10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7685719795400051989</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693735707138854164</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2329,33 +3390,33 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>#trading #cpi #trading #fx #sotrading</t>
+          <t>Vùng cung cầu trong trading. #trading #fx #Shorts</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>#trading #cpi #trading #fx #sotrading</t>
+          <t>Vùng cung cầu trong trading. #trading #fx #Shorts</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>99% trầy trái tài khoản không phải vì rốt kỹ thuật, cũng chẳng phải vì thị trường cố tình đi ngược lại họ. Lý do thực sự là vì tất cả chúng ta đều từng mắc kẹt trong một áo tưởng điên cuồng, đi tìm một chén thánh giao dịch. Kịch bản này quen không? Nạp tiền, ăn vài lệnh đầu, bạn tự tin tháo stoplots vì cay cũ, để rồi tài khoản trái khét, sáng ra với đầu chống rỗng, vòng xoay đó cứ lập lại. Tại sao? Vì tư duy của bạn chưa thay đổi, bạn không chấp nhận mình có thể sai, bạn ảo tưởng nhồi nhét thêm vài chỉ báo là kiểm soát được thị trường, tỉnh lại đi, bạn sẽ bị nó nghiền nát. Nhiều người cậy mình có kỹ năng, họ stoplots lại thật hẹp, phí giao dịch sẽ ăn món hết, khoản phí này mới là lưỡi giao, nó lặng lặng gióc thịt tài khoản, chứ không phải do nhà cái. Ở thị trường này, sự thật mất lòng nhất là không có gì là tuyệt đối, và cũng chẳng có chén thánh nào cứu được bạn, lối thoát duy nhất để tồn tại và bất phá chỉ gói gọn trong hai chữ, từ duy và kỷ luật. Hãy học cách chấp nhận dùi do, trở thành người quản trị vốn tàn nhẫn, giao dịch là bài toán sắc xuất, kiểm soát nghiêm ngặt số tiền sẽ mất, để không bị đá vang khỏi cuộc chơi. Đừng để thị trường biến bạn thành một con bạc khát nước và tước đi sự tự tôn cuối cùng của mình. Khi sự hương phấn tột độ, hay nỗi sợ hãi tột cùng ập đến, thì kỷ luật chính là chiếc mỏ neo duy nhất giữ bạn lại với cuộc chơi.</t>
+          <t>Bẽ vùng cầu càng nhiều đường, bạn càng thua nhiều hơn, vì sao vùng cầu là nơi phe mua thắng thế, còn vùng cung là nơi phe bán thắng thế. Psylum phổ biến là vẽ mọi đường ngang đi qua thật nhiều đỉnh và đáy. Cách này không có quy tắc, đường nào cũng đúng, nên bạn không thể giao dịch được. Cách đúng thứ nhất, chỉ vẽ những vùng gần giá hiện tại nhất. Thứ 2, vẽ từ điểm cao nhất hoặc thấp nhất của đỉnh và đáy. Thứ 3, giá rời vùng càng nhanh và mạnh, vùng đó càng mạnh, nhưng vùng mạnh cũng đừng vào bừa. Hay chờ tín hiệu nên rõ ràng rồi, mới vào lệnh. Ví dụ thực tế, khung lớn phá đỉnh đi lên, giá hồi về vùng cầu, rồi tạo tín hiệu mua, sau đó giá tăng mạnh và chạm mục tiêu chốt lời. Kênh nhẫn chờ tín hiệu giúp bạn tránh một lệnh thua, theo dõi để xem thêm cách đọc biểu đồ, nội dung chỉ để học hỏi, không phải lời khuyên đầu tư.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1:10</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7685348661768899860</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693564151402302740</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2379,79 +3440,4502 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>#trading #crypto #fx #cpi #sotrading</t>
+          <t>2 mẫu nến đảo chiều đáng học: chòm râu &amp; nhấn chìm lần hai Đọc nến từ...</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>#trading #crypto #fx #cpi #sotrading</t>
+          <t>2 mẫu nến đảo chiều đáng học: chòm râu &amp; nhấn chìm lần hai Đọc nến từ bản chất mua – bán và 2 mẫu nến đảo chiều tại vùng cản. Nội dung chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #trading #fx</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sang tuần thứ 4, sự bế tắc đã biến A từ một người phân tích cẩn trọng thành một con bạc khát nước. Cậu không còn nhìn biểu đồ để tìm dòng tiền nữa. Cậu nhìn nó bằng ánh mắt của kẻ muốn trả thù. 10 giờ tối, một cây nến xanh bất phá, chỉ một lệnh all in này thôi. Gỡ lại 10.000 đô rồi mình sẽ đánh kỷ luật. A kéo tối đa đòn 7, nhắm mắt bấm bay và giết khoát tháo luôn stop loss. 5 phút đầu, tài khoản xanh mướt. Nhưng rồi giá khượng lại, đến giút chân đỏ quạch đâm xuống, phá vỡ mọi hỗ trợ. A chết lặng, mùa hôi lạnh túa ra, cậu cầu nguyện, cậu rán mắt vào những con số âm. Âm 1 ngàn dưới, âm 3 ngàn, âm 5 ngàn dưới, thanh lý hiện lên lạnh léo. Căn phòng rơi vào tính lặng. Không có tiếng gạo thét, chỉ có sự chống rõm tột cùng. Tại sao không cắt lỗ lúc nãy? Đêm đó, A mất ngủ, tự thể độc sẽ không bao giờ lặp lại. Nhưng bị kịch lớn nhất không phải là mất 10.000 đô. Vì gốc dễ tư duy chưa hề đập đi xay lại, bàn tay A lại tiếp tục bóp ngắn xóa điện ngục lại bắt đầu quay. Cuốn đi tất cả trong thị trường này, danh giới giữa một trader và một con bạc mỏng manh đến đáng sợ. Có thể bạn đang cười A, nhưng đã bao giờ bạn thấy bóng dáng mình trong đó. Còn anh em, anh em nhìn nhận thế nào về nhân vật A, hãy để lại ý kiến xuống phật bình luận nhé.</t>
+          <t>Nên nhấn chìm xuất hiện là đảo chiều. Chưa chắc đâu, mỗi cây nén là một cuộc chiến giữa phê mua và phê bán. Nén có 5 yếu tố, giám mở, giá đóng, cao nhất, thấp nhất và thời gian. Sau một sóng tăng, nên nhấn chìm giảm chỉ là nhịp hồi. Lực mua vẫn còn bẫu thứ nhất. Nên chỏm râu, từ 3 cây có râu dài trở lên. Râu càng dài, thị trường càng từ chối giám mạnh tại vùng đó. Bẫu thứ 2, nên nhấn chìm mở đỉnh, hoặc đáy lần thứ 2, đừng vào ở lần chạm đầu, hãy đợi nến đóng cửa rồi mới hành động. Đặt cắt lỗ dưới râu nén hoặc dưới vùng cản để kiểm soát rủi do. Điểm vào tốt phải có quý tắc rõ ràng đến nơi chỉ việc kiểm tra. Hãy tự hỏi, phê nào đang mạnh hơn? Theo dõi để học thêm và nhớ đây chỉ là kiến thức giáo dục.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1:11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7684604753577495829</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693471867973176596</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SO Trading</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>#fx #crypto #trading #sotrading #fomc</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>#fx #crypto #trading #sotrading #fomc</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Đã bao giờ bạn ngồi thẫn thờ trước màn hình lúc 3 giờ sáng, nhìn chân chân vào con số không tròn chính chưa? Ánh sáng đỏ từ nến sắp hắt lên khuôn mặt phở phạc, và hai bàn tay thì lạnh toát. Cảm giác đó, sự tuyệt vọng đến tột cùng. Bạn gục đầu xuống, tự tác vào mặt mình vì sự ngu ngốc. Tại sao không giết khoát cắt lỗ? Tại sao lại gun dày kéo dày? Tại sao lại mù quán ô lín bấu viếu vào một phép màu? Nhưng điều đâm nắt trái tim bạn không phải là những con số vô chi. Số tiền đó lẽ ra là tiền bìm sữa cho con. Bạn phải gượng cười, nuốt ngược cái hố sâu hấm vào dạ dày. Bạn thấy mình giống một kẻ lừa đảo thảm hại. Bạn gào thét đổ lỗi cho nhà cái quét râu. Nhưng sâu thằm, bạn biết rõ sự thật. Chẳng ai xan tìm bạn cả. Chính sự do dự bóp nghẹt stop loss đã tạo ra phịt tài khoản. Chính lòng tham của bạn đã tự tay châm ngòi nổ. Thị trường không có sự chắc ẩn. Lối thoát duy nhất là giết chết cảm xúc. Đánh như một cổ máy máu lạnh. Tự bóp chết cảm xúc. Hay để thị trường bóp chết bạn.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sotrading01/video/7687234989431278868</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SO Trading</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>#trading #cpi #sotrading #crypto #fx</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>#trading #cpi #sotrading #crypto #fx</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1:10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sotrading01/video/7686468492828331285</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SO Trading</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>#trading #cpi #fx #sotrading #crypto</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>#trading #cpi #fx #sotrading #crypto</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Cùng nhận một tín hiệu. Tại sao mỗi người lại có một kết quả khác nhau? Ba người cùng nhận được một tín hiệu với đầy đủ điểm vào, điểm dừng và mục tiêu. Người đầu tiên thực hiện đúng vùng giá, chọn khối lượng phù hợp và chỉ chấp nhận mức dùi do đã tính trước. Người thứ 2 xem tín hiệu muộn. Giá đã chạy khỏi vùng vào nhưng vì sợ bỏ lỡ nên vẫn quyết định tham gia. Người thứ 3 thấy cơ hội hấp dẫn nên tự ý tăng khối lượng lên nhiều lần. Khi thị trường biến động ngược hướng, người đầu chịu đúng dùi do trong kế hoạch, người thứ 2 tổn thất lớn, còn người thứ 3 chạm giấy hạn, thổi bay tài khoản. Như vậy, vấn đề không chỉ nằm ở tín hiệu. Cùng một tín hiệu, nhưng điểm vào, khối lượng và cách kiểm soát dùi do khác nhau sẽ tạo ra kết quả hoàn toàn khác nhau. Đó là lý do mình phát triển hệ thống tiếp nhận và thực thi tín hiệu tự động. Hệ thống hỗ trợ thiết lập điểm vào, điểm dừng, mục tiêu và khối lượng chuẩn sát dựa trên mức dùi do bạn đã cài. Hệ thống không hứa hẹn mọi lệnh đều thắng. Mục tiêu là hạn chế sai sót và ép bạn tuân thủ, tín hiệu, tín hiệu tạo cơ hội, nhưng thực hiện quyết định kết quả, bạn hay gặp vấn đề điểm vào, khối lượng hay cảm xúc, bình luận để xem hệ thống hoạt động nhá.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1:10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sotrading01/video/7686097369682922772</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SO Trading</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>#trading #cpi #fx #sotrading #crypto</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>#trading #cpi #fx #sotrading #crypto</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Nếu tay bạn dùn lên và nhịp tim đập thỉnh thịch mỗi khi bấm lệnh, thì hãy rút sạch tiền và xóa áp đi. Bạn không phải là một trader, bạn đang tự nguyện bước vào lò mổ. Mạng xã hội đã lừa rối bạn, những video khoe siêu xe, những cú chốt lời xanh mướt x5 x10 tài khoản chỉ sau một đêm. Đó chỉ là mồi nhử và sự tham laam của bạn, chính là chiếc lưỡi câu. Họ làm bạn nghiện cái cảm giác nghẹt thờ, Nghiện lượng hốc môn kích thích bơm thẳng lên áo mỗi khi nến rật lên rật xuống, mắt bạn rán chặt vào màn hình trường đường quest stop lot. Bạn tưởng mình đang phân bằng chính những đồng áo máu của gia đình mình. Và đây là sự thật tàn nhẫn nhất mà đám thầy bà ngoài kia không bao giờ dám nói cho bạn biết. Một hệ thống giao dịch thực sự kiếm được tiền nó tẻ nhạt đến mức đáng sợ. Đúng vậy, chán ngắt. Trong khi bạn đang gào thét, đập bàn đập ghế vì một lệnh lỗ, thì những kẻ đang âm thầm lấy tiền của bạn ngoài kia. Họ vô cảm. Họ coi tiền trên màn hình chỉ là con số, đó là trò chơi của sắc xuất. Kỳ luật không phải gồng mình chịu đựng, nó là cố máy máu lạnh, không hy vọng, cũng không có sợ hãi, nhạt nhéo như việc bạn đánh dăng. Đã đến lúc bạn phải lựa chọn, hoặc là tự tay bóp chết cảm xúc và ảo tưởng của mình. Hoặc là để thị trường nhai nát tài khoản của bạn và nhổ ra không thương tiếc.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1:10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sotrading01/video/7685719795400051989</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SO Trading</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>#trading #cpi #trading #fx #sotrading</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>#trading #cpi #trading #fx #sotrading</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99% trầy trái tài khoản không phải vì rốt kỹ thuật, cũng chẳng phải vì thị trường cố tình đi ngược lại họ. Lý do thực sự là vì tất cả chúng ta đều từng mắc kẹt trong một áo tưởng điên cuồng, đi tìm một chén thánh giao dịch. Kịch bản này quen không? Nạp tiền, ăn vài lệnh đầu, bạn tự tin tháo stoplots vì cay cũ, để rồi tài khoản trái khét, sáng ra với đầu chống rỗng, vòng xoay đó cứ lập lại. Tại sao? Vì tư duy của bạn chưa thay đổi, bạn không chấp nhận mình có thể sai, bạn ảo tưởng nhồi nhét thêm vài chỉ báo là kiểm soát được thị trường, tỉnh lại đi, bạn sẽ bị nó nghiền nát. Nhiều người cậy mình có kỹ năng, họ stoplots lại thật hẹp, phí giao dịch sẽ ăn món hết, khoản phí này mới là lưỡi giao, nó lặng lặng gióc thịt tài khoản, chứ không phải do nhà cái. Ở thị trường này, sự thật mất lòng nhất là không có gì là tuyệt đối, và cũng chẳng có chén thánh nào cứu được bạn, lối thoát duy nhất để tồn tại và bất phá chỉ gói gọn trong hai chữ, từ duy và kỷ luật. Hãy học cách chấp nhận dùi do, trở thành người quản trị vốn tàn nhẫn, giao dịch là bài toán sắc xuất, kiểm soát nghiêm ngặt số tiền sẽ mất, để không bị đá vang khỏi cuộc chơi. Đừng để thị trường biến bạn thành một con bạc khát nước và tước đi sự tự tôn cuối cùng của mình. Khi sự hương phấn tột độ, hay nỗi sợ hãi tột cùng ập đến, thì kỷ luật chính là chiếc mỏ neo duy nhất giữ bạn lại với cuộc chơi.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1:10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sotrading01/video/7685348661768899860</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SO Trading</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>#trading #crypto #fx #cpi #sotrading</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>#trading #crypto #fx #cpi #sotrading</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sang tuần thứ 4, sự bế tắc đã biến A từ một người phân tích cẩn trọng thành một con bạc khát nước. Cậu không còn nhìn biểu đồ để tìm dòng tiền nữa. Cậu nhìn nó bằng ánh mắt của kẻ muốn trả thù. 10 giờ tối, một cây nến xanh bất phá, chỉ một lệnh all in này thôi. Gỡ lại 10.000 đô rồi mình sẽ đánh kỷ luật. A kéo tối đa đòn 7, nhắm mắt bấm bay và giết khoát tháo luôn stop loss. 5 phút đầu, tài khoản xanh mướt. Nhưng rồi giá khượng lại, đến giút chân đỏ quạch đâm xuống, phá vỡ mọi hỗ trợ. A chết lặng, mùa hôi lạnh túa ra, cậu cầu nguyện, cậu rán mắt vào những con số âm. Âm 1 ngàn dưới, âm 3 ngàn, âm 5 ngàn dưới, thanh lý hiện lên lạnh léo. Căn phòng rơi vào tính lặng. Không có tiếng gạo thét, chỉ có sự chống rõm tột cùng. Tại sao không cắt lỗ lúc nãy? Đêm đó, A mất ngủ, tự thể độc sẽ không bao giờ lặp lại. Nhưng bị kịch lớn nhất không phải là mất 10.000 đô. Vì gốc dễ tư duy chưa hề đập đi xay lại, bàn tay A lại tiếp tục bóp ngắn xóa điện ngục lại bắt đầu quay. Cuốn đi tất cả trong thị trường này, danh giới giữa một trader và một con bạc mỏng manh đến đáng sợ. Có thể bạn đang cười A, nhưng đã bao giờ bạn thấy bóng dáng mình trong đó. Còn anh em, anh em nhìn nhận thế nào về nhân vật A, hãy để lại ý kiến xuống phật bình luận nhé.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1:11</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sotrading01/video/7684604753577495829</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SO Trading</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>#cpi #sotrading #trading #fx #crypto</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>#cpi #sotrading #trading #fx #crypto</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>không phải là một kẻ ngốc. Trước khi nạp 10.000 đô đầu tiên, cậu đã dành hàng tháng trời cày nát các mô hình price action. Bước vào thị trường với một sự tự tin đầy tính toán. Những tuần đầu tiên, tiền nổ liên hồi. Cảm giác hoác môn hương phấn tiết ra tột độ khiến A bắt đầu tin rằng, mình sinh ra là để làm trader. Để tối đa hóa tỷ lệ lợi nhuận rùi do, ABOV STOP LOST lại thật hẹp. Cậu tự hào khoe những lệnh bắt đỉnh đáy như một phù thủy tài chính. Nhưng tuần trang mật kết thúc nhanh chóng. Giá vừa liếm S lờ thì ngay lập tức quay đầu bay đúng hướng. A, cây cú đập bàn, lũ nhà cái lại cố tình quét dâu mình. Cậu không hề nhận ra sự thật tàn nhẫn khoảng cách entry và S lờ quá ngắn khiến tỷ lệ phí giao dịch phình to khổng lồ vào cậu. Chính lưỡi giao vô hình của phí ẩn đang lặng lặng giọc thịt tài khoản. Tài khoản rơi từ 10.000 xuống 7.000 đô. Sự tự tin biến mất, nỗi sợ lên ngôi. Thay vì giữ kỷ luật 1% gốc, A run tay hạ cửa chỉ dám đánh 70 đô cho lệnh tiếp theo. Cái bẫy chính thức sập xuống, sai thì mất liên tục, mà đúng thì 140 đô thu về chỉ như cho đùa trước hố sâu 3.000 đô đang vẫn gì máu. Liệu A có kịp nhận ra nút thắt trước khi tài khoản vệch.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1:09</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sotrading01/video/7684276294971854101</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Trạng thái Script</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Thời lượng</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Tiêu đề Video</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Chủ đề cốt lõi</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Số dòng thoại</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Xem video YouTube</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Đọc File Script cục bộ</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Trích đoạn thoại mở đầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>You're Using Liquidity Wrong</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Liquidity &amp; Bẫy giá</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RKU7D9PxLgY</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\001_RKU7D9PxLgY_You're_Using_Liquidity_Wrong.md</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] Is this liquidity? Is this liquidity? Is [00:00:02] this liquidity? Or is this liquidity? If [00:00:05] you cannot answer this question, you are [00:00:07] using liquidity wrong. Liquidity is one [00:00:09] of the most powerful tools in technical [00:00:12] analysis, because you are essen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>I Stole a Trading Strategy Worth $60 Billion</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JRRc63tUdy8</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\002_JRRc63tUdy8_I_Stole_a_Trading_Strategy_Worth_$60_Billion.md</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This is a research paper curated by an [00:00:02] 80 billion dollar hedge fund revealing [00:00:05] their exact entry model, the criteria [00:00:07] for when they enter, how they calculate [00:00:09] how big their position sizing will be, [00:00:12] and most importantly, the exact strateg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>SO Trading</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>#cpi #sotrading #trading #fx #crypto</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>#cpi #sotrading #trading #fx #crypto</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>không phải là một kẻ ngốc. Trước khi nạp 10.000 đô đầu tiên, cậu đã dành hàng tháng trời cày nát các mô hình price action. Bước vào thị trường với một sự tự tin đầy tính toán. Những tuần đầu tiên, tiền nổ liên hồi. Cảm giác hoác môn hương phấn tiết ra tột độ khiến A bắt đầu tin rằng, mình sinh ra là để làm trader. Để tối đa hóa tỷ lệ lợi nhuận rùi do, ABOV STOP LOST lại thật hẹp. Cậu tự hào khoe những lệnh bắt đỉnh đáy như một phù thủy tài chính. Nhưng tuần trang mật kết thúc nhanh chóng. Giá vừa liếm S lờ thì ngay lập tức quay đầu bay đúng hướng. A, cây cú đập bàn, lũ nhà cái lại cố tình quét dâu mình. Cậu không hề nhận ra sự thật tàn nhẫn khoảng cách entry và S lờ quá ngắn khiến tỷ lệ phí giao dịch phình to khổng lồ vào cậu. Chính lưỡi giao vô hình của phí ẩn đang lặng lặng giọc thịt tài khoản. Tài khoản rơi từ 10.000 xuống 7.000 đô. Sự tự tin biến mất, nỗi sợ lên ngôi. Thay vì giữ kỷ luật 1% gốc, A run tay hạ cửa chỉ dám đánh 70 đô cho lệnh tiếp theo. Cái bẫy chính thức sập xuống, sai thì mất liên tục, mà đúng thì 140 đô thu về chỉ như cho đùa trước hố sâu 3.000 đô đang vẫn gì máu. Liệu A có kịp nhận ra nút thắt trước khi tài khoản vệch.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1:09</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7684276294971854101</t>
-        </is>
-      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>How to Avoid False Breakouts (Avoid The Trap)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Liquidity &amp; Bẫy giá</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2yePksvT64I</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\003_2yePksvT64I_How_to_Avoid_False_Breakouts_(Avoid_The_Trap).md</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] What if I told you. False breakouts are one [00:00:02] of the most common ways trader s lose money. They see price break a high, enter the trade [00:00:07] expecting it to go up, and unfortunately  price does exactly the opposite. [00:00:11] If only there was a way to avoid these false  b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>How To Find Stocks To Trade</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=j64xW7NovNs</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\004_j64xW7NovNs_How_To_Find_Stocks_To_Trade.md</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:04] [music] [00:00:12] &gt;&gt; I quickly figured out one of the biggest [00:00:14] issues in the trading YouTube world. [00:00:16] Every trading YouTuber out there just [00:00:18] shows their glorious trading strategy. [00:00:20] But what they don't show you is how they [00:00:22] actually pick ou</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>I Reveal My Most Profitable Trading Strategy</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fi7OxEzvhjw</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\005_fi7OxEzvhjw_I_Reveal_My_Most_Profitable_Trading_Strategy.md</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I have made $213,000 [00:00:02] in the past 3 months of trading and I [00:00:04] didn't use any fancy indicators, no [00:00:07] random trend lines, just pure price [00:00:10] action, baby. You see, every single day [00:00:12] something very specific happens at the [00:00:14] open and clos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Stop Taking Trades Until You See This (Pullback)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ju-cTa_dHAk</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\006_Ju-cTa_dHAk_Stop_Taking_Trades_Until_You_See_This_(Pullback).md</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] There s one signal that tells you exactly  when you should be entering a trade. [00:00:04] And today I m going to show you that signal.  It shows up on almost every single chart. And [00:00:09] once you see it, you can not unsee it. And once you get good at spotting it, [00:00:13] you can</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TOP 3 Trading Strategies Explained in 8 Minutes</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=j8Q3MIwGYOk</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\007_j8Q3MIwGYOk_TOP_3_Trading_Strategies_Explained_in_8_Minutes.md</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[00:00:00] These are my top three favorite trading [00:00:02] strategies that I've backtested over and [00:00:04] over and every single month that I [00:00:06] tested them all three ended up being [00:00:08] profitable in the long term. And by the [00:00:11] end of this video, you too will know all </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>The Secret To Using The Volume Profile</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Orderflow &amp; Volume</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3X95la3CCS0</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\008_3X95la3CCS0_The_Secret_To_Using_The_Volume_Profile.md</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This is the volume profile And it can give you entries so [00:00:03] precise that the moment I started implementing  this into my own personal trading strategy. [00:00:09] I instantly saw my winrate start to skyrocket. And after watching this video, you will not only [00:00:14] know how t</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Investing For Beginners (Start With Just $100)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>402</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J5Gy_nYIO1o</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\009_J5Gy_nYIO1o_Investing_For_Beginners_(Start_With_Just_$100).md</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] On average, the government prints $6 [00:00:02] billion per year. Six billion, which [00:00:04] relates to an average of 3% inflation. [00:00:08] Which means the money that you have [00:00:10] saved currently is worth 3% less every [00:00:13] year. Meaning, if you have the mindset [00:00:</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>I Ranked The Most Popular Trading Indicators</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nRPNt-Cnkl4</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\010_nRPNt-Cnkl4_I_Ranked_The_Most_Popular_Trading_Indicators.md</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] Indicators, you love them, you hate [00:00:01] them. Some of them work, some of them [00:00:03] don't. The reality is not all indicators [00:00:06] are created equal and most traders are [00:00:08] using indicators that are literally [00:00:10] designed to lose nowadays. Not [00:00:12] ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Volume Doesn't Work (Unless You Do This)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Orderflow &amp; Volume</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>301</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aVt0WUJuV6E</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\011_aVt0WUJuV6E_Volume_Doesn't_Work_(Unless_You_Do_This).md</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[00:00:00] The big players can easily manipulate [00:00:02] price, but they can't manipulate volume [00:00:04] not easily. Volume feed is very useful. [00:00:06] You can actually tell from price and [00:00:08] volume relationships whether somebody's [00:00:11] playing with you or not. [00:00:12] &gt;&gt; </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>How I Would Learn To Trade (If I Could Start Over)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=F6HKKVi1EZY</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\012_F6HKKVi1EZY_How_I_Would_Learn_To_Trade_(If_I_Could_Start_Over).md</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I have made $303,000 [00:00:02] last year in trading alone. Now, for [00:00:04] some context, I've been trading for 11 [00:00:07] years now. Got to feel old. I originally [00:00:09] went to college for finance, graduated, [00:00:11] got my degree, and was thinking about [00:00:12] going i</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>The Only Fibonnaci Guide You'll Ever Need</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vMQ0cYlDkA8</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\013_vMQ0cYlDkA8_The_Only_Fibonnaci_Guide_You'll_Ever_Need.md</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I found a strategy so good that if you [00:00:02] use it correctly, it can not only [00:00:04] predict the exact point where price is [00:00:06] going to reverse, like it did here, [00:00:08] here, here, and here, but it can also [00:00:11] find the perfect places to set your [00:00:13] t</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>This Gap is About to Break The Stock Market</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ICqUb68YGcU</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\014_ICqUb68YGcU_This_Gap_is_About_to_Break_The_Stock_Market.md</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This black line is the S&amp;P 500. The blue [00:00:03] line is job openings. If you look [00:00:05] closely, they both seem to be very [00:00:07] correlated, very correlated. When the [00:00:09] blue line goes up, the black line goes [00:00:11] up. When the blue line goes down, the [00:00:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>A Once in a Lifetime Economic Reset is Coming</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L1bQnXn9IoE</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\015_L1bQnXn9IoE_A_Once_in_a_Lifetime_Economic_Reset_is_Coming.md</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] We had major bottoms in 78, 82, 86, 90 [00:00:04] because they always rig things to be [00:00:06] good in the election year. [00:00:08] &gt;&gt; This is Stanley Drunken Miller, one of [00:00:10] the greatest traders to ever live, being [00:00:12] known to average 30% every single year [00:00:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>How To Use TradingView For Beginners (My Secrets)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>333</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RPwg5Vg-wnM</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\016_RPwg5Vg-wnM_How_To_Use_TradingView_For_Beginners_(My_Secrets).md</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] So, you want to learn how to use Trading [00:00:01] View like a pro? Well, that's why you [00:00:03] clicked this video, right? Well, lucky [00:00:05] for you, I have thousands of hours on [00:00:07] Trading View. If your screen time [00:00:09] doesn't look like this, are you even a [00:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>The Only Liquidity Guide You'll EVER NEED</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Liquidity &amp; Bẫy giá</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>217</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9REzGB3R6HU</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\017_9REzGB3R6HU_The_Only_Liquidity_Guide_You'll_EVER_NEED.md</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:02] The algorithm. [00:00:03] I started focusing on the algorithms a [00:00:06] very long time ago. They're written by a [00:00:08] programmer and they have to be written [00:00:10] to go somewhere. Okay? Where are they [00:00:12] written to go? These technical areas [00:00:14] that we're put</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>The Trading Strategy That Made Him $1.4 Million</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>403</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T2tcUgQeoPI</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\018_T2tcUgQeoPI_The_Trading_Strategy_That_Made_Him_$1.4_Million.md</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This is a guy named Trader Kane. In a [00:00:02] single month, he turned just $130,000 [00:00:06] into $1.4 million trading stocks in a [00:00:09] month. 1.4 million in a month. That's [00:00:11] insane. Now, I don't know about you, but [00:00:14] I would also like 1.4 million in a [00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>DAY TRADING Explained in 11 Minutes</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=edfHZq5lrTA</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\019_edfHZq5lrTA_DAY_TRADING_Explained_in_11_Minutes.md</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I have 12 minutes to explain day trading. So naturally, I'm going to put $60,000 [00:00:05] of my own money on the line. What could  possibly go wrong? (nervous laugh). Oh god. [00:00:10] Day trading is basically a game of patient  people taking money from impatient people. [00:00:15] But</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>The ONLY Orderflow Guide You'll EVER NEED</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Orderflow &amp; Volume</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ljk9BovCSqI</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\020_ljk9BovCSqI_The_ONLY_Orderflow_Guide_You'll_EVER_NEED.md</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This is a candlestick. The foundation of trading. But to be honest, it doesn t give [00:00:04] us very much information. What if we could enable a secret tool, [00:00:08] where it gives us 10x the amount of data. But not only that. [00:00:12] Telling us exactly who s in control.  The buye</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>How To Grow a Small Trading Account</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LJRC6WRBmEg</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\021_LJRC6WRBmEg_How_To_Grow_a_Small_Trading_Account.md</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] So, you're new to day trading and have a [00:00:02] very small amount of money in your [00:00:03] account and you want to grow this [00:00:05] balance as quickly as humanly possible. [00:00:07] So, you can have millions of dollars and [00:00:09] sail your private yacht to pick up a [00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Do This To INSTANTLY Become More Profitable</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>274</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BI_W4URQ7U0</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\022_BI_W4URQ7U0_Do_This_To_INSTANTLY_Become_More_Profitable.md</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] Risk management. One of those things you [00:00:02] hear about all the time, but oddly [00:00:03] enough, never pay really much attention [00:00:05] to it. That is until now. What if I told [00:00:08] you all you had to do was apply one [00:00:10] simple tweak to your current strategy [00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Candlestick Patterns Don't Work (Unless You Do This)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wIeYqqXcgtU</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\023_wIeYqqXcgtU_Candlestick_Patterns_Don't_Work_(Unless_You_Do_This).md</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This is a candlestick. And if formed in [00:00:02] a specific formation, it can tell you a [00:00:04] story of what the market is planning to [00:00:06] do next. But what if I told you [00:00:09] everything you know about candlestick [00:00:10] patterns is a lie. Hammers, dogeis, [00:00:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>How To Day Trade As A Complete Beginner</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Scalping &amp; Day Trading</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l0UsErg8OLA</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\024_l0UsErg8OLA_How_To_Day_Trade_As_A_Complete_Beginner.md</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This exact strategy is what I use on a [00:00:02] day-to-day basis and has been back [00:00:04] tested thousands of times and every [00:00:06] month that I tested it, it has been [00:00:08] profitable in the long term. The core of [00:00:10] this strategy uses supply and demand. [00:00:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>I Copied Politician's Trades For a Month</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>194</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5vajkhwbIG4</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\025_5vajkhwbIG4_I_Copied_Politician's_Trades_For_a_Month.md</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] These are some of the wealthiest people [00:00:02] on the planet with net worths of [00:00:04] hundreds of millions of dollars. But how [00:00:06] did they get so rich? Well, what if I [00:00:08] told you these were politicians? Now, [00:00:10] you may think they made their money [00:00:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Turn $100 Into $10,000 With This Trading Strategy</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B4ch-Lf8wJc</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\026_B4ch-Lf8wJc_Turn_$100_Into_$10,000_With_This_Trading_Strategy.md</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I ve carefully curated a trading strategy,  where I ve backtested thousands of trades. [00:00:04] After hours of testing and Backtest after  backtest. I think I finally curated the [00:00:09] perfect strategy. And this is the [00:00:11] exact strategy I ll be using in 2025. And I m sharin</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>How To Know When To Buy &amp; Sell Crypto Currency</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=frqKQMaRK_E</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\027_frqKQMaRK_E_How_To_Know_When_To_Buy_&amp;_Sell_Crypto_Currency.md</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This exact tool has predicted the Exact  bottom of bitcoin every single time. [00:00:04] And if you followed just this one  tool for the past 5 years on Bitcoin, [00:00:08] Meaning you bought when it said to buy and sold  when it said to sell. You would have made 5,142% [00:00:15] Not onl</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>I Found The Secret to Technical Analysis</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>298</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p-HKL7NmDxs</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\028_p-HKL7NmDxs_I_Found_The_Secret_to_Technical_Analysis.md</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I found a strategy so profitable that it [00:00:02] got me this win this win this win and [00:00:05] all of these win not only that but this [00:00:08] strategy is set up in such a way that [00:00:10] every single time you use it it gives [00:00:12] you risk rewards that are absolutely [0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>I Reveal My Day Trading Strategy</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lxg-6QdBI6k</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\029_lxg-6QdBI6k_I_Reveal_My_Day_Trading_Strategy.md</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[00:00:00] Every single morning at exactly 10am,  something specific happens in the market. [00:00:04] And if you get good at spotting it,  you can make a ton of fn money. [00:00:08] For example, here are the past 9 trading days. But, if you look closely. [00:00:12] At exactly 10am on all of these  </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>The Only Trading Strategy You'll Ever Need</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=e-QmGJU1XYc</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\030_e-QmGJU1XYc_The_Only_Trading_Strategy_You'll_Ever_Need.md</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I have a 3 step formula that I  ve backtested 1000 s of times [00:00:03] And every single month that I tested  it, it was profitable in the long term. [00:00:07] No indicators, no patterns,  just pure price action baby. [00:00:18] And by the end of this video,  you too will know this stra</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>I Found a Secret To Orderblocks</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Supply Demand &amp; OB</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qmsGqitE2LE</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\031_qmsGqitE2LE_I_Found_a_Secret_To_Orderblocks.md</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] Okay, so you get multiple  orderblocks on your chart. [00:00:02] Cool. But then you're [00:00:03] stuck with the decision on which one to trade. Now this is actually a very important decision. [00:00:08] Do you trade this orderblock? Yeah, you could,  but it turns out, it was too weak and</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>The ONLY Supply &amp; Demand Guide You'll EVER NEED</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Supply Demand &amp; OB</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1z382y4v39Y</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\032_1z382y4v39Y_The_ONLY_Supply_&amp;_Demand_Guide_You'll_EVER_NEED.md</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] Supply and Demand absolutely everybody is talking about it. [00:00:03] Including this hedge fund manager that explains  exactly how he uses it in an interview. But we [00:00:09] ll get to that in a little bit. But why should we learn supply [00:00:12] and demand in the first place? To und</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>This One Candle Can Change Your Life</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fGZId6WmCns</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\033_fGZId6WmCns_This_One_Candle_Can_Change_Your_Life.md</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This one candle can completely change your life. [00:01:04] This is how you do it. If you are overall bullish, [00:03:08] you want to buy below the market open. If you are overall bearish, you want to [00:04:07] sell above the market open. Here s what I mean. [00:04:10] Go to the daily ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>How I Find Reversals (Never Guess Again)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sNKfxl4yHzw</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\034_sNKfxl4yHzw_How_I_Find_Reversals_(Never_Guess_Again).md</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[00:00:00] You wake up. Brush your teeth. [00:00:01] Pour your morning cup of joe. Pack your suitcase. [00:00:04] You order an uber. Head to the airport. Run to the terminal. [00:00:09] Fly to Nebraska. What s in Nebraska? Nothing. [00:00:13] You fly back to wherever you live.  Go to your computer. </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>The Only Indicator You’ll Ever Need</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HFKRgIRzeQ8</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\035_HFKRgIRzeQ8_The_Only_Indicator_You’ll_Ever_Need.md</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I found an indicator that  is dangerously accurate. [00:00:03] And as you can see, it works fn amazing. One day I was searching the internet for what [00:00:08] I hoped to be the best indicator out there. Now some people would call this a waste of [00:00:12] time because there s not an in</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>The Greatest Crypto Trader to Ever Live</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BAPF8Ng_bvs</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\036_BAPF8Ng_bvs_The_Greatest_Crypto_Trader_to_Ever_Live.md</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] A secret faceless crypto trader has been  gaining hundreds of thousands of followers [00:00:04] recently on X and he might be known for being  one of the best crypto traders of all time. [00:00:10] His name is GCRclassic. He started with just $1,200 [00:00:15] and is estimated to have tra</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>I Found A Secret To Fair Value Gaps</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZTMregh_428</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\037_ZTMregh_428_I_Found_A_Secret_To_Fair_Value_Gaps.md</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] The fair value gap. One of the biggest trends [00:00:02] going on in trading space right now. And there s a reason for that [00:00:05] Because of how well they work in the market. But not all fair value gaps are created equal. [00:00:11] For instance, this fair value  gap ended up not wor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>How I Avoid False Breakouts (New Technique)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Breakout / Fakeout</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9azX4PfaW3A</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\038_9azX4PfaW3A_How_I_Avoid_False_Breakouts_(New_Technique).md</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] Has this ever happened to you? You get this very classic chart [00:00:02] setup. Where price made a high, retracted back  down, and came back to test this high again. [00:00:08] You watch closely as the candle slowly  starts to come to this resistance point. [00:00:13] Tons of volume star</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>How To Start Trading Crypto As A Complete Beginner</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nnDhFKHQRjc</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\039_nnDhFKHQRjc_How_To_Start_Trading_Crypto_As_A_Complete_Beginner.md</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:03] Look I m sure you ve heard about it  I mean you clicked this video didn t ya? [00:00:07] The biggest bullrun of crypto is currently  happening and within the next few months [00:00:11] many coins could 10x, 100x, or even a 1000x. So if you invested just $1,000 and you find a gem [00:00:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>How I Find Altcoins BEFORE They Explode</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t5je_tY5CrI</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\040_t5je_tY5CrI_How_I_Find_Altcoins_BEFORE_They_Explode.md</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] How I Find Altcoins Before They Blow Up I found this altcoin called Render when it [00:00:02] was 57 cents After I found this altcoin, I entered and [00:00:06] shared the entry with my private Discord group. Today at the making of this video it is now [00:00:10] at $7.31. A TWO HUNDRED PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>How She Made MILLIONS Using The MACD</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mJqnG6-7kSs</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\041_mJqnG6-7kSs_How_She_Made_MILLIONS_Using_The_MACD.md</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This is Linda an absolute legend of trading. She s A professional trader who has worked [00:00:07] for several hedge funds and even  started her OWN hedge fund in 2002. [00:00:12] And did I mention she made all of her  millions trading using ONE specific strategy? [00:00:22] Well, I was i</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>You're Using The RSI WRONG...</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NT_qg2qPR1c</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\042_NT_qg2qPR1c_You're_Using_The_RSI_WRONG....md</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] The RSI Or, if you re fancy, the relative strength index. [00:00:04] The rsi is one of the most popular  trading indicators out there. [00:00:10] If you even have the slightest clue about  trading, you have heard about this indicator. [00:00:15] Books, websites, videos, there s tons of  i</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>This Indicator Predicts The Future</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BDaQhZ8wPbk</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\043_BDaQhZ8wPbk_This_Indicator_Predicts_The_Future.md</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This indicator predicts the  EXACT future of the chart [00:00:03] And its fn amazing. One day I was looking through the public [00:00:06] library of indicators on Tradingview for fun. Yeah, I search trading indicators for [00:00:11] fun. I have no life guys. But while I was doing this, [0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>I Found an UPGRADED Version of The Heiken Ashi</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=as2HK0ACjI8</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\044_as2HK0ACjI8_I_Found_an_UPGRADED_Version_of_The_Heiken_Ashi.md</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] You NEED to stop using the heiken ashi RIGHT NOW! [00:00:03] I found an indicator that is infinitely better than the heiken ashi. [00:00:06] The heiken ashi, is an indicator that a lot of traders use to find the general direction [00:00:10] of the market. Clearing out the noise of regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>The Trading Strategy That Made Him $82 Million</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gtTt_7E89TA</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\045_gtTt_7E89TA_The_Trading_Strategy_That_Made_Him_$82_Million.md</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[00:00:00] This secret strategy [00:00:01] made a day trader $82 million dollars Which he now uses for fast cars, multi million [00:00:07] dollar yachts, and luxurious mansions But what does this prestigious day [00:00:12] trader look like? This. This is him. [00:00:16] But don t let his looks fool </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>How I Made $70,536 Day Trading in 60 Days</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jOf-ahjQUH4</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\046_jOf-ahjQUH4_How_I_Made_$70,536_Day_Trading_in_60_Days.md</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I ve been using this secret trading strategy that I found a while back and it s made me [00:00:04] $70,000. You know how many chipotle burritos that is? [00:00:08] It s a lot. But the crazy thing is, I did all of this [00:00:11] in just the span of just 60 days. I know impressive right? [</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>The Trading Strategy That Made Him $153 Million</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jU2YQC7TC0k</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\047_jU2YQC7TC0k_The_Trading_Strategy_That_Made_Him_$153_Million.md</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:28] This is is Takeshi kotegawa Kote..a.ga..wa. [00:00:38] I think that s how you pronounce it. [00:00:40] He is one of the most famous intra day traders on the stock market who made millions of dollars [00:00:45] in the early 2000 s. [00:00:46] To be specific he traded from just $13,000 to 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Get PERFECT Entries Using Fibonacci Retracement</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Fibonacci OTE</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Rbas7vi_CS8</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\048_Rbas7vi_CS8_Get_PERFECT_Entries_Using_Fibonacci_Retracement.md</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This, is the FIBONNACI RETRACEMENT tool. Yeah, you probably have heard of it. [00:00:06] And unfortunately, most traders use the Fibonacci tool completely wrong. [00:00:10] I m going to show you how to use it correctly and give you an amazing strategy using it. [00:00:15] These strategies</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>The Strategy That Made Him $1.1 Million In 12 Months</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9JEmsSItdt4</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\049_9JEmsSItdt4_The_Strategy_That_Made_Him_$1.1_Million_In_12_Months.md</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This, is Larry Williams. A professional trader who turned $10,000 into [00:00:05] $1.1 million in just 12 months of trading. Which is 11,300%! [00:00:12] Now if you re like me, you re thinking, how did he do it? [00:00:20] Well I decided to look for the answer of that specific question. S</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>How To Start Trading Stocks As A Complete Beginner - Ep.4</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LALSCcgJCPc</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\050_LALSCcgJCPc_How_To_Start_Trading_Stocks_As_A_Complete_Beginner_-_Ep.4.md</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] I am proud to announce the greatest series to ever be on youtube. [00:00:07] Episode 4. You guys love this series. [00:00:09] So here we are, making episode 4. I know I know Im taking huge amounts of time [00:00:13] to upload these episodes. But don t they say good things take time or som</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>The ULTIMATE Supply &amp; Demand Guide (My Secrets)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Supply Demand &amp; OB</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fPSQ_NnmqWI</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\051_fPSQ_NnmqWI_The_ULTIMATE_Supply_&amp;_Demand_Guide_(My_Secrets).md</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] this is Supply and this is demand and [00:00:03] these are three insane tricks I'm going [00:00:05] to be sharing with you including this [00:00:07] trick that'll make your zones three [00:00:09] times more accurate supply and demand [00:00:11] one of the most important subjects to [00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>I Reveal My Reversal Strategy [AMAZING]</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4cT8WTyxhYY</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\052_4cT8WTyxhYY_I_Reveal_My_Reversal_Strategy_[AMAZING].md</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[00:00:00] reversals one of the best ways to trade [00:00:02] because you are sniping the exact point [00:00:05] of where price changes Direction meaning [00:00:07] if you trade the exact reversal point [00:00:09] you are not only getting insane RIS [00:00:11] reward ratios but you're also making a </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>How To Start Trading Stocks As A Complete Beginner - Ep.3</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1QZgFes-2oA</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\053_1QZgFes-2oA_How_To_Start_Trading_Stocks_As_A_Complete_Beginner_-_Ep.3.md</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This is. Holy sht, you guys did it. [00:00:10] You got episode 2, to 5,000 likes. Now I know, I know, it reached 5,000 likes [00:00:15] a couple weeks ago and you guys have been absolutely spamming me with comments to release [00:00:22] episode 3. Well, here it is. [00:00:34] Now, if ther</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>I Added Machine Learning To An Indicator</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O1QTi40BoC4</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\054_O1QTi40BoC4_I_Added_Machine_Learning_To_An_Indicator.md</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] This last week was one of the most  pivotal points in my trading career. [00:00:03] I finally took a leap of faith into  the magical world of machine learning. [00:00:11] As scary as it might sound, I truly  think this is where trading is heading. [00:00:15] Every day computers are gettin</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Genius Trading Advice For 15 Minutes Straight...</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gYzEtRqk3Mc</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\055_gYzEtRqk3Mc_Genius_Trading_Advice_For_15_Minutes_Straight....md</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[00:00:00] I wanted to see if I could scavenge the internet for interviews with professional traders. [00:00:05] Traders that actually make a living from trading. Not those tiktokers that say they fly to their [00:00:09] home office in a helicopter. Yeah, those guys. I hate those guys. [00:00:18] I </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>I Found an Upgraded Version of The MACD [INSANE]</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>334</v>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=auK8PGULXXw</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\056_auK8PGULXXw_I_Found_an_Upgraded_Version_of_The_MACD_[INSANE].md</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] the macd indicator an absolute Staple in [00:00:03] the trading World used by millions every [00:00:05] single day but if you've used the macd [00:00:07] before you'll notice it comes with a [00:00:10] slight flop you see the macd is great [00:00:12] when the market is trending it actuall</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>How To Start Trading Stocks As A Complete Beginner - Ep.2</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I9unIJnobQU</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\057_I9unIJnobQU_How_To_Start_Trading_Stocks_As_A_Complete_Beginner_-_Ep.2.md</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] Imagine you were a brand new trader. Fresh out the womb. And you wanted to learn how [00:00:03] to make money trading stocks just like the big boys. [00:00:08] But you wanted just one place, one video series, to learn absolutely everything. [00:00:14] No bulls. Just pure knowledge. A-Z, e</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>I Gave an Ai Bot $30,000 to Trade Stocks</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=P9iWPk7IW-M</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\058_P9iWPk7IW-M_I_Gave_an_Ai_Bot_$30,000_to_Trade_Stocks.md</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:21] On November 30th 2022 the world changed forever. Artificial intelligence or Ai became accessible [00:00:27] to the general public For free And this happened because of a little thing [00:00:32] called, chatgpt *chatgpt* montage. [00:00:34] Ai is  getting more and more powerful every singl</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Đã có Full Script</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>How To Start Trading Stocks As A Complete Beginner</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=i5OZQQWj5-I</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\059_i5OZQQWj5-I_How_To_Start_Trading_Stocks_As_A_Complete_Beginner.md</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>[00:00:00] In the world of stock trading, its so easy  to get overwhelmed and lost in the endless [00:00:04] abyss of information that s out there.  There s free ebooks, paid courses, and scammy [00:00:10] youtubers. and its extremely hard to decipher what  s good information and what s bad informat</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>How To Avoid Consolidating Markets (My Secret)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=StvsfMYSTrw</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\060_StvsfMYSTrw_How_To_Avoid_Consolidating_Markets_(My_Secret).md</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>How To Use The 2023 Market Crash To Get Rich</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iejtmtoCvq4</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\061_iejtmtoCvq4_How_To_Use_The_2023_Market_Crash_To_Get_Rich.md</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>I Created A FREE Indicator (It's Amazing)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tqlZN_xAydQ</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\062_tqlZN_xAydQ_I_Created_A_FREE_Indicator_(It's_Amazing).md</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Smart Money Concepts - The Blueprint To Trade Like Banks</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FNUeYlhbXkU</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\063_FNUeYlhbXkU_Smart_Money_Concepts_-_The_Blueprint_To_Trade_Like_Banks.md</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>What Do Hedge Funds Think of Technical Analysis?</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f19bfHpCths</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\064_f19bfHpCths_What_Do_Hedge_Funds_Think_of_Technical_Analysis.md</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>I Created An Indicator To Copy Hedge Funds</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qoKwgUTCwWQ</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\065_qoKwgUTCwWQ_I_Created_An_Indicator_To_Copy_Hedge_Funds.md</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>I Tested Divergences - Do They Actually Make Money?</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RolCMR0WH4k</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\066_RolCMR0WH4k_I_Tested_Divergences_-_Do_They_Actually_Make_Money.md</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>This Trading Mistake DESTROYS Trading Accounts</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bwgPf5A-Hh0</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\067_bwgPf5A-Hh0_This_Trading_Mistake_DESTROYS_Trading_Accounts.md</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>I Made A Breakout Probability Tool (ITS AMAZING)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Breakout / Fakeout</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A-oxG8MwDkw</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\068_A-oxG8MwDkw_I_Made_A_Breakout_Probability_Tool_(ITS_AMAZING).md</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>It's Coming...</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZPSLoK1gwFs</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\069_ZPSLoK1gwFs_It's_Coming....md</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>How I Would Learn To Day Trade (If I Could Start Over)</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Scalping &amp; Day Trading</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LJR8v7XKt6g</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\070_LJR8v7XKt6g_How_I_Would_Learn_To_Day_Trade_(If_I_Could_Start_Over).md</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>I Tested This Strategy And It Profited 1,040%</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lDxNPG0VPlI</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\071_lDxNPG0VPlI_I_Tested_This_Strategy_And_It_Profited_1,040%.md</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Triangle Trading Pattern Tips (My Secret Strategy)</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WAAy0YVxUEw</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\072_WAAy0YVxUEw_Triangle_Trading_Pattern_Tips_(My_Secret_Strategy).md</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>How To Get AMAZING Entries (My Secret Technique)</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IyrbbmKv3RE</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\073_IyrbbmKv3RE_How_To_Get_AMAZING_Entries_(My_Secret_Technique).md</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr"/>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>The Most Powerful Strategy I’ve Found Yet...</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c8QjxXAGxtw</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\074_c8QjxXAGxtw_The_Most_Powerful_Strategy_I’ve_Found_Yet....md</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr"/>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>I Created The World’s BEST Indicator (seriously)</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gVltpoP3HSY</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\075_gVltpoP3HSY_I_Created_The_World’s_BEST_Indicator_(seriously).md</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr"/>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>The Housing Market Bubble Just Popped</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_7c82-V5cnU</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\076__7c82-V5cnU_The_Housing_Market_Bubble_Just_Popped.md</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>How Hedge Funds Manipulate The Stock Market</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rrKJkkb_EHI</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\077_rrKJkkb_EHI_How_Hedge_Funds_Manipulate_The_Stock_Market.md</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Price Action Is Hard (Until You See This)</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fe2JO2e49P0</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\078_fe2JO2e49P0_Price_Action_Is_Hard_(Until_You_See_This).md</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>I Found The 4 BEST Confirmation Indicators</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8TqdpJD5WPQ</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\079_8TqdpJD5WPQ_I_Found_The_4_BEST_Confirmation_Indicators.md</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Secret Formula For Drawing Support &amp; Resistances</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9NbmBDUysOA</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\080_9NbmBDUysOA_Secret_Formula_For_Drawing_Support_&amp;_Resistances.md</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr"/>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>How To Double Your Account Size Within 30 Days</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aFC7uTJrQdc</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\081_aFC7uTJrQdc_How_To_Double_Your_Account_Size_Within_30_Days.md</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>I Tested A CRAZY RSI Scalping Strategy 100 Times</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cxZOD1iOKVc</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\082_cxZOD1iOKVc_I_Tested_A_CRAZY_RSI_Scalping_Strategy_100_Times.md</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr"/>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>If Your Chart Does This... BUY</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sfkF5bKVl28</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\083_sfkF5bKVl28_If_Your_Chart_Does_This..._BUY.md</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr"/>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>I Tested The MACD - Does It Actually Make Money?</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1pklphKzE7A</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\084_1pklphKzE7A_I_Tested_The_MACD_-_Does_It_Actually_Make_Money.md</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr"/>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>How To Retire A Millionaire On A Low Salary</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=__GgylTdKmA</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\085___GgylTdKmA_How_To_Retire_A_Millionaire_On_A_Low_Salary.md</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr"/>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>10 EPIC Hidden Gems on TradingView</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hQ4M1rib9HY</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\086_hQ4M1rib9HY_10_EPIC_Hidden_Gems_on_TradingView.md</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr"/>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>The #1 Trading Indicator on TradingView</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v6OxMgYptFs</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\087_v6OxMgYptFs_The_#1_Trading_Indicator_on_TradingView.md</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr"/>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>How To Find Stocks To Day Trade</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Scalping &amp; Day Trading</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Wk-h2CwEH5k</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\088_Wk-h2CwEH5k_How_To_Find_Stocks_To_Day_Trade.md</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Top 5 FREE Trading Tools for Beginner Traders 2024</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=e7vzK-fEQks</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\089_e7vzK-fEQks_Top_5_FREE_Trading_Tools_for_Beginner_Traders_2024.md</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>How To Read Level 2 Market Data</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vhOCI2eXP8E</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\090_vhOCI2eXP8E_How_To_Read_Level_2_Market_Data.md</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr"/>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Charlie Munger: Why Diversification is For Idiots</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zZT9OLwR2Z0</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\091_zZT9OLwR2Z0_Charlie_Munger_Why_Diversification_is_For_Idiots.md</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr"/>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Warren Buffet: How To Invest in 2022</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fIAEwjoCyDg</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\092_fIAEwjoCyDg_Warren_Buffet_How_To_Invest_in_2022.md</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>How to Tell If a Stock Is UNDERVALUED or OVERVALUED</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d9brQ4uTYxY</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\093_d9brQ4uTYxY_How_to_Tell_If_a_Stock_Is_UNDERVALUED_or_OVERVALUED.md</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr"/>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>The 6 Biggest Trading Mistakes You're Probably Making</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_T7-bzowp7k</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\094__T7-bzowp7k_The_6_Biggest_Trading_Mistakes_You're_Probably_Making.md</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr"/>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>The ONLY Candlestick Pattern Guide You'll EVER NEED</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tW13N4Hll88</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\095_tW13N4Hll88_The_ONLY_Candlestick_Pattern_Guide_You'll_EVER_NEED.md</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Best Finviz Screener Settings [Find Stocks Before They EXPLODE]</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CJoN7wLfWNo</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\096_CJoN7wLfWNo_Best_Finviz_Screener_Settings_[Find_Stocks_Before_They_EXPLO.md</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr"/>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>The ULTIMATE Fibonacci Retracement Tool Guide - Best Tips &amp; Tricks</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Fibonacci OTE</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iL76k2A9ono</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\097_iL76k2A9ono_The_ULTIMATE_Fibonacci_Retracement_Tool_Guide_-_Best_Tips_&amp;_.md</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr"/>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>How To Know Where to Set Your Stop Loss</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=txXUUeMDos8</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\098_txXUUeMDos8_How_To_Know_Where_to_Set_Your_Stop_Loss.md</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr"/>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Highly Profitable DEMA + SuperTrend Trading Strategy</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g-PLctW8aU0</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\099_g-PLctW8aU0_Highly_Profitable_DEMA_+_SuperTrend_Trading_Strategy.md</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr"/>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>How to Backtest a Trading Strategy on Tradingview</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OwvElpGjLKI</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\100_OwvElpGjLKI_How_to_Backtest_a_Trading_Strategy_on_Tradingview.md</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr"/>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>How To Grow A Small Stock Account</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5nPRbWwxPUQ</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\101_5nPRbWwxPUQ_How_To_Grow_A_Small_Stock_Account.md</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr"/>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>BEST Scalping Trading Strategy For Beginners (How To Scalp Forex, Stocks, and Crypto)</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Scalping &amp; Day Trading</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XBcMiYK7qYY</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\102_XBcMiYK7qYY_BEST_Scalping_Trading_Strategy_For_Beginners_(How_To_Scalp_F.md</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr"/>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>How to Avoid False Breakouts (My Secret Technique)</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Breakout / Fakeout</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZudTPpJCbbA</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\103_ZudTPpJCbbA_How_to_Avoid_False_Breakouts_(My_Secret_Technique).md</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr"/>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>How To Identify Trends in Markets (Never Guess Again)</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=21b5QF-b0rE</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\104_21b5QF-b0rE_How_To_Identify_Trends_in_Markets_(Never_Guess_Again).md</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr"/>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Four Price Action Secrets (The Ultimate Guide To Price Action)</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0L6Rcgp6j7Y</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\105_0L6Rcgp6j7Y_Four_Price_Action_Secrets_(The_Ultimate_Guide_To_Price_Actio.md</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr"/>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>The Heikin Ashi Trading Strategy (Simple &amp; Effective)</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Price Action</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2G78zkuQSc0</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\106_2G78zkuQSc0_The_Heikin_Ashi_Trading_Strategy_(Simple_&amp;_Effective).md</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr"/>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>EASY Scalping Strategy For Day Trading (High Win Rate Strategy)</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Scalping &amp; Day Trading</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bKPs2aOsvsk</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\107_bKPs2aOsvsk_EASY_Scalping_Strategy_For_Day_Trading_(High_Win_Rate_Strate.md</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr"/>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Bollinger Band + RSI Trading Strategy That Actually Works</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pCmJ8wsAS_w</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\108_pCmJ8wsAS_w_Bollinger_Band_+_RSI_Trading_Strategy_That_Actually_Works.md</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Không có phụ đề</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr"/>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>BEST MACD Trading Strategy [86% Win Rate]</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ báo kỹ thuật</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rf_EQvubKlk</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>tradinglab_transcripts\109_rf_EQvubKlk_BEST_MACD_Trading_Strategy_[86%_Win_Rate].md</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/research/MASTER_VIDEO_DATABASE.xlsx
+++ b/docs/research/MASTER_VIDEO_DATABASE.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,20 +562,70 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yin tập trade</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cách nhận biết giá sideway đang tạo đáy hay phân phối. #trading #trad...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cách nhận biết giá sideway đang tạo đáy hay phân phối. #trading #trader #kienthuckinhte #smc</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Nhiều đại vợ Cảm ơn các bạn đã đón xem video này, hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Cảm ơn các bạn đã đón xem video này, hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Cảm ơn các bạn đã đón xem video này, hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Cảm ơn các bạn đã đón xem video này, hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Cảm ơn các bạn đã đón xem video này, hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1:15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yin.tp.trade/video/7694660547685551380</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>TradingLab</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>How to Avoid False Breakouts (Avoid The Trap)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Quy tắc Phân biệt Fakeout vs Breakout &amp; Bộ lọc Fibonacci Golden Zone:
 1. Fakeout (Phá vỡ giả): Nến chỉ quét râu (wick) qua đỉnh/đáy rồi đóng nến ngược lại bên trong -&gt; Tín hiệu từ chối giá và gom thanh khoản.
@@ -588,7 +638,7 @@
    - Bước 4: Chờ giá hồi về Golden Zone (0.618 - 0.79) mới kích hoạt Buy. SL đặt dưới đáy Fakeout, TP tại đỉnh Breakout. R:R cực cao.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>What if I told you false breakouts are
 one of the most common ways traders lose
@@ -805,47 +855,47 @@
 inside my Telegram. See you in there.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=2yePksvT64I</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>TradingLab</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>You're Using Liquidity Wrong</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Quy tắc phân biệt Vùng Cản Thật (Real Zone) và Vùng Mồi Nhử (Inducement Zone):
 1. Vùng B (Inducement): Là đỉnh hồi đầu tiên (minor high/low) sau cú phá vỡ. Nếu phía trên Vùng B còn khoảng trống Imbalance (FVG) chưa lấp, Vùng B 100% là bẫy mồi nhử thanh khoản -&gt; CẤM vào lệnh tại B.
@@ -855,7 +905,7 @@
 5. SL: Đặt trên đỉnh Vùng A. TP: Vùng Demand/Supply đối diện. Tỷ lệ R:R tối ưu đạt 1:5+.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>[00:00:00] Is this liquidity? Is this liquidity? Is
 [00:00:02] this liquidity? Or is this liquidity? If
@@ -1063,52 +1113,52 @@
 [00:07:45] works for you. See you next time.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>7:50</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=RKU7D9PxLgY</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Wysetrade</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ULTIMATE Supertrend Indicator Trading Strategy (FREE FULL COURSE)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Khóa học chiến lược Supertrend toàn diện: 1. Tham số chuẩn Factor 2.5 - 3.0 (ATR 10). 2. Không trade tín hiệu đảo chiều độc lập (tránh whipsaw). 3. Quy tắc hợp lưu: Supertrend định hướng Bias + Price Action/Key Levels kích hoạt Entry. 4. Chiến lược Dynamic Trailing Stoploss theo dải Supertrend bắt trọn sóng dài. 5. Bộ lọc đa khung thời gian (HTF Trend Filter).</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>[00:00:00] One of the most effective trading tools
 [00:00:02] is the super trend indicator, but you'd
@@ -1426,52 +1476,52 @@
 [00:12:08] change. Two, you had this key sup</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>17:02</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=As6Sr3OzhzE</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>TRADING RUSH</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>How I Increased Win Rate In Trading (WITH PROOF)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>5 Quy tắc tăng Win Rate dựa trên dữ liệu thực nghiệm: 1. Tỷ lệ R:R tối ưu 1.5:1 (Sweet Spot). 2. Đặt TP dưới Swing High khi pullback sâu. 3. Mua sát đáy Support và chốt sớm khi vừa thoát vùng cản. 4. Hạ R:R khi thị trường xấu để bảo vệ vốn. 5. Kiên nhẫn đứng ngoài khi không có setup.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>[00:00:01] when I started trading around 8 years
 [00:00:03] ago I saw many people giving advice on
@@ -1681,52 +1731,52 @@
 [00:07:42] [Music]</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>7:44</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=IpSlHWMGgY4</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>The Trading Channel</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>The Only Price Action Trading Video You Will Ever Need (Full Course)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Khóa học Price Action toàn diện: Xác định cấu trúc thị trường (Market Structure), các vùng Hỗ trợ/Kháng cự chính (Major Support &amp; Resistance), đường Xu hướng (Trendlines), các mô hình nến kích hoạt lệnh (Engulfing, Pin bar) và cách đo lường tỷ lệ R:R tối thiểu 1:2.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>**`[00:00:00]`** this video currently has over 21 million this video currently has over 21 million views on YouTube and the reason so many views on YouTube and the reason so many views on YouTube and the reason so many Traders found that video valuable is Traders found that video valuable is Traders found that video valuable is because I poured a ton of time and because I poured a ton of time and because I poured a ton of time and effort to ensure that by the end of that.
 **`[00:00:12]`** effort to ensure that by the end of that effort to ensure that by the end of that video Traders knew everything they video Traders knew everything they video Traders knew everything they needed to know about technical analysis needed to know about technical analysis needed to know about technical analysis in this video I'm doing the same exact in this video I'm doing the same exact in this video I'm doing the same exact thing for Price action so throughout the.
@@ -1762,52 +1812,52 @@
 **`[00:04:47]`** this Market to be in an uptrend and this this Market to be in an uptrend and this process just continues as we go higher process just continues as we go higher process just continues as we go higher this move here we go from the low of our this move here we go from the low of our this move here we go from the low of our pullback we break and close above that pullback we break and close a</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>47:16</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=td5TjsqDCKw</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>🔴 ƯU TIÊN 2 (Mới thêm - Khóa học 2.5h)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Jason Graystone</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Trading for Beginners Part 1 - FULL TRADING COURSE TUTORIAL</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Khóa học Trading cơ bản đến nâng cao 2.5 giờ: Bản chất thị trường tài chính, quản lý rủi ro và vốn (Risk Management 1%), toán học xác suất trong trading, xây dựng kế hoạch giao dịch (Trading Plan), tâm lý kỷ luật và nhật ký giao dịch.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>**`[00:00:00]`** all right welcome to the video this is all right welcome to the video this is trading for beginners or trading for trading for beginners or trading for trading for beginners or trading for dummies as the thumbnail says and the dummies as the thumbnail says and the dummies as the thumbnail says and the goal of this video is to get you from goal of this video is to get you from goal of this video is to get you from struggling or zero profits or complete.
 **`[00:00:10]`** struggling or zero profits or complete struggling or zero profits or complete beginner right through to consistently beginner right through to consistently beginner right through to consistently profitable Trader which means it's a profitable Trader which means it's a profitable Trader which means it's a comp like complete and comprehensive comp like complete and comprehensive comp like complete and comprehensive program all in itself which means it's.
@@ -1843,52 +1893,52 @@
 **`[00:04:16]`** question of what's the real deal and not question of what's the real deal and not only that you'll learn so much in this only that you'll learn so much in this only that you'll learn so much in this lesson that you won't need to go and lesson that yo</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2:26:39</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=_YVQN6_nkfs</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>🔴 ƯU TIÊN 1 (Mới thêm - Xem ngay)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Rayner Teo</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>The Ultimate Candlestick Patterns Trading Course (Khóa Học Nến Toàn Diện)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Hệ thống T.A.E Framework (Trend - Area of Value - Entry Trigger), kỹ thuật gộp nến đa khung (2 nến 1h = 1 nến Pin bar 2h), mô hình nến Engulfing, Hammer, Shooting Star, Morning/Evening Star, Tweezer. Quy tắc không trade nến độc lập mà phải tại cản/MA động.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t># TOÀN BỘ SCRIPT (LỜI THOẠI) KHÓA HỌC: THE ULTIMATE CANDLESTICK PATTERNS TRADING COURSE
 - **Kênh YouTube:** [Rayner Teo (@tradingwithrayner)](https://www.youtube.com/@tradingwithrayner)
@@ -1953,64 +2003,14 @@
 **`[00:11:47]`** did close higher above the first so if you look at it this second candle over here it it closed higher above this one over here so that's why you got a bullish bullish close okay and similar for this right this candle it closed right but it didn't exceed the open of this candle so that's why it's still red on the two hour ti</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>38:10</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=C3KRwfj9F8Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Vnrebates</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Khám Phá Setup Giao Dịch Của Trader Nhận Payout 2 Triệu USD</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Đây là xét óp giúp Trader Can Pay Out gần 2 triệu đô từ ProfFirm. Chị tôi vai! Lấy giây bút ra ghi nè. Đầu tiên, chờ phiền Á kết thúc, đánh giấu đỉnh và đáy phiền Á. Kích theo, chờ 1 trong 2 vị trí này bị quét. Ở đây, đáy phiền Á đã bị quét. Vào khung M1, chờ phiền Âu mở cửa. Sau khi phiền Âu bắt đầu, giá đóng cửa tạo CISD. Vào lạnh mùa, Stop Loss dứa đáy vừa quét, thê pe ở đỉnh phiền Á. Nhưng nhớ quản lý lạnh, chốt 1 nữa ở đỉnh củ. Ông đã thử xét óp phiền Á này chưa? Comment cho tôi biết nhé!</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1m - 11m</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7696474697961196808</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thế Nào Là Một Khối Order Block (OB) Chất Lượng</t>
+          <t>Khám Phá Setup Giao Dịch Của Trader Nhận Payout 2 Triệu USD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Giả chạp OrderBlock rồi, mua được chưa ông? Thử đi! Sao kỳ với ta? Để tôi chỉ ông cách chọn ra OrderBlock chất lượng, sẽ cần những yếu tố gì. 1. OrderBlock đó phải tạo ra phá vỡ câu trúc BRS. 2. Theo sau OrderBlock, phải có 1 app Vega. 3. OrderBlock nằm ở vùng premium cho lệnh bán hoặc discount cho lệnh mua. Ở đây, OrderBlock giảm nằm ở premium. 4. Có quét thanh khoảng trước khi giá hồi về OrderBlock. Chỉ vào lệnh khi OrderBlock có ít nhất 3 trên 4 yếu tố. Vào lệnh bán tại OrderBlock, stoplock trên đỉnh OrderBlock RR12. Anh chọp TP luôn! Ông có chọn OrderBlock theo 4 yếu tố này chưa? Comment cho tôi biết nhé!</t>
+          <t>Đây là xét óp giúp Trader Can Pay Out gần 2 triệu đô từ ProfFirm. Chị tôi vai! Lấy giây bút ra ghi nè. Đầu tiên, chờ phiền Á kết thúc, đánh giấu đỉnh và đáy phiền Á. Kích theo, chờ 1 trong 2 vị trí này bị quét. Ở đây, đáy phiền Á đã bị quét. Vào khung M1, chờ phiền Âu mở cửa. Sau khi phiền Âu bắt đầu, giá đóng cửa tạo CISD. Vào lạnh mùa, Stop Loss dứa đáy vừa quét, thê pe ở đỉnh phiền Á. Nhưng nhớ quản lý lạnh, chốt 1 nữa ở đỉnh củ. Ông đã thử xét óp phiền Á này chưa? Comment cho tôi biết nhé!</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7696091260565769490</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7696474697961196808</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fibonacci OTE Trong Forex: Cách Chọn Điểm Vào Lệnh An Toàn</t>
+          <t>Thế Nào Là Một Khối Order Block (OB) Chất Lượng</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Gia phá đỉnh rồi quay về tét đỉnh con nén en-gu-fing mua thôi! Quang, nếu mua ở đây mà đặt stop-loss ngay dưới vùng đỉnh cũ thì rất không an toàn. Còn nếu đặt stop-loss dưới đấy thì rơ rơ lại rất thấp. Xem nè! Trời ơi, dính stop-loss rồi! Vậy phải làm sao hả ông? Bấu chốt là chúng ta phải tìm được điểm entry có stop-loss an toàn và rơ rơ tốt. Dùng Fibo OTE, kéo từ đáy lên đỉnh theo sưu hướng tăng. Lúc này, ông thấy vùng OTE từ 0.705 đến 0.79 trùng với FVG. Entry ở đây, stop-loss dưới đấy vẫn an toàn mà rơ rơ tốt hơn nhiều. Ông đã biết dùng OTE kết hợp FVG chưa? Comment cho tôi biết nhé!</t>
+          <t>Giả chạp OrderBlock rồi, mua được chưa ông? Thử đi! Sao kỳ với ta? Để tôi chỉ ông cách chọn ra OrderBlock chất lượng, sẽ cần những yếu tố gì. 1. OrderBlock đó phải tạo ra phá vỡ câu trúc BRS. 2. Theo sau OrderBlock, phải có 1 app Vega. 3. OrderBlock nằm ở vùng premium cho lệnh bán hoặc discount cho lệnh mua. Ở đây, OrderBlock giảm nằm ở premium. 4. Có quét thanh khoảng trước khi giá hồi về OrderBlock. Chỉ vào lệnh khi OrderBlock có ít nhất 3 trên 4 yếu tố. Vào lệnh bán tại OrderBlock, stoplock trên đỉnh OrderBlock RR12. Anh chọp TP luôn! Ông có chọn OrderBlock theo 4 yếu tố này chưa? Comment cho tôi biết nhé!</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7695729577947155720</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7696091260565769490</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Toàn Diện Về Fair Value Gap (FVG)</t>
+          <t>Fibonacci OTE Trong Forex: Cách Chọn Điểm Vào Lệnh An Toàn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hôm nay sẽ là 1 video khá là dài Mình sẽ hướng dẫn cho anh em những cái thứ chi tiết và thật chiến nhất về FVG, 1 công cụ cực kìa bánh mẽ trong phương pháp ICT Đầu tiên FVG sẽ được chia hình 4 loại hả? Dạy đầu tiên mà chúng ta sẽ học, đó chính là FVG Breakaway Nó sẽ được hình thành từ 3 cái nến tăng liên tiếp với anh em Và nó sẽ là dạy mở rộng Thì khi anh em thấy xuất hiện 3 cái nến tăng liên tiếp Hình thành 1 cái FVG Nó báo hiệu 1 cái động lực tăng mạnh của thị trường Và khả năng cái nha, khả năng cao Những cái FVG Breakaway này á Đến 80% giá nó sẽ tăng tiếp tục Và nó không quay về test cái FVG Thói chúng ta sẽ xem bí dụ mà Ở đây chúng ta có Cây nến khung H1 Anh em thấy không? Đây là 3 cây nến tăng liên tiếp Và nó tạo ra 1 cái buồn FVG ở đây Đúng không? Thì anh em quay xác anh em thấy được đỏ ràng là Giá đó không có test về cái FVG này Ở đây cũng có rất nhiều trường hợp như vậy hả? Này nè mình Khi nó tạo ra 1 cái FVG Breakaway á Ở đây nè Anh em thấy không? Thì giá nó liên tiếp tục tăng lên, tăng lên, tăng lên Cho đến ngày hôm sau nó mới quay về test Mà khi mà nó đi xa như vậy nó quay về test Thì nó không còn mạnh nữa Những FVG được tạo ra thì chúng ta sẽ muốn nó phải test liền Thì khi anh em thấy FVG Breakaway như thế này nè Thì anh em sẽ phải vào trong khung M5 Để anh em tìm kiếm những lệnh tiếp diễn Ok, mình sẽ vào trong khung M5 Mình vào trong khung M5 nè Rồi, mình sẽ tui vào chỗ này Thì trong khung M5 nó lại tiếp tục tạo ra 1 cái FVG Đúng không? Ở đây Thì bây giờ anh em có thể follow hell cái FVG mở năm này rồi Tại vì khi mà nó tạo ra FVG Breakaway ở khung H1 Thì trong khung M5 nó cũng sẽ tạo 1 cái động lực tăng Và lúc này anh em chỉ cần mua ở cái FVG trong khung M5 là được Rồi chúng ta cùng xem giá chạy ha Giá quay về test cái FVG trong khung M5 nè Mà tăng lên Đó chính là cách mà chúng ta sẽ giao dịch với FVG Breakaway Tiếp tục mình sẽ đến với 1 cái FVG bình thường Đó là 1 cái FVG có 2 cái nến tăng và 1 cái nến giảm như thế này Nó không phải là dẹn mở rộng anh em ha Thì với cái FVG dẹn này Giá nó có khả năng test lại cái FVG Sau đó mới tăng ha Thì chúng ta sẽ cùng vào trong cái bí dụ của EU dưới đây Thì bí bí EU này sẽ khá ngược lại là sẽ gồm là 2 cái nến giảm và 1 cái nến tăng Thì nó là FVG dẹn thường nhưng mà nằm trong xuống giảm anh em ha Thì chúng ta cũng có 1 cái FVG chỗ này Mình sẽ đặt lên nó là FVG H1 đi Cho anh em dễ quay xác rồi Rồi bây giờ mình sẽ vào trong khung M5 Tại vì đây là FVG dẹn thường, không phải là dẹn Breakaway Thì giá có khả năng sẽ test lại ha Vào trong khung M5 Rồi mình chờ test lại cái FVG này Rồi thì khi nó test lại cái FVG này rồi Nhưng mà M5 vẫn đang là 1 cái xuống dẹn này, 1 xuống tăng ha Thì mình sẽ chờ nó phá vào cái đáy này Rồi thì khi nó phá vào cái đáy này Nó hình thành cho mình 1 cái FVG Mở 5 ở đây, đúng chưa? Mình sẽ NG ở cái FVG mở 5 này Đặt stop-lock ở trên đây Và đặt cái mức tê bê là 2R 2R này mà Cùng sẽ nhá nó chạy ha Giá test lại cái FVG này Và sạch xuống, đó chính là cách chúng ta ứng dụng FVG bình thường ha Rồi tiếp tục 1 vàng FVG nữa Đó là EFVG Cũng tương tự như thế này, chúng ta có 1 cái FVG tăng đúng không? Đây Và nếu như cái FVG tăng này Nó bị phá bởi 1 cái nến Thay là nhiều cái nến nhứng chìm ha Nó chung là nhứng chìm cái FVG Như thế này Đó Nhứng chìm ha Thì cái FVG này Nó sẽ không còn là FVG nữa Nhưng mà nó sẽ là EFVG Nó sẽ trành EFVG Thì với EFVG, nghĩa là 1 cái FVG bị nhứng chìm Chúng ta sẽ chờ nó test lại và xeo xuống Hoặc là nếu như nó tạo 3 cái nến giảm Mà 1 cái nến tăng nhứng chìm thì chúng ta sẽ bài lên ha Tương tự chúng ta có 1 cái bí vụ ở đây Thử này ha Đây là 3 cái nến giảm đúng chưa? 3 cái nến giảm 1, 2, 3 Nó tạo chúng ta 1 cái FVG Đúng không? Và cái FVG này đã bị nhứng chìm Bởi cái nến tăng này Thì chỗ này nó sẽ trở thành EFVG Rồi cái nhiệm vụ chúng ta chỉ là vì 3 lại khi giá test cái EFVG Đã X lời dưới đây và tề bên trên Rồi cùng xem giá chạy đẹp Giá test lại cái EFVG và Tiếp tục tăng lên Đó là cách xài EFVG ha Rồi 1 dạng FVG nữa Đó là B rồi B B được đựng dễ như thế nào Nếu dư Mình sẽ kéo 3 cái nến giảm Chưa có 3 cái nữa này đi Thì chúng ta sẽ có 1 cái FVG tăng đúng không? Nhưng nếu như cái FVG tăng này Bị nhứng chìm bởi 1 cái FVG giảm đối diện Đây, trái hẹn như thế này là 1 cái 3 cái nến giảm đúng không? 3 cái nến giảm này tạo 1 cái FVG đối diện ở đây Đúng chưa? Đó Thì đây gọi là B rồi B Hay gọi là Subton ha Đây là cái dạng mạnh nha ném Dạng mạnh của FVG đảo chiều Tại vì khi mà Nên nó biết là khi mà giá tạo 1 FVG Chứng đó động lực tăng nó rất là mạnh đúng không? Nhưng mà nó lại bị nhứng chìm Bởi 1 cái động lực giảm Chứng tạo là tại cái vị trí này nha Là cái bên bán nó nhảy vào rất mạnh Thì anh em sẽ canh nó test lại cái FVG này Để anh em bán xuống ha Đó chính là Subton Thì gọi là B rồi B Rồi chúng ta sẽ cùng nhau Nhìn vào cái ví dụ con HU với đây Đây Sau khi giá nó sang ra hành khoảng cái đỉnh bên đây Nè em thấy không? Này nó sang hành khoảng cái đỉnh nè Mình sẽ tua lại ha Nó sang hành khoảng cái đỉnh xong Nó tạo chúng ta 1 cái FVG Đúng chưa? FVG Rồi Và FVG này bị diễn em Bị nhứng chìm bởi cái FVG đối diện Chính là cái FVG này Đúng không? Này FVG tăng bị nhứng chìm bởi FVG giảm Sau đó nó test lại bằng cái nánh này Đây cái nánh này Khi nó tạo được cái FVG giảm nhứng chìm rồi Thì chúng ta tham cú Subton rồi Thì anh em sẽ đặt 1 cái lệnh cell Ngay tại cái FVG giảm được tạo ra X lời đặt trên đây Và TB TB về đáy gần nhất Chính là vị trí này Rồi cùng xem giá chạy ha Giá test lại Và sắp mạnh xuống ha Đó chính là Subton Bây giờ mình nói là khi sẽ là Subton Giá đi rất là mạnh đúng không? Nó sắp rất là mạnh ha Rồi tiếp tục Chúng ta đến với cái FVG Cuối cùng Cái FVG này không dùng để vào lệnh Mà FVG này dùng để làm gì anh em? Dùng để làm đến TB Làm đến TB ha Hay còn gọi là ReFVG ReFVG Nghĩa là sao? Nghĩa là Đây là cái điểm mà anh em sẽ chốt lời Cái điểm này sẽ chốt lời Nếu như anh em có lệnh mua Thì nếu như anh em có 1 cái lệnh mua ở đây Mình giả sử ở đây là 1 case FVG Đúng không? Anh em mua ở đây Anh em phải tới bệp đầu Tên bệp đầu thì đương nhiên là chúng ta sẽ Nhìn những cái cản rồi Thì ở đây có 1 cái FVG đói diện nữa nào Đúng không? Một cái FVG nó diễn nữa Thì nếu như anh em mua ở đây Anh em có thể TB ở đây Và nếu như nó lụng ở đây Thì nó sẽ lên đầu Nó sẽ tìm kiếm ở đâu tiếp Nó sẽ tìm kiếm cái FVG trên đây Thì cái FVG này cũng gọi là ReFVG luôn Và cái FVG này cũng gọi là ReFVG Cả hai cái này đều là ReFVG ha Tao cùng xem giá nó chạy tiếp Nó thì khi giá nó Nó lại tiếp tục Test về cái FVG này Đúng không? Đó tiện em có thể mua ha Có thể mua lên từ đây Rồi giá nó tiếp tục tăng lên thôi Rồi thì TB của này sẽ lâu TB này sẽ là cái ReFVG này Ở chỗ này nó cũng sẽ có 1 cái FVG nào Anh em cũng có thể mua ở cái FVG này Hét lờ dưới đây Và TB cũng về cái ReFVG luôn Hai lần chúng ta được TB về cái ReFVG này Và nếu em kia giá nó chạm đến cái ReFVG này ha Nó sẽ có phản ứng mạnh Mình không biết là nó có xuyên được cái FVG này không Hay là từ cái ReFVG này nó sẽ đảo chiều Nhưng đây là cái điểm TB đẹp nhất Đó thì đây là cái ứng dụng của ReFVG ha Rồi thì trong video hôm nay mình đã chia sẻ cho anh em Hết tất cả những các loại ReFVG có trên thị trường Hầu tiên là ReqAway ReFVG ReFVG bình thường ReFVG BW Và ReFVG Đó là những loại ReFVG mà anh em cần biết Để có thể áp dụng nó vào trong cái quá trình trái đình của mình ha Ok cám ơn em đã theo dõi video này Và nếu anh em thấy hay Các bạn có thể lưu video và bấm vào cái link bio Để tiếp cận những phương pháp trái đình hiệu quả nhất ha Ok cám ơn em đã theo dõi video</t>
+          <t>Gia phá đỉnh rồi quay về tét đỉnh con nén en-gu-fing mua thôi! Quang, nếu mua ở đây mà đặt stop-loss ngay dưới vùng đỉnh cũ thì rất không an toàn. Còn nếu đặt stop-loss dưới đấy thì rơ rơ lại rất thấp. Xem nè! Trời ơi, dính stop-loss rồi! Vậy phải làm sao hả ông? Bấu chốt là chúng ta phải tìm được điểm entry có stop-loss an toàn và rơ rơ tốt. Dùng Fibo OTE, kéo từ đáy lên đỉnh theo sưu hướng tăng. Lúc này, ông thấy vùng OTE từ 0.705 đến 0.79 trùng với FVG. Entry ở đây, stop-loss dưới đấy vẫn an toàn mà rơ rơ tốt hơn nhiều. Ông đã biết dùng OTE kết hợp FVG chưa? Comment cho tôi biết nhé!</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7474060511584324885</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7695729577947155720</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xác Định Thanh Khoản Thị Trường (Liquidity ICT)</t>
+          <t>Hướng Dẫn Toàn Diện Về Fair Value Gap (FVG)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ICT đã từng nói, tị trường chỉ làm có 2 việc thôi Thứ nhất là quay thanh khỏe và thứ 2 là lắp này các FVG Điều này có nghĩa là nếu như anh em vào một cái lệnh nào đó mà anh em chưa tìm nấy thanh khỏe thì rất có thể anh em sẽ trở thành thanh khỏe ICT là một trader với quan điểm dâu dịch là tị trường luôn luôn tìm thanh khỏe trước khi có những bước đi tiếp theo Thì sau khi tham khảo vào cái tư duy của ICT thì mình đã rút ra được một số các bài học và hôm nay mình sẽ chia sẻ anh em để có thể tăng thêm một cái tự lời hắn của mình Ok, nè Ma, thì anh em nhìn 2 cái bí vụ với đây thì anh em thấy khi giá nó phải hướng tới một cái buồn giá nào đó thì sẽ có 2 trường hợp xảy ra đúng không? Một là giá chạm đứng cái buồn này và tăng lên Nếu anh em ba này sẽ thắng Còn hai, nó chạm buồn này nhưng mà nó không tăng mà nó xuyên luôn thì anh em sẽ thua Anh em nghĩ là chỉ có 2 trường hợp thôi hả? Còn 1 trường hợp nữa đó là giá nó vét đáy xong nó mới thanh Đó Vậy thì nếu như anh em chọn 1 cái chờ về đây anh em ba lên thì anh em có tới 2 trường hợp mà anh em có thể thua được và là cái này và cái này Vậy thì thông bình hơn nó sẽ chờ cái gì? Ta sẽ chờ giá nó vét xong rồi chúng ta mới bầu lệnh thì lúc đó anh em có thể loại được bớt thêm 1 trường hợp thua nữa thì cái thể thắng nó sẽ tăng lên đúng không? Rồi bây giờ nó sẽ cùng nhau nhìn vào cái trạng này Đây là 1 cái cấu chút tăng đúng rồi anh em, chút tăng này thì có nhiều nên sẽ canh 3 cái giá qua bên bùn đáy này Thì khi giá trạm bùn đáy này nó sức hiểm cơ nến bin ba đứt rau thì là phần anh em sẽ vào buồn ở đây x lờ dưới cái đáy này và bề bề thì chúng ta cùng xem giá nó đi như thế nào hả? Mới vụng ta 1 vài trành bị x lờ sau đó nó mới tăng lên thì mình sẽ vào lệnh khi này bị béc rồi và tiếp tục tăng lên nè sau khi béc xong anh em phải tăng lên nó đóng đến qua cái nến này thì lúc này đây chỉ là 1 cái phá bởi giả thôi nè thì chúng ta mới bắt đầu vào lệnh mua vị trí này đạt sublots như đây và tb lên trần cùng xem giá nó chạy hả? Sau khi được bấy đựng sublots rồi thì giá nó đi rất là nhanh và đạt được tb đó là cách để thông minh nhớ nè chờ giá quá thân ngoại thông chúng ta mới vào chúng ta sẽ có tự lệnh hắn cao hơn ok nè mà lô video lại để xem kì cứng thiết</t>
+          <t>Hôm nay sẽ là 1 video khá là dài Mình sẽ hướng dẫn cho anh em những cái thứ chi tiết và thật chiến nhất về FVG, 1 công cụ cực kìa bánh mẽ trong phương pháp ICT Đầu tiên FVG sẽ được chia hình 4 loại hả? Dạy đầu tiên mà chúng ta sẽ học, đó chính là FVG Breakaway Nó sẽ được hình thành từ 3 cái nến tăng liên tiếp với anh em Và nó sẽ là dạy mở rộng Thì khi anh em thấy xuất hiện 3 cái nến tăng liên tiếp Hình thành 1 cái FVG Nó báo hiệu 1 cái động lực tăng mạnh của thị trường Và khả năng cái nha, khả năng cao Những cái FVG Breakaway này á Đến 80% giá nó sẽ tăng tiếp tục Và nó không quay về test cái FVG Thói chúng ta sẽ xem bí dụ mà Ở đây chúng ta có Cây nến khung H1 Anh em thấy không? Đây là 3 cây nến tăng liên tiếp Và nó tạo ra 1 cái buồn FVG ở đây Đúng không? Thì anh em quay xác anh em thấy được đỏ ràng là Giá đó không có test về cái FVG này Ở đây cũng có rất nhiều trường hợp như vậy hả? Này nè mình Khi nó tạo ra 1 cái FVG Breakaway á Ở đây nè Anh em thấy không? Thì giá nó liên tiếp tục tăng lên, tăng lên, tăng lên Cho đến ngày hôm sau nó mới quay về test Mà khi mà nó đi xa như vậy nó quay về test Thì nó không còn mạnh nữa Những FVG được tạo ra thì chúng ta sẽ muốn nó phải test liền Thì khi anh em thấy FVG Breakaway như thế này nè Thì anh em sẽ phải vào trong khung M5 Để anh em tìm kiếm những lệnh tiếp diễn Ok, mình sẽ vào trong khung M5 Mình vào trong khung M5 nè Rồi, mình sẽ tui vào chỗ này Thì trong khung M5 nó lại tiếp tục tạo ra 1 cái FVG Đúng không? Ở đây Thì bây giờ anh em có thể follow hell cái FVG mở năm này rồi Tại vì khi mà nó tạo ra FVG Breakaway ở khung H1 Thì trong khung M5 nó cũng sẽ tạo 1 cái động lực tăng Và lúc này anh em chỉ cần mua ở cái FVG trong khung M5 là được Rồi chúng ta cùng xem giá chạy ha Giá quay về test cái FVG trong khung M5 nè Mà tăng lên Đó chính là cách mà chúng ta sẽ giao dịch với FVG Breakaway Tiếp tục mình sẽ đến với 1 cái FVG bình thường Đó là 1 cái FVG có 2 cái nến tăng và 1 cái nến giảm như thế này Nó không phải là dẹn mở rộng anh em ha Thì với cái FVG dẹn này Giá nó có khả năng test lại cái FVG Sau đó mới tăng ha Thì chúng ta sẽ cùng vào trong cái bí dụ của EU dưới đây Thì bí bí EU này sẽ khá ngược lại là sẽ gồm là 2 cái nến giảm và 1 cái nến tăng Thì nó là FVG dẹn thường nhưng mà nằm trong xuống giảm anh em ha Thì chúng ta cũng có 1 cái FVG chỗ này Mình sẽ đặt lên nó là FVG H1 đi Cho anh em dễ quay xác rồi Rồi bây giờ mình sẽ vào trong khung M5 Tại vì đây là FVG dẹn thường, không phải là dẹn Breakaway Thì giá có khả năng sẽ test lại ha Vào trong khung M5 Rồi mình chờ test lại cái FVG này Rồi thì khi nó test lại cái FVG này rồi Nhưng mà M5 vẫn đang là 1 cái xuống dẹn này, 1 xuống tăng ha Thì mình sẽ chờ nó phá vào cái đáy này Rồi thì khi nó phá vào cái đáy này Nó hình thành cho mình 1 cái FVG Mở 5 ở đây, đúng chưa? Mình sẽ NG ở cái FVG mở 5 này Đặt stop-lock ở trên đây Và đặt cái mức tê bê là 2R 2R này mà Cùng sẽ nhá nó chạy ha Giá test lại cái FVG này Và sạch xuống, đó chính là cách chúng ta ứng dụng FVG bình thường ha Rồi tiếp tục 1 vàng FVG nữa Đó là EFVG Cũng tương tự như thế này, chúng ta có 1 cái FVG tăng đúng không? Đây Và nếu như cái FVG tăng này Nó bị phá bởi 1 cái nến Thay là nhiều cái nến nhứng chìm ha Nó chung là nhứng chìm cái FVG Như thế này Đó Nhứng chìm ha Thì cái FVG này Nó sẽ không còn là FVG nữa Nhưng mà nó sẽ là EFVG Nó sẽ trành EFVG Thì với EFVG, nghĩa là 1 cái FVG bị nhứng chìm Chúng ta sẽ chờ nó test lại và xeo xuống Hoặc là nếu như nó tạo 3 cái nến giảm Mà 1 cái nến tăng nhứng chìm thì chúng ta sẽ bài lên ha Tương tự chúng ta có 1 cái bí vụ ở đây Thử này ha Đây là 3 cái nến giảm đúng chưa? 3 cái nến giảm 1, 2, 3 Nó tạo chúng ta 1 cái FVG Đúng không? Và cái FVG này đã bị nhứng chìm Bởi cái nến tăng này Thì chỗ này nó sẽ trở thành EFVG Rồi cái nhiệm vụ chúng ta chỉ là vì 3 lại khi giá test cái EFVG Đã X lời dưới đây và tề bên trên Rồi cùng xem giá chạy đẹp Giá test lại cái EFVG và Tiếp tục tăng lên Đó là cách xài EFVG ha Rồi 1 dạng FVG nữa Đó là B rồi B B được đựng dễ như thế nào Nếu dư Mình sẽ kéo 3 cái nến giảm Chưa có 3 cái nữa này đi Thì chúng ta sẽ có 1 cái FVG tăng đúng không? Nhưng nếu như cái FVG tăng này Bị nhứng chìm bởi 1 cái FVG giảm đối diện Đây, trái hẹn như thế này là 1 cái 3 cái nến giảm đúng không? 3 cái nến giảm này tạo 1 cái FVG đối diện ở đây Đúng chưa? Đó Thì đây gọi là B rồi B Hay gọi là Subton ha Đây là cái dạng mạnh nha ném Dạng mạnh của FVG đảo chiều Tại vì khi mà Nên nó biết là khi mà giá tạo 1 FVG Chứng đó động lực tăng nó rất là mạnh đúng không? Nhưng mà nó lại bị nhứng chìm Bởi 1 cái động lực giảm Chứng tạo là tại cái vị trí này nha Là cái bên bán nó nhảy vào rất mạnh Thì anh em sẽ canh nó test lại cái FVG này Để anh em bán xuống ha Đó chính là Subton Thì gọi là B rồi B Rồi chúng ta sẽ cùng nhau Nhìn vào cái ví dụ con HU với đây Đây Sau khi giá nó sang ra hành khoảng cái đỉnh bên đây Nè em thấy không? Này nó sang hành khoảng cái đỉnh nè Mình sẽ tua lại ha Nó sang hành khoảng cái đỉnh xong Nó tạo chúng ta 1 cái FVG Đúng chưa? FVG Rồi Và FVG này bị diễn em Bị nhứng chìm bởi cái FVG đối diện Chính là cái FVG này Đúng không? Này FVG tăng bị nhứng chìm bởi FVG giảm Sau đó nó test lại bằng cái nánh này Đây cái nánh này Khi nó tạo được cái FVG giảm nhứng chìm rồi Thì chúng ta tham cú Subton rồi Thì anh em sẽ đặt 1 cái lệnh cell Ngay tại cái FVG giảm được tạo ra X lời đặt trên đây Và TB TB về đáy gần nhất Chính là vị trí này Rồi cùng xem giá chạy ha Giá test lại Và sắp mạnh xuống ha Đó chính là Subton Bây giờ mình nói là khi sẽ là Subton Giá đi rất là mạnh đúng không? Nó sắp rất là mạnh ha Rồi tiếp tục Chúng ta đến với cái FVG Cuối cùng Cái FVG này không dùng để vào lệnh Mà FVG này dùng để làm gì anh em? Dùng để làm đến TB Làm đến TB ha Hay còn gọi là ReFVG ReFVG Nghĩa là sao? Nghĩa là Đây là cái điểm mà anh em sẽ chốt lời Cái điểm này sẽ chốt lời Nếu như anh em có lệnh mua Thì nếu như anh em có 1 cái lệnh mua ở đây Mình giả sử ở đây là 1 case FVG Đúng không? Anh em mua ở đây Anh em phải tới bệp đầu Tên bệp đầu thì đương nhiên là chúng ta sẽ Nhìn những cái cản rồi Thì ở đây có 1 cái FVG đói diện nữa nào Đúng không? Một cái FVG nó diễn nữa Thì nếu như anh em mua ở đây Anh em có thể TB ở đây Và nếu như nó lụng ở đây Thì nó sẽ lên đầu Nó sẽ tìm kiếm ở đâu tiếp Nó sẽ tìm kiếm cái FVG trên đây Thì cái FVG này cũng gọi là ReFVG luôn Và cái FVG này cũng gọi là ReFVG Cả hai cái này đều là ReFVG ha Tao cùng xem giá nó chạy tiếp Nó thì khi giá nó Nó lại tiếp tục Test về cái FVG này Đúng không? Đó tiện em có thể mua ha Có thể mua lên từ đây Rồi giá nó tiếp tục tăng lên thôi Rồi thì TB của này sẽ lâu TB này sẽ là cái ReFVG này Ở chỗ này nó cũng sẽ có 1 cái FVG nào Anh em cũng có thể mua ở cái FVG này Hét lờ dưới đây Và TB cũng về cái ReFVG luôn Hai lần chúng ta được TB về cái ReFVG này Và nếu em kia giá nó chạm đến cái ReFVG này ha Nó sẽ có phản ứng mạnh Mình không biết là nó có xuyên được cái FVG này không Hay là từ cái ReFVG này nó sẽ đảo chiều Nhưng đây là cái điểm TB đẹp nhất Đó thì đây là cái ứng dụng của ReFVG ha Rồi thì trong video hôm nay mình đã chia sẻ cho anh em Hết tất cả những các loại ReFVG có trên thị trường Hầu tiên là ReqAway ReFVG ReFVG bình thường ReFVG BW Và ReFVG Đó là những loại ReFVG mà anh em cần biết Để có thể áp dụng nó vào trong cái quá trình trái đình của mình ha Ok cám ơn em đã theo dõi video này Và nếu anh em thấy hay Các bạn có thể lưu video và bấm vào cái link bio Để tiếp cận những phương pháp trái đình hiệu quả nhất ha Ok cám ơn em đã theo dõi video</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vn_rebates/video/7446381153868598534</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7474060511584324885</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+          <t>🟡 Ưu tiên 2 (Cốt lõi SMC/ICT)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2235,32 +2235,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SO Trading</t>
+          <t>Vnrebates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3 lỗi vào lệnh khiến bạn bị cắt lỗ oan (và cách sửa) Sửa lỗi quan trọ...</t>
+          <t>Xác Định Thanh Khoản Thị Trường (Liquidity ICT)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3 lỗi vào lệnh khiến bạn bị cắt lỗ oan (và cách sửa) Sửa lỗi quan trọng hơn tìm phương pháp mới. 3 lỗi hay gặp: tin tín hiệu khung nhỏ mà quên khung lớn, vào lệnh ngược để gỡ, đóng lệnh vì giá lình xình. Nguồn: nội dung do SO TRADING tự biên soạn. #Shorts #Trading</t>
+          <t>SMC &amp; ICT: Setup phiên Á - Âu quét thanh khoản, 4 tiêu chí khối Order Block chuẩn (BOS, FVG, Premium/Discount, Sweep), Fibonacci OTE 0.618 - 0.786 lồng ghép FVG, giáo trình FVG 11 phút.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bị cắt lỗ oan liên tục, có thể lỗi nằm ở chính bạn, không phải phương pháp. Mới giao dịch, ai cũng đi tìm phương pháp tốt nhất. Nhưng sửa từng lỗi sai của mình còn quan trọng hơn nhiều. Lỗi thứ nhất: Thấy tín hiệu đẹp ở khung M5 mà quên nhìn khung lớn. Cấu trúc giảm, nến nhấn chìm, vậy mà vài nến sau đã dính cắt lỗ, lý do nằm ở khung M15, đợt giảm đó nằm giữa vùng bò rất mạnh. Gấu con đang đánh vào căn cứ của bò mẹ. Trước khi tin tín hiệu, hãy hỏi 3 điều: Khung lớn có ngược mình không? Phe mình đã thất bại mấy lần ở đó? Và giá có đang đi ngang lộn xộn không? Nếu có, hãy đứng ngoài. Lỗi thứ hai: Vào lệnh ngược lại để gỡ. Vừa bị cắt lỗ là muốn gỡ ngay. Lệnh đó đến từ cảm xúc, không phải từ phương pháp. Nguy hiểm nhất là khi lệnh gỡ lại thắng. Bạn tưởng cách này hiệu quả, lần sau gấp đôi khối lượng. Một lệnh thắng chẳng chứng minh được gì. Lỗi thứ ba: Đóng lệnh vì giá lình xình. Vừa đóng ở hòa vốn thì giá chạy thẳng tới điểm chốt lời. Một lệnh thắng bị biến thành lệnh hòa/thua. Đã có phương pháp được kiểm chứng thì hãy tin nó, đúng quy tắc vào lệnh, đúng quy tắc chốt lời, không để cảm xúc chen vào. Tóm lại: Nhìn khung lớn trước, không vào lệnh để gỡ, không đóng lệnh trái quy tắc. Sửa được 3 lỗi này đáng giá hơn tìm một phương pháp mới. Theo dõi SO Trading để giao dịch kỷ luật hơn mỗi ngày.</t>
+          <t>ICT đã từng nói, tị trường chỉ làm có 2 việc thôi Thứ nhất là quay thanh khỏe và thứ 2 là lắp này các FVG Điều này có nghĩa là nếu như anh em vào một cái lệnh nào đó mà anh em chưa tìm nấy thanh khỏe thì rất có thể anh em sẽ trở thành thanh khỏe ICT là một trader với quan điểm dâu dịch là tị trường luôn luôn tìm thanh khỏe trước khi có những bước đi tiếp theo Thì sau khi tham khảo vào cái tư duy của ICT thì mình đã rút ra được một số các bài học và hôm nay mình sẽ chia sẻ anh em để có thể tăng thêm một cái tự lời hắn của mình Ok, nè Ma, thì anh em nhìn 2 cái bí vụ với đây thì anh em thấy khi giá nó phải hướng tới một cái buồn giá nào đó thì sẽ có 2 trường hợp xảy ra đúng không? Một là giá chạm đứng cái buồn này và tăng lên Nếu anh em ba này sẽ thắng Còn hai, nó chạm buồn này nhưng mà nó không tăng mà nó xuyên luôn thì anh em sẽ thua Anh em nghĩ là chỉ có 2 trường hợp thôi hả? Còn 1 trường hợp nữa đó là giá nó vét đáy xong nó mới thanh Đó Vậy thì nếu như anh em chọn 1 cái chờ về đây anh em ba lên thì anh em có tới 2 trường hợp mà anh em có thể thua được và là cái này và cái này Vậy thì thông bình hơn nó sẽ chờ cái gì? Ta sẽ chờ giá nó vét xong rồi chúng ta mới bầu lệnh thì lúc đó anh em có thể loại được bớt thêm 1 trường hợp thua nữa thì cái thể thắng nó sẽ tăng lên đúng không? Rồi bây giờ nó sẽ cùng nhau nhìn vào cái trạng này Đây là 1 cái cấu chút tăng đúng rồi anh em, chút tăng này thì có nhiều nên sẽ canh 3 cái giá qua bên bùn đáy này Thì khi giá trạm bùn đáy này nó sức hiểm cơ nến bin ba đứt rau thì là phần anh em sẽ vào buồn ở đây x lờ dưới cái đáy này và bề bề thì chúng ta cùng xem giá nó đi như thế nào hả? Mới vụng ta 1 vài trành bị x lờ sau đó nó mới tăng lên thì mình sẽ vào lệnh khi này bị béc rồi và tiếp tục tăng lên nè sau khi béc xong anh em phải tăng lên nó đóng đến qua cái nến này thì lúc này đây chỉ là 1 cái phá bởi giả thôi nè thì chúng ta mới bắt đầu vào lệnh mua vị trí này đạt sublots như đây và tb lên trần cùng xem giá nó chạy hả? Sau khi được bấy đựng sublots rồi thì giá nó đi rất là nhanh và đạt được tb đó là cách để thông minh nhớ nè chờ giá quá thân ngoại thông chúng ta mới vào chúng ta sẽ có tự lệnh hắn cao hơn ok nè mà lô video lại để xem kì cứng thiết</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1:21</t>
+          <t>1m - 11m</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696679708485897478</t>
+          <t>https://www.tiktok.com/@vn_rebates/video/7446381153868598534</t>
         </is>
       </c>
     </row>
@@ -2290,27 +2290,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Đọc nến theo luật bò gấu: vẽ căn cứ, chờ tín hiệu Đọc nến là đọc hành...</t>
+          <t>3 lỗi vào lệnh khiến bạn bị cắt lỗ oan (và cách sửa) Sửa lỗi quan trọ...</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Đọc nến theo luật bò gấu: vẽ căn cứ, chờ tín hiệu Đọc nến là đọc hành vi mua bán: phe nào chiếm ưu thế, phe nào cạn lực.</t>
+          <t>3 lỗi vào lệnh khiến bạn bị cắt lỗ oan (và cách sửa) Sửa lỗi quan trọng hơn tìm phương pháp mới. 3 lỗi hay gặp: tin tín hiệu khung nhỏ mà quên khung lớn, vào lệnh ngược để gỡ, đóng lệnh vì giá lình xình. Nguồn: nội dung do SO TRADING tự biên soạn. #Shorts #Trading</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Đọc nén không phải thuộc tên mẫu nén, mà là xem phê nào đang thắng. Trước hết, vẽ căn cứ của hai phê, vùng bò và vùng gấu ở khung đang giao dịch và khung kề trên. Giá chạy qua lại giữa hai vùng, có tín hiệu thì bật lại, không có thể phá qua vào vùng đổi vai. Vùng mạnh nhất là nơi bắt đầu một con sóng với những cây nén thân dài và giúp. Nhưng vùng mạnh mới là sắc xuất, cần thêm tín hiệu, nén nhỏ, dần có dâu hoặc cặp nén nhấn trìm. Tín hiệu xuất hiện lưng trừng thì kém tin cậy hơn tín hiệu ngay tại căn cứ. Tín hiệu đẹp mà tỉ lệ lời lộ kém hoặc ngực bối cảnh thì vẫn bỏ qua, phá thật hay phá giả. Xem nhịp hồi. Hồi về vùng vừa phá rồi đi tiếp theo hướng phá là phá thật, dữ lệnh bằng căn cứ. Rồi cắt lỗ ra sau căn cứ mới nhất và chốt khi ra tới căn cứ của phê kia. Bụng đích là sắc xuất cao, không phải thắng mọi lệnh. Tâm lý ổn định thì lợi nhuận mới đều. Theo dõi Sotrading để học đọc lên mỗi ngày.</t>
+          <t>Bị cắt lỗ oan liên tục, có thể lỗi nằm ở chính bạn, không phải phương pháp. Mới giao dịch, ai cũng đi tìm phương pháp tốt nhất. Nhưng sửa từng lỗi sai của mình còn quan trọng hơn nhiều. Lỗi thứ nhất: Thấy tín hiệu đẹp ở khung M5 mà quên nhìn khung lớn. Cấu trúc giảm, nến nhấn chìm, vậy mà vài nến sau đã dính cắt lỗ, lý do nằm ở khung M15, đợt giảm đó nằm giữa vùng bò rất mạnh. Gấu con đang đánh vào căn cứ của bò mẹ. Trước khi tin tín hiệu, hãy hỏi 3 điều: Khung lớn có ngược mình không? Phe mình đã thất bại mấy lần ở đó? Và giá có đang đi ngang lộn xộn không? Nếu có, hãy đứng ngoài. Lỗi thứ hai: Vào lệnh ngược lại để gỡ. Vừa bị cắt lỗ là muốn gỡ ngay. Lệnh đó đến từ cảm xúc, không phải từ phương pháp. Nguy hiểm nhất là khi lệnh gỡ lại thắng. Bạn tưởng cách này hiệu quả, lần sau gấp đôi khối lượng. Một lệnh thắng chẳng chứng minh được gì. Lỗi thứ ba: Đóng lệnh vì giá lình xình. Vừa đóng ở hòa vốn thì giá chạy thẳng tới điểm chốt lời. Một lệnh thắng bị biến thành lệnh hòa/thua. Đã có phương pháp được kiểm chứng thì hãy tin nó, đúng quy tắc vào lệnh, đúng quy tắc chốt lời, không để cảm xúc chen vào. Tóm lại: Nhìn khung lớn trước, không vào lệnh để gỡ, không đóng lệnh trái quy tắc. Sửa được 3 lỗi này đáng giá hơn tìm một phương pháp mới. Theo dõi SO Trading để giao dịch kỷ luật hơn mỗi ngày.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1:21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696533638371970325</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696679708485897478</t>
         </is>
       </c>
     </row>
@@ -2340,27 +2340,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7 bài học sau một buổi luyện tập giao dịch trên dữ liệu quá khứ #Shor...</t>
+          <t>Đọc nến theo luật bò gấu: vẽ căn cứ, chờ tín hiệu Đọc nến là đọc hành...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7 bài học sau một buổi luyện tập giao dịch trên dữ liệu quá khứ #Shorts Bảy bài học rút ra từ buổi luyện vào lệnh trên dữ liệu quá khứ BTCUSD (M15 + H1): bức tranh lớn, vùng cản, chờ tín hiệu, tỷ lệ lời/lỗ, lệnh chờ phá, quản lý lệnh và thống kê. Nguồn: nội dung do SO TRADING tự biên soạn. #Shorts #trading #bitcoin</t>
+          <t>Đọc nến theo luật bò gấu: vẽ căn cứ, chờ tín hiệu Đọc nến là đọc hành vi mua bán: phe nào chiếm ưu thế, phe nào cạn lực.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Điện tập trên dữ liệu quá khứ, mình rút ra 7 bài học đáng giá 1. Xem bức tranh lớn trước. Khung lớn đi ngang thì đứng ngoài, hoặc chỉ canh vùng cản mạnh. 2. Chỉ vẽ vùng cản mạnh. Nơi bắt đầu còn sóng giúp. Vùng bị phá thì xóa đi. 3. Chờ phê ngực lại thất bại nhiều lần rồi mới vào. Đừng đặt sẵn lệnh trờ ngay vùng cản. 4. Tính tỉ lệ lời trên lỗ trước khi vào. Cản phía trước quá gần thì bỏ qua. 5. Dùng lệnh trờ phá để giá tự sắc nhận. Không phá thì lệnh không khớp, bạn không mất gì. 6. Rời cắt lỗ theo cấu trúc. Người mới cứ đặt chốt lời gấp đôi dùi do rồi để lệnh trại. 7. Đọc thống kê. Nhưng vài lệnh thì chưa nói lên điều gì. Cần hàng trăm lệnh mới đáng tin và chỉ luyện một phương pháp. Lặp lại đủ nhiều, nó sẽ thành phản xạ. Luyện tập không phải để đoán đúng từng lệnh, mà để đọc vùng cản, chờ tín hiệu và quản lý lệnh thành phản xạ. Theo dõi short reading để học thêm mỗi ngày.</t>
+          <t>Đọc nén không phải thuộc tên mẫu nén, mà là xem phê nào đang thắng. Trước hết, vẽ căn cứ của hai phê, vùng bò và vùng gấu ở khung đang giao dịch và khung kề trên. Giá chạy qua lại giữa hai vùng, có tín hiệu thì bật lại, không có thể phá qua vào vùng đổi vai. Vùng mạnh nhất là nơi bắt đầu một con sóng với những cây nén thân dài và giúp. Nhưng vùng mạnh mới là sắc xuất, cần thêm tín hiệu, nén nhỏ, dần có dâu hoặc cặp nén nhấn trìm. Tín hiệu xuất hiện lưng trừng thì kém tin cậy hơn tín hiệu ngay tại căn cứ. Tín hiệu đẹp mà tỉ lệ lời lộ kém hoặc ngực bối cảnh thì vẫn bỏ qua, phá thật hay phá giả. Xem nhịp hồi. Hồi về vùng vừa phá rồi đi tiếp theo hướng phá là phá thật, dữ lệnh bằng căn cứ. Rồi cắt lỗ ra sau căn cứ mới nhất và chốt khi ra tới căn cứ của phê kia. Bụng đích là sắc xuất cao, không phải thắng mọi lệnh. Tâm lý ổn định thì lợi nhuận mới đều. Theo dõi Sotrading để học đọc lên mỗi ngày.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696421857871908116</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696533638371970325</t>
         </is>
       </c>
     </row>
@@ -2390,27 +2390,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vào lệnh phá vỡ: 7 bài học chọn cú phá đẹp Không phải cú phá vỡ vùng ...</t>
+          <t>7 bài học sau một buổi luyện tập giao dịch trên dữ liệu quá khứ #Shor...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Vào lệnh phá vỡ: 7 bài học chọn cú phá đẹp Không phải cú phá vỡ vùng cản nào cũng đáng vào lệnh. 7 bài học: vùng nhiều đỉnh, khung lớn, độ nén, chốt lời, dời cắt lỗ, ưu nhược điểm so với chờ hồi. Nguồn: nội dung do SO TRADING cung cấp. Nội dung chỉ mang tính giáo dục, không phải khuyến nghị đầu tư. #Shorts #trading #phavo</t>
+          <t>7 bài học sau một buổi luyện tập giao dịch trên dữ liệu quá khứ #Shorts Bảy bài học rút ra từ buổi luyện vào lệnh trên dữ liệu quá khứ BTCUSD (M15 + H1): bức tranh lớn, vùng cản, chờ tín hiệu, tỷ lệ lời/lỗ, lệnh chờ phá, quản lý lệnh và thống kê. Nguồn: nội dung do SO TRADING tự biên soạn. #Shorts #trading #bitcoin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Không phải cú pha vỡ nào cũng đáng vào lệnh. Đây là 7 bài học để chọn cú pha đẹp. Giá phá qua vùng cản mới chỉ là điều kiện đầu tiên chưa đủ để vào lệnh. Phá vùng nhiều đỉnh mạnh hơn phá một đỉnh vì phê bán đã rồn hết lực mà vẫn thua. Nhìn khung lớn hơn để biết phê mua có chiếm yêu thế. Và lệnh có thể đi xa tới đầu. Đẹp nhất là khi các đáy cao dần nén sát vùng đỉnh rồi bung lên. Cắt lỗ đặt dưới đáy gần nhất. Đặt trốt lời gấp đôi rủi do rồi nhìn sang bên trái. Có vùng cản nguy hiểm phía trước thì bỏ qua. Giá đi đúng hướng thì dời điểm cắt lỗ lên dưới đáy cao hơn mới. Lệnh phá vỡ cho kết quả rất nhanh vì phê ngược lại đã cạn lực. Nhưng chọn điểm vào kém thì cắt lỗ rất xa. Làm hỏng tỷ lệ lời trên lỗ. Chờ giá hồi về thì cắt lỗ ngắn hơn nhưng giá thường phải đi ngang một thời gian. Tìm vùng nhiều đỉnh, chờ giá nén rồi phá và chỉ vào khi phía trước còn chỗ chạy. Theo dõi SO Trading để xem thêm.</t>
+          <t>Điện tập trên dữ liệu quá khứ, mình rút ra 7 bài học đáng giá 1. Xem bức tranh lớn trước. Khung lớn đi ngang thì đứng ngoài, hoặc chỉ canh vùng cản mạnh. 2. Chỉ vẽ vùng cản mạnh. Nơi bắt đầu còn sóng giúp. Vùng bị phá thì xóa đi. 3. Chờ phê ngực lại thất bại nhiều lần rồi mới vào. Đừng đặt sẵn lệnh trờ ngay vùng cản. 4. Tính tỉ lệ lời trên lỗ trước khi vào. Cản phía trước quá gần thì bỏ qua. 5. Dùng lệnh trờ phá để giá tự sắc nhận. Không phá thì lệnh không khớp, bạn không mất gì. 6. Rời cắt lỗ theo cấu trúc. Người mới cứ đặt chốt lời gấp đôi dùi do rồi để lệnh trại. 7. Đọc thống kê. Nhưng vài lệnh thì chưa nói lên điều gì. Cần hàng trăm lệnh mới đáng tin và chỉ luyện một phương pháp. Lặp lại đủ nhiều, nó sẽ thành phản xạ. Luyện tập không phải để đoán đúng từng lệnh, mà để đọc vùng cản, chờ tín hiệu và quản lý lệnh thành phản xạ. Theo dõi short reading để học thêm mỗi ngày.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696331802654280980</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696421857871908116</t>
         </is>
       </c>
     </row>
@@ -2440,27 +2440,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Giao dịch như lính bắn tỉa: đo độ chính xác, đừng đếm số lệnh 7 bài h...</t>
+          <t>Vào lệnh phá vỡ: 7 bài học chọn cú phá đẹp Không phải cú phá vỡ vùng ...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Giao dịch như lính bắn tỉa: đo độ chính xác, đừng đếm số lệnh 7 bài học từ hình ảnh lính bắn tỉa: chính xác hơn số lượng, kẻ thù là chính mình, phương pháp là vũ khí, luyện hàng nghìn lần, luyện trên dữ liệu quá khứ, tự bóp cò, khung nhỏ không nhiễu. Nguồn: nội dung do kênh SO TRADING tổng hợp. Chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #giaodich #trading</t>
+          <t>Vào lệnh phá vỡ: 7 bài học chọn cú phá đẹp Không phải cú phá vỡ vùng cản nào cũng đáng vào lệnh. 7 bài học: vùng nhiều đỉnh, khung lớn, độ nén, chốt lời, dời cắt lỗ, ưu nhược điểm so với chờ hồi. Nguồn: nội dung do SO TRADING cung cấp. Nội dung chỉ mang tính giáo dục, không phải khuyến nghị đầu tư. #Shorts #trading #phavo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lính bán tỉa, không bán ít. Họ bán chính xác, bán tỉa là độ chính xác, không phải ít hay nhiều lệnh. Vào ít mà sai nhiều thì vẫn không giỏi, kẻ thù không phải thị trường. Bạn không điều khiển được giá, chỉ điều khiển được chính mình. Phương Pháp là vũ khí. Đừng ra chận tay không, cũng đừng mang quá nhiều thứ mà không thạo thứ nào. Sạ thủ giỏi bán hàng nghìn viên khi luyện tập. Simo hay he hạ khoảng 500 linh năm mục tiêu trong 100 ngày. Các luyện nhanh nhất là vào lệnh trên dữ liệu quá khứ. Một giờ tua biểu đồ bằng 6 tuần giao dịch thật. Càng nhiều lệnh, bạn càng sớm thấy lỗi của mình, mà không tốn một đồng tiền thật. Gia trận thì tự mình bóp cỏ. Theo tín hiệu mù quán, không ai có lợi nhuận ổn địch. Không nhỏ, không hề nhéo, chỉ là bạn chưa hiểu. Luyện đủ lâu, biểu đồ nào cũng đọc được. Đừng đếm số lệnh, hãy đò độ chính xác của mỗi phát bán theo dõi Soul Trading để luyện từng phát bán chính xác hơn.</t>
+          <t>Không phải cú pha vỡ nào cũng đáng vào lệnh. Đây là 7 bài học để chọn cú pha đẹp. Giá phá qua vùng cản mới chỉ là điều kiện đầu tiên chưa đủ để vào lệnh. Phá vùng nhiều đỉnh mạnh hơn phá một đỉnh vì phê bán đã rồn hết lực mà vẫn thua. Nhìn khung lớn hơn để biết phê mua có chiếm yêu thế. Và lệnh có thể đi xa tới đầu. Đẹp nhất là khi các đáy cao dần nén sát vùng đỉnh rồi bung lên. Cắt lỗ đặt dưới đáy gần nhất. Đặt trốt lời gấp đôi rủi do rồi nhìn sang bên trái. Có vùng cản nguy hiểm phía trước thì bỏ qua. Giá đi đúng hướng thì dời điểm cắt lỗ lên dưới đáy cao hơn mới. Lệnh phá vỡ cho kết quả rất nhanh vì phê ngược lại đã cạn lực. Nhưng chọn điểm vào kém thì cắt lỗ rất xa. Làm hỏng tỷ lệ lời trên lỗ. Chờ giá hồi về thì cắt lỗ ngắn hơn nhưng giá thường phải đi ngang một thời gian. Tìm vùng nhiều đỉnh, chờ giá nén rồi phá và chỉ vào khi phía trước còn chỗ chạy. Theo dõi SO Trading để xem thêm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696144076411817268</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696331802654280980</t>
         </is>
       </c>
     </row>
@@ -2490,27 +2490,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kế hoạch một ngày giao dịch: 7 bài học để không chơi cho vui Giao dịc...</t>
+          <t>Giao dịch như lính bắn tỉa: đo độ chính xác, đừng đếm số lệnh 7 bài h...</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kế hoạch một ngày giao dịch: 7 bài học để không chơi cho vui Giao dịch thành công không cao siêu, nó dành cho người có kế hoạch. 7 bài học: coi giao dịch là công việc, chọn khung giờ cố định, lướt nhanh đầu ngày, đừng ép vào lệnh, luyện tập thật nhiều, không dán mắt vào giá, kiểm tra trước khi vào lệnh. Nguồn: nội dung do kênh SO TRADING tổng hợp. Nội dung chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #giaodich #trading #kehoach</t>
+          <t>Giao dịch như lính bắn tỉa: đo độ chính xác, đừng đếm số lệnh 7 bài học từ hình ảnh lính bắn tỉa: chính xác hơn số lượng, kẻ thù là chính mình, phương pháp là vũ khí, luyện hàng nghìn lần, luyện trên dữ liệu quá khứ, tự bóp cò, khung nhỏ không nhiễu. Nguồn: nội dung do kênh SO TRADING tổng hợp. Chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #giaodich #trading</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Giao dịch như một trò chơi, đó là cách nhanh nhất để mất tiền, hãy coi giao dịch là công việc. Tự do, nhưng phải có kế hoạch rõ ràng, chọn một khung giờ cố định trùng lúc thị trường mạnh nhất, phiên Âu và phiên Mỹ không cần ngồi cả ngày. Não không thể tập trung liên tục, nhất là khi có tiền dính vào, đầu ngày, lượt nhanh các cặp tiền khoảng 10 phút để nắm su hướng, rồi tắt máy, đừng cố tìm lý do để vào lệnh. Không giao dịch cũng là một phần của công việc. Phần lớn thời gian là luyện tập, 99 phần chuẩn bị, một phần thực chiến để biểu đồ sắn nhưng đừng dám mắt vào giá. Liết trưa đầy một phút là đủ, trước khi vào lệnh, kiểm tra, su hướng lớn, vùng cản, điểm cắt lỗ và tỷ lệ lời trên lỗ, vào lệnh rồi thì đừng ngồi canh và đừng kỳ vọng thắng mọi lệnh vài lệnh không nói lên điều gì. Kết quả chỉ rõ khi số lệnh đủ nhiều, ưu khóa cần nhớ là chuẩn bị. Theo dõi show trading để xây kế hoạch giao dịch của riêng bạn.</t>
+          <t>Lính bán tỉa, không bán ít. Họ bán chính xác, bán tỉa là độ chính xác, không phải ít hay nhiều lệnh. Vào ít mà sai nhiều thì vẫn không giỏi, kẻ thù không phải thị trường. Bạn không điều khiển được giá, chỉ điều khiển được chính mình. Phương Pháp là vũ khí. Đừng ra chận tay không, cũng đừng mang quá nhiều thứ mà không thạo thứ nào. Sạ thủ giỏi bán hàng nghìn viên khi luyện tập. Simo hay he hạ khoảng 500 linh năm mục tiêu trong 100 ngày. Các luyện nhanh nhất là vào lệnh trên dữ liệu quá khứ. Một giờ tua biểu đồ bằng 6 tuần giao dịch thật. Càng nhiều lệnh, bạn càng sớm thấy lỗi của mình, mà không tốn một đồng tiền thật. Gia trận thì tự mình bóp cỏ. Theo tín hiệu mù quán, không ai có lợi nhuận ổn địch. Không nhỏ, không hề nhéo, chỉ là bạn chưa hiểu. Luyện đủ lâu, biểu đồ nào cũng đọc được. Đừng đếm số lệnh, hãy đò độ chính xác của mỗi phát bán theo dõi Soul Trading để luyện từng phát bán chính xác hơn.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7696052072612973844</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696144076411817268</t>
         </is>
       </c>
     </row>
@@ -2540,27 +2540,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Độ nén của giá: 7 điều giúp cắt lỗ ngắn, thắng nhiều hơn #Shorts Độ n...</t>
+          <t>Kế hoạch một ngày giao dịch: 7 bài học để không chơi cho vui Giao dịc...</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Độ nén của giá: 7 điều giúp cắt lỗ ngắn, thắng nhiều hơn #Shorts Độ nén của giá là gì, vì sao giá nén rồi bung, cách nhìn hình dạng vùng nén và đặt cắt lỗ ngắn mà an toàn. Nội dung do kênh SO TRADING tổng hợp. Giao dịch luôn có rủi ro, đây không phải lời khuyên đầu tư. #Shorts #trading #giaodich</t>
+          <t>Kế hoạch một ngày giao dịch: 7 bài học để không chơi cho vui Giao dịch thành công không cao siêu, nó dành cho người có kế hoạch. 7 bài học: coi giao dịch là công việc, chọn khung giờ cố định, lướt nhanh đầu ngày, đừng ép vào lệnh, luyện tập thật nhiều, không dán mắt vào giá, kiểm tra trước khi vào lệnh. Nguồn: nội dung do kênh SO TRADING tổng hợp. Nội dung chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #giaodich #trading #kehoach</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Có một điều ít ai nói tới, nhưng giúp bạn thắng nhiều hơn và cắt lỗ ngắn hơn, đó là độ nén của giá. Hôm nay mình đi qua 7 điều cần nắm. 1. Giá đi ngang, đáy cao dần, đỉnh thấp dần, biên độ thu hẹp, tức là giá đăng nén. Nén càng sát nhau thì nén càng mạnh, sống bên trong càng lớn thì nén càng yếu. 2. Giá nén vì lực 2 phê ngang nhau, phê mua đẩy đáy lên, phê bán ép đỉnh xuống. 3. Nén thì sẽ bung như quả bóng bơm quá căng, nén càng mạnh, bung càng mạnh. Hướng bung thì nhìn bối cảnh lớn, trong xu hướng tăng dễ phá lên, trong vùng giảm dễ phá xuống. 4. Tất cả chỉ là sắc suất, việc của mình là tăng sắc suất, không tìm sự chắc chắn. 5. Tạm ra cần là hai phê ngang sức, đáy giúp lên là phê mua mạnh hơn, đỉnh giúp xuống là phê bán mạnh hơn, vùng giá mở rộng như cái loa thì đứng ngoài. Vì cả hai phê đều loạn. 6. Vùng nén cho điểm cắt lỗ vừa an toàn vừa ngắn vì vào lệnh ngay chỗ giá hẹp nhất. 7. Đừng rời cắt lỗ ra xa. Giá đã phá căn cứ thì phê kia đã thắng thế, tìm vùng nén, chờ giá bùng, vào lệnh với cắt lỗ ngắn. Theo dõi show trading để học thêm.</t>
+          <t>Giao dịch như một trò chơi, đó là cách nhanh nhất để mất tiền, hãy coi giao dịch là công việc. Tự do, nhưng phải có kế hoạch rõ ràng, chọn một khung giờ cố định trùng lúc thị trường mạnh nhất, phiên Âu và phiên Mỹ không cần ngồi cả ngày. Não không thể tập trung liên tục, nhất là khi có tiền dính vào, đầu ngày, lượt nhanh các cặp tiền khoảng 10 phút để nắm su hướng, rồi tắt máy, đừng cố tìm lý do để vào lệnh. Không giao dịch cũng là một phần của công việc. Phần lớn thời gian là luyện tập, 99 phần chuẩn bị, một phần thực chiến để biểu đồ sắn nhưng đừng dám mắt vào giá. Liết trưa đầy một phút là đủ, trước khi vào lệnh, kiểm tra, su hướng lớn, vùng cản, điểm cắt lỗ và tỷ lệ lời trên lỗ, vào lệnh rồi thì đừng ngồi canh và đừng kỳ vọng thắng mọi lệnh vài lệnh không nói lên điều gì. Kết quả chỉ rõ khi số lệnh đủ nhiều, ưu khóa cần nhớ là chuẩn bị. Theo dõi show trading để xây kế hoạch giao dịch của riêng bạn.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1:10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695960796676803861</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7696052072612973844</t>
         </is>
       </c>
     </row>
@@ -2590,27 +2590,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hiểu đúng đa khung thời gian: 6 điều đừng học vẹt Sáu điều cần hiểu đ...</t>
+          <t>Độ nén của giá: 7 điều giúp cắt lỗ ngắn, thắng nhiều hơn #Shorts Độ n...</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hiểu đúng đa khung thời gian: 6 điều đừng học vẹt Sáu điều cần hiểu đúng về đa khung thời gian trong giao dịch: không cần xem nhiều khung, không cần cùng hướng, vùng cản lớn nhỏ và cách vào lệnh theo cung cầu. #Shorts #trading #dakhungthoigian</t>
+          <t>Độ nén của giá: 7 điều giúp cắt lỗ ngắn, thắng nhiều hơn #Shorts Độ nén của giá là gì, vì sao giá nén rồi bung, cách nhìn hình dạng vùng nén và đặt cắt lỗ ngắn mà an toàn. Nội dung do kênh SO TRADING tổng hợp. Giao dịch luôn có rủi ro, đây không phải lời khuyên đầu tư. #Shorts #trading #giaodich</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Xem nhiều khung thời gian hơn, không có nghĩa là giao dịch tốt hơn. Đa khung thời gian, ai cũng quan tâm, nhưng nhiều người chỉ học vẹt. Đây là 6 điều cần hiểu đúng. 1. Xem nhiều khung, không phải càng nhiều càng tốt. Lệnh ở khung 10 năm, chỉ 5 trong 1, 2 cây đến hức 4, còn chưa hết 1 đến ngày. Cùng quá lớn gần như không có tác dụng với lệnh đó. Xem chúng chỉ làm bạn phân vần khi tín hiệu đẹp xuất hiện. 2. Không cần mọi khung cùng 1 hướng. Khung lớn có thể đang giảm, nhưng 1 cây nén tăng của nó là cả su hướng tăng dài ở khung nhỏ. 3. Khung thời gian, chỉ là cách con người đóng khung giá. Giá đi thành 1 đường duy nhất như sợi chỉ, gom lại thì thành nén. 4. Không có vùng cản của 15 hay của 1. Chỉ có vùng cản lớn hơn và vùng cản nhỏ hơn. 5. Muốn nhìn tổng thể, hãy thu nhỏ biểu đồ hoặc lên đúng 1 khung kỳ trên. Đừng nhảy lên khung quá xa. 6. Vào lệnh theo kịch bản cung cầu. Giá phá đỉnh cũ rồi đi ngang, phê mua chiếm ưu thế thì chờ giá phá vùng đỉnh đó. Khi đó vào lệnh mua, cách lỗ đặt dưới vùng vừa phá chất lời nhắm tới vùng cản lớn hơn phía trên. Đừng học thuộc phải xem bao nhiêu khung. Hãy hiểu giá được tạo ra thế nào, rồi chọn cách nhìn thuận tiện nhất cho mình. Rưu duy sai giống con đỉa, bám càng lâu càng hút cạn tiền bạc. Theo dõi sò trading để giao dịch đúng bản chất.</t>
+          <t>Có một điều ít ai nói tới, nhưng giúp bạn thắng nhiều hơn và cắt lỗ ngắn hơn, đó là độ nén của giá. Hôm nay mình đi qua 7 điều cần nắm. 1. Giá đi ngang, đáy cao dần, đỉnh thấp dần, biên độ thu hẹp, tức là giá đăng nén. Nén càng sát nhau thì nén càng mạnh, sống bên trong càng lớn thì nén càng yếu. 2. Giá nén vì lực 2 phê ngang nhau, phê mua đẩy đáy lên, phê bán ép đỉnh xuống. 3. Nén thì sẽ bung như quả bóng bơm quá căng, nén càng mạnh, bung càng mạnh. Hướng bung thì nhìn bối cảnh lớn, trong xu hướng tăng dễ phá lên, trong vùng giảm dễ phá xuống. 4. Tất cả chỉ là sắc suất, việc của mình là tăng sắc suất, không tìm sự chắc chắn. 5. Tạm ra cần là hai phê ngang sức, đáy giúp lên là phê mua mạnh hơn, đỉnh giúp xuống là phê bán mạnh hơn, vùng giá mở rộng như cái loa thì đứng ngoài. Vì cả hai phê đều loạn. 6. Vùng nén cho điểm cắt lỗ vừa an toàn vừa ngắn vì vào lệnh ngay chỗ giá hẹp nhất. 7. Đừng rời cắt lỗ ra xa. Giá đã phá căn cứ thì phê kia đã thắng thế, tìm vùng nén, chờ giá bùng, vào lệnh với cắt lỗ ngắn. Theo dõi show trading để học thêm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1:19</t>
+          <t>1:10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695799603068734741</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695960796676803861</t>
         </is>
       </c>
     </row>
@@ -2640,27 +2640,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7 bài học sau 5 năm đi cùng thị trường | SO TRADING Bảy bài học kinh ...</t>
+          <t>Hiểu đúng đa khung thời gian: 6 điều đừng học vẹt Sáu điều cần hiểu đ...</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7 bài học sau 5 năm đi cùng thị trường | SO TRADING Bảy bài học kinh nghiệm sau 5 năm tham gia thị trường: biết đứng ngoài, có kịch bản, quản lý rủi ro, tránh khoảng trống cuối tuần. #trading #crypto #fx</t>
+          <t>Hiểu đúng đa khung thời gian: 6 điều đừng học vẹt Sáu điều cần hiểu đúng về đa khung thời gian trong giao dịch: không cần xem nhiều khung, không cần cùng hướng, vùng cản lớn nhỏ và cách vào lệnh theo cung cầu. #Shorts #trading #dakhungthoigian</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SU Trading chia sẻ 5 năm trong thị trường mình rút ra 7 bài học này 1. Thị trường đi ngang thì đứng ngoài chỉ hành động khi khung lớn cho lý do rõ ràng 2. Có kịch bản trước khi vào lệnh Giá không phá nổi vùng cản thì thoát dù lời chưa nhiều 3. Điểm vào chưa đẹp thì chờ ở vùng tốt hơn để cắt lỗ gần hơn và rủi do nhỏ hơn 4. Lệnh đang lời thì rời cắt lỗ về hòa vốn và chốt trước 1 phần khi giá chạm vùng nguy hiểm 5. Đừng giữ lệnh ngắn hạn qua cuối tuần vì khoảng chống giá đầu tuần rất nguy hiểm 6. Đừng bắt đầu bằng khung thời gian nhỏ Chọn khung lớn đặt lệnh xong rồi để đó 7. Ýt yếu tố ủng hộ thì khả năng thắng thấp Và thua như vậy là bình thường, muốn biết phương pháp hiệu quả đến đâu Hãy thống kê theo từng cặp tiền và từng khung thời gian Tóm lại, đứng ngoài khi thị trường không rõ và luôn có kịch bản trước khi vào lệnh Đây là kinh nghiệm cá nhân, không phải lời khuyên đầu tư Gé SO Trading để cùng trao đổi thêm nhé!</t>
+          <t>Xem nhiều khung thời gian hơn, không có nghĩa là giao dịch tốt hơn. Đa khung thời gian, ai cũng quan tâm, nhưng nhiều người chỉ học vẹt. Đây là 6 điều cần hiểu đúng. 1. Xem nhiều khung, không phải càng nhiều càng tốt. Lệnh ở khung 10 năm, chỉ 5 trong 1, 2 cây đến hức 4, còn chưa hết 1 đến ngày. Cùng quá lớn gần như không có tác dụng với lệnh đó. Xem chúng chỉ làm bạn phân vần khi tín hiệu đẹp xuất hiện. 2. Không cần mọi khung cùng 1 hướng. Khung lớn có thể đang giảm, nhưng 1 cây nén tăng của nó là cả su hướng tăng dài ở khung nhỏ. 3. Khung thời gian, chỉ là cách con người đóng khung giá. Giá đi thành 1 đường duy nhất như sợi chỉ, gom lại thì thành nén. 4. Không có vùng cản của 15 hay của 1. Chỉ có vùng cản lớn hơn và vùng cản nhỏ hơn. 5. Muốn nhìn tổng thể, hãy thu nhỏ biểu đồ hoặc lên đúng 1 khung kỳ trên. Đừng nhảy lên khung quá xa. 6. Vào lệnh theo kịch bản cung cầu. Giá phá đỉnh cũ rồi đi ngang, phê mua chiếm ưu thế thì chờ giá phá vùng đỉnh đó. Khi đó vào lệnh mua, cách lỗ đặt dưới vùng vừa phá chất lời nhắm tới vùng cản lớn hơn phía trên. Đừng học thuộc phải xem bao nhiêu khung. Hãy hiểu giá được tạo ra thế nào, rồi chọn cách nhìn thuận tiện nhất cho mình. Rưu duy sai giống con đỉa, bám càng lâu càng hút cạn tiền bạc. Theo dõi sò trading để giao dịch đúng bản chất.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1:19</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695696836140616980</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695799603068734741</t>
         </is>
       </c>
     </row>
@@ -2690,27 +2690,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7 bài học từ 3 lệnh thực tế: 2 thắng, 1 thua vì lỗi bất cẩn Hai lệnh ...</t>
+          <t>7 bài học sau 5 năm đi cùng thị trường | SO TRADING Bảy bài học kinh ...</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7 bài học từ 3 lệnh thực tế: 2 thắng, 1 thua vì lỗi bất cẩn Hai lệnh thắng, một lệnh thua vì một lỗi bất cẩn. Bảy bài học về chờ xu hướng rõ, vào lệnh khi đủ yếu tố, đặt lệnh chờ, quản lý khối lượng, kiểm soát cảm xúc và giữ điểm cắt lỗ. Nguồn: kinh nghiệm giao dịch thực tế của SO TRADING. #Shorts #trading #giaodich</t>
+          <t>7 bài học sau 5 năm đi cùng thị trường | SO TRADING Bảy bài học kinh nghiệm sau 5 năm tham gia thị trường: biết đứng ngoài, có kịch bản, quản lý rủi ro, tránh khoảng trống cuối tuần. #trading #crypto #fx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2 lệnh thắng, 1 lệnh thua vì 1 lỗi bất cảnh. Đây là 7 bài học đắt giá. 1. Su hướng gió là lợi thế lớn nhất. Nó không xuất hiện thường xuyên nên hãy kiên nhận trở. 2. Gom đủ 3 yếu tố rồi mới vào. Su hướng vung cản của phê mình và tín hiệu đến xác nhận. 3. Giá đã chạy xa thì đặt lệnh trở vùng đỉnh cũ. Không khớp cũng không mất tiền, tính khối lượng trước để biết thua mất bao nhiêu. Chốt lời mặc định gấp 2 lần rủi do. 4. Tận dụng núp phê nâu mở cửa, đầu giờ chiều giờ Việt Nam khi tín hiệu xuất hiện nhiều. 5. Vào lệnh xong đừng nhìn biểu đồ quá nhiều, nhìn nhiều dễ chốt sớm rồi tiếc, hãy gạt cảm xúc gắn với tiền. Chỉ vui khi làm đúng kịch bản, chỉ ái náy khi làm sai kịch bản. 6. Lệnh rủi do thì hoặc đứng ngoài, hoặc canh tới nơi tới chốn. Không canh được thì đóng lệnh. 7. Giữ điểm cắt lỗ, đừng rời hay bỏ, và xem lại lệnh cũ để thấy lỗi hay lặp lại. Còn vốn thì còn lấy lại được, và phần lời chính là kinh nghiệm, trở xu hướng rõ, đủ yếu tố mới vào, làm đúng kịch bản. Theo dõi SO Trading để học giao dịch có kỷ luật.</t>
+          <t>SU Trading chia sẻ 5 năm trong thị trường mình rút ra 7 bài học này 1. Thị trường đi ngang thì đứng ngoài chỉ hành động khi khung lớn cho lý do rõ ràng 2. Có kịch bản trước khi vào lệnh Giá không phá nổi vùng cản thì thoát dù lời chưa nhiều 3. Điểm vào chưa đẹp thì chờ ở vùng tốt hơn để cắt lỗ gần hơn và rủi do nhỏ hơn 4. Lệnh đang lời thì rời cắt lỗ về hòa vốn và chốt trước 1 phần khi giá chạm vùng nguy hiểm 5. Đừng giữ lệnh ngắn hạn qua cuối tuần vì khoảng chống giá đầu tuần rất nguy hiểm 6. Đừng bắt đầu bằng khung thời gian nhỏ Chọn khung lớn đặt lệnh xong rồi để đó 7. Ýt yếu tố ủng hộ thì khả năng thắng thấp Và thua như vậy là bình thường, muốn biết phương pháp hiệu quả đến đâu Hãy thống kê theo từng cặp tiền và từng khung thời gian Tóm lại, đứng ngoài khi thị trường không rõ và luôn có kịch bản trước khi vào lệnh Đây là kinh nghiệm cá nhân, không phải lời khuyên đầu tư Gé SO Trading để cùng trao đổi thêm nhé!</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1:09</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695602506377809173</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695696836140616980</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3 lỗi tâm lý giao dịch khiến bạn cháy tài khoản (và cách sửa) Phương ...</t>
+          <t>7 bài học từ 3 lệnh thực tế: 2 thắng, 1 thua vì lỗi bất cẩn Hai lệnh ...</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3 lỗi tâm lý giao dịch khiến bạn cháy tài khoản (và cách sửa) Phương pháp chỉ là một phần, tâm lý mới quyết định. 3 lỗi gần như ai cũng gặp: sợ bỏ lỡ (FOMO), trả thù thị trường, chốt lời sớm - gồng lỗ dài, cùng cách sửa đơn giản cho từng lỗi. Nguồn: nội dung BlackRose Admin (08/10/2026), biên soạn lại bởi SO TRADING. Nội dung chỉ mang tính tham khảo, không phải khuyến nghị đầu tư. #Shorts #trading #tamlygiaodich</t>
+          <t>7 bài học từ 3 lệnh thực tế: 2 thắng, 1 thua vì lỗi bất cẩn Hai lệnh thắng, một lệnh thua vì một lỗi bất cẩn. Bảy bài học về chờ xu hướng rõ, vào lệnh khi đủ yếu tố, đặt lệnh chờ, quản lý khối lượng, kiểm soát cảm xúc và giữ điểm cắt lỗ. Nguồn: kinh nghiệm giao dịch thực tế của SO TRADING. #Shorts #trading #giaodich</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Ba lỗi tâm lý này đang âm thầm đốt tài khoản của bạn. Phương pháp giao dịch không phải tất cả. Phần lớn thành công đến từ tâm lý. Lỗi 1. Sợ bỏ lỡ cơ hội. Thấy giá chạy, thấy người khác lời là vào lệnh bừa. Cách sửa, rời nhóm chát tín hiệu, tự luyện tập và xây chiến lược vào lệnh của riêng bạn. Lỗi 2. Chả thủ tị trường. Thua xong là gấp đôi khối lượng để gỡ lại. Cách sửa. Chỉ nắp ít khoảng 2 phần chăm vốn để có khoảng dừng mà tỉnh lại và đi từ nhỏ đến lớn. 10 đô và 1 nghìn đô cho cảm xúc rất khác nhau. Lỗi 3. Chốt lời sớm, gồng lỗ dài. Thắng thì ăn ít, thua thì lỗ nhiều. Cách sửa. Đặt sẵn chốt lời và cắt lỗ. Ban đầu cho 2 mức bằng nhau. Đặt xong thì đừng nhìn tài khoản. Giữ từ 1 tuần đến 1 tháng để thành thói quen. Ba lỗi như 3 tảng đá trên đường. Quay lại. Hoặc vượt qua từng tảng 1. Bạn đang vướng lỗi nào? Theo dõi sốt trading để học giao dịch bên vững hơn.</t>
+          <t>2 lệnh thắng, 1 lệnh thua vì 1 lỗi bất cảnh. Đây là 7 bài học đắt giá. 1. Su hướng gió là lợi thế lớn nhất. Nó không xuất hiện thường xuyên nên hãy kiên nhận trở. 2. Gom đủ 3 yếu tố rồi mới vào. Su hướng vung cản của phê mình và tín hiệu đến xác nhận. 3. Giá đã chạy xa thì đặt lệnh trở vùng đỉnh cũ. Không khớp cũng không mất tiền, tính khối lượng trước để biết thua mất bao nhiêu. Chốt lời mặc định gấp 2 lần rủi do. 4. Tận dụng núp phê nâu mở cửa, đầu giờ chiều giờ Việt Nam khi tín hiệu xuất hiện nhiều. 5. Vào lệnh xong đừng nhìn biểu đồ quá nhiều, nhìn nhiều dễ chốt sớm rồi tiếc, hãy gạt cảm xúc gắn với tiền. Chỉ vui khi làm đúng kịch bản, chỉ ái náy khi làm sai kịch bản. 6. Lệnh rủi do thì hoặc đứng ngoài, hoặc canh tới nơi tới chốn. Không canh được thì đóng lệnh. 7. Giữ điểm cắt lỗ, đừng rời hay bỏ, và xem lại lệnh cũ để thấy lỗi hay lặp lại. Còn vốn thì còn lấy lại được, và phần lời chính là kinh nghiệm, trở xu hướng rõ, đủ yếu tố mới vào, làm đúng kịch bản. Theo dõi SO Trading để học giao dịch có kỷ luật.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1:09</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695389393443409173</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695602506377809173</t>
         </is>
       </c>
     </row>
@@ -2790,27 +2790,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chứng khoán, tiền điện tử hay ngoại hối: chọn thị trường nào? So sánh...</t>
+          <t>3 lỗi tâm lý giao dịch khiến bạn cháy tài khoản (và cách sửa) Phương ...</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chứng khoán, tiền điện tử hay ngoại hối: chọn thị trường nào? So sánh 3 thị trường theo 4 đặc điểm: pháp lý, thanh khoản, thời gian giao dịch, nền tảng. Nguồn: nội dung do tác giả cung cấp. #Shorts #trading #xuhuong #crypto #fx</t>
+          <t>3 lỗi tâm lý giao dịch khiến bạn cháy tài khoản (và cách sửa) Phương pháp chỉ là một phần, tâm lý mới quyết định. 3 lỗi gần như ai cũng gặp: sợ bỏ lỡ (FOMO), trả thù thị trường, chốt lời sớm - gồng lỗ dài, cùng cách sửa đơn giản cho từng lỗi. Nguồn: nội dung BlackRose Admin (08/10/2026), biên soạn lại bởi SO TRADING. Nội dung chỉ mang tính tham khảo, không phải khuyến nghị đầu tư. #Shorts #trading #tamlygiaodich</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Trứng khoán, tiền điện tử hay ngoại hối, chọn sai thị trường là mất tiền. Bối thị trường có đặc điểm riêng, hãy xét bốn thứ, pháp lý, thanh khoản, thời gian giao dịch và nền tảng. Pháp lý, trứng khoán được nhà nước bảo hộ chặt trẽ. Tiền điện tử và ngoại hối thì chưa được công nhận. Vì vậy, giữ số tiền lớn lâu dài thì trứng khoán an toàn hơn, đừng ném cả tài sản vào sản không tên tuổi. Thanh khoản, ngoại hối lớn nhất, rồi trứng khoán, rồi tiền điện tử. Nhưng trứng khoán Việt Nam thấp nhất nên chỉ hợp đầu tư dài hạn. Cổ phiếu và tiền điện tử dễ bị thao túng, biến động vài chục phần trăm. Cặp tiền lệch 1 phần trăm 1 ngày đã là nhiều. Thời gian, trứng khoán chỉ mở khoảng 4 tiếng 1 ngày, ngoại hối 24h, 5 ngày, tiền điện tử 24h, 7 ngày, nền tảng. Sanh ngoại hối giao dịch được tiền tệ, tiền điện tử, chỉ số và vàng. Nhưng đó là hợp đồng tranh lệch bạn không sở hữu tài sản. Tóm lại, trứng khoán hợp dài hạn, ngoại hối chỉ hợp ngắn hạn. Tiền điện tử hợp cả 2 nhưng rủi do cao, và dù chọn thị trường nào cũng phải chọn sản uy tín. Sanh kém thì ở đâu cũng dễ mất tiền, theo dõi để học cách bảo vệ và làm sinh lời đồng vốn của bạn mỗi ngày.</t>
+          <t>Ba lỗi tâm lý này đang âm thầm đốt tài khoản của bạn. Phương pháp giao dịch không phải tất cả. Phần lớn thành công đến từ tâm lý. Lỗi 1. Sợ bỏ lỡ cơ hội. Thấy giá chạy, thấy người khác lời là vào lệnh bừa. Cách sửa, rời nhóm chát tín hiệu, tự luyện tập và xây chiến lược vào lệnh của riêng bạn. Lỗi 2. Chả thủ tị trường. Thua xong là gấp đôi khối lượng để gỡ lại. Cách sửa. Chỉ nắp ít khoảng 2 phần chăm vốn để có khoảng dừng mà tỉnh lại và đi từ nhỏ đến lớn. 10 đô và 1 nghìn đô cho cảm xúc rất khác nhau. Lỗi 3. Chốt lời sớm, gồng lỗ dài. Thắng thì ăn ít, thua thì lỗ nhiều. Cách sửa. Đặt sẵn chốt lời và cắt lỗ. Ban đầu cho 2 mức bằng nhau. Đặt xong thì đừng nhìn tài khoản. Giữ từ 1 tuần đến 1 tháng để thành thói quen. Ba lỗi như 3 tảng đá trên đường. Quay lại. Hoặc vượt qua từng tảng 1. Bạn đang vướng lỗi nào? Theo dõi sốt trading để học giao dịch bên vững hơn.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1:13</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7695191312605187348</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695389393443409173</t>
         </is>
       </c>
     </row>
@@ -2840,27 +2840,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Đầu tư và giao dịch khác nhau ở đâu? Đầu tư và giao dịch giống nhau ở...</t>
+          <t>Chứng khoán, tiền điện tử hay ngoại hối: chọn thị trường nào? So sánh...</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Đầu tư và giao dịch khác nhau ở đâu? Đầu tư và giao dịch giống nhau ở bản chất mua rẻ bán đắt, khác nhau ở thời gian giữ lệnh và tâm lý. Video giải thích ngắn gọn, dễ hiểu. #trading #fx #crypto</t>
+          <t>Chứng khoán, tiền điện tử hay ngoại hối: chọn thị trường nào? So sánh 3 thị trường theo 4 đặc điểm: pháp lý, thanh khoản, thời gian giao dịch, nền tảng. Nguồn: nội dung do tác giả cung cấp. #Shorts #trading #xuhuong #crypto #fx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Đầu tư và giao dịch khác nhau ở đâu? Hầu hết mọi người đều hiểu sai, ở cả 3 thị trường, bản chất đều giống nhau, mua giá thấp, bán giá cao, chứng khoán, mua bán cổ phiếu, tức quyền sở hữu một phần công ty, tiền điện tử là Bitcoin và các đồng khác. Ngoại hối là Đô Là Mỹ, Yên Nhật khác nhau chính là thời gian giữ lệnh, giữ nhiều tháng, nhiều năm là đầu tư. Giữ theo food, giờ, ngay là giao dịch, đầu tư không tốn nhiều thời gian như giao dịch, nhưng vẫn mang lại nguồn thu nhập tốt, nhưng có người đầu tư mà nhìn giá cả ngày, lỗ thì mất ngủ. Đó là tâm lý giao dịch, ngược lại, có người giao dịch ít lệnh và đúng lúc vẫn có thời gian cho việc khác, che tên sản phẩm đi, chỉ còn nến và giá. Chọn thị trường theo đặc điểm, không phải vì biết nó trước, đầu tư hay giao dịch chỉ đa, kết quả nằm ở cách bạn dùng nó, theo dõi để học thêm nha.</t>
+          <t>Trứng khoán, tiền điện tử hay ngoại hối, chọn sai thị trường là mất tiền. Bối thị trường có đặc điểm riêng, hãy xét bốn thứ, pháp lý, thanh khoản, thời gian giao dịch và nền tảng. Pháp lý, trứng khoán được nhà nước bảo hộ chặt trẽ. Tiền điện tử và ngoại hối thì chưa được công nhận. Vì vậy, giữ số tiền lớn lâu dài thì trứng khoán an toàn hơn, đừng ném cả tài sản vào sản không tên tuổi. Thanh khoản, ngoại hối lớn nhất, rồi trứng khoán, rồi tiền điện tử. Nhưng trứng khoán Việt Nam thấp nhất nên chỉ hợp đầu tư dài hạn. Cổ phiếu và tiền điện tử dễ bị thao túng, biến động vài chục phần trăm. Cặp tiền lệch 1 phần trăm 1 ngày đã là nhiều. Thời gian, trứng khoán chỉ mở khoảng 4 tiếng 1 ngày, ngoại hối 24h, 5 ngày, tiền điện tử 24h, 7 ngày, nền tảng. Sanh ngoại hối giao dịch được tiền tệ, tiền điện tử, chỉ số và vàng. Nhưng đó là hợp đồng tranh lệch bạn không sở hữu tài sản. Tóm lại, trứng khoán hợp dài hạn, ngoại hối chỉ hợp ngắn hạn. Tiền điện tử hợp cả 2 nhưng rủi do cao, và dù chọn thị trường nào cũng phải chọn sản uy tín. Sanh kém thì ở đâu cũng dễ mất tiền, theo dõi để học cách bảo vệ và làm sinh lời đồng vốn của bạn mỗi ngày.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1:13</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694935798524742932</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7695191312605187348</t>
         </is>
       </c>
     </row>
@@ -2890,27 +2890,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4 bước vào lệnh chuẩn: cấu trúc, khung lớn, vùng cản, tín hiệu yếu dầ...</t>
+          <t>Đầu tư và giao dịch khác nhau ở đâu? Đầu tư và giao dịch giống nhau ở...</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4 bước vào lệnh chuẩn: cấu trúc, khung lớn, vùng cản, tín hiệu yếu dần Phương pháp vào lệnh gồm bốn bước kèm ví dụ ETHUSD khung M15. Nội dung do tác giả chia sẻ, không phải lời khuyên đầu tư.  #trading #fx #cypto</t>
+          <t>Đầu tư và giao dịch khác nhau ở đâu? Đầu tư và giao dịch giống nhau ở bản chất mua rẻ bán đắt, khác nhau ở thời gian giữ lệnh và tâm lý. Video giải thích ngắn gọn, dễ hiểu. #trading #fx #crypto</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Vào lệnh, đúng không phải đoán mò. Mà đi theo bốn bước. Bước 1, xác định cấu trúc trên khung đang giao dịch. Bước 2, tìm thêm yêu tố ủng hộ ở khung lớn hơn một bậc. Bước 3, chờ giá hồi về vùng cản quan trọng. Bước 4, chờ phê ngược lại yếu dần rồi mới vào lệnh. Ví dụ mua ATHSD 015, giá phá đỉnh 2 lần, đáy quan trọng vẫn được giữ. Chờ giá hồi về đỉnh cũ rồi mới mua, cắt lỗ dưới vùng đó. Lệnh lời gấp 3 rủi do, không xem thêm chỉ cần lớn hơn một bậc. 15 xem, 1, 1 xem, hư bốn, hư bốn xem khung ngày, cách này dùng được cho mọi thị trường. Khung lớn ủng hộ rõ, chỉ cần tín hiệu vừa phải ở khung nhỏ. Duyên đời mới chỉ là một chân của cái kiểu 3 chân. Theo rõi để xem 2 chân còn lại. Quán lý vốn và kỷ luật.</t>
+          <t>Đầu tư và giao dịch khác nhau ở đâu? Hầu hết mọi người đều hiểu sai, ở cả 3 thị trường, bản chất đều giống nhau, mua giá thấp, bán giá cao, chứng khoán, mua bán cổ phiếu, tức quyền sở hữu một phần công ty, tiền điện tử là Bitcoin và các đồng khác. Ngoại hối là Đô Là Mỹ, Yên Nhật khác nhau chính là thời gian giữ lệnh, giữ nhiều tháng, nhiều năm là đầu tư. Giữ theo food, giờ, ngay là giao dịch, đầu tư không tốn nhiều thời gian như giao dịch, nhưng vẫn mang lại nguồn thu nhập tốt, nhưng có người đầu tư mà nhìn giá cả ngày, lỗ thì mất ngủ. Đó là tâm lý giao dịch, ngược lại, có người giao dịch ít lệnh và đúng lúc vẫn có thời gian cho việc khác, che tên sản phẩm đi, chỉ còn nến và giá. Chọn thị trường theo đặc điểm, không phải vì biết nó trước, đầu tư hay giao dịch chỉ đa, kết quả nằm ở cách bạn dùng nó, theo dõi để học thêm nha.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694847427051883796</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694935798524742932</t>
         </is>
       </c>
     </row>
@@ -2940,27 +2940,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cách đọc cấu trúc thị trường: biết ngay phe mua hay phe bán thắng Các...</t>
+          <t>4 bước vào lệnh chuẩn: cấu trúc, khung lớn, vùng cản, tín hiệu yếu dầ...</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cách đọc cấu trúc thị trường: biết ngay phe mua hay phe bán thắng Cách đọc cấu trúc tăng, cấu trúc giảm và vùng đi ngang để biết nên mua, bán hay đứng ngoài. Nguồn: nội dung do tác giả cung cấp. #Shorts</t>
+          <t>4 bước vào lệnh chuẩn: cấu trúc, khung lớn, vùng cản, tín hiệu yếu dần Phương pháp vào lệnh gồm bốn bước kèm ví dụ ETHUSD khung M15. Nội dung do tác giả chia sẻ, không phải lời khuyên đầu tư.  #trading #fx #cypto</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Phần lớn người giao dịch thua lỗ chỉ vì một lý do. Không biết phê nào đang thắng, họ đổi phương pháp liên tục, vào lệnh theo cảm hứng và càng thua càng mất kiểm soát. Việc đầu tiên cần làm là biết lực mua hay lực bán đang chiếm ưu thế. Cấu chúc tăng là đáy sau cao hơn đáy trước. Đỉnh sau cao hơn đỉnh trước. Cấu chúc giảm thì ngược lại. Đỉnh thấp dần và đáy thấp dần. Hãy coi đó là một cuộc chiến. Mỗi đỉnh cũ là căn cứ của phê bán. Phê mua phá qua thì phê bán phải lùi. Một đáy chỉ quan trọng khi con sóng đi lên từ đáy đó phá qua đỉnh cũ. Phá qua, nghĩa là nến đóng cửa vượt qua. Râu nến quét rồi rút lại thì không tính. Giá nằm giữa đỉnh cao nhất và đáy quan trọng thì bị kẹp, thường đi ngang. Phá xuống đáy quan trọng cũng chưa phải xu hướng giảm. Chỉ khi giá hồi lên rồi phá tiếp đáy vừa tạo. xu hướng giảm mới được xác nhận. Cấu chúc tăng thì yêu tiên mua. Cấu chúc giảm thì yêu tiên bán. Còn rằng co thì đứng ngoài. Theo dõi để học thêm cách đọc thị trường.</t>
+          <t>Vào lệnh, đúng không phải đoán mò. Mà đi theo bốn bước. Bước 1, xác định cấu trúc trên khung đang giao dịch. Bước 2, tìm thêm yêu tố ủng hộ ở khung lớn hơn một bậc. Bước 3, chờ giá hồi về vùng cản quan trọng. Bước 4, chờ phê ngược lại yếu dần rồi mới vào lệnh. Ví dụ mua ATHSD 015, giá phá đỉnh 2 lần, đáy quan trọng vẫn được giữ. Chờ giá hồi về đỉnh cũ rồi mới mua, cắt lỗ dưới vùng đó. Lệnh lời gấp 3 rủi do, không xem thêm chỉ cần lớn hơn một bậc. 15 xem, 1, 1 xem, hư bốn, hư bốn xem khung ngày, cách này dùng được cho mọi thị trường. Khung lớn ủng hộ rõ, chỉ cần tín hiệu vừa phải ở khung nhỏ. Duyên đời mới chỉ là một chân của cái kiểu 3 chân. Theo rõi để xem 2 chân còn lại. Quán lý vốn và kỷ luật.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694698536717356308</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694847427051883796</t>
         </is>
       </c>
     </row>
@@ -2990,27 +2990,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Học nhiều phương pháp vẫn mất tiền? Vì bạn chưa kiểm chứng Vì sao nhi...</t>
+          <t>Cách đọc cấu trúc thị trường: biết ngay phe mua hay phe bán thắng Các...</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Học nhiều phương pháp vẫn mất tiền? Vì bạn chưa kiểm chứng Vì sao nhiều người học phương pháp giao dịch vẫn thua lỗ, và cách kiểm chứng phương pháp bằng thống kê trước khi dùng tiền thật. #trading #crypto #btc #xuhuong</t>
+          <t>Cách đọc cấu trúc thị trường: biết ngay phe mua hay phe bán thắng Cách đọc cấu trúc tăng, cấu trúc giảm và vùng đi ngang để biết nên mua, bán hay đứng ngoài. Nguồn: nội dung do tác giả cung cấp. #Shorts</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Vì sao học nhiều phương pháp mà tài khoản vẫn cứ giảm, bạn tìm đủ loại phương pháp, cái nào nghe cũng hay như bí quyết, nhưng khi áp dụng thật, tài khoản cứ giảm dần vì có rất ít phương pháp thực sự đúng. Ngắn hạn, phương pháp nào cũng có lúc thắng lúc thua. Vào bừa cũng chỉ có 2 khả năng giá lên hoặc giá xuống. Vì vậy, hãy thống kê hàng trăm hàng nghìn lệnh. Nếu tỷ lệ thắng chỉ 50-50 thì chẳng khác gì may dùi. Hãy bỏ kiến thức chấp vá quay về biểu đồ giá. Mua giá thấp, bán giá cao hơn thì lời. Ngược lại thì lỗ, dù là chuyên gia hay người mới, lời hay lỗ cũng chỉ do giá. Hiểu cách giá di chuyển, bạn sẽ thấy quy luật, rút ra quý tắc, rồi kiểm trứng qua hàng trăm lệnh để biết tỷ lệ thắng và tỷ lệ lợi nhuận trên rủi do. Dùng tiền thật khi chưa kiểm trứng, giống như đi trong dừng mà không biết lối ra. Lộ trình đúng là tự nghiên cứu, thống kê kiểm trứng, rồi mới dùng tiền thật. Theo dõi kênh để học cách kiểm trứng phương pháp của riêng bạn.</t>
+          <t>Phần lớn người giao dịch thua lỗ chỉ vì một lý do. Không biết phê nào đang thắng, họ đổi phương pháp liên tục, vào lệnh theo cảm hứng và càng thua càng mất kiểm soát. Việc đầu tiên cần làm là biết lực mua hay lực bán đang chiếm ưu thế. Cấu chúc tăng là đáy sau cao hơn đáy trước. Đỉnh sau cao hơn đỉnh trước. Cấu chúc giảm thì ngược lại. Đỉnh thấp dần và đáy thấp dần. Hãy coi đó là một cuộc chiến. Mỗi đỉnh cũ là căn cứ của phê bán. Phê mua phá qua thì phê bán phải lùi. Một đáy chỉ quan trọng khi con sóng đi lên từ đáy đó phá qua đỉnh cũ. Phá qua, nghĩa là nến đóng cửa vượt qua. Râu nến quét rồi rút lại thì không tính. Giá nằm giữa đỉnh cao nhất và đáy quan trọng thì bị kẹp, thường đi ngang. Phá xuống đáy quan trọng cũng chưa phải xu hướng giảm. Chỉ khi giá hồi lên rồi phá tiếp đáy vừa tạo. xu hướng giảm mới được xác nhận. Cấu chúc tăng thì yêu tiên mua. Cấu chúc giảm thì yêu tiên bán. Còn rằng co thì đứng ngoài. Theo dõi để học thêm cách đọc thị trường.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694588383363861781</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694698536717356308</t>
         </is>
       </c>
     </row>
@@ -3040,27 +3040,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Giá hồi cạn kiệt chưa? Cách chờ phe bán thất bại trước khi vào lệnh #...</t>
+          <t>Học nhiều phương pháp vẫn mất tiền? Vì bạn chưa kiểm chứng Vì sao nhi...</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Giá hồi cạn kiệt chưa? Cách chờ phe bán thất bại trước khi vào lệnh #Shorts Khi nào nhịp hồi trong xu hướng đã cạn kiệt để vào lệnh thuận xu hướng? Tóm tắt cách đọc lực mua bán bằng hành động giá: chờ phe bán thất bại 2–3 lần, có nến xác nhận rồi mới vào, đặt dừng lỗ dưới vùng cản và chốt lời ở vùng phe bán.</t>
+          <t>Học nhiều phương pháp vẫn mất tiền? Vì bạn chưa kiểm chứng Vì sao nhiều người học phương pháp giao dịch vẫn thua lỗ, và cách kiểm chứng phương pháp bằng thống kê trước khi dùng tiền thật. #trading #crypto #btc #xuhuong</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Giá vừa hồi về vùng cản bạn có nên mua ngay không? Câu trả lời thường là chưa. Giao dịch theo xu hướng nghĩa là, xu hướng tăng thì canh mua, xu hướng giảm thì canh bán. Nhưng không ai đuổi theo giá đã chạy xa vì càng đi xa, lực mua càng yếu dần. Bạn chỉ vào lệnh khi giá hồi và đồng thời phải hỏi. Nhịp hồi này đã cạn kiệt thật chưa? Hãy nhìn lực hay phè. Tại vùng cản phê mua, hối lượng mua lớn hơn bán nên giá bật lên. Nếu phê bán phá được vùng đó, nó thành vùng của phê bán. Và giá sẽ tiếp tục bị đẩy xuống. Dấu hiệu cạn kiệt là phê bán nhiều lần không phán nổi vùng giá. Hai đáy là lực bán giảm. Ba đáy kèm đến mua mạnh mới là cơ hội đẹp. Còn chưa có tín hiệu thì cứ đứng ngoài chờ. Đừng mua vội nếu điểm dừng lỗ quá xa hoặc điểm vào sát vùng cản của phê bán. Dừng lỗ dưới vùng cản phê mua, chốt lời ở vùng phê bán. Không có gì chắc chắn 100% thì bạn kiểm soát được là tỷ lệ thắng và tỷ lệ lợi nhuận trên rủi do. Kinh nhẫn trở phê, bán thất bại, theo dõi để học thêm cách độc lực mua bán và đừng vào lệnh khi nhịp hồi chưa cạn kiệt.</t>
+          <t>Vì sao học nhiều phương pháp mà tài khoản vẫn cứ giảm, bạn tìm đủ loại phương pháp, cái nào nghe cũng hay như bí quyết, nhưng khi áp dụng thật, tài khoản cứ giảm dần vì có rất ít phương pháp thực sự đúng. Ngắn hạn, phương pháp nào cũng có lúc thắng lúc thua. Vào bừa cũng chỉ có 2 khả năng giá lên hoặc giá xuống. Vì vậy, hãy thống kê hàng trăm hàng nghìn lệnh. Nếu tỷ lệ thắng chỉ 50-50 thì chẳng khác gì may dùi. Hãy bỏ kiến thức chấp vá quay về biểu đồ giá. Mua giá thấp, bán giá cao hơn thì lời. Ngược lại thì lỗ, dù là chuyên gia hay người mới, lời hay lỗ cũng chỉ do giá. Hiểu cách giá di chuyển, bạn sẽ thấy quy luật, rút ra quý tắc, rồi kiểm trứng qua hàng trăm lệnh để biết tỷ lệ thắng và tỷ lệ lợi nhuận trên rủi do. Dùng tiền thật khi chưa kiểm trứng, giống như đi trong dừng mà không biết lối ra. Lộ trình đúng là tự nghiên cứu, thống kê kiểm trứng, rồi mới dùng tiền thật. Theo dõi kênh để học cách kiểm trứng phương pháp của riêng bạn.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1:03</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694492170773908757</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694588383363861781</t>
         </is>
       </c>
     </row>
@@ -3090,27 +3090,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tìm vùng mua Bitcoin bằng cuộc chiến mua bán | Nến nhấn chìm + Fibona...</t>
+          <t>Giá hồi cạn kiệt chưa? Cách chờ phe bán thất bại trước khi vào lệnh #...</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tìm vùng mua Bitcoin bằng cuộc chiến mua bán | Nến nhấn chìm + Fibonacci Cách đọc cuộc chiến phe mua - phe bán để tìm vùng mua Bitcoin, kết hợp nến nhấn chìm, Fibonacci và chia vốn nhiều giỏ.  #trading #crypto #btc</t>
+          <t>Giá hồi cạn kiệt chưa? Cách chờ phe bán thất bại trước khi vào lệnh #Shorts Khi nào nhịp hồi trong xu hướng đã cạn kiệt để vào lệnh thuận xu hướng? Tóm tắt cách đọc lực mua bán bằng hành động giá: chờ phe bán thất bại 2–3 lần, có nến xác nhận rồi mới vào, đặt dừng lỗ dưới vùng cản và chốt lời ở vùng phe bán.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bitcoin giảm sâu, nhưng có một vùng giá mà phê mua luôn lao vào. Bạn có biết nó nằm ở đâu không? Thì trường tiền điện tử chạy theo Bitcoin. Bitcoin chiếm phần lớn vốn hóa nên nó tăng thì cả thị trường tăng theo. Nguồn đọc giá, hãy nhìn cuộc chiến mua bán. Phê mua đẩy giá lên, rồi phê bán lại kéo giá xuống. Khi giá phá vùng cản của phê mua, phê bán chiếm yếu thế, hãy tìm vùng cản kế tiếp của phê mua nơi giá có thể bật lại. Phê bán thất bại nhiều lần, bóng đến dài kéo giá lên. Đây là dấu hiệu lực bán đang yếu dần, đừng vội vào lệnh. Hãy chờ tín hiệu rõ ràng, như cặp nên nhấn chìm tăng giá tại vùng cản mạnh. Vùng đó càng đáng tin khi chùng với mức Fibonacci của sống tăng trước đó. Các đồng lớn đều tạo tín hiệu tương tự. Sau khi đã giảm sâu từ 60 đến 70-3% mua ở vùng này, nếu giá giảm thêm thì bạn vẫn mua rẻ hơn người mua ở đỉnh. Giá quay lại đỉnh, bạn đã lại gấp đôi, đừng bỏ hết, vốn vào một giò. Chiếc vào nhiều đồng lớn, chỉ cần một đồng bay cao là đủ bù các đồng còn lại. Theo dõi để xem thêm phân tích mỗi ngày, đây không phải lời khuyên tài chính.</t>
+          <t>Giá vừa hồi về vùng cản bạn có nên mua ngay không? Câu trả lời thường là chưa. Giao dịch theo xu hướng nghĩa là, xu hướng tăng thì canh mua, xu hướng giảm thì canh bán. Nhưng không ai đuổi theo giá đã chạy xa vì càng đi xa, lực mua càng yếu dần. Bạn chỉ vào lệnh khi giá hồi và đồng thời phải hỏi. Nhịp hồi này đã cạn kiệt thật chưa? Hãy nhìn lực hay phè. Tại vùng cản phê mua, hối lượng mua lớn hơn bán nên giá bật lên. Nếu phê bán phá được vùng đó, nó thành vùng của phê bán. Và giá sẽ tiếp tục bị đẩy xuống. Dấu hiệu cạn kiệt là phê bán nhiều lần không phán nổi vùng giá. Hai đáy là lực bán giảm. Ba đáy kèm đến mua mạnh mới là cơ hội đẹp. Còn chưa có tín hiệu thì cứ đứng ngoài chờ. Đừng mua vội nếu điểm dừng lỗ quá xa hoặc điểm vào sát vùng cản của phê bán. Dừng lỗ dưới vùng cản phê mua, chốt lời ở vùng phê bán. Không có gì chắc chắn 100% thì bạn kiểm soát được là tỷ lệ thắng và tỷ lệ lợi nhuận trên rủi do. Kinh nhẫn trở phê, bán thất bại, theo dõi để học thêm cách độc lực mua bán và đừng vào lệnh khi nhịp hồi chưa cạn kiệt.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1:05</t>
+          <t>1:03</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694281608039271701</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694492170773908757</t>
         </is>
       </c>
     </row>
@@ -3140,27 +3140,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Thị trường đi ngang: nhận biết &amp; tránh bị quét lệnh. #trading #fx #xu...</t>
+          <t>Tìm vùng mua Bitcoin bằng cuộc chiến mua bán | Nến nhấn chìm + Fibona...</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thị trường đi ngang: nhận biết &amp; tránh bị quét lệnh. #trading #fx #xuhuong</t>
+          <t>Tìm vùng mua Bitcoin bằng cuộc chiến mua bán | Nến nhấn chìm + Fibonacci Cách đọc cuộc chiến phe mua - phe bán để tìm vùng mua Bitcoin, kết hợp nến nhấn chìm, Fibonacci và chia vốn nhiều giỏ.  #trading #crypto #btc</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lệnh của bạn hay bị quét. Thủ phạm chính là thị trường đi ngang. Thực tế không có lý thuyết nào xác định chính xác khi nào thị trường đi ngang. Nhưng có một cách dễ hiểu. Nhìn cuộc chiến giữa phê mua và phê bán. Phê mua phá đỉnh, phê bán phá đáy thì su hướng rõ ràng. Nhưng khi cả hai cùng thất bại, không ai chiêm yêu thế, thị trường bắt đầu đi ngang. Dấu hiệu nhận biết, ít nhất hai đỉnh và hai đáy ra cứ bật lại trong một hình chữ nhật. Thực tế, đỉnh đáy có thể lệch một chút. Giá phản ứng càng nhiều ở hai vùng cản thì vùng đi ngang cảng rõ. Chỉ khi một con sóng mạnh phá ra ngoài, một phê mới thật sự chiến thắng. Hãy chú ý biên độ. Nếu vùng đi ngang quá nhỏ so với sóng trước đó, su hướng cũ gần như không bị ảnh hưởng. Hãy nhìn khung thời gian lớn hơn. Đoạn trông như su hướng ở khung nhỏ có thể chỉ là một phần của vùng đi ngang ở khung H4 hay ngày. Ví dụ, giá hồi về vùng cản của phê bán, đỉnh thấp dần, rồi nến xanh phá vùng cản xác nhận lực bán đá cạn. Đó là điểm vào lệnh mua. Đặt cắt lỗ sau vùng cản, chốt lời ở các vùng cản kế tiếp và đừng chỉ chốt ở tỷ lệ một ăn một. Cần có lý do để kỳ vọng tỷ lệ cao hơn. Muốn xác xuất thắng cao. Hãy đứng ngoài khi thị trường đi ngang theo dõi để học thêm nhé!</t>
+          <t>Bitcoin giảm sâu, nhưng có một vùng giá mà phê mua luôn lao vào. Bạn có biết nó nằm ở đâu không? Thì trường tiền điện tử chạy theo Bitcoin. Bitcoin chiếm phần lớn vốn hóa nên nó tăng thì cả thị trường tăng theo. Nguồn đọc giá, hãy nhìn cuộc chiến mua bán. Phê mua đẩy giá lên, rồi phê bán lại kéo giá xuống. Khi giá phá vùng cản của phê mua, phê bán chiếm yếu thế, hãy tìm vùng cản kế tiếp của phê mua nơi giá có thể bật lại. Phê bán thất bại nhiều lần, bóng đến dài kéo giá lên. Đây là dấu hiệu lực bán đang yếu dần, đừng vội vào lệnh. Hãy chờ tín hiệu rõ ràng, như cặp nên nhấn chìm tăng giá tại vùng cản mạnh. Vùng đó càng đáng tin khi chùng với mức Fibonacci của sống tăng trước đó. Các đồng lớn đều tạo tín hiệu tương tự. Sau khi đã giảm sâu từ 60 đến 70-3% mua ở vùng này, nếu giá giảm thêm thì bạn vẫn mua rẻ hơn người mua ở đỉnh. Giá quay lại đỉnh, bạn đã lại gấp đôi, đừng bỏ hết, vốn vào một giò. Chiếc vào nhiều đồng lớn, chỉ cần một đồng bay cao là đủ bù các đồng còn lại. Theo dõi để xem thêm phân tích mỗi ngày, đây không phải lời khuyên tài chính.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1:11</t>
+          <t>1:05</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694189318134369556</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694281608039271701</t>
         </is>
       </c>
     </row>
@@ -3190,27 +3190,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lý thuyết Dow: vì sao vào lệnh theo sách vẫn thua? Lý thuyết Dow là n...</t>
+          <t>Thị trường đi ngang: nhận biết &amp; tránh bị quét lệnh. #trading #fx #xu...</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lý thuyết Dow: vì sao vào lệnh theo sách vẫn thua? Lý thuyết Dow là nền móng của phân tích kỹ thuật, nhưng áp dụng quá cứng nhắc rất dễ thua. Video tóm tắt nhược điểm của định nghĩa xu hướng và cách hỏi "phe mua hay phe bán đang chiếm ưu thế" trước mỗi lệnh. #trading #fx #xuhuong</t>
+          <t>Thị trường đi ngang: nhận biết &amp; tránh bị quét lệnh. #trading #fx #xuhuong</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Học lý thuyết đào mà vào lệnh vẫn thua. Vấn đề nằm ở chỗ áp dụng quá cứng nhắc. Lý thuyết đào là nền móng của phân tích kỹ thuật. Nhưng chỉ thuộc định nghĩa thì chưa đủ để giao dịch. Theo sách, gia pha đáy quan trọng nghĩa là su hướng tăng đã đảo chiều thành giảm. Nhưng đáy nào mới là đáy quan trọng. Khung hết bốn và khung hết, một cho da hai đáy khác nhau. Nhiều khi bạn vội canh bán, giá lại chạm vùng cản của phê mua và bật tăng trở lại. Bởi phá đáy ở khung nhỏ chỉ cho thấy phê bán thắng một hiệp. Bức tranh lớn, phê mua vẫn mạnh hơn. Vậy hãy tự hỏi, lúc này phê mua hay phê bán đang chiếm yêu thế? Vẽ các vùng cản gần nhất của hai phê, rồi so sánh xóng giảm với xóng tăng trước đó. Phê mua còn mạnh thì canh mua ở vùng cản của phê mua đặt cắt lỗ bên dưới, chốt lời ở các vùng cản phía trên. Đừng áp dụng máy móc, theo dõi kênh để học cách vào lệnh theo su hướng hiệu quả.</t>
+          <t>Lệnh của bạn hay bị quét. Thủ phạm chính là thị trường đi ngang. Thực tế không có lý thuyết nào xác định chính xác khi nào thị trường đi ngang. Nhưng có một cách dễ hiểu. Nhìn cuộc chiến giữa phê mua và phê bán. Phê mua phá đỉnh, phê bán phá đáy thì su hướng rõ ràng. Nhưng khi cả hai cùng thất bại, không ai chiêm yêu thế, thị trường bắt đầu đi ngang. Dấu hiệu nhận biết, ít nhất hai đỉnh và hai đáy ra cứ bật lại trong một hình chữ nhật. Thực tế, đỉnh đáy có thể lệch một chút. Giá phản ứng càng nhiều ở hai vùng cản thì vùng đi ngang cảng rõ. Chỉ khi một con sóng mạnh phá ra ngoài, một phê mới thật sự chiến thắng. Hãy chú ý biên độ. Nếu vùng đi ngang quá nhỏ so với sóng trước đó, su hướng cũ gần như không bị ảnh hưởng. Hãy nhìn khung thời gian lớn hơn. Đoạn trông như su hướng ở khung nhỏ có thể chỉ là một phần của vùng đi ngang ở khung H4 hay ngày. Ví dụ, giá hồi về vùng cản của phê bán, đỉnh thấp dần, rồi nến xanh phá vùng cản xác nhận lực bán đá cạn. Đó là điểm vào lệnh mua. Đặt cắt lỗ sau vùng cản, chốt lời ở các vùng cản kế tiếp và đừng chỉ chốt ở tỷ lệ một ăn một. Cần có lý do để kỳ vọng tỷ lệ cao hơn. Muốn xác xuất thắng cao. Hãy đứng ngoài khi thị trường đi ngang theo dõi để học thêm nhé!</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1:11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7694116254126263573</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694189318134369556</t>
         </is>
       </c>
     </row>
@@ -3240,27 +3240,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vai Đầu Vai: 3 dấu hiệu mô hình đẹp và 2 điểm vào lệnh #Shorts Cách c...</t>
+          <t>Lý thuyết Dow: vì sao vào lệnh theo sách vẫn thua? Lý thuyết Dow là n...</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Vai Đầu Vai: 3 dấu hiệu mô hình đẹp và 2 điểm vào lệnh #Shorts Cách chọn mô hình Vai Đầu Vai đẹp và hai điểm vào lệnh. Tóm ý từ video 'Phương Pháp Vào Lệnh Với Mô Hình VAI ĐẦU VAI Hoàn Hảo'</t>
+          <t>Lý thuyết Dow: vì sao vào lệnh theo sách vẫn thua? Lý thuyết Dow là nền móng của phân tích kỹ thuật, nhưng áp dụng quá cứng nhắc rất dễ thua. Video tóm tắt nhược điểm của định nghĩa xu hướng và cách hỏi "phe mua hay phe bán đang chiếm ưu thế" trước mỗi lệnh. #trading #fx #xuhuong</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Vài đầu vai nhìn đâu cũng thấy nhưng đa số vào lệnh sai ngay từ đầu. Vài đầu vai có 3 đỉnh, đỉnh giữa cao nhất, báo hiệu giá đảo chiều từ tăng sang giảm. Nhưng giá chỉ thật sự đảo chiều khi phá qua đường neckline, chưa phá thì phê bán chưa thắng. Dấu hiệu 1, các đỉnh trạm neckline phải nằm ngang nhau, không lệch quá nhiều. Dấu hiệu 2, vai phải càng gần neckline, phê bán càng yếu và điểm cắt lỗ càng gần. Dấu hiệu 3, mỗi bên có thể có nhiều vai, tranh chấp càng lâu thì cú phá càng đáng tin. Điểm vào thứ nhất, giá đóng cửa vượt neckline thì vào lệnh, cắt lỗ ở mức gần nhất. Điểm vào thứ 2, nếu nên phá quá dài, hãy chờ giá hồi về neckline dù mới vào, cẩn thận. Mô hình nhỏ nằm trong su hương lớn, ngược chiều rất dễ thất bại, hãy nhìn thêm vùng cản gần đó. Nếu giá chỉ chạy được 1 error thì bỏ qua, lưu lại 3 dấu hiệu này và theo dõi để học thêm. Nội dung chỉ mang tính giáo dục.</t>
+          <t>Học lý thuyết đào mà vào lệnh vẫn thua. Vấn đề nằm ở chỗ áp dụng quá cứng nhắc. Lý thuyết đào là nền móng của phân tích kỹ thuật. Nhưng chỉ thuộc định nghĩa thì chưa đủ để giao dịch. Theo sách, gia pha đáy quan trọng nghĩa là su hướng tăng đã đảo chiều thành giảm. Nhưng đáy nào mới là đáy quan trọng. Khung hết bốn và khung hết, một cho da hai đáy khác nhau. Nhiều khi bạn vội canh bán, giá lại chạm vùng cản của phê mua và bật tăng trở lại. Bởi phá đáy ở khung nhỏ chỉ cho thấy phê bán thắng một hiệp. Bức tranh lớn, phê mua vẫn mạnh hơn. Vậy hãy tự hỏi, lúc này phê mua hay phê bán đang chiếm yêu thế? Vẽ các vùng cản gần nhất của hai phê, rồi so sánh xóng giảm với xóng tăng trước đó. Phê mua còn mạnh thì canh mua ở vùng cản của phê mua đặt cắt lỗ bên dưới, chốt lời ở các vùng cản phía trên. Đừng áp dụng máy móc, theo dõi kênh để học cách vào lệnh theo su hướng hiệu quả.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693923604710378772</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7694116254126263573</t>
         </is>
       </c>
     </row>
@@ -3290,27 +3290,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3 Bước Để Có Điểm Vào Lệnh Hoàn Hảo | Đọc Biểu Đồ Từ Khung Lớn Cách t...</t>
+          <t>Vai Đầu Vai: 3 dấu hiệu mô hình đẹp và 2 điểm vào lệnh #Shorts Cách c...</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3 Bước Để Có Điểm Vào Lệnh Hoàn Hảo | Đọc Biểu Đồ Từ Khung Lớn Cách tìm điểm vào lệnh có nhiều yếu tố ủng hộ: từ khung ngày, H4 đến H1. Nội dung chỉ để học, không phải lời khuyên đầu tư. #trading #fx #crypto</t>
+          <t>Vai Đầu Vai: 3 dấu hiệu mô hình đẹp và 2 điểm vào lệnh #Shorts Cách chọn mô hình Vai Đầu Vai đẹp và hai điểm vào lệnh. Tóm ý từ video 'Phương Pháp Vào Lệnh Với Mô Hình VAI ĐẦU VAI Hoàn Hảo'</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bạn vào lệnh đúng lúc mà vẫn thua. Vấn đề nằm ở chỗ này, điểm vào đẹp không đến từ một cây nén mà từ nhiều yếu tố cùng ủng hộ. Bước 1, nhìn khu ngài chỉ vẽ vùng cung cầu gần nhất. Một cây nén tăng quá mạnh thường không bền, đó là vùng bán tiềm năng. Bước 2, sang khung 4 giờ, chờ giá phá vùng cản bằng đến thân dài. Nên thân ngắn hay giúp chân thì cẩn thận rất dễ là phá giả. Bước 3, đừng đuổi giá, hãy chờ giá hồi về vùng rồi mới tìm tín hiệu. Mẫu nén đẹp chưa đủ, phải thấy bên kia lao vào rồi thất bại. Đừng dùng quá nhiều khung thời gian vì sẽ làm dối phân tích của bạn. Dừng lỗ đặt trên vùng cản, chốt lời mặc định khoảng 2 error. Đừng đặt chốt lời quá xa, chỉ cần thắng trên 50% là đã có lời. Lưu video lại và theo dõi để xem thêm cách đọc biểu đồ nhé.</t>
+          <t>Vài đầu vai nhìn đâu cũng thấy nhưng đa số vào lệnh sai ngay từ đầu. Vài đầu vai có 3 đỉnh, đỉnh giữa cao nhất, báo hiệu giá đảo chiều từ tăng sang giảm. Nhưng giá chỉ thật sự đảo chiều khi phá qua đường neckline, chưa phá thì phê bán chưa thắng. Dấu hiệu 1, các đỉnh trạm neckline phải nằm ngang nhau, không lệch quá nhiều. Dấu hiệu 2, vai phải càng gần neckline, phê bán càng yếu và điểm cắt lỗ càng gần. Dấu hiệu 3, mỗi bên có thể có nhiều vai, tranh chấp càng lâu thì cú phá càng đáng tin. Điểm vào thứ nhất, giá đóng cửa vượt neckline thì vào lệnh, cắt lỗ ở mức gần nhất. Điểm vào thứ 2, nếu nên phá quá dài, hãy chờ giá hồi về neckline dù mới vào, cẩn thận. Mô hình nhỏ nằm trong su hương lớn, ngược chiều rất dễ thất bại, hãy nhìn thêm vùng cản gần đó. Nếu giá chỉ chạy được 1 error thì bỏ qua, lưu lại 3 dấu hiệu này và theo dõi để học thêm. Nội dung chỉ mang tính giáo dục.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693801024087264533</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693923604710378772</t>
         </is>
       </c>
     </row>
@@ -3340,27 +3340,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3 bước tìm điểm vào lệnh đẹp trong trading Cách chọn điểm vào lệnh đơ...</t>
+          <t>3 Bước Để Có Điểm Vào Lệnh Hoàn Hảo | Đọc Biểu Đồ Từ Khung Lớn Cách t...</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3 bước tìm điểm vào lệnh đẹp trong trading Cách chọn điểm vào lệnh đơn giản: nhìn cấu trúc thị trường, tìm vùng mua tiềm năng, chờ tín hiệu 3 giai đoạn. #trading #fx #crypto</t>
+          <t>3 Bước Để Có Điểm Vào Lệnh Hoàn Hảo | Đọc Biểu Đồ Từ Khung Lớn Cách tìm điểm vào lệnh có nhiều yếu tố ủng hộ: từ khung ngày, H4 đến H1. Nội dung chỉ để học, không phải lời khuyên đầu tư. #trading #fx #crypto</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Một điểm và lệnh đơn giản mà rất nhiều người bỏ qua. Bước 1, nhìn cấu chúc thị trường. Tăng, giảm, đi ngang có quy luật hoặc đi ngang không quy luật, đi ngang không quy luật thì đứng ngoài. Vì rất dễ bị quét lệnh. Bước 2, tìm vùng mua tiềm năng. Đó là đầu con sóng tăng và đỉnh cũ vừa bị phá. Nhưng nếu giá phá quá yếu hoặc phá xa rồi bị kéo về mạnh thì vùng đó không còn tốt. Khi Phi Bonacci không phải 5 hoặc không phải 6, 1, 8 trùng đỉnh cũ, đó là vùng đẹp. Bước 3, trở tín hiệu. Giá chạm vùng có thể đảo chiều, quét giả hoặc đi tiếp. Giai đoạn 1, lực bán yếu dần, nén giút chân, giai đoạn 2, tranh chấp, những cây, nén nhỏ, đi ngang. Giai đoạn 3, một nén tăng mạnh bứt phá, xác nhận xu hướng. Thếu một giai đoạn thì đứng ngoài, kiên nhẫn, quản lý vốn, kiểm tra lại nhiều lần. Ý hiệu ích thì nhấn thích và đăng ký nhé. Nội dung chỉ để học, không phải lời quên đầu tư.</t>
+          <t>Bạn vào lệnh đúng lúc mà vẫn thua. Vấn đề nằm ở chỗ này, điểm vào đẹp không đến từ một cây nén mà từ nhiều yếu tố cùng ủng hộ. Bước 1, nhìn khu ngài chỉ vẽ vùng cung cầu gần nhất. Một cây nén tăng quá mạnh thường không bền, đó là vùng bán tiềm năng. Bước 2, sang khung 4 giờ, chờ giá phá vùng cản bằng đến thân dài. Nên thân ngắn hay giúp chân thì cẩn thận rất dễ là phá giả. Bước 3, đừng đuổi giá, hãy chờ giá hồi về vùng rồi mới tìm tín hiệu. Mẫu nén đẹp chưa đủ, phải thấy bên kia lao vào rồi thất bại. Đừng dùng quá nhiều khung thời gian vì sẽ làm dối phân tích của bạn. Dừng lỗ đặt trên vùng cản, chốt lời mặc định khoảng 2 error. Đừng đặt chốt lời quá xa, chỉ cần thắng trên 50% là đã có lời. Lưu video lại và theo dõi để xem thêm cách đọc biểu đồ nhé.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693735707138854164</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693801024087264533</t>
         </is>
       </c>
     </row>
@@ -3390,27 +3390,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vùng cung cầu trong trading. #trading #fx #Shorts</t>
+          <t>3 bước tìm điểm vào lệnh đẹp trong trading Cách chọn điểm vào lệnh đơ...</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Vùng cung cầu trong trading. #trading #fx #Shorts</t>
+          <t>3 bước tìm điểm vào lệnh đẹp trong trading Cách chọn điểm vào lệnh đơn giản: nhìn cấu trúc thị trường, tìm vùng mua tiềm năng, chờ tín hiệu 3 giai đoạn. #trading #fx #crypto</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bẽ vùng cầu càng nhiều đường, bạn càng thua nhiều hơn, vì sao vùng cầu là nơi phe mua thắng thế, còn vùng cung là nơi phe bán thắng thế. Psylum phổ biến là vẽ mọi đường ngang đi qua thật nhiều đỉnh và đáy. Cách này không có quy tắc, đường nào cũng đúng, nên bạn không thể giao dịch được. Cách đúng thứ nhất, chỉ vẽ những vùng gần giá hiện tại nhất. Thứ 2, vẽ từ điểm cao nhất hoặc thấp nhất của đỉnh và đáy. Thứ 3, giá rời vùng càng nhanh và mạnh, vùng đó càng mạnh, nhưng vùng mạnh cũng đừng vào bừa. Hay chờ tín hiệu nên rõ ràng rồi, mới vào lệnh. Ví dụ thực tế, khung lớn phá đỉnh đi lên, giá hồi về vùng cầu, rồi tạo tín hiệu mua, sau đó giá tăng mạnh và chạm mục tiêu chốt lời. Kênh nhẫn chờ tín hiệu giúp bạn tránh một lệnh thua, theo dõi để xem thêm cách đọc biểu đồ, nội dung chỉ để học hỏi, không phải lời khuyên đầu tư.</t>
+          <t>Một điểm và lệnh đơn giản mà rất nhiều người bỏ qua. Bước 1, nhìn cấu chúc thị trường. Tăng, giảm, đi ngang có quy luật hoặc đi ngang không quy luật, đi ngang không quy luật thì đứng ngoài. Vì rất dễ bị quét lệnh. Bước 2, tìm vùng mua tiềm năng. Đó là đầu con sóng tăng và đỉnh cũ vừa bị phá. Nhưng nếu giá phá quá yếu hoặc phá xa rồi bị kéo về mạnh thì vùng đó không còn tốt. Khi Phi Bonacci không phải 5 hoặc không phải 6, 1, 8 trùng đỉnh cũ, đó là vùng đẹp. Bước 3, trở tín hiệu. Giá chạm vùng có thể đảo chiều, quét giả hoặc đi tiếp. Giai đoạn 1, lực bán yếu dần, nén giút chân, giai đoạn 2, tranh chấp, những cây, nén nhỏ, đi ngang. Giai đoạn 3, một nén tăng mạnh bứt phá, xác nhận xu hướng. Thếu một giai đoạn thì đứng ngoài, kiên nhẫn, quản lý vốn, kiểm tra lại nhiều lần. Ý hiệu ích thì nhấn thích và đăng ký nhé. Nội dung chỉ để học, không phải lời quên đầu tư.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693564151402302740</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693735707138854164</t>
         </is>
       </c>
     </row>
@@ -3440,27 +3440,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2 mẫu nến đảo chiều đáng học: chòm râu &amp; nhấn chìm lần hai Đọc nến từ...</t>
+          <t>Vùng cung cầu trong trading. #trading #fx #Shorts</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2 mẫu nến đảo chiều đáng học: chòm râu &amp; nhấn chìm lần hai Đọc nến từ bản chất mua – bán và 2 mẫu nến đảo chiều tại vùng cản. Nội dung chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #trading #fx</t>
+          <t>Vùng cung cầu trong trading. #trading #fx #Shorts</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nên nhấn chìm xuất hiện là đảo chiều. Chưa chắc đâu, mỗi cây nén là một cuộc chiến giữa phê mua và phê bán. Nén có 5 yếu tố, giám mở, giá đóng, cao nhất, thấp nhất và thời gian. Sau một sóng tăng, nên nhấn chìm giảm chỉ là nhịp hồi. Lực mua vẫn còn bẫu thứ nhất. Nên chỏm râu, từ 3 cây có râu dài trở lên. Râu càng dài, thị trường càng từ chối giám mạnh tại vùng đó. Bẫu thứ 2, nên nhấn chìm mở đỉnh, hoặc đáy lần thứ 2, đừng vào ở lần chạm đầu, hãy đợi nến đóng cửa rồi mới hành động. Đặt cắt lỗ dưới râu nén hoặc dưới vùng cản để kiểm soát rủi do. Điểm vào tốt phải có quý tắc rõ ràng đến nơi chỉ việc kiểm tra. Hãy tự hỏi, phê nào đang mạnh hơn? Theo dõi để học thêm và nhớ đây chỉ là kiến thức giáo dục.</t>
+          <t>Bẽ vùng cầu càng nhiều đường, bạn càng thua nhiều hơn, vì sao vùng cầu là nơi phe mua thắng thế, còn vùng cung là nơi phe bán thắng thế. Psylum phổ biến là vẽ mọi đường ngang đi qua thật nhiều đỉnh và đáy. Cách này không có quy tắc, đường nào cũng đúng, nên bạn không thể giao dịch được. Cách đúng thứ nhất, chỉ vẽ những vùng gần giá hiện tại nhất. Thứ 2, vẽ từ điểm cao nhất hoặc thấp nhất của đỉnh và đáy. Thứ 3, giá rời vùng càng nhanh và mạnh, vùng đó càng mạnh, nhưng vùng mạnh cũng đừng vào bừa. Hay chờ tín hiệu nên rõ ràng rồi, mới vào lệnh. Ví dụ thực tế, khung lớn phá đỉnh đi lên, giá hồi về vùng cầu, rồi tạo tín hiệu mua, sau đó giá tăng mạnh và chạm mục tiêu chốt lời. Kênh nhẫn chờ tín hiệu giúp bạn tránh một lệnh thua, theo dõi để xem thêm cách đọc biểu đồ, nội dung chỉ để học hỏi, không phải lời khuyên đầu tư.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7693471867973176596</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693564151402302740</t>
         </is>
       </c>
     </row>
@@ -3490,27 +3490,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>#fx #crypto #trading #sotrading #fomc</t>
+          <t>2 mẫu nến đảo chiều đáng học: chòm râu &amp; nhấn chìm lần hai Đọc nến từ...</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>#fx #crypto #trading #sotrading #fomc</t>
+          <t>2 mẫu nến đảo chiều đáng học: chòm râu &amp; nhấn chìm lần hai Đọc nến từ bản chất mua – bán và 2 mẫu nến đảo chiều tại vùng cản. Nội dung chỉ mang tính giáo dục, không phải lời khuyên đầu tư. #Shorts #trading #fx</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Đã bao giờ bạn ngồi thẫn thờ trước màn hình lúc 3 giờ sáng, nhìn chân chân vào con số không tròn chính chưa? Ánh sáng đỏ từ nến sắp hắt lên khuôn mặt phở phạc, và hai bàn tay thì lạnh toát. Cảm giác đó, sự tuyệt vọng đến tột cùng. Bạn gục đầu xuống, tự tác vào mặt mình vì sự ngu ngốc. Tại sao không giết khoát cắt lỗ? Tại sao lại gun dày kéo dày? Tại sao lại mù quán ô lín bấu viếu vào một phép màu? Nhưng điều đâm nắt trái tim bạn không phải là những con số vô chi. Số tiền đó lẽ ra là tiền bìm sữa cho con. Bạn phải gượng cười, nuốt ngược cái hố sâu hấm vào dạ dày. Bạn thấy mình giống một kẻ lừa đảo thảm hại. Bạn gào thét đổ lỗi cho nhà cái quét râu. Nhưng sâu thằm, bạn biết rõ sự thật. Chẳng ai xan tìm bạn cả. Chính sự do dự bóp nghẹt stop loss đã tạo ra phịt tài khoản. Chính lòng tham của bạn đã tự tay châm ngòi nổ. Thị trường không có sự chắc ẩn. Lối thoát duy nhất là giết chết cảm xúc. Đánh như một cổ máy máu lạnh. Tự bóp chết cảm xúc. Hay để thị trường bóp chết bạn.</t>
+          <t>Nên nhấn chìm xuất hiện là đảo chiều. Chưa chắc đâu, mỗi cây nén là một cuộc chiến giữa phê mua và phê bán. Nén có 5 yếu tố, giám mở, giá đóng, cao nhất, thấp nhất và thời gian. Sau một sóng tăng, nên nhấn chìm giảm chỉ là nhịp hồi. Lực mua vẫn còn bẫu thứ nhất. Nên chỏm râu, từ 3 cây có râu dài trở lên. Râu càng dài, thị trường càng từ chối giám mạnh tại vùng đó. Bẫu thứ 2, nên nhấn chìm mở đỉnh, hoặc đáy lần thứ 2, đừng vào ở lần chạm đầu, hãy đợi nến đóng cửa rồi mới hành động. Đặt cắt lỗ dưới râu nén hoặc dưới vùng cản để kiểm soát rủi do. Điểm vào tốt phải có quý tắc rõ ràng đến nơi chỉ việc kiểm tra. Hãy tự hỏi, phê nào đang mạnh hơn? Theo dõi để học thêm và nhớ đây chỉ là kiến thức giáo dục.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7687234989431278868</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7693471867973176596</t>
         </is>
       </c>
     </row>
@@ -3540,27 +3540,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>#trading #cpi #sotrading #crypto #fx</t>
+          <t>#fx #crypto #trading #sotrading #fomc</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>#trading #cpi #sotrading #crypto #fx</t>
+          <t>#fx #crypto #trading #sotrading #fomc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn</t>
+          <t>Đã bao giờ bạn ngồi thẫn thờ trước màn hình lúc 3 giờ sáng, nhìn chân chân vào con số không tròn chính chưa? Ánh sáng đỏ từ nến sắp hắt lên khuôn mặt phở phạc, và hai bàn tay thì lạnh toát. Cảm giác đó, sự tuyệt vọng đến tột cùng. Bạn gục đầu xuống, tự tác vào mặt mình vì sự ngu ngốc. Tại sao không giết khoát cắt lỗ? Tại sao lại gun dày kéo dày? Tại sao lại mù quán ô lín bấu viếu vào một phép màu? Nhưng điều đâm nắt trái tim bạn không phải là những con số vô chi. Số tiền đó lẽ ra là tiền bìm sữa cho con. Bạn phải gượng cười, nuốt ngược cái hố sâu hấm vào dạ dày. Bạn thấy mình giống một kẻ lừa đảo thảm hại. Bạn gào thét đổ lỗi cho nhà cái quét râu. Nhưng sâu thằm, bạn biết rõ sự thật. Chẳng ai xan tìm bạn cả. Chính sự do dự bóp nghẹt stop loss đã tạo ra phịt tài khoản. Chính lòng tham của bạn đã tự tay châm ngòi nổ. Thị trường không có sự chắc ẩn. Lối thoát duy nhất là giết chết cảm xúc. Đánh như một cổ máy máu lạnh. Tự bóp chết cảm xúc. Hay để thị trường bóp chết bạn.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1:10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7686468492828331285</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7687234989431278868</t>
         </is>
       </c>
     </row>
@@ -3590,17 +3590,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>#trading #cpi #fx #sotrading #crypto</t>
+          <t>#trading #cpi #sotrading #crypto #fx</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>#trading #cpi #fx #sotrading #crypto</t>
+          <t>#trading #cpi #sotrading #crypto #fx</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Cùng nhận một tín hiệu. Tại sao mỗi người lại có một kết quả khác nhau? Ba người cùng nhận được một tín hiệu với đầy đủ điểm vào, điểm dừng và mục tiêu. Người đầu tiên thực hiện đúng vùng giá, chọn khối lượng phù hợp và chỉ chấp nhận mức dùi do đã tính trước. Người thứ 2 xem tín hiệu muộn. Giá đã chạy khỏi vùng vào nhưng vì sợ bỏ lỡ nên vẫn quyết định tham gia. Người thứ 3 thấy cơ hội hấp dẫn nên tự ý tăng khối lượng lên nhiều lần. Khi thị trường biến động ngược hướng, người đầu chịu đúng dùi do trong kế hoạch, người thứ 2 tổn thất lớn, còn người thứ 3 chạm giấy hạn, thổi bay tài khoản. Như vậy, vấn đề không chỉ nằm ở tín hiệu. Cùng một tín hiệu, nhưng điểm vào, khối lượng và cách kiểm soát dùi do khác nhau sẽ tạo ra kết quả hoàn toàn khác nhau. Đó là lý do mình phát triển hệ thống tiếp nhận và thực thi tín hiệu tự động. Hệ thống hỗ trợ thiết lập điểm vào, điểm dừng, mục tiêu và khối lượng chuẩn sát dựa trên mức dùi do bạn đã cài. Hệ thống không hứa hẹn mọi lệnh đều thắng. Mục tiêu là hạn chế sai sót và ép bạn tuân thủ, tín hiệu, tín hiệu tạo cơ hội, nhưng thực hiện quyết định kết quả, bạn hay gặp vấn đề điểm vào, khối lượng hay cảm xúc, bình luận để xem hệ thống hoạt động nhá.</t>
+          <t>Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn Hãy subscribe cho kênh Ghiền Mì Gõ Để không bỏ lỡ những video hấp dẫn</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7686097369682922772</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7686468492828331285</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Nếu tay bạn dùn lên và nhịp tim đập thỉnh thịch mỗi khi bấm lệnh, thì hãy rút sạch tiền và xóa áp đi. Bạn không phải là một trader, bạn đang tự nguyện bước vào lò mổ. Mạng xã hội đã lừa rối bạn, những video khoe siêu xe, những cú chốt lời xanh mướt x5 x10 tài khoản chỉ sau một đêm. Đó chỉ là mồi nhử và sự tham laam của bạn, chính là chiếc lưỡi câu. Họ làm bạn nghiện cái cảm giác nghẹt thờ, Nghiện lượng hốc môn kích thích bơm thẳng lên áo mỗi khi nến rật lên rật xuống, mắt bạn rán chặt vào màn hình trường đường quest stop lot. Bạn tưởng mình đang phân bằng chính những đồng áo máu của gia đình mình. Và đây là sự thật tàn nhẫn nhất mà đám thầy bà ngoài kia không bao giờ dám nói cho bạn biết. Một hệ thống giao dịch thực sự kiếm được tiền nó tẻ nhạt đến mức đáng sợ. Đúng vậy, chán ngắt. Trong khi bạn đang gào thét, đập bàn đập ghế vì một lệnh lỗ, thì những kẻ đang âm thầm lấy tiền của bạn ngoài kia. Họ vô cảm. Họ coi tiền trên màn hình chỉ là con số, đó là trò chơi của sắc xuất. Kỳ luật không phải gồng mình chịu đựng, nó là cố máy máu lạnh, không hy vọng, cũng không có sợ hãi, nhạt nhéo như việc bạn đánh dăng. Đã đến lúc bạn phải lựa chọn, hoặc là tự tay bóp chết cảm xúc và ảo tưởng của mình. Hoặc là để thị trường nhai nát tài khoản của bạn và nhổ ra không thương tiếc.</t>
+          <t>Cùng nhận một tín hiệu. Tại sao mỗi người lại có một kết quả khác nhau? Ba người cùng nhận được một tín hiệu với đầy đủ điểm vào, điểm dừng và mục tiêu. Người đầu tiên thực hiện đúng vùng giá, chọn khối lượng phù hợp và chỉ chấp nhận mức dùi do đã tính trước. Người thứ 2 xem tín hiệu muộn. Giá đã chạy khỏi vùng vào nhưng vì sợ bỏ lỡ nên vẫn quyết định tham gia. Người thứ 3 thấy cơ hội hấp dẫn nên tự ý tăng khối lượng lên nhiều lần. Khi thị trường biến động ngược hướng, người đầu chịu đúng dùi do trong kế hoạch, người thứ 2 tổn thất lớn, còn người thứ 3 chạm giấy hạn, thổi bay tài khoản. Như vậy, vấn đề không chỉ nằm ở tín hiệu. Cùng một tín hiệu, nhưng điểm vào, khối lượng và cách kiểm soát dùi do khác nhau sẽ tạo ra kết quả hoàn toàn khác nhau. Đó là lý do mình phát triển hệ thống tiếp nhận và thực thi tín hiệu tự động. Hệ thống hỗ trợ thiết lập điểm vào, điểm dừng, mục tiêu và khối lượng chuẩn sát dựa trên mức dùi do bạn đã cài. Hệ thống không hứa hẹn mọi lệnh đều thắng. Mục tiêu là hạn chế sai sót và ép bạn tuân thủ, tín hiệu, tín hiệu tạo cơ hội, nhưng thực hiện quyết định kết quả, bạn hay gặp vấn đề điểm vào, khối lượng hay cảm xúc, bình luận để xem hệ thống hoạt động nhá.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7685719795400051989</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7686097369682922772</t>
         </is>
       </c>
     </row>
@@ -3690,17 +3690,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>#trading #cpi #trading #fx #sotrading</t>
+          <t>#trading #cpi #fx #sotrading #crypto</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>#trading #cpi #trading #fx #sotrading</t>
+          <t>#trading #cpi #fx #sotrading #crypto</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>99% trầy trái tài khoản không phải vì rốt kỹ thuật, cũng chẳng phải vì thị trường cố tình đi ngược lại họ. Lý do thực sự là vì tất cả chúng ta đều từng mắc kẹt trong một áo tưởng điên cuồng, đi tìm một chén thánh giao dịch. Kịch bản này quen không? Nạp tiền, ăn vài lệnh đầu, bạn tự tin tháo stoplots vì cay cũ, để rồi tài khoản trái khét, sáng ra với đầu chống rỗng, vòng xoay đó cứ lập lại. Tại sao? Vì tư duy của bạn chưa thay đổi, bạn không chấp nhận mình có thể sai, bạn ảo tưởng nhồi nhét thêm vài chỉ báo là kiểm soát được thị trường, tỉnh lại đi, bạn sẽ bị nó nghiền nát. Nhiều người cậy mình có kỹ năng, họ stoplots lại thật hẹp, phí giao dịch sẽ ăn món hết, khoản phí này mới là lưỡi giao, nó lặng lặng gióc thịt tài khoản, chứ không phải do nhà cái. Ở thị trường này, sự thật mất lòng nhất là không có gì là tuyệt đối, và cũng chẳng có chén thánh nào cứu được bạn, lối thoát duy nhất để tồn tại và bất phá chỉ gói gọn trong hai chữ, từ duy và kỷ luật. Hãy học cách chấp nhận dùi do, trở thành người quản trị vốn tàn nhẫn, giao dịch là bài toán sắc xuất, kiểm soát nghiêm ngặt số tiền sẽ mất, để không bị đá vang khỏi cuộc chơi. Đừng để thị trường biến bạn thành một con bạc khát nước và tước đi sự tự tôn cuối cùng của mình. Khi sự hương phấn tột độ, hay nỗi sợ hãi tột cùng ập đến, thì kỷ luật chính là chiếc mỏ neo duy nhất giữ bạn lại với cuộc chơi.</t>
+          <t>Nếu tay bạn dùn lên và nhịp tim đập thỉnh thịch mỗi khi bấm lệnh, thì hãy rút sạch tiền và xóa áp đi. Bạn không phải là một trader, bạn đang tự nguyện bước vào lò mổ. Mạng xã hội đã lừa rối bạn, những video khoe siêu xe, những cú chốt lời xanh mướt x5 x10 tài khoản chỉ sau một đêm. Đó chỉ là mồi nhử và sự tham laam của bạn, chính là chiếc lưỡi câu. Họ làm bạn nghiện cái cảm giác nghẹt thờ, Nghiện lượng hốc môn kích thích bơm thẳng lên áo mỗi khi nến rật lên rật xuống, mắt bạn rán chặt vào màn hình trường đường quest stop lot. Bạn tưởng mình đang phân bằng chính những đồng áo máu của gia đình mình. Và đây là sự thật tàn nhẫn nhất mà đám thầy bà ngoài kia không bao giờ dám nói cho bạn biết. Một hệ thống giao dịch thực sự kiếm được tiền nó tẻ nhạt đến mức đáng sợ. Đúng vậy, chán ngắt. Trong khi bạn đang gào thét, đập bàn đập ghế vì một lệnh lỗ, thì những kẻ đang âm thầm lấy tiền của bạn ngoài kia. Họ vô cảm. Họ coi tiền trên màn hình chỉ là con số, đó là trò chơi của sắc xuất. Kỳ luật không phải gồng mình chịu đựng, nó là cố máy máu lạnh, không hy vọng, cũng không có sợ hãi, nhạt nhéo như việc bạn đánh dăng. Đã đến lúc bạn phải lựa chọn, hoặc là tự tay bóp chết cảm xúc và ảo tưởng của mình. Hoặc là để thị trường nhai nát tài khoản của bạn và nhổ ra không thương tiếc.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7685348661768899860</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7685719795400051989</t>
         </is>
       </c>
     </row>
@@ -3740,27 +3740,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>#trading #crypto #fx #cpi #sotrading</t>
+          <t>#trading #cpi #trading #fx #sotrading</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>#trading #crypto #fx #cpi #sotrading</t>
+          <t>#trading #cpi #trading #fx #sotrading</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sang tuần thứ 4, sự bế tắc đã biến A từ một người phân tích cẩn trọng thành một con bạc khát nước. Cậu không còn nhìn biểu đồ để tìm dòng tiền nữa. Cậu nhìn nó bằng ánh mắt của kẻ muốn trả thù. 10 giờ tối, một cây nến xanh bất phá, chỉ một lệnh all in này thôi. Gỡ lại 10.000 đô rồi mình sẽ đánh kỷ luật. A kéo tối đa đòn 7, nhắm mắt bấm bay và giết khoát tháo luôn stop loss. 5 phút đầu, tài khoản xanh mướt. Nhưng rồi giá khượng lại, đến giút chân đỏ quạch đâm xuống, phá vỡ mọi hỗ trợ. A chết lặng, mùa hôi lạnh túa ra, cậu cầu nguyện, cậu rán mắt vào những con số âm. Âm 1 ngàn dưới, âm 3 ngàn, âm 5 ngàn dưới, thanh lý hiện lên lạnh léo. Căn phòng rơi vào tính lặng. Không có tiếng gạo thét, chỉ có sự chống rõm tột cùng. Tại sao không cắt lỗ lúc nãy? Đêm đó, A mất ngủ, tự thể độc sẽ không bao giờ lặp lại. Nhưng bị kịch lớn nhất không phải là mất 10.000 đô. Vì gốc dễ tư duy chưa hề đập đi xay lại, bàn tay A lại tiếp tục bóp ngắn xóa điện ngục lại bắt đầu quay. Cuốn đi tất cả trong thị trường này, danh giới giữa một trader và một con bạc mỏng manh đến đáng sợ. Có thể bạn đang cười A, nhưng đã bao giờ bạn thấy bóng dáng mình trong đó. Còn anh em, anh em nhìn nhận thế nào về nhân vật A, hãy để lại ý kiến xuống phật bình luận nhé.</t>
+          <t>99% trầy trái tài khoản không phải vì rốt kỹ thuật, cũng chẳng phải vì thị trường cố tình đi ngược lại họ. Lý do thực sự là vì tất cả chúng ta đều từng mắc kẹt trong một áo tưởng điên cuồng, đi tìm một chén thánh giao dịch. Kịch bản này quen không? Nạp tiền, ăn vài lệnh đầu, bạn tự tin tháo stoplots vì cay cũ, để rồi tài khoản trái khét, sáng ra với đầu chống rỗng, vòng xoay đó cứ lập lại. Tại sao? Vì tư duy của bạn chưa thay đổi, bạn không chấp nhận mình có thể sai, bạn ảo tưởng nhồi nhét thêm vài chỉ báo là kiểm soát được thị trường, tỉnh lại đi, bạn sẽ bị nó nghiền nát. Nhiều người cậy mình có kỹ năng, họ stoplots lại thật hẹp, phí giao dịch sẽ ăn món hết, khoản phí này mới là lưỡi giao, nó lặng lặng gióc thịt tài khoản, chứ không phải do nhà cái. Ở thị trường này, sự thật mất lòng nhất là không có gì là tuyệt đối, và cũng chẳng có chén thánh nào cứu được bạn, lối thoát duy nhất để tồn tại và bất phá chỉ gói gọn trong hai chữ, từ duy và kỷ luật. Hãy học cách chấp nhận dùi do, trở thành người quản trị vốn tàn nhẫn, giao dịch là bài toán sắc xuất, kiểm soát nghiêm ngặt số tiền sẽ mất, để không bị đá vang khỏi cuộc chơi. Đừng để thị trường biến bạn thành một con bạc khát nước và tước đi sự tự tôn cuối cùng của mình. Khi sự hương phấn tột độ, hay nỗi sợ hãi tột cùng ập đến, thì kỷ luật chính là chiếc mỏ neo duy nhất giữ bạn lại với cuộc chơi.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1:11</t>
+          <t>1:10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sotrading01/video/7684604753577495829</t>
+          <t>https://www.tiktok.com/@sotrading01/video/7685348661768899860</t>
         </is>
       </c>
     </row>
@@ -3790,25 +3790,75 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>#trading #crypto #fx #cpi #sotrading</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>#trading #crypto #fx #cpi #sotrading</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sang tuần thứ 4, sự bế tắc đã biến A từ một người phân tích cẩn trọng thành một con bạc khát nước. Cậu không còn nhìn biểu đồ để tìm dòng tiền nữa. Cậu nhìn nó bằng ánh mắt của kẻ muốn trả thù. 10 giờ tối, một cây nến xanh bất phá, chỉ một lệnh all in này thôi. Gỡ lại 10.000 đô rồi mình sẽ đánh kỷ luật. A kéo tối đa đòn 7, nhắm mắt bấm bay và giết khoát tháo luôn stop loss. 5 phút đầu, tài khoản xanh mướt. Nhưng rồi giá khượng lại, đến giút chân đỏ quạch đâm xuống, phá vỡ mọi hỗ trợ. A chết lặng, mùa hôi lạnh túa ra, cậu cầu nguyện, cậu rán mắt vào những con số âm. Âm 1 ngàn dưới, âm 3 ngàn, âm 5 ngàn dưới, thanh lý hiện lên lạnh léo. Căn phòng rơi vào tính lặng. Không có tiếng gạo thét, chỉ có sự chống rõm tột cùng. Tại sao không cắt lỗ lúc nãy? Đêm đó, A mất ngủ, tự thể độc sẽ không bao giờ lặp lại. Nhưng bị kịch lớn nhất không phải là mất 10.000 đô. Vì gốc dễ tư duy chưa hề đập đi xay lại, bàn tay A lại tiếp tục bóp ngắn xóa điện ngục lại bắt đầu quay. Cuốn đi tất cả trong thị trường này, danh giới giữa một trader và một con bạc mỏng manh đến đáng sợ. Có thể bạn đang cười A, nhưng đã bao giờ bạn thấy bóng dáng mình trong đó. Còn anh em, anh em nhìn nhận thế nào về nhân vật A, hãy để lại ý kiến xuống phật bình luận nhé.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1:11</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sotrading01/video/7684604753577495829</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>🟢 Ưu tiên 3 (Thực chiến Price Action)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SO Trading</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>#cpi #sotrading #trading #fx #crypto</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>#cpi #sotrading #trading #fx #crypto</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>không phải là một kẻ ngốc. Trước khi nạp 10.000 đô đầu tiên, cậu đã dành hàng tháng trời cày nát các mô hình price action. Bước vào thị trường với một sự tự tin đầy tính toán. Những tuần đầu tiên, tiền nổ liên hồi. Cảm giác hoác môn hương phấn tiết ra tột độ khiến A bắt đầu tin rằng, mình sinh ra là để làm trader. Để tối đa hóa tỷ lệ lợi nhuận rùi do, ABOV STOP LOST lại thật hẹp. Cậu tự hào khoe những lệnh bắt đỉnh đáy như một phù thủy tài chính. Nhưng tuần trang mật kết thúc nhanh chóng. Giá vừa liếm S lờ thì ngay lập tức quay đầu bay đúng hướng. A, cây cú đập bàn, lũ nhà cái lại cố tình quét dâu mình. Cậu không hề nhận ra sự thật tàn nhẫn khoảng cách entry và S lờ quá ngắn khiến tỷ lệ phí giao dịch phình to khổng lồ vào cậu. Chính lưỡi giao vô hình của phí ẩn đang lặng lặng giọc thịt tài khoản. Tài khoản rơi từ 10.000 xuống 7.000 đô. Sự tự tin biến mất, nỗi sợ lên ngôi. Thay vì giữ kỷ luật 1% gốc, A run tay hạ cửa chỉ dám đánh 70 đô cho lệnh tiếp theo. Cái bẫy chính thức sập xuống, sai thì mất liên tục, mà đúng thì 140 đô thu về chỉ như cho đùa trước hố sâu 3.000 đô đang vẫn gì máu. Liệu A có kịp nhận ra nút thắt trước khi tài khoản vệch.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1:09</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@sotrading01/video/7684276294971854101</t>
         </is>
